--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B012DCA-618F-7848-B37D-0ED948A5F98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E79E4C-9700-5941-B1AA-B8688C681C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,12 +161,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2376,9 +2406,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2388,6 +2415,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2395,12 +2431,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15136,7 +15166,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15154,12 +15184,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>103.38</v>
-    <v>2.2547000000000001</v>
-    <v>-51.63</v>
-    <v>-5.9028999999999998E-2</v>
-    <v>-6.53</v>
-    <v>-7.9340000000000001E-3</v>
+    <v>105.46</v>
+    <v>2.1894</v>
+    <v>-4.6744000000000003</v>
+    <v>-5.6799999999999993E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15167,35 +15195,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>930.88</v>
+    <v>829</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46234.909704015627</v>
+    <v>46237.674561885935</v>
     <v>0</v>
-    <v>818</v>
-    <v>929524320790</v>
+    <v>770.15</v>
+    <v>924245086150</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>919.65</v>
-    <v>18.632300000000001</v>
-    <v>874.66</v>
+    <v>783.39</v>
+    <v>18.526499999999999</v>
     <v>823.03</v>
-    <v>816.5</v>
+    <v>818.35559999999998</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>54184317</v>
-    <v>50529428</v>
+    <v>24279062</v>
+    <v>49389334</v>
     <v>1984</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15207,30 +15249,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.14</v>
+    <v>47.47</v>
     <v>39.47</v>
-    <v>0.41</v>
-    <v>8.8710000000000004E-3</v>
+    <v>0.82</v>
+    <v>1.7585E-2</v>
     <v>US</v>
-    <v>46.86</v>
+    <v>47.47</v>
     <v>Index</v>
-    <v>3</v>
-    <v>46.51</v>
+    <v>6</v>
+    <v>46.82</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.69</v>
-    <v>46.22</v>
+    <v>46.84</v>
     <v>46.63</v>
+    <v>47.45</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15252,8 +15294,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15274,7 +15314,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15284,6 +15323,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15319,7 +15363,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15330,16 +15374,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15433,19 +15474,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15517,9 +15552,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15527,9 +15559,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16014,18 +16043,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="241" t="s">
+      <c r="B2" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="242"/>
-      <c r="E2" s="241" t="s">
+      <c r="C2" s="241"/>
+      <c r="E2" s="240" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="242"/>
-      <c r="H2" s="241" t="s">
+      <c r="F2" s="241"/>
+      <c r="H2" s="240" t="s">
         <v>333</v>
       </c>
-      <c r="I2" s="242"/>
+      <c r="I2" s="241"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -16040,7 +16069,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>943192.38</v>
+        <v>937835.51760000002</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -16048,7 +16077,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>541.23797874688739</v>
+        <v>549.74801266888994</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16064,7 +16093,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>918786.38</v>
+        <v>913429.51760000002</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -16072,7 +16101,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>530.53040027865063</v>
+        <v>535.25824961846001</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16081,7 +16110,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>248</v>
@@ -16096,23 +16125,23 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>172.82666091307053</v>
+        <v>174.43005596971361</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>816.5</v>
+      <c r="C6" s="212" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>18.633235227529998</v>
+        <v>18.527407742811864</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -16120,7 +16149,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>802.24085036536019</v>
+        <v>809.47996071608281</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16129,14 +16158,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-51.63</v>
+        <v>-4.6744000000000003</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>10.384287502492413</v>
+        <v>10.325309927553892</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -16144,23 +16173,23 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>511.70897257599222</v>
+        <v>517.22906974328657</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-6.53</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>270</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.6471799952412677E-2</v>
+        <v>2.6623005347350473E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -16168,7 +16197,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.37826206508147669</v>
+        <v>-0.36796538113347477</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16177,37 +16206,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.9028999999999998E-2</v>
+        <v>-5.6799999999999993E-3</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>293</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.3667545532969638E-2</v>
+        <v>5.3974091458529765E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-7.9340000000000001E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>298</v>
       </c>
       <c r="F10" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>1.1895770404760904E-3</v>
+        <v>1.1963718359390913E-3</v>
       </c>
       <c r="H10" s="188" t="s">
         <v>376</v>
       </c>
       <c r="I10" s="216">
         <f ca="1">DDM!C26</f>
-        <v>4.0900488180775083</v>
+        <v>4.1647624878204406</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16223,7 +16252,7 @@
       </c>
       <c r="F11" s="197">
         <f ca="1">Statement!AC163</f>
-        <v>6.4396194549408892E-4</v>
+        <v>6.4764021899526322E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16232,7 +16261,7 @@
       </c>
       <c r="C12" s="213" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>103.38</v>
+        <v>105.46</v>
       </c>
       <c r="E12" s="189" t="s">
         <v>102</v>
@@ -16248,7 +16277,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2547000000000001</v>
+        <v>2.1894</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>104</v>
@@ -16264,7 +16293,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>50529428</v>
+        <v>49389334</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>105</v>
@@ -16280,7 +16309,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>2.5875951203083298E-2</v>
+        <v>2.6023753144322159E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16293,10 +16322,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="243" t="s">
+      <c r="B17" s="242" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="243"/>
+      <c r="C17" s="242"/>
       <c r="E17" s="188" t="s">
         <v>301</v>
       </c>
@@ -16369,14 +16398,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="243" t="s">
+      <c r="B25" s="242" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="243"/>
-      <c r="E25" s="241" t="s">
+      <c r="C25" s="242"/>
+      <c r="E25" s="240" t="s">
         <v>348</v>
       </c>
-      <c r="F25" s="242"/>
+      <c r="F25" s="241"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -16385,12 +16414,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="2">
+      <c r="E26" s="189" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.63</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16405,7 +16434,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16425,15 +16454,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="240" t="s">
+      <c r="B33" s="243" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="240"/>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
+      <c r="C33" s="243"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16478,24 +16507,24 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="240"/>
-      <c r="C43" s="240"/>
-      <c r="D43" s="240"/>
-      <c r="E43" s="240"/>
-      <c r="F43" s="240"/>
-      <c r="G43" s="240"/>
-      <c r="H43" s="240"/>
+      <c r="B43" s="243"/>
+      <c r="C43" s="243"/>
+      <c r="D43" s="243"/>
+      <c r="E43" s="243"/>
+      <c r="F43" s="243"/>
+      <c r="G43" s="243"/>
+      <c r="H43" s="243"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="240" t="s">
+      <c r="B46" s="243" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="240"/>
-      <c r="D46" s="240"/>
-      <c r="E46" s="240"/>
-      <c r="F46" s="240"/>
-      <c r="G46" s="240"/>
-      <c r="H46" s="240"/>
+      <c r="C46" s="243"/>
+      <c r="D46" s="243"/>
+      <c r="E46" s="243"/>
+      <c r="F46" s="243"/>
+      <c r="G46" s="243"/>
+      <c r="H46" s="243"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="41" t="s">
@@ -16614,24 +16643,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="240"/>
-      <c r="C66" s="240"/>
-      <c r="D66" s="240"/>
-      <c r="E66" s="240"/>
-      <c r="F66" s="240"/>
-      <c r="G66" s="240"/>
-      <c r="H66" s="240"/>
+      <c r="B66" s="243"/>
+      <c r="C66" s="243"/>
+      <c r="D66" s="243"/>
+      <c r="E66" s="243"/>
+      <c r="F66" s="243"/>
+      <c r="G66" s="243"/>
+      <c r="H66" s="243"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="240" t="s">
+      <c r="B69" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="240"/>
-      <c r="D69" s="240"/>
-      <c r="E69" s="240"/>
-      <c r="F69" s="240"/>
-      <c r="G69" s="240"/>
-      <c r="H69" s="240"/>
+      <c r="C69" s="243"/>
+      <c r="D69" s="243"/>
+      <c r="E69" s="243"/>
+      <c r="F69" s="243"/>
+      <c r="G69" s="243"/>
+      <c r="H69" s="243"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -16646,28 +16675,28 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="240"/>
-      <c r="C76" s="240"/>
-      <c r="D76" s="240"/>
-      <c r="E76" s="240"/>
-      <c r="F76" s="240"/>
-      <c r="G76" s="240"/>
-      <c r="H76" s="240"/>
+      <c r="B76" s="243"/>
+      <c r="C76" s="243"/>
+      <c r="D76" s="243"/>
+      <c r="E76" s="243"/>
+      <c r="F76" s="243"/>
+      <c r="G76" s="243"/>
+      <c r="H76" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16737,36 +16766,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="240" t="s">
+      <c r="S2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240" t="s">
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -17966,35 +17995,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="P2" s="240" t="s">
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="P2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -20024,20 +20053,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -21430,6 +21459,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21437,12 +21472,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21480,20 +21509,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="S2" s="254"/>
       <c r="T2" s="254"/>
       <c r="U2" s="254"/>
@@ -22502,16 +22531,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22574,10 +22603,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="243"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22594,7 +22623,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22603,7 +22632,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>943192.38</v>
+        <v>937835.51760000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22621,7 +22650,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22630,7 +22659,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.2547000000000001</v>
+        <v>2.1894</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22662,10 +22691,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="243" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="240"/>
+      <c r="C15" s="243"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22673,7 +22702,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.0300487805865057E-3</v>
+        <v>6.0642831976520937E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22682,7 +22711,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99396995121941345</v>
+        <v>0.99393571680234793</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22700,7 +22729,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14809149999999999</v>
+        <v>0.14597300000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22709,7 +22738,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14744145169637959</v>
+        <v>0.14533210835882257</v>
       </c>
     </row>
   </sheetData>
@@ -22754,20 +22783,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -22960,7 +22989,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>656010.24401870964</v>
+        <v>666235.09645299753</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23014,23 +23043,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37800.984935286942</v>
+        <v>37870.602520565852</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>53687.235510816361</v>
+        <v>53885.167782972152</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>66961.270042211356</v>
+        <v>67331.916936629525</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>62717.542152575195</v>
+        <v>63180.844423172624</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>44880.150725935142</v>
+        <v>45294.951749031556</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23049,14 +23078,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>329805.54027710791</v>
+        <v>338041.73910617625</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="240" t="s">
+      <c r="B13" s="243" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="240"/>
+      <c r="C13" s="243"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23072,14 +23101,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14744145169637959</v>
+        <v>0.14533210835882257</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="243" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="240"/>
+      <c r="C18" s="243"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23087,7 +23116,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>266047.18336682499</v>
+        <v>267563.48341237172</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,7 +23125,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>329805.54027710791</v>
+        <v>338041.73910617625</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23105,7 +23134,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>595852.72364393296</v>
+        <v>605605.2225185479</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23132,7 +23161,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>620258.72364393296</v>
+        <v>630011.2225185479</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23150,7 +23179,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>541.23797874688739</v>
+        <v>549.74801266888994</v>
       </c>
     </row>
   </sheetData>
@@ -23193,20 +23222,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -24138,10 +24167,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="243" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="240"/>
+      <c r="C37" s="243"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -24159,7 +24188,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14744145169637959</v>
+        <v>0.14533210835882257</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24185,7 +24214,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>583581.83871933364</v>
+        <v>588999.95406275522</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -24212,7 +24241,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>607987.83871933364</v>
+        <v>613405.95406275522</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24230,14 +24259,14 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>530.53040027865063</v>
+        <v>535.25824961846001</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="240" t="s">
+      <c r="B49" s="243" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="240"/>
+      <c r="C49" s="243"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -24254,7 +24283,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14809149999999999</v>
+        <v>0.14597300000000002</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24289,14 +24318,14 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>172.82666091307053</v>
+        <v>174.43005596971361</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="240" t="s">
+      <c r="B57" s="243" t="s">
         <v>327</v>
       </c>
-      <c r="C57" s="240"/>
+      <c r="C57" s="243"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -24313,7 +24342,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14744145169637959</v>
+        <v>0.14533210835882257</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24339,7 +24368,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>894962.01451870275</v>
+        <v>903258.03498063097</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24366,7 +24395,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>919368.01451870275</v>
+        <v>927664.03498063097</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24384,7 +24413,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>802.24085036536019</v>
+        <v>809.47996071608281</v>
       </c>
     </row>
   </sheetData>
@@ -24436,10 +24465,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="243"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24448,7 +24477,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>541.23797874688739</v>
+        <v>549.74801266888994</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24457,7 +24486,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>530.53040027865063</v>
+        <v>535.25824961846001</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24466,7 +24495,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>172.82666091307053</v>
+        <v>174.43005596971361</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24475,7 +24504,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>802.24085036536019</v>
+        <v>809.47996071608281</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24484,7 +24513,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>511.70897257599222</v>
+        <v>517.22906974328657</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24493,7 +24522,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24502,7 +24531,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.37826206508147669</v>
+        <v>-0.36796538113347477</v>
       </c>
     </row>
   </sheetData>
@@ -24558,20 +24587,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -24934,10 +24963,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="243" t="s">
         <v>371</v>
       </c>
-      <c r="C20" s="240"/>
+      <c r="C20" s="243"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24972,7 +25001,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14809149999999999</v>
+        <v>0.14597300000000002</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24989,7 +25018,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C23/(C24-C25)</f>
-        <v>4.0900488180775083</v>
+        <v>4.1647624878204406</v>
       </c>
     </row>
   </sheetData>
@@ -25038,20 +25067,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -25226,7 +25255,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1418213.0747681747</v>
+        <v>1440317.9420962355</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25280,23 +25309,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>6115.9704802633933</v>
+        <v>6127.2341840320096</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12205.914627798489</v>
+        <v>12250.914978310726</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>24359.887344434803</v>
+        <v>24494.725237845421</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48616.111903822479</v>
+        <v>48975.245158404825</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>97025.339371487469</v>
+        <v>97922.087920380203</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25315,7 +25344,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>712998.81917489739</v>
+        <v>730804.46317554498</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25331,7 +25360,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25340,7 +25369,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>819.95397954181055</v>
+        <v>837.0067942024076</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25379,7 +25408,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14744145169637959</v>
+        <v>0.14533210835882257</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25397,7 +25426,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>929200.87</v>
+        <v>923923.47239999997</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25424,7 +25453,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>904794.87</v>
+        <v>899517.47239999997</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25440,7 +25469,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>188323.22372780665</v>
+        <v>189770.2074789732</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25449,7 +25478,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>712998.81917489739</v>
+        <v>730804.46317554498</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25458,7 +25487,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>901322.0429027041</v>
+        <v>920574.67065451818</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25485,7 +25514,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>925728.0429027041</v>
+        <v>944980.67065451818</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -25503,7 +25532,7 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>819.95397954181055</v>
+        <v>837.0067942024076</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -25950,17 +25979,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32567,7 +32596,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32638,7 +32667,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33944,7 +33973,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>18.633235227529998</v>
+        <v>18.527407742811864</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33981,7 +34010,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.384287502492413</v>
+        <v>10.325309927553892</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34042,7 +34071,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>9.2252181208053692</v>
+        <v>9.17282348199039</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34103,7 +34132,7 @@
       </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>943192.38</v>
+        <v>937835.51760000002</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34164,7 +34193,7 @@
       </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>918786.38</v>
+        <v>913429.51760000002</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34201,7 +34230,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>10.177751955158739</v>
+        <v>10.118411919268006</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34238,7 +34267,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC12</f>
-        <v>15.508775382745641</v>
+        <v>15.418353520247118</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34373,7 +34402,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
-        <v>37.776048542133928</v>
+        <v>37.561499423261779</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34410,7 +34439,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="102"/>
-        <v>37.155836236973563</v>
+        <v>36.939204050851693</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34447,7 +34476,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
-        <v>2.6471799952412677E-2</v>
+        <v>2.6623005347350473E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34484,7 +34513,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.3667545532969638E-2</v>
+        <v>5.3974091458529765E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34521,7 +34550,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="158">
         <f ca="1">AC82/AC117</f>
-        <v>6.4396194549408892E-4</v>
+        <v>6.4764021899526322E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34558,7 +34587,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="158">
         <f ca="1">-AC63/AC153</f>
-        <v>1.1895770404760904E-3</v>
+        <v>1.1963718359390913E-3</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34595,7 +34624,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="158">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.790726935262136E-3</v>
+        <v>1.8009554642612524E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35098,7 +35127,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>2.5875951203083298E-2</v>
+        <v>2.6023753144322159E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -36973,15 +37002,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="240"/>
-      <c r="E4" s="240" t="s">
+      <c r="C4" s="243"/>
+      <c r="E4" s="243" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36989,7 +37018,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37005,7 +37034,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>943192.38</v>
+        <v>937835.51760000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37025,7 +37054,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>918786.38</v>
+        <v>913429.51760000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37045,7 +37074,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>18.633235227529998</v>
+        <v>18.527407742811864</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>248</v>
@@ -37065,7 +37094,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.384287502492413</v>
+        <v>10.325309927553892</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>249</v>
@@ -37085,7 +37114,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.2252181208053692</v>
+        <v>9.17282348199039</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37105,7 +37134,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.177751955158739</v>
+        <v>10.118411919268006</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37114,18 +37143,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>15.508775382745641</v>
+        <v>15.418353520247118</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="243" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="E15" s="240" t="s">
+      <c r="C15" s="243"/>
+      <c r="E15" s="243" t="s">
         <v>251</v>
       </c>
-      <c r="F15" s="240"/>
+      <c r="F15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37176,14 +37205,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="240" t="s">
+      <c r="B21" s="243" t="s">
         <v>250</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="E21" s="240" t="s">
+      <c r="C21" s="243"/>
+      <c r="E21" s="243" t="s">
         <v>254</v>
       </c>
-      <c r="F21" s="240"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37252,14 +37281,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="243" t="s">
         <v>255</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="E29" s="240" t="s">
+      <c r="C29" s="243"/>
+      <c r="E29" s="243" t="s">
         <v>261</v>
       </c>
-      <c r="F29" s="240"/>
+      <c r="F29" s="243"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37335,14 +37364,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="243" t="s">
         <v>273</v>
       </c>
-      <c r="C37" s="240"/>
-      <c r="E37" s="240" t="s">
+      <c r="C37" s="243"/>
+      <c r="E37" s="243" t="s">
         <v>276</v>
       </c>
-      <c r="F37" s="240"/>
+      <c r="F37" s="243"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37350,7 +37379,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.3667545532969638E-2</v>
+        <v>5.3974091458529765E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>275</v>
@@ -37366,7 +37395,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>2.6471799952412677E-2</v>
+        <v>2.6623005347350473E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>277</v>
@@ -37382,7 +37411,7 @@
       </c>
       <c r="C40" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.4396194549408892E-4</v>
+        <v>6.4764021899526322E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>278</v>
@@ -37398,7 +37427,7 @@
       </c>
       <c r="C41" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1895770404760904E-3</v>
+        <v>1.1963718359390913E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37407,18 +37436,18 @@
       </c>
       <c r="C42" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.790726935262136E-3</v>
+        <v>1.8009554642612524E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="240" t="s">
+      <c r="B45" s="243" t="s">
         <v>284</v>
       </c>
-      <c r="C45" s="240"/>
-      <c r="E45" s="240" t="s">
+      <c r="C45" s="243"/>
+      <c r="E45" s="243" t="s">
         <v>290</v>
       </c>
-      <c r="F45" s="240"/>
+      <c r="F45" s="243"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37451,18 +37480,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>2.5875951203083298E-2</v>
+        <v>2.6023753144322159E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+      <c r="B51" s="243" t="s">
         <v>287</v>
       </c>
-      <c r="C51" s="240"/>
-      <c r="E51" s="240" t="s">
+      <c r="C51" s="243"/>
+      <c r="E51" s="243" t="s">
         <v>308</v>
       </c>
-      <c r="F51" s="240"/>
+      <c r="F51" s="243"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37630,7 +37659,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC116</f>
-        <v>823.03</v>
+        <v>818.35559999999998</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37659,7 +37688,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>943192.38</v>
+        <v>937835.51760000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37688,7 +37717,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>918786.38</v>
+        <v>913429.51760000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37717,7 +37746,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>18.633235227529998</v>
+        <v>18.527407742811864</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37746,7 +37775,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.384287502492413</v>
+        <v>10.325309927553892</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37775,7 +37804,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.2252181208053692</v>
+        <v>9.17282348199039</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37804,7 +37833,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.177751955158739</v>
+        <v>10.118411919268006</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37833,7 +37862,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>15.508775382745641</v>
+        <v>15.418353520247118</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38606,7 +38635,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.3667545532969638E-2</v>
+        <v>5.3974091458529765E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38635,7 +38664,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>2.6471799952412677E-2</v>
+        <v>2.6623005347350473E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38664,7 +38693,7 @@
       </c>
       <c r="I53" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.4396194549408892E-4</v>
+        <v>6.4764021899526322E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38693,7 +38722,7 @@
       </c>
       <c r="I54" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1895770404760904E-3</v>
+        <v>1.1963718359390913E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38722,7 +38751,7 @@
       </c>
       <c r="I55" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.790726935262136E-3</v>
+        <v>1.8009554642612524E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38958,7 +38987,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>2.5875951203083298E-2</v>
+        <v>2.6023753144322159E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39564,14 +39593,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="244" t="s">
+      <c r="C3" s="246" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="F3" s="246" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>319</v>
       </c>
-      <c r="G3" s="245"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39638,19 +39667,19 @@
       <c r="B7" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="244">
         <f>Statement!AA89</f>
         <v>0.73746856663872595</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.4571551446081066</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -39677,19 +39706,19 @@
       <c r="B9" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="244">
         <f>Statement!AA90</f>
         <v>4.8321048321048318E-2</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.10478163300535129</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -39716,19 +39745,19 @@
       <c r="B11" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="244">
         <f>Statement!AA91</f>
         <v>0.97442973810194311</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.9931584948688705</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -39755,19 +39784,19 @@
       <c r="B13" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="244">
         <f>Statement!AA95</f>
         <v>7.2839506172839505E-2</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.29798356982823004</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -39794,19 +39823,19 @@
       <c r="B15" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="244">
         <f>Statement!AA96</f>
         <v>1.0649519677719244</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>14.360995850622407</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -39833,19 +39862,19 @@
       <c r="B17" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="244">
         <f>Statement!AA98</f>
         <v>1.0488211824446863</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>13.983023872679045</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -39872,22 +39901,22 @@
       <c r="B19" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6269702276707531E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -39914,22 +39943,22 @@
       <c r="B21" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.0439105219552611</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>13.684523809523812</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39978,22 +40007,22 @@
       <c r="B25" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.66922421142369992</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>3.4304907368123319</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40021,22 +40050,22 @@
       <c r="B27" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.98979387632579552</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.613921113689095</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40064,22 +40093,22 @@
       <c r="B29" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.94736842105263153</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.4666666666666666</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="245"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="188" t="str">
@@ -40107,22 +40136,22 @@
       <c r="B32" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C32" s="247">
+      <c r="C32" s="244">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.77687443541102075</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="F32" s="247">
+      <c r="D32" s="245"/>
+      <c r="F32" s="244">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>3.066450088600118</v>
       </c>
-      <c r="G32" s="248"/>
+      <c r="G32" s="245"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="188" t="str">
@@ -40150,22 +40179,22 @@
       <c r="B34" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="247">
+      <c r="C34" s="244">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.0263759451380341</v>
       </c>
-      <c r="D34" s="248"/>
-      <c r="F34" s="247">
+      <c r="D34" s="245"/>
+      <c r="F34" s="244">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>6.5320261437908496</v>
       </c>
-      <c r="G34" s="248"/>
+      <c r="G34" s="245"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="188" t="str">
@@ -40193,22 +40222,22 @@
       <c r="B36" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="247">
+      <c r="C36" s="244">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.49409933860718452</v>
       </c>
-      <c r="D36" s="248"/>
-      <c r="F36" s="247">
+      <c r="D36" s="245"/>
+      <c r="F36" s="244">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.5394777265745008</v>
       </c>
-      <c r="G36" s="248"/>
+      <c r="G36" s="245"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="188" t="str">
@@ -40236,25 +40265,49 @@
       <c r="B38" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="247">
+      <c r="C38" s="244">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.71122599704579026</v>
       </c>
-      <c r="D38" s="248"/>
-      <c r="F38" s="247">
+      <c r="D38" s="245"/>
+      <c r="F38" s="244">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.1118012422360248</v>
       </c>
-      <c r="G38" s="248"/>
+      <c r="G38" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40263,30 +40316,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E79E4C-9700-5941-B1AA-B8688C681C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E4F058-1BA0-6A49-ABE6-8DCA684BCED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2406,6 +2376,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2415,15 +2388,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2431,6 +2395,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15166,7 +15136,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15184,10 +15154,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>105.46</v>
-    <v>2.1894</v>
-    <v>-4.6744000000000003</v>
-    <v>-5.6799999999999993E-3</v>
+    <v>118.52</v>
+    <v>2.2385000000000002</v>
+    <v>58.43</v>
+    <v>6.0980999999999994E-2</v>
+    <v>-0.74</v>
+    <v>-7.2789999999999997E-4</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15195,49 +15167,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>829</v>
+    <v>1017.77</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46237.674561885935</v>
+    <v>46269.899971839841</v>
     <v>0</v>
-    <v>770.15</v>
-    <v>924245086150</v>
+    <v>969</v>
+    <v>1148129629870</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>783.39</v>
-    <v>18.526499999999999</v>
-    <v>823.03</v>
-    <v>818.35559999999998</v>
+    <v>971.33500000000004</v>
+    <v>23.014299999999999</v>
+    <v>958.16</v>
+    <v>1016.59</v>
+    <v>1015.85</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>24279062</v>
-    <v>49389334</v>
+    <v>35072497</v>
+    <v>30343720</v>
     <v>1984</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15249,30 +15207,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.47</v>
+    <v>48.06</v>
     <v>39.47</v>
-    <v>0.82</v>
-    <v>1.7585E-2</v>
+    <v>-0.34</v>
+    <v>-7.0889999999999998E-3</v>
     <v>US</v>
-    <v>47.47</v>
+    <v>47.68</v>
     <v>Index</v>
-    <v>6</v>
-    <v>46.82</v>
+    <v>3</v>
+    <v>47.32</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.84</v>
-    <v>46.63</v>
-    <v>47.45</v>
+    <v>47.66</v>
+    <v>47.96</v>
+    <v>47.62</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15294,6 +15252,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15314,6 +15274,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15323,11 +15284,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15363,7 +15319,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15374,13 +15330,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15474,13 +15433,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15552,6 +15517,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15559,6 +15527,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16043,18 +16014,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="240" t="s">
+      <c r="B2" s="241" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="241"/>
-      <c r="E2" s="240" t="s">
+      <c r="C2" s="242"/>
+      <c r="E2" s="241" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="241"/>
-      <c r="H2" s="240" t="s">
+      <c r="F2" s="242"/>
+      <c r="H2" s="241" t="s">
         <v>333</v>
       </c>
-      <c r="I2" s="241"/>
+      <c r="I2" s="242"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -16069,7 +16040,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>937835.51760000002</v>
+        <v>1165012.1400000001</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -16077,7 +16048,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>549.74801266888994</v>
+        <v>539.72115865524631</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16093,7 +16064,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>913429.51760000002</v>
+        <v>1140606.1400000001</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -16101,7 +16072,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>535.25824961846001</v>
+        <v>529.67777868951578</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16110,7 +16081,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>248</v>
@@ -16125,23 +16096,23 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>174.43005596971361</v>
+        <v>172.63034811371932</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="212" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>1015.85</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>18.527407742811864</v>
+        <v>23.015395064523432</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -16149,7 +16120,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>809.47996071608281</v>
+        <v>800.93534730730278</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16158,14 +16129,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.6744000000000003</v>
+        <v>58.43</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>10.325309927553892</v>
+        <v>12.826461771938765</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -16173,23 +16144,23 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>517.22906974328657</v>
+        <v>510.74115819144606</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.74</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>270</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.6623005347350473E-2</v>
+        <v>2.143153632716651E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -16197,7 +16168,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.36796538113347477</v>
+        <v>-0.49759376130844685</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16206,37 +16177,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.6799999999999993E-3</v>
+        <v>6.0980999999999994E-2</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>293</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.3974091458529765E-2</v>
+        <v>4.3449178134744589E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-7.2789999999999997E-4</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>298</v>
       </c>
       <c r="F10" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>1.1963718359390913E-3</v>
+        <v>9.6308009288212208E-4</v>
       </c>
       <c r="H10" s="188" t="s">
         <v>376</v>
       </c>
       <c r="I10" s="216">
         <f ca="1">DDM!C26</f>
-        <v>4.1647624878204406</v>
+        <v>4.081029129084726</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16252,7 +16223,7 @@
       </c>
       <c r="F11" s="197">
         <f ca="1">Statement!AC163</f>
-        <v>6.4764021899526322E-4</v>
+        <v>5.213507903874719E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16261,7 +16232,7 @@
       </c>
       <c r="C12" s="213" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>105.46</v>
+        <v>118.52</v>
       </c>
       <c r="E12" s="189" t="s">
         <v>102</v>
@@ -16277,7 +16248,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1894</v>
+        <v>2.2385000000000002</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>104</v>
@@ -16293,7 +16264,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>49389334</v>
+        <v>30343720</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>105</v>
@@ -16309,7 +16280,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>2.6023753144322159E-2</v>
+        <v>2.0949137920571365E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16322,10 +16293,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="242" t="s">
+      <c r="B17" s="243" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="242"/>
+      <c r="C17" s="243"/>
       <c r="E17" s="188" t="s">
         <v>301</v>
       </c>
@@ -16398,14 +16369,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="242" t="s">
+      <c r="B25" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="242"/>
-      <c r="E25" s="240" t="s">
+      <c r="C25" s="243"/>
+      <c r="E25" s="241" t="s">
         <v>348</v>
       </c>
-      <c r="F25" s="241"/>
+      <c r="F25" s="242"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -16414,12 +16385,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="5">
+      <c r="E26" s="189" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.45</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16434,7 +16405,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16454,15 +16425,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="243" t="s">
+      <c r="B33" s="240" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16507,24 +16478,24 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="243"/>
-      <c r="C43" s="243"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="243"/>
-      <c r="F43" s="243"/>
-      <c r="G43" s="243"/>
-      <c r="H43" s="243"/>
+      <c r="B43" s="240"/>
+      <c r="C43" s="240"/>
+      <c r="D43" s="240"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
+      <c r="G43" s="240"/>
+      <c r="H43" s="240"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="243" t="s">
+      <c r="B46" s="240" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="243"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="243"/>
-      <c r="F46" s="243"/>
-      <c r="G46" s="243"/>
-      <c r="H46" s="243"/>
+      <c r="C46" s="240"/>
+      <c r="D46" s="240"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
+      <c r="G46" s="240"/>
+      <c r="H46" s="240"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="41" t="s">
@@ -16643,24 +16614,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="243"/>
-      <c r="C66" s="243"/>
-      <c r="D66" s="243"/>
-      <c r="E66" s="243"/>
-      <c r="F66" s="243"/>
-      <c r="G66" s="243"/>
-      <c r="H66" s="243"/>
+      <c r="B66" s="240"/>
+      <c r="C66" s="240"/>
+      <c r="D66" s="240"/>
+      <c r="E66" s="240"/>
+      <c r="F66" s="240"/>
+      <c r="G66" s="240"/>
+      <c r="H66" s="240"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="243" t="s">
+      <c r="B69" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="243"/>
-      <c r="D69" s="243"/>
-      <c r="E69" s="243"/>
-      <c r="F69" s="243"/>
-      <c r="G69" s="243"/>
-      <c r="H69" s="243"/>
+      <c r="C69" s="240"/>
+      <c r="D69" s="240"/>
+      <c r="E69" s="240"/>
+      <c r="F69" s="240"/>
+      <c r="G69" s="240"/>
+      <c r="H69" s="240"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -16675,28 +16646,28 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="243"/>
-      <c r="C76" s="243"/>
-      <c r="D76" s="243"/>
-      <c r="E76" s="243"/>
-      <c r="F76" s="243"/>
-      <c r="G76" s="243"/>
-      <c r="H76" s="243"/>
+      <c r="B76" s="240"/>
+      <c r="C76" s="240"/>
+      <c r="D76" s="240"/>
+      <c r="E76" s="240"/>
+      <c r="F76" s="240"/>
+      <c r="G76" s="240"/>
+      <c r="H76" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B76:H76"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16766,36 +16737,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -17995,35 +17966,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -20053,20 +20024,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -21459,12 +21430,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21472,6 +21437,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21509,20 +21480,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="S2" s="254"/>
       <c r="T2" s="254"/>
       <c r="U2" s="254"/>
@@ -22531,16 +22502,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22603,10 +22574,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="240" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22623,7 +22594,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22632,7 +22603,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>937835.51760000002</v>
+        <v>1165012.1400000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22650,7 +22621,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22659,7 +22630,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.1894</v>
+        <v>2.2385000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22691,10 +22662,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="240" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22702,7 +22673,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.0642831976520937E-3</v>
+        <v>4.8875315107834811E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22711,7 +22682,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99393571680234793</v>
+        <v>0.99511246848921653</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22729,7 +22700,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14597300000000002</v>
+        <v>0.1483525</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22738,7 +22709,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14533210835882257</v>
+        <v>0.14782434112611598</v>
       </c>
     </row>
   </sheetData>
@@ -22783,20 +22754,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -22989,7 +22960,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>666235.09645299753</v>
+        <v>654187.78373207781</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23043,23 +23014,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37870.602520565852</v>
+        <v>37788.375342471423</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>53885.167782972152</v>
+        <v>53651.423678486972</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>67331.916936629525</v>
+        <v>66894.281889070655</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>63180.844423172624</v>
+        <v>62633.899142086506</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>45294.951749031556</v>
+        <v>44805.345400708451</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23078,14 +23049,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>338041.73910617625</v>
+        <v>328341.12236608833</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="240" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23101,14 +23072,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14533210835882257</v>
+        <v>0.14782434112611598</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="240" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23116,7 +23087,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>267563.48341237172</v>
+        <v>265773.32545282401</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23125,7 +23096,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>338041.73910617625</v>
+        <v>328341.12236608833</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23134,7 +23105,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>605605.2225185479</v>
+        <v>594114.44781891233</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23161,7 +23132,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>630011.2225185479</v>
+        <v>618520.44781891233</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23179,7 +23150,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>549.74801266888994</v>
+        <v>539.72115865524631</v>
       </c>
     </row>
   </sheetData>
@@ -23222,20 +23193,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -24167,10 +24138,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="240" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="243"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -24188,7 +24159,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14533210835882257</v>
+        <v>0.14782434112611598</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24214,7 +24185,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>588999.95406275522</v>
+        <v>582604.73437818512</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -24241,7 +24212,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>613405.95406275522</v>
+        <v>607010.73437818512</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24259,14 +24230,14 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>535.25824961846001</v>
+        <v>529.67777868951578</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="240" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="243"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -24283,7 +24254,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14597300000000002</v>
+        <v>0.1483525</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24318,14 +24289,14 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>174.43005596971361</v>
+        <v>172.63034811371932</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="243" t="s">
+      <c r="B57" s="240" t="s">
         <v>327</v>
       </c>
-      <c r="C57" s="243"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -24342,7 +24313,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14533210835882257</v>
+        <v>0.14782434112611598</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24368,7 +24339,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>903258.03498063097</v>
+        <v>893465.90801416896</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24395,7 +24366,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>927664.03498063097</v>
+        <v>917871.90801416896</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24413,7 +24384,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>809.47996071608281</v>
+        <v>800.93534730730278</v>
       </c>
     </row>
   </sheetData>
@@ -24465,10 +24436,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="240" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24477,7 +24448,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>549.74801266888994</v>
+        <v>539.72115865524631</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24486,7 +24457,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>535.25824961846001</v>
+        <v>529.67777868951578</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24495,7 +24466,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>174.43005596971361</v>
+        <v>172.63034811371932</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24504,7 +24475,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>809.47996071608281</v>
+        <v>800.93534730730278</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24513,7 +24484,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>517.22906974328657</v>
+        <v>510.74115819144606</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24522,7 +24493,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24531,7 +24502,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.36796538113347477</v>
+        <v>-0.49759376130844685</v>
       </c>
     </row>
   </sheetData>
@@ -24587,20 +24558,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -24963,10 +24934,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="240" t="s">
         <v>371</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -25001,7 +24972,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14597300000000002</v>
+        <v>0.1483525</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25018,7 +24989,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C23/(C24-C25)</f>
-        <v>4.1647624878204406</v>
+        <v>4.081029129084726</v>
       </c>
     </row>
   </sheetData>
@@ -25067,20 +25038,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -25255,7 +25226,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1440317.9420962355</v>
+        <v>1414273.1408566041</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25309,23 +25280,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>6127.2341840320096</v>
+        <v>6113.9303244960265</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12250.914978310726</v>
+        <v>12197.772726582705</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>24494.725237845421</v>
+        <v>24335.517677269134</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48975.245158404825</v>
+        <v>48551.275211912616</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>97922.087920380203</v>
+        <v>96863.619503137743</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25344,7 +25315,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>730804.46317554498</v>
+        <v>709832.92863085668</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25360,7 +25331,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25369,7 +25340,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>837.0067942024076</v>
+        <v>816.91855099579709</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25408,7 +25379,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14533210835882257</v>
+        <v>0.14782434112611598</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25426,7 +25397,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>923923.47239999997</v>
+        <v>1147730.1100000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25453,7 +25424,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>899517.47239999997</v>
+        <v>1123324.1100000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25469,7 +25440,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>189770.2074789732</v>
+        <v>188062.11544339822</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25478,7 +25449,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>730804.46317554498</v>
+        <v>709832.92863085668</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25487,7 +25458,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>920574.67065451818</v>
+        <v>897895.04407425493</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25514,7 +25485,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>944980.67065451818</v>
+        <v>922301.04407425493</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -25532,7 +25503,7 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>837.0067942024076</v>
+        <v>816.91855099579709</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -25979,17 +25950,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32596,7 +32567,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32667,7 +32638,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33973,7 +33944,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>18.527407742811864</v>
+        <v>23.015395064523432</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34010,7 +33981,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.325309927553892</v>
+        <v>12.826461771938765</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34071,7 +34042,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>9.17282348199039</v>
+        <v>11.394802728247489</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34132,7 +34103,7 @@
       </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>937835.51760000002</v>
+        <v>1165012.1400000001</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34193,7 +34164,7 @@
       </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>913429.51760000002</v>
+        <v>1140606.1400000001</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34230,7 +34201,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>10.118411919268006</v>
+        <v>12.634935197288257</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34267,7 +34238,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC12</f>
-        <v>15.418353520247118</v>
+        <v>19.253011157436323</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34402,7 +34373,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
-        <v>37.561499423261779</v>
+        <v>46.660210669657168</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34439,7 +34410,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="102"/>
-        <v>36.939204050851693</v>
+        <v>46.126255102656771</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34476,7 +34447,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
-        <v>2.6623005347350473E-2</v>
+        <v>2.143153632716651E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34513,7 +34484,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.3974091458529765E-2</v>
+        <v>4.3449178134744589E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34550,7 +34521,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="158">
         <f ca="1">AC82/AC117</f>
-        <v>6.4764021899526322E-4</v>
+        <v>5.213507903874719E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34587,7 +34558,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="158">
         <f ca="1">-AC63/AC153</f>
-        <v>1.1963718359390913E-3</v>
+        <v>9.6308009288212208E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34624,7 +34595,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="158">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.8009554642612524E-3</v>
+        <v>1.4497703002476865E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35127,7 +35098,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>2.6023753144322159E-2</v>
+        <v>2.0949137920571365E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37002,15 +36973,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="240" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -37018,7 +36989,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37034,7 +37005,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>937835.51760000002</v>
+        <v>1165012.1400000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37054,7 +37025,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>913429.51760000002</v>
+        <v>1140606.1400000001</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37074,7 +37045,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>18.527407742811864</v>
+        <v>23.015395064523432</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>248</v>
@@ -37094,7 +37065,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.325309927553892</v>
+        <v>12.826461771938765</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>249</v>
@@ -37114,7 +37085,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.17282348199039</v>
+        <v>11.394802728247489</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37134,7 +37105,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.118411919268006</v>
+        <v>12.634935197288257</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37143,18 +37114,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>15.418353520247118</v>
+        <v>19.253011157436323</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="240" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>251</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37205,14 +37176,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="240" t="s">
         <v>250</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>254</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37281,14 +37252,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="240" t="s">
         <v>255</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>261</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37364,14 +37335,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="240" t="s">
         <v>273</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>276</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37379,7 +37350,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.3974091458529765E-2</v>
+        <v>4.3449178134744589E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>275</v>
@@ -37395,7 +37366,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>2.6623005347350473E-2</v>
+        <v>2.143153632716651E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>277</v>
@@ -37411,7 +37382,7 @@
       </c>
       <c r="C40" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.4764021899526322E-4</v>
+        <v>5.213507903874719E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>278</v>
@@ -37427,7 +37398,7 @@
       </c>
       <c r="C41" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1963718359390913E-3</v>
+        <v>9.6308009288212208E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37436,18 +37407,18 @@
       </c>
       <c r="C42" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.8009554642612524E-3</v>
+        <v>1.4497703002476865E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="240" t="s">
         <v>284</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>290</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37480,18 +37451,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>2.6023753144322159E-2</v>
+        <v>2.0949137920571365E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="240" t="s">
         <v>287</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>308</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37659,7 +37630,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC116</f>
-        <v>818.35559999999998</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37688,7 +37659,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>937835.51760000002</v>
+        <v>1165012.1400000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37717,7 +37688,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>913429.51760000002</v>
+        <v>1140606.1400000001</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37746,7 +37717,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>18.527407742811864</v>
+        <v>23.015395064523432</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37775,7 +37746,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.325309927553892</v>
+        <v>12.826461771938765</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37804,7 +37775,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.17282348199039</v>
+        <v>11.394802728247489</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37833,7 +37804,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.118411919268006</v>
+        <v>12.634935197288257</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37862,7 +37833,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>15.418353520247118</v>
+        <v>19.253011157436323</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38635,7 +38606,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.3974091458529765E-2</v>
+        <v>4.3449178134744589E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38664,7 +38635,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>2.6623005347350473E-2</v>
+        <v>2.143153632716651E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38693,7 +38664,7 @@
       </c>
       <c r="I53" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.4764021899526322E-4</v>
+        <v>5.213507903874719E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38722,7 +38693,7 @@
       </c>
       <c r="I54" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1963718359390913E-3</v>
+        <v>9.6308009288212208E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38751,7 +38722,7 @@
       </c>
       <c r="I55" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.8009554642612524E-3</v>
+        <v>1.4497703002476865E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38987,7 +38958,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>2.6023753144322159E-2</v>
+        <v>2.0949137920571365E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39593,14 +39564,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="244" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="245"/>
+      <c r="F3" s="246" t="s">
         <v>319</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="245"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39667,19 +39638,19 @@
       <c r="B7" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="247">
         <f>Statement!AA89</f>
         <v>0.73746856663872595</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.4571551446081066</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -39706,19 +39677,19 @@
       <c r="B9" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="247">
         <f>Statement!AA90</f>
         <v>4.8321048321048318E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.10478163300535129</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -39745,19 +39716,19 @@
       <c r="B11" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="247">
         <f>Statement!AA91</f>
         <v>0.97442973810194311</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.9931584948688705</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -39784,19 +39755,19 @@
       <c r="B13" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="247">
         <f>Statement!AA95</f>
         <v>7.2839506172839505E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.29798356982823004</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -39823,19 +39794,19 @@
       <c r="B15" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="247">
         <f>Statement!AA96</f>
         <v>1.0649519677719244</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>14.360995850622407</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -39862,19 +39833,19 @@
       <c r="B17" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="247">
         <f>Statement!AA98</f>
         <v>1.0488211824446863</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>13.983023872679045</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -39901,22 +39872,22 @@
       <c r="B19" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6269702276707531E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -39943,22 +39914,22 @@
       <c r="B21" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.0439105219552611</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>13.684523809523812</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40007,22 +39978,22 @@
       <c r="B25" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.66922421142369992</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>3.4304907368123319</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40050,22 +40021,22 @@
       <c r="B27" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.98979387632579552</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.613921113689095</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40093,22 +40064,22 @@
       <c r="B29" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.94736842105263153</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.4666666666666666</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="188" t="str">
@@ -40136,22 +40107,22 @@
       <c r="B32" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C32" s="244">
+      <c r="C32" s="247">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.77687443541102075</v>
       </c>
-      <c r="D32" s="245"/>
-      <c r="F32" s="244">
+      <c r="D32" s="248"/>
+      <c r="F32" s="247">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>3.066450088600118</v>
       </c>
-      <c r="G32" s="245"/>
+      <c r="G32" s="248"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="188" t="str">
@@ -40179,22 +40150,22 @@
       <c r="B34" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="244">
+      <c r="C34" s="247">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.0263759451380341</v>
       </c>
-      <c r="D34" s="245"/>
-      <c r="F34" s="244">
+      <c r="D34" s="248"/>
+      <c r="F34" s="247">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>6.5320261437908496</v>
       </c>
-      <c r="G34" s="245"/>
+      <c r="G34" s="248"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="188" t="str">
@@ -40222,22 +40193,22 @@
       <c r="B36" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="244">
+      <c r="C36" s="247">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.49409933860718452</v>
       </c>
-      <c r="D36" s="245"/>
-      <c r="F36" s="244">
+      <c r="D36" s="248"/>
+      <c r="F36" s="247">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.5394777265745008</v>
       </c>
-      <c r="G36" s="245"/>
+      <c r="G36" s="248"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="188" t="str">
@@ -40265,49 +40236,25 @@
       <c r="B38" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="244">
+      <c r="C38" s="247">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.71122599704579026</v>
       </c>
-      <c r="D38" s="245"/>
-      <c r="F38" s="244">
+      <c r="D38" s="248"/>
+      <c r="F38" s="247">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.1118012422360248</v>
       </c>
-      <c r="G38" s="245"/>
+      <c r="G38" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40316,6 +40263,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E4F058-1BA0-6A49-ABE6-8DCA684BCED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EE16C3-9505-8F4F-AABE-296A86B8052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2376,9 +2376,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2388,6 +2385,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2395,12 +2401,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14928,7 +14928,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -15154,12 +15154,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>118.52</v>
+    <v>154.65</v>
     <v>2.2385000000000002</v>
-    <v>58.43</v>
-    <v>6.0980999999999994E-2</v>
-    <v>-0.74</v>
-    <v>-7.2789999999999997E-4</v>
+    <v>-2.15</v>
+    <v>-2.2000000000000001E-3</v>
+    <v>0.19</v>
+    <v>1.9480000000000002E-4</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15167,25 +15167,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>1017.77</v>
+    <v>993.99</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46269.899971839841</v>
+    <v>46276.999989652344</v>
     <v>0</v>
-    <v>969</v>
-    <v>1148129629870</v>
+    <v>967.38</v>
+    <v>1101451817180</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>971.33500000000004</v>
-    <v>23.014299999999999</v>
-    <v>958.16</v>
-    <v>1016.59</v>
-    <v>1015.85</v>
+    <v>993.19500000000005</v>
+    <v>22.127300000000002</v>
+    <v>977.41</v>
+    <v>975.26</v>
+    <v>975.45</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>35072497</v>
-    <v>30343720</v>
+    <v>21740290</v>
+    <v>28045808</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15207,19 +15207,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>48.12</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>0.22</v>
+    <v>4.62E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>48.12</v>
     <v>Index</v>
     <v>3</v>
-    <v>47.32</v>
+    <v>47.48</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
+    <v>47.54</v>
     <v>47.62</v>
+    <v>47.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15441,9 +15441,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16014,18 +16014,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="241" t="s">
+      <c r="B2" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="242"/>
-      <c r="E2" s="241" t="s">
+      <c r="C2" s="241"/>
+      <c r="E2" s="240" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="242"/>
-      <c r="H2" s="241" t="s">
+      <c r="F2" s="241"/>
+      <c r="H2" s="240" t="s">
         <v>333</v>
       </c>
-      <c r="I2" s="242"/>
+      <c r="I2" s="241"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>1165012.1400000001</v>
+        <v>1117647.96</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>539.72115865524631</v>
+        <v>547.86252718665423</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>1140606.1400000001</v>
+        <v>1093241.96</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -16072,7 +16072,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>529.67777868951578</v>
+        <v>534.21883237825875</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>248</v>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>172.63034811371932</v>
+        <v>174.15557400143445</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -16105,14 +16105,14 @@
       </c>
       <c r="C6" s="212" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>1015.85</v>
+        <v>975.45</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>23.015395064523432</v>
+        <v>22.079692098709529</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>800.93534730730278</v>
+        <v>807.88844297483342</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16129,14 +16129,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>58.43</v>
+        <v>-2.15</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>12.826461771938765</v>
+        <v>12.304995236723752</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>510.74115819144606</v>
+        <v>516.03134413529517</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16153,14 +16153,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.74</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>270</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.143153632716651E-2</v>
+        <v>2.233977146077375E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.49759376130844685</v>
+        <v>-0.47087818208960158</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16177,14 +16177,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.0980999999999994E-2</v>
+        <v>-2.2000000000000001E-3</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>293</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>4.3449178134744589E-2</v>
+        <v>4.5290486639460246E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16193,21 +16193,21 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-7.2789999999999997E-4</v>
+        <v>1.9480000000000002E-4</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>298</v>
       </c>
       <c r="F10" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>9.6308009288212208E-4</v>
+        <v>1.0038939273865808E-3</v>
       </c>
       <c r="H10" s="188" t="s">
         <v>376</v>
       </c>
       <c r="I10" s="216">
         <f ca="1">DDM!C26</f>
-        <v>4.081029129084726</v>
+        <v>4.1518386714116255</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="F11" s="197">
         <f ca="1">Statement!AC163</f>
-        <v>5.213507903874719E-4</v>
+        <v>5.4344482496975171E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="C12" s="213" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>118.52</v>
+        <v>154.65</v>
       </c>
       <c r="E12" s="189" t="s">
         <v>102</v>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>30343720</v>
+        <v>28045808</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>105</v>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>2.0949137920571365E-2</v>
+        <v>2.1836929760959793E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16293,10 +16293,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="243" t="s">
+      <c r="B17" s="242" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="243"/>
+      <c r="C17" s="242"/>
       <c r="E17" s="188" t="s">
         <v>301</v>
       </c>
@@ -16369,14 +16369,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="243" t="s">
+      <c r="B25" s="242" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="243"/>
-      <c r="E25" s="241" t="s">
+      <c r="C25" s="242"/>
+      <c r="E25" s="240" t="s">
         <v>348</v>
       </c>
-      <c r="F25" s="242"/>
+      <c r="F25" s="241"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16425,15 +16425,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="240" t="s">
+      <c r="B33" s="243" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="240"/>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
+      <c r="C33" s="243"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16478,24 +16478,24 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="240"/>
-      <c r="C43" s="240"/>
-      <c r="D43" s="240"/>
-      <c r="E43" s="240"/>
-      <c r="F43" s="240"/>
-      <c r="G43" s="240"/>
-      <c r="H43" s="240"/>
+      <c r="B43" s="243"/>
+      <c r="C43" s="243"/>
+      <c r="D43" s="243"/>
+      <c r="E43" s="243"/>
+      <c r="F43" s="243"/>
+      <c r="G43" s="243"/>
+      <c r="H43" s="243"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="240" t="s">
+      <c r="B46" s="243" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="240"/>
-      <c r="D46" s="240"/>
-      <c r="E46" s="240"/>
-      <c r="F46" s="240"/>
-      <c r="G46" s="240"/>
-      <c r="H46" s="240"/>
+      <c r="C46" s="243"/>
+      <c r="D46" s="243"/>
+      <c r="E46" s="243"/>
+      <c r="F46" s="243"/>
+      <c r="G46" s="243"/>
+      <c r="H46" s="243"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="41" t="s">
@@ -16614,24 +16614,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="240"/>
-      <c r="C66" s="240"/>
-      <c r="D66" s="240"/>
-      <c r="E66" s="240"/>
-      <c r="F66" s="240"/>
-      <c r="G66" s="240"/>
-      <c r="H66" s="240"/>
+      <c r="B66" s="243"/>
+      <c r="C66" s="243"/>
+      <c r="D66" s="243"/>
+      <c r="E66" s="243"/>
+      <c r="F66" s="243"/>
+      <c r="G66" s="243"/>
+      <c r="H66" s="243"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="240" t="s">
+      <c r="B69" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="240"/>
-      <c r="D69" s="240"/>
-      <c r="E69" s="240"/>
-      <c r="F69" s="240"/>
-      <c r="G69" s="240"/>
-      <c r="H69" s="240"/>
+      <c r="C69" s="243"/>
+      <c r="D69" s="243"/>
+      <c r="E69" s="243"/>
+      <c r="F69" s="243"/>
+      <c r="G69" s="243"/>
+      <c r="H69" s="243"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -16646,28 +16646,28 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="240"/>
-      <c r="C76" s="240"/>
-      <c r="D76" s="240"/>
-      <c r="E76" s="240"/>
-      <c r="F76" s="240"/>
-      <c r="G76" s="240"/>
-      <c r="H76" s="240"/>
+      <c r="B76" s="243"/>
+      <c r="C76" s="243"/>
+      <c r="D76" s="243"/>
+      <c r="E76" s="243"/>
+      <c r="F76" s="243"/>
+      <c r="G76" s="243"/>
+      <c r="H76" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16737,36 +16737,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="240" t="s">
+      <c r="S2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240" t="s">
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -17966,35 +17966,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="P2" s="240" t="s">
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="P2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -20024,20 +20024,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -21430,6 +21430,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21437,12 +21443,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21480,20 +21480,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="S2" s="254"/>
       <c r="T2" s="254"/>
       <c r="U2" s="254"/>
@@ -22502,16 +22502,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22574,10 +22574,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="243"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22594,7 +22594,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1165012.1400000001</v>
+        <v>1117647.96</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="C11" s="139">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22662,10 +22662,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="243" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="240"/>
+      <c r="C15" s="243"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.8875315107834811E-3</v>
+        <v>5.0936024673474446E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99511246848921653</v>
+        <v>0.99490639753265253</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1483525</v>
+        <v>0.14633399999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14782434112611598</v>
+        <v>0.1457938540199526</v>
       </c>
     </row>
   </sheetData>
@@ -22754,20 +22754,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -22960,7 +22960,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>654187.78373207781</v>
+        <v>663969.66870370845</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23014,23 +23014,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37788.375342471423</v>
+        <v>37855.340973877588</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>53651.423678486972</v>
+        <v>53841.745959987173</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>66894.281889070655</v>
+        <v>67250.54708209369</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>62633.899142086506</v>
+        <v>63079.060492673736</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>44805.345400708451</v>
+        <v>45203.757782457957</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23049,14 +23049,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>328341.12236608833</v>
+        <v>336214.00386481558</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="240" t="s">
+      <c r="B13" s="243" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="240"/>
+      <c r="C13" s="243"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23072,14 +23072,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14782434112611598</v>
+        <v>0.1457938540199526</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="243" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="240"/>
+      <c r="C18" s="243"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>265773.32545282401</v>
+        <v>267230.45229109016</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>328341.12236608833</v>
+        <v>336214.00386481558</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>594114.44781891233</v>
+        <v>603444.45615590573</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23132,7 +23132,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>618520.44781891233</v>
+        <v>627850.45615590573</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>539.72115865524631</v>
+        <v>547.86252718665423</v>
       </c>
     </row>
   </sheetData>
@@ -23193,20 +23193,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -24138,10 +24138,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="243" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="240"/>
+      <c r="C37" s="243"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14782434112611598</v>
+        <v>0.1457938540199526</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>582604.73437818512</v>
+        <v>587808.7819054845</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>607010.73437818512</v>
+        <v>612214.7819054845</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24230,14 +24230,14 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>529.67777868951578</v>
+        <v>534.21883237825875</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="240" t="s">
+      <c r="B49" s="243" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="240"/>
+      <c r="C49" s="243"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -24254,7 +24254,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1483525</v>
+        <v>0.14633399999999999</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24289,14 +24289,14 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>172.63034811371932</v>
+        <v>174.15557400143445</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="240" t="s">
+      <c r="B57" s="243" t="s">
         <v>327</v>
       </c>
-      <c r="C57" s="240"/>
+      <c r="C57" s="243"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14782434112611598</v>
+        <v>0.1457938540199526</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>893465.90801416896</v>
+        <v>901434.1556491591</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>917871.90801416896</v>
+        <v>925840.1556491591</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24384,7 +24384,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>800.93534730730278</v>
+        <v>807.88844297483342</v>
       </c>
     </row>
   </sheetData>
@@ -24436,10 +24436,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="243"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>539.72115865524631</v>
+        <v>547.86252718665423</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>529.67777868951578</v>
+        <v>534.21883237825875</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>172.63034811371932</v>
+        <v>174.15557400143445</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>800.93534730730278</v>
+        <v>807.88844297483342</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>510.74115819144606</v>
+        <v>516.03134413529517</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24502,7 +24502,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.49759376130844685</v>
+        <v>-0.47087818208960158</v>
       </c>
     </row>
   </sheetData>
@@ -24558,20 +24558,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -24934,10 +24934,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="243" t="s">
         <v>371</v>
       </c>
-      <c r="C20" s="240"/>
+      <c r="C20" s="243"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24972,7 +24972,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1483525</v>
+        <v>0.14633399999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C23/(C24-C25)</f>
-        <v>4.081029129084726</v>
+        <v>4.1518386714116255</v>
       </c>
     </row>
   </sheetData>
@@ -25038,20 +25038,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -25226,7 +25226,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1414273.1408566041</v>
+        <v>1435420.3672743812</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25280,23 +25280,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>6113.9303244960265</v>
+        <v>6124.7649581854248</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12197.772726582705</v>
+        <v>12241.042928478111</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>24335.517677269134</v>
+        <v>24465.123641452814</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48551.275211912616</v>
+        <v>48896.346356166898</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>96863.619503137743</v>
+        <v>97724.937834823068</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25315,7 +25315,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>709832.92863085668</v>
+        <v>726853.12546375406</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>816.91855099579709</v>
+        <v>833.2252800556779</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14782434112611598</v>
+        <v>0.1457938540199526</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>1147730.1100000001</v>
+        <v>1101068.54</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>1123324.1100000001</v>
+        <v>1076662.54</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>188062.11544339822</v>
+        <v>189452.21571910632</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>709832.92863085668</v>
+        <v>726853.12546375406</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25458,7 +25458,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>897895.04407425493</v>
+        <v>916305.34118286031</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25485,7 +25485,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>922301.04407425493</v>
+        <v>940711.34118286031</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>816.91855099579709</v>
+        <v>833.2252800556779</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -25950,17 +25950,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32567,7 +32567,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32638,7 +32638,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33944,7 +33944,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>23.015395064523432</v>
+        <v>22.079692098709529</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33981,7 +33981,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>12.826461771938765</v>
+        <v>12.304995236723752</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>11.394802728247489</v>
+        <v>10.931541042849767</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1165012.1400000001</v>
+        <v>1117647.96</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>1140606.1400000001</v>
+        <v>1093241.96</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34201,7 +34201,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>12.634935197288257</v>
+        <v>12.110263863349358</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34238,7 +34238,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC12</f>
-        <v>19.253011157436323</v>
+        <v>18.453521259895684</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34373,7 +34373,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
-        <v>46.660210669657168</v>
+        <v>44.763215315603972</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34410,7 +34410,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="102"/>
-        <v>46.126255102656771</v>
+        <v>44.210841733579024</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34447,7 +34447,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
-        <v>2.143153632716651E-2</v>
+        <v>2.233977146077375E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34484,7 +34484,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.3449178134744589E-2</v>
+        <v>4.5290486639460246E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34521,7 +34521,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="158">
         <f ca="1">AC82/AC117</f>
-        <v>5.213507903874719E-4</v>
+        <v>5.4344482496975171E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34558,7 +34558,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="158">
         <f ca="1">-AC63/AC153</f>
-        <v>9.6308009288212208E-4</v>
+        <v>1.0038939273865808E-3</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34595,7 +34595,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="158">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.4497703002476865E-3</v>
+        <v>1.5112093078038635E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35098,7 +35098,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>2.0949137920571365E-2</v>
+        <v>2.1836929760959793E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -36973,15 +36973,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="240"/>
-      <c r="E4" s="240" t="s">
+      <c r="C4" s="243"/>
+      <c r="E4" s="243" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36989,7 +36989,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37005,7 +37005,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>1165012.1400000001</v>
+        <v>1117647.96</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>1140606.1400000001</v>
+        <v>1093241.96</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37045,7 +37045,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>23.015395064523432</v>
+        <v>22.079692098709529</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>248</v>
@@ -37065,7 +37065,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>12.826461771938765</v>
+        <v>12.304995236723752</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>249</v>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>11.394802728247489</v>
+        <v>10.931541042849767</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>12.634935197288257</v>
+        <v>12.110263863349358</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37114,18 +37114,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>19.253011157436323</v>
+        <v>18.453521259895684</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="243" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="E15" s="240" t="s">
+      <c r="C15" s="243"/>
+      <c r="E15" s="243" t="s">
         <v>251</v>
       </c>
-      <c r="F15" s="240"/>
+      <c r="F15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37176,14 +37176,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="240" t="s">
+      <c r="B21" s="243" t="s">
         <v>250</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="E21" s="240" t="s">
+      <c r="C21" s="243"/>
+      <c r="E21" s="243" t="s">
         <v>254</v>
       </c>
-      <c r="F21" s="240"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37252,14 +37252,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="243" t="s">
         <v>255</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="E29" s="240" t="s">
+      <c r="C29" s="243"/>
+      <c r="E29" s="243" t="s">
         <v>261</v>
       </c>
-      <c r="F29" s="240"/>
+      <c r="F29" s="243"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37335,14 +37335,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="243" t="s">
         <v>273</v>
       </c>
-      <c r="C37" s="240"/>
-      <c r="E37" s="240" t="s">
+      <c r="C37" s="243"/>
+      <c r="E37" s="243" t="s">
         <v>276</v>
       </c>
-      <c r="F37" s="240"/>
+      <c r="F37" s="243"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37350,7 +37350,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>4.3449178134744589E-2</v>
+        <v>4.5290486639460246E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>275</v>
@@ -37366,7 +37366,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>2.143153632716651E-2</v>
+        <v>2.233977146077375E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>277</v>
@@ -37382,7 +37382,7 @@
       </c>
       <c r="C40" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>5.213507903874719E-4</v>
+        <v>5.4344482496975171E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>278</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C41" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>9.6308009288212208E-4</v>
+        <v>1.0038939273865808E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37407,18 +37407,18 @@
       </c>
       <c r="C42" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.4497703002476865E-3</v>
+        <v>1.5112093078038635E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="240" t="s">
+      <c r="B45" s="243" t="s">
         <v>284</v>
       </c>
-      <c r="C45" s="240"/>
-      <c r="E45" s="240" t="s">
+      <c r="C45" s="243"/>
+      <c r="E45" s="243" t="s">
         <v>290</v>
       </c>
-      <c r="F45" s="240"/>
+      <c r="F45" s="243"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37451,18 +37451,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>2.0949137920571365E-2</v>
+        <v>2.1836929760959793E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+      <c r="B51" s="243" t="s">
         <v>287</v>
       </c>
-      <c r="C51" s="240"/>
-      <c r="E51" s="240" t="s">
+      <c r="C51" s="243"/>
+      <c r="E51" s="243" t="s">
         <v>308</v>
       </c>
-      <c r="F51" s="240"/>
+      <c r="F51" s="243"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC116</f>
-        <v>1016.59</v>
+        <v>975.26</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37659,7 +37659,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>1165012.1400000001</v>
+        <v>1117647.96</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>1140606.1400000001</v>
+        <v>1093241.96</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37717,7 +37717,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>23.015395064523432</v>
+        <v>22.079692098709529</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37746,7 +37746,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>12.826461771938765</v>
+        <v>12.304995236723752</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37775,7 +37775,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>11.394802728247489</v>
+        <v>10.931541042849767</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37804,7 +37804,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>12.634935197288257</v>
+        <v>12.110263863349358</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37833,7 +37833,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>19.253011157436323</v>
+        <v>18.453521259895684</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>4.3449178134744589E-2</v>
+        <v>4.5290486639460246E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38635,7 +38635,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>2.143153632716651E-2</v>
+        <v>2.233977146077375E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38664,7 +38664,7 @@
       </c>
       <c r="I53" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>5.213507903874719E-4</v>
+        <v>5.4344482496975171E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38693,7 +38693,7 @@
       </c>
       <c r="I54" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>9.6308009288212208E-4</v>
+        <v>1.0038939273865808E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38722,7 +38722,7 @@
       </c>
       <c r="I55" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.4497703002476865E-3</v>
+        <v>1.5112093078038635E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38958,7 +38958,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>2.0949137920571365E-2</v>
+        <v>2.1836929760959793E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39564,14 +39564,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="244" t="s">
+      <c r="C3" s="246" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="F3" s="246" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>319</v>
       </c>
-      <c r="G3" s="245"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39638,19 +39638,19 @@
       <c r="B7" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="244">
         <f>Statement!AA89</f>
         <v>0.73746856663872595</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.4571551446081066</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -39677,19 +39677,19 @@
       <c r="B9" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="244">
         <f>Statement!AA90</f>
         <v>4.8321048321048318E-2</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.10478163300535129</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -39716,19 +39716,19 @@
       <c r="B11" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="244">
         <f>Statement!AA91</f>
         <v>0.97442973810194311</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.9931584948688705</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -39755,19 +39755,19 @@
       <c r="B13" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="244">
         <f>Statement!AA95</f>
         <v>7.2839506172839505E-2</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.29798356982823004</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -39794,19 +39794,19 @@
       <c r="B15" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="244">
         <f>Statement!AA96</f>
         <v>1.0649519677719244</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>14.360995850622407</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -39833,19 +39833,19 @@
       <c r="B17" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="244">
         <f>Statement!AA98</f>
         <v>1.0488211824446863</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>13.983023872679045</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -39872,22 +39872,22 @@
       <c r="B19" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6269702276707531E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -39914,22 +39914,22 @@
       <c r="B21" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.0439105219552611</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>13.684523809523812</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39978,22 +39978,22 @@
       <c r="B25" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.66922421142369992</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>3.4304907368123319</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40021,22 +40021,22 @@
       <c r="B27" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.98979387632579552</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.613921113689095</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40064,22 +40064,22 @@
       <c r="B29" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.94736842105263153</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.4666666666666666</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="245"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="188" t="str">
@@ -40107,22 +40107,22 @@
       <c r="B32" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C32" s="247">
+      <c r="C32" s="244">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.77687443541102075</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="F32" s="247">
+      <c r="D32" s="245"/>
+      <c r="F32" s="244">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>3.066450088600118</v>
       </c>
-      <c r="G32" s="248"/>
+      <c r="G32" s="245"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="188" t="str">
@@ -40150,22 +40150,22 @@
       <c r="B34" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="247">
+      <c r="C34" s="244">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.0263759451380341</v>
       </c>
-      <c r="D34" s="248"/>
-      <c r="F34" s="247">
+      <c r="D34" s="245"/>
+      <c r="F34" s="244">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>6.5320261437908496</v>
       </c>
-      <c r="G34" s="248"/>
+      <c r="G34" s="245"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="188" t="str">
@@ -40193,22 +40193,22 @@
       <c r="B36" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="247">
+      <c r="C36" s="244">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.49409933860718452</v>
       </c>
-      <c r="D36" s="248"/>
-      <c r="F36" s="247">
+      <c r="D36" s="245"/>
+      <c r="F36" s="244">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.5394777265745008</v>
       </c>
-      <c r="G36" s="248"/>
+      <c r="G36" s="245"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="188" t="str">
@@ -40236,25 +40236,49 @@
       <c r="B38" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="247">
+      <c r="C38" s="244">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.71122599704579026</v>
       </c>
-      <c r="D38" s="248"/>
-      <c r="F38" s="247">
+      <c r="D38" s="245"/>
+      <c r="F38" s="244">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.1118012422360248</v>
       </c>
-      <c r="G38" s="248"/>
+      <c r="G38" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40263,30 +40287,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EE16C3-9505-8F4F-AABE-296A86B8052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F2C4FC-ADB9-2D46-9EAF-FC5354935DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,12 +161,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2376,6 +2406,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2385,15 +2418,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2401,6 +2425,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15136,7 +15166,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15155,11 +15185,9 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>154.65</v>
-    <v>2.2385000000000002</v>
-    <v>-2.15</v>
-    <v>-2.2000000000000001E-3</v>
-    <v>0.19</v>
-    <v>1.9480000000000002E-4</v>
+    <v>2.2370000000000001</v>
+    <v>44</v>
+    <v>4.2146999999999997E-2</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15167,35 +15195,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>993.99</v>
+    <v>1089.07</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46276.999989652344</v>
+    <v>46287.767626238281</v>
     <v>0</v>
-    <v>967.38</v>
-    <v>1101451817180</v>
+    <v>1030.0150000000001</v>
+    <v>1228734408280</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>993.19500000000005</v>
-    <v>22.127300000000002</v>
-    <v>977.41</v>
-    <v>975.26</v>
-    <v>975.45</v>
+    <v>1033</v>
+    <v>24.63</v>
+    <v>1043.96</v>
+    <v>1087.96</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>21740290</v>
-    <v>28045808</v>
+    <v>20306923</v>
+    <v>25909773</v>
     <v>1984</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15207,30 +15249,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.12</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.62E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>48.12</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>3</v>
-    <v>47.48</v>
+    <v>6</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.54</v>
-    <v>47.62</v>
-    <v>47.84</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15252,8 +15294,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15274,7 +15314,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15284,6 +15323,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15319,7 +15363,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15330,16 +15374,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15433,19 +15474,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15517,9 +15552,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15527,9 +15559,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16014,18 +16043,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="240" t="s">
+      <c r="B2" s="241" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="241"/>
-      <c r="E2" s="240" t="s">
+      <c r="C2" s="242"/>
+      <c r="E2" s="241" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="241"/>
-      <c r="H2" s="240" t="s">
+      <c r="F2" s="242"/>
+      <c r="H2" s="241" t="s">
         <v>333</v>
       </c>
-      <c r="I2" s="241"/>
+      <c r="I2" s="242"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -16040,7 +16069,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>1117647.96</v>
+        <v>1246802.1600000001</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -16048,7 +16077,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>547.86252718665423</v>
+        <v>540.7449403569484</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16064,7 +16093,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>1093241.96</v>
+        <v>1222396.1600000001</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -16072,7 +16101,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>534.21883237825875</v>
+        <v>530.25359083120281</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16081,7 +16110,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>248</v>
@@ -16096,23 +16125,23 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>174.15557400143445</v>
+        <v>172.85187754425812</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>975.45</v>
+      <c r="C6" s="212" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>22.079692098709529</v>
+        <v>24.63119764546072</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -16120,7 +16149,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>807.88844297483342</v>
+        <v>801.81700984249812</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16129,14 +16158,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.15</v>
+        <v>44</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>12.304995236723752</v>
+        <v>13.726947293794449</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -16144,23 +16173,23 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>516.03134413529517</v>
+        <v>511.41685464372688</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.19</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>270</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.233977146077375E-2</v>
+        <v>2.002563101109802E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -16168,7 +16197,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.47087818208960158</v>
+        <v>-0.52993046192532178</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16177,37 +16206,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.2000000000000001E-3</v>
+        <v>4.2146999999999997E-2</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>293</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>4.5290486639460246E-2</v>
+        <v>4.0598919077907275E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.9480000000000002E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>298</v>
       </c>
       <c r="F10" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>1.0038939273865808E-3</v>
+        <v>8.999021945871507E-4</v>
       </c>
       <c r="H10" s="188" t="s">
         <v>376</v>
       </c>
       <c r="I10" s="216">
         <f ca="1">DDM!C26</f>
-        <v>4.1518386714116255</v>
+        <v>4.0912094055464268</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16223,7 +16252,7 @@
       </c>
       <c r="F11" s="197">
         <f ca="1">Statement!AC163</f>
-        <v>5.4344482496975171E-4</v>
+        <v>4.8715026287731166E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16248,7 +16277,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2385000000000002</v>
+        <v>2.2370000000000001</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>104</v>
@@ -16264,7 +16293,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>28045808</v>
+        <v>25909773</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>105</v>
@@ -16280,7 +16309,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>2.1836929760959793E-2</v>
+        <v>1.9574877861937613E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16293,10 +16322,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="242" t="s">
+      <c r="B17" s="243" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="242"/>
+      <c r="C17" s="243"/>
       <c r="E17" s="188" t="s">
         <v>301</v>
       </c>
@@ -16369,14 +16398,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="242" t="s">
+      <c r="B25" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="242"/>
-      <c r="E25" s="240" t="s">
+      <c r="C25" s="243"/>
+      <c r="E25" s="241" t="s">
         <v>348</v>
       </c>
-      <c r="F25" s="241"/>
+      <c r="F25" s="242"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -16385,12 +16414,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="2">
+      <c r="E26" s="189" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.84</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16405,7 +16434,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16425,15 +16454,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="243" t="s">
+      <c r="B33" s="240" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16478,24 +16507,24 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="243"/>
-      <c r="C43" s="243"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="243"/>
-      <c r="F43" s="243"/>
-      <c r="G43" s="243"/>
-      <c r="H43" s="243"/>
+      <c r="B43" s="240"/>
+      <c r="C43" s="240"/>
+      <c r="D43" s="240"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
+      <c r="G43" s="240"/>
+      <c r="H43" s="240"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="243" t="s">
+      <c r="B46" s="240" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="243"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="243"/>
-      <c r="F46" s="243"/>
-      <c r="G46" s="243"/>
-      <c r="H46" s="243"/>
+      <c r="C46" s="240"/>
+      <c r="D46" s="240"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
+      <c r="G46" s="240"/>
+      <c r="H46" s="240"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="41" t="s">
@@ -16614,24 +16643,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="243"/>
-      <c r="C66" s="243"/>
-      <c r="D66" s="243"/>
-      <c r="E66" s="243"/>
-      <c r="F66" s="243"/>
-      <c r="G66" s="243"/>
-      <c r="H66" s="243"/>
+      <c r="B66" s="240"/>
+      <c r="C66" s="240"/>
+      <c r="D66" s="240"/>
+      <c r="E66" s="240"/>
+      <c r="F66" s="240"/>
+      <c r="G66" s="240"/>
+      <c r="H66" s="240"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="243" t="s">
+      <c r="B69" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="243"/>
-      <c r="D69" s="243"/>
-      <c r="E69" s="243"/>
-      <c r="F69" s="243"/>
-      <c r="G69" s="243"/>
-      <c r="H69" s="243"/>
+      <c r="C69" s="240"/>
+      <c r="D69" s="240"/>
+      <c r="E69" s="240"/>
+      <c r="F69" s="240"/>
+      <c r="G69" s="240"/>
+      <c r="H69" s="240"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -16646,28 +16675,28 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="243"/>
-      <c r="C76" s="243"/>
-      <c r="D76" s="243"/>
-      <c r="E76" s="243"/>
-      <c r="F76" s="243"/>
-      <c r="G76" s="243"/>
-      <c r="H76" s="243"/>
+      <c r="B76" s="240"/>
+      <c r="C76" s="240"/>
+      <c r="D76" s="240"/>
+      <c r="E76" s="240"/>
+      <c r="F76" s="240"/>
+      <c r="G76" s="240"/>
+      <c r="H76" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B76:H76"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16737,36 +16766,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -17966,35 +17995,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -20024,20 +20053,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -21430,12 +21459,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21443,6 +21466,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21480,20 +21509,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="S2" s="254"/>
       <c r="T2" s="254"/>
       <c r="U2" s="254"/>
@@ -21956,24 +21985,24 @@
         <v>72</v>
       </c>
       <c r="C15" s="133">
-        <f>-Statement!M83</f>
-        <v>-6.3364425860405277E-2</v>
+        <f>Statement!M83</f>
+        <v>6.3364425860405277E-2</v>
       </c>
       <c r="D15" s="133">
-        <f>-Statement!N83</f>
-        <v>-9.2780273743600455E-2</v>
+        <f>Statement!N83</f>
+        <v>9.2780273743600455E-2</v>
       </c>
       <c r="E15" s="133">
-        <f>-Statement!O83</f>
+        <f>Statement!O83</f>
         <v>0</v>
       </c>
       <c r="F15" s="133">
-        <f>-Statement!P83</f>
-        <v>-0.36370967741935484</v>
+        <f>Statement!P83</f>
+        <v>0.36370967741935484</v>
       </c>
       <c r="G15" s="134">
-        <f>-Statement!Q83</f>
-        <v>-0.1164284234514191</v>
+        <f>Statement!Q83</f>
+        <v>0.1164284234514191</v>
       </c>
       <c r="H15" s="133">
         <f>Overview!$C$26</f>
@@ -22267,11 +22296,11 @@
       </c>
       <c r="C27" s="130">
         <f>C10*(1-C15)</f>
-        <v>6681.118687680927</v>
+        <v>5884.8813123190739</v>
       </c>
       <c r="D27" s="130">
         <f t="shared" ref="D27:L27" si="6">D10*(1-D15)</f>
-        <v>10602.154215860412</v>
+        <v>8801.8457841395884</v>
       </c>
       <c r="E27" s="130">
         <f t="shared" si="6"/>
@@ -22279,11 +22308,11 @@
       </c>
       <c r="F27" s="130">
         <f t="shared" si="6"/>
-        <v>1778.2774193548387</v>
+        <v>829.7225806451612</v>
       </c>
       <c r="G27" s="135">
         <f t="shared" si="6"/>
-        <v>10907.505697120363</v>
+        <v>8632.4943028796351</v>
       </c>
       <c r="H27" s="130">
         <f t="shared" si="6"/>
@@ -22312,11 +22341,11 @@
       </c>
       <c r="C28" s="94">
         <f>C27+C20-C21+C22</f>
-        <v>2495.1186876809261</v>
+        <v>1698.8813123190739</v>
       </c>
       <c r="D28" s="94">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
-        <v>4406.1542158604134</v>
+        <v>2605.8457841395884</v>
       </c>
       <c r="E28" s="94">
         <f t="shared" si="7"/>
@@ -22324,11 +22353,11 @@
       </c>
       <c r="F28" s="94">
         <f t="shared" si="7"/>
-        <v>288.27741935483937</v>
+        <v>-660.27741935483937</v>
       </c>
       <c r="G28" s="131">
         <f t="shared" si="7"/>
-        <v>3064.505697120363</v>
+        <v>789.49430287963332</v>
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
@@ -22502,16 +22531,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22574,10 +22603,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="240" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22594,7 +22623,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22603,7 +22632,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1117647.96</v>
+        <v>1246802.1600000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22621,7 +22650,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22630,7 +22659,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.2385000000000002</v>
+        <v>2.2370000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22662,10 +22691,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="240" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22673,7 +22702,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.0936024673474446E-3</v>
+        <v>4.5683749525438294E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22682,7 +22711,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99490639753265253</v>
+        <v>0.99543162504745619</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22700,7 +22729,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14633399999999999</v>
+        <v>0.148058</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22709,7 +22738,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1457938540199526</v>
+        <v>0.14756567536811427</v>
       </c>
     </row>
   </sheetData>
@@ -22754,20 +22783,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -22874,11 +22903,11 @@
       </c>
       <c r="C7" s="116">
         <f>'FCF &amp; Other'!C28</f>
-        <v>2495.1186876809261</v>
+        <v>1698.8813123190739</v>
       </c>
       <c r="D7" s="116">
         <f>'FCF &amp; Other'!D28</f>
-        <v>4406.1542158604134</v>
+        <v>2605.8457841395884</v>
       </c>
       <c r="E7" s="116">
         <f>'FCF &amp; Other'!E28</f>
@@ -22886,11 +22915,11 @@
       </c>
       <c r="F7" s="116">
         <f>'FCF &amp; Other'!F28</f>
-        <v>288.27741935483937</v>
+        <v>-660.27741935483937</v>
       </c>
       <c r="G7" s="117">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3064.505697120363</v>
+        <v>789.49430287963332</v>
       </c>
       <c r="H7" s="116">
         <f>'FCF &amp; Other'!H28</f>
@@ -22960,7 +22989,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>663969.66870370845</v>
+        <v>655417.85786577209</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23014,23 +23043,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37855.340973877588</v>
+        <v>37796.892988965577</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>53841.745959987173</v>
+        <v>53675.612882686808</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>67250.54708209369</v>
+        <v>66939.526778362866</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>63079.060492673736</v>
+        <v>62690.389934394116</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>45203.757782457957</v>
+        <v>44855.864663975146</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23049,14 +23078,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>336214.00386481558</v>
+        <v>329329.41440067842</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="240" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23072,14 +23101,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1457938540199526</v>
+        <v>0.14756567536811427</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="240" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23087,7 +23116,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>267230.45229109016</v>
+        <v>265958.2872483845</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,7 +23125,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>336214.00386481558</v>
+        <v>329329.41440067842</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23105,7 +23134,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>603444.45615590573</v>
+        <v>595287.70164906292</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23132,7 +23161,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>627850.45615590573</v>
+        <v>619693.70164906292</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23150,7 +23179,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>547.86252718665423</v>
+        <v>540.7449403569484</v>
       </c>
     </row>
   </sheetData>
@@ -23193,20 +23222,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23368,11 +23397,11 @@
       </c>
       <c r="C8" s="92">
         <f>'FCF &amp; Other'!C28</f>
-        <v>2495.1186876809261</v>
+        <v>1698.8813123190739</v>
       </c>
       <c r="D8" s="92">
         <f>'FCF &amp; Other'!D28</f>
-        <v>4406.1542158604134</v>
+        <v>2605.8457841395884</v>
       </c>
       <c r="E8" s="92">
         <f>'FCF &amp; Other'!E28</f>
@@ -23380,11 +23409,11 @@
       </c>
       <c r="F8" s="92">
         <f>'FCF &amp; Other'!F28</f>
-        <v>288.27741935483937</v>
+        <v>-660.27741935483937</v>
       </c>
       <c r="G8" s="93">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3064.505697120363</v>
+        <v>789.49430287963332</v>
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
@@ -23574,26 +23603,26 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>0.76590966899281587</v>
+        <v>0.53385982013213984</v>
       </c>
       <c r="E14" s="95">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
 IF(E8=0,0,IF(E8&gt;0,1,-1)),
 (E8-D8)/ABS(D8)
 )</f>
-        <v>-2.9420564012939407</v>
+        <v>-4.2837706866929555</v>
       </c>
       <c r="F14" s="95">
         <f t="shared" si="3"/>
-        <v>1.0336890755352155</v>
+        <v>0.92283774461203227</v>
       </c>
       <c r="G14" s="96">
         <f t="shared" si="3"/>
-        <v>9.6304049202975452</v>
+        <v>2.1957008974364935</v>
       </c>
       <c r="H14" s="95">
         <f t="shared" si="3"/>
-        <v>13.153805316941147</v>
+        <v>53.939493383920606</v>
       </c>
       <c r="I14" s="95">
         <f t="shared" si="3"/>
@@ -24106,11 +24135,11 @@
       </c>
       <c r="C34" s="153">
         <f>C32/C8</f>
-        <v>36.650008054323891</v>
+        <v>53.827256405081414</v>
       </c>
       <c r="D34" s="153">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
-        <v>13.669476157506351</v>
+        <v>23.113347829939599</v>
       </c>
       <c r="E34" s="153">
         <f t="shared" si="13"/>
@@ -24118,11 +24147,11 @@
       </c>
       <c r="F34" s="153">
         <f t="shared" si="13"/>
-        <v>385.36580578743502</v>
+        <v>-168.2508847698424</v>
       </c>
       <c r="G34" s="154">
         <f t="shared" si="13"/>
-        <v>45.648797498223601</v>
+        <v>177.19063898213824</v>
       </c>
       <c r="H34" s="141"/>
       <c r="I34" s="141"/>
@@ -24138,10 +24167,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="240" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="243"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -24159,7 +24188,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1457938540199526</v>
+        <v>0.14756567536811427</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24185,7 +24214,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>587808.7819054845</v>
+        <v>583264.61509255844</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -24212,7 +24241,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>612214.7819054845</v>
+        <v>607670.61509255844</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24230,14 +24259,14 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>534.21883237825875</v>
+        <v>530.25359083120281</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="240" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="243"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -24254,7 +24283,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14633399999999999</v>
+        <v>0.148058</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24289,14 +24318,14 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>174.15557400143445</v>
+        <v>172.85187754425812</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="243" t="s">
+      <c r="B57" s="240" t="s">
         <v>327</v>
       </c>
-      <c r="C57" s="243"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -24313,7 +24342,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1457938540199526</v>
+        <v>0.14756567536811427</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24339,7 +24368,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>901434.1556491591</v>
+        <v>894476.29327950289</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24366,7 +24395,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>925840.1556491591</v>
+        <v>918882.29327950289</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24384,7 +24413,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>807.88844297483342</v>
+        <v>801.81700984249812</v>
       </c>
     </row>
   </sheetData>
@@ -24436,10 +24465,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="240" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24448,7 +24477,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>547.86252718665423</v>
+        <v>540.7449403569484</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24457,7 +24486,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>534.21883237825875</v>
+        <v>530.25359083120281</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24466,7 +24495,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>174.15557400143445</v>
+        <v>172.85187754425812</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24475,7 +24504,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>807.88844297483342</v>
+        <v>801.81700984249812</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24484,7 +24513,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>516.03134413529517</v>
+        <v>511.41685464372688</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24493,7 +24522,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24502,7 +24531,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.47087818208960158</v>
+        <v>-0.52993046192532178</v>
       </c>
     </row>
   </sheetData>
@@ -24558,20 +24587,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="252"/>
       <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -24934,10 +24963,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="240" t="s">
         <v>371</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24972,7 +25001,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14633399999999999</v>
+        <v>0.148058</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24989,7 +25018,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C23/(C24-C25)</f>
-        <v>4.1518386714116255</v>
+        <v>4.0912094055464268</v>
       </c>
     </row>
   </sheetData>
@@ -25038,20 +25067,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="252"/>
       <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -25158,11 +25187,11 @@
       </c>
       <c r="C7" s="116">
         <f>'FCF &amp; Other'!C28</f>
-        <v>2495.1186876809261</v>
+        <v>1698.8813123190739</v>
       </c>
       <c r="D7" s="116">
         <f>'FCF &amp; Other'!D28</f>
-        <v>4406.1542158604134</v>
+        <v>2605.8457841395884</v>
       </c>
       <c r="E7" s="116">
         <f>'FCF &amp; Other'!E28</f>
@@ -25170,31 +25199,31 @@
       </c>
       <c r="F7" s="116">
         <f>'FCF &amp; Other'!F28</f>
-        <v>288.27741935483937</v>
+        <v>-660.27741935483937</v>
       </c>
       <c r="G7" s="117">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3064.505697120363</v>
+        <v>789.49430287963332</v>
       </c>
       <c r="H7" s="130">
         <f>G7*(1+$C$17)</f>
-        <v>7017.7180464056319</v>
+        <v>1807.9419535943603</v>
       </c>
       <c r="I7" s="130">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>16070.574326268897</v>
+        <v>4140.1870737310846</v>
       </c>
       <c r="J7" s="130">
         <f t="shared" si="0"/>
-        <v>36801.615207155774</v>
+        <v>9481.0283988441843</v>
       </c>
       <c r="K7" s="130">
         <f t="shared" si="0"/>
-        <v>84275.698824386724</v>
+        <v>21711.555033353183</v>
       </c>
       <c r="L7" s="130">
         <f t="shared" si="0"/>
-        <v>192991.3503078456</v>
+        <v>49719.461026378791</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -25226,7 +25255,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1435420.3672743812</v>
+        <v>365037.68474415585</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25280,23 +25309,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>6124.7649581854248</v>
+        <v>1575.4583745408834</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12241.042928478111</v>
+        <v>3143.8720721071741</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>24465.123641452814</v>
+        <v>6273.6862906046717</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48896.346356166898</v>
+        <v>12519.319733814935</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>97724.937834823068</v>
+        <v>24982.659211412654</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25315,7 +25344,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>726853.12546375406</v>
+        <v>183421.37845074185</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25331,7 +25360,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25340,7 +25369,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>833.2252800556779</v>
+        <v>227.0348752287176</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25379,7 +25408,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1457938540199526</v>
+        <v>0.14756567536811427</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25397,7 +25426,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>1101068.54</v>
+        <v>1228306.8400000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25424,7 +25453,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>1076662.54</v>
+        <v>1203900.8400000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25440,7 +25469,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>189452.21571910632</v>
+        <v>48494.995682480316</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25449,7 +25478,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>726853.12546375406</v>
+        <v>183421.37845074185</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25458,7 +25487,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>916305.34118286031</v>
+        <v>231916.37413322215</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25485,7 +25514,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>940711.34118286031</v>
+        <v>256322.37413322215</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -25503,7 +25532,7 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>833.2252800556779</v>
+        <v>227.0348752287176</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -25568,11 +25597,11 @@
       </c>
       <c r="C41" s="116">
         <f>C7</f>
-        <v>2495.1186876809261</v>
+        <v>1698.8813123190739</v>
       </c>
       <c r="D41" s="116">
         <f t="shared" si="2"/>
-        <v>4406.1542158604134</v>
+        <v>2605.8457841395884</v>
       </c>
       <c r="E41" s="116">
         <f t="shared" si="2"/>
@@ -25580,31 +25609,31 @@
       </c>
       <c r="F41" s="116">
         <f t="shared" si="2"/>
-        <v>288.27741935483937</v>
+        <v>-660.27741935483937</v>
       </c>
       <c r="G41" s="117">
         <f t="shared" si="2"/>
-        <v>3064.505697120363</v>
+        <v>789.49430287963332</v>
       </c>
       <c r="H41" s="147">
         <f t="shared" si="2"/>
-        <v>7017.7180464056319</v>
+        <v>1807.9419535943603</v>
       </c>
       <c r="I41" s="147">
         <f t="shared" si="2"/>
-        <v>16070.574326268897</v>
+        <v>4140.1870737310846</v>
       </c>
       <c r="J41" s="147">
         <f t="shared" si="2"/>
-        <v>36801.615207155774</v>
+        <v>9481.0283988441843</v>
       </c>
       <c r="K41" s="147">
         <f t="shared" si="2"/>
-        <v>84275.698824386724</v>
+        <v>21711.555033353183</v>
       </c>
       <c r="L41" s="147">
         <f t="shared" si="2"/>
-        <v>192991.3503078456</v>
+        <v>49719.461026378791</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -25633,23 +25662,23 @@
       </c>
       <c r="H42" s="147">
         <f>H41/H43</f>
-        <v>28070.872185622527</v>
+        <v>7231.767814377441</v>
       </c>
       <c r="I42" s="147">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>64282.29730507559</v>
+        <v>16560.748294924339</v>
       </c>
       <c r="J42" s="147">
         <f t="shared" si="3"/>
-        <v>147206.46082862309</v>
+        <v>37924.113595376737</v>
       </c>
       <c r="K42" s="147">
         <f t="shared" si="3"/>
-        <v>337102.79529754689</v>
+        <v>86846.220133412731</v>
       </c>
       <c r="L42" s="147">
         <f t="shared" si="3"/>
-        <v>771965.40123138239</v>
+        <v>198877.84410551516</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -25658,11 +25687,11 @@
       </c>
       <c r="C43" s="95">
         <f>C41/C42</f>
-        <v>0.39712218489271461</v>
+        <v>0.27039333317190417</v>
       </c>
       <c r="D43" s="95">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
-        <v>0.45414906368381913</v>
+        <v>0.26858851619661805</v>
       </c>
       <c r="E43" s="95">
         <f t="shared" si="4"/>
@@ -25670,11 +25699,11 @@
       </c>
       <c r="F43" s="95">
         <f t="shared" si="4"/>
-        <v>0.2210716406095394</v>
+        <v>-0.50634771422917124</v>
       </c>
       <c r="G43" s="96">
         <f t="shared" si="4"/>
-        <v>0.313664861527161</v>
+        <v>8.0808014624322758E-2</v>
       </c>
       <c r="H43" s="172">
         <v>0.25</v>
@@ -25718,23 +25747,23 @@
       </c>
       <c r="H44" s="147">
         <f>H41/H45</f>
-        <v>701771.8046405632</v>
+        <v>180794.19535943601</v>
       </c>
       <c r="I44" s="147">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>803528.71631344489</v>
+        <v>207009.35368655424</v>
       </c>
       <c r="J44" s="147">
         <f t="shared" si="5"/>
-        <v>876228.9335037088</v>
+        <v>225738.77140105198</v>
       </c>
       <c r="K44" s="147">
         <f t="shared" si="5"/>
-        <v>1203938.5546340959</v>
+        <v>310165.07190504542</v>
       </c>
       <c r="L44" s="147">
         <f t="shared" si="5"/>
-        <v>1286609.0020523041</v>
+        <v>331463.07350919198</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -25743,11 +25772,11 @@
       </c>
       <c r="C45" s="95">
         <f>C41/C44</f>
-        <v>9.0060230560582058E-2</v>
+        <v>6.1320386656526761E-2</v>
       </c>
       <c r="D45" s="95">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
-        <v>0.14325229910463663</v>
+        <v>8.4720911117094358E-2</v>
       </c>
       <c r="E45" s="95">
         <f t="shared" si="6"/>
@@ -25755,11 +25784,11 @@
       </c>
       <c r="F45" s="95">
         <f t="shared" si="6"/>
-        <v>1.1480125019108733E-2</v>
+        <v>-2.6294349860811573E-2</v>
       </c>
       <c r="G45" s="96">
         <f t="shared" si="6"/>
-        <v>8.1986882581207204E-2</v>
+        <v>2.1121897984901099E-2</v>
       </c>
       <c r="H45" s="172">
         <v>0.01</v>
@@ -25784,19 +25813,19 @@
       <c r="C46" s="141"/>
       <c r="D46" s="95">
         <f>D41/C41-1</f>
-        <v>0.76590966899281598</v>
+        <v>0.53385982013213984</v>
       </c>
       <c r="E46" s="95">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
-        <v>-2.9420564012939407</v>
+        <v>-4.2837706866929555</v>
       </c>
       <c r="F46" s="95">
         <f t="shared" si="7"/>
-        <v>-1.0336890755352155</v>
+        <v>-0.92283774461203238</v>
       </c>
       <c r="G46" s="96">
         <f t="shared" si="7"/>
-        <v>9.6304049202975452</v>
+        <v>-2.1957008974364935</v>
       </c>
       <c r="H46" s="173">
         <f t="shared" si="7"/>
@@ -25804,7 +25833,7 @@
       </c>
       <c r="I46" s="173">
         <f t="shared" si="7"/>
-        <v>1.29</v>
+        <v>1.2899999999999996</v>
       </c>
       <c r="J46" s="173">
         <f t="shared" si="7"/>
@@ -25842,11 +25871,11 @@
       </c>
       <c r="H47" s="173">
         <f t="shared" si="7"/>
-        <v>1.873170131588795</v>
+        <v>-0.25979858604120354</v>
       </c>
       <c r="I47" s="173">
         <f t="shared" si="7"/>
-        <v>1.29</v>
+        <v>1.2899999999999996</v>
       </c>
       <c r="J47" s="173">
         <f t="shared" si="7"/>
@@ -25884,7 +25913,7 @@
       </c>
       <c r="H48" s="173">
         <f t="shared" si="8"/>
-        <v>17.774996111096453</v>
+        <v>3.8369146385423516</v>
       </c>
       <c r="I48" s="173">
         <f t="shared" si="8"/>
@@ -25900,7 +25929,7 @@
       </c>
       <c r="L48" s="173">
         <f t="shared" si="8"/>
-        <v>6.8666666666666876E-2</v>
+        <v>6.8666666666667098E-2</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
@@ -25950,17 +25979,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32567,7 +32596,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32638,7 +32667,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33944,7 +33973,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>22.079692098709529</v>
+        <v>24.63119764546072</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33981,7 +34010,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>12.304995236723752</v>
+        <v>13.726947293794449</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34042,7 +34071,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>10.931541042849767</v>
+        <v>12.19477820579008</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34103,7 +34132,7 @@
       </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1117647.96</v>
+        <v>1246802.1600000001</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34164,7 +34193,7 @@
       </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>1093241.96</v>
+        <v>1222396.1600000001</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34201,7 +34230,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>12.110263863349358</v>
+        <v>13.5409548707269</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34238,7 +34267,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC12</f>
-        <v>18.453521259895684</v>
+        <v>20.633596543051503</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34373,7 +34402,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
-        <v>44.763215315603972</v>
+        <v>49.936004485741755</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34410,7 +34439,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="102"/>
-        <v>44.210841733579024</v>
+        <v>49.433853751364204</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34447,7 +34476,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
-        <v>2.233977146077375E-2</v>
+        <v>2.002563101109802E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34484,7 +34513,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.5290486639460246E-2</v>
+        <v>4.0598919077907275E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34521,7 +34550,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="158">
         <f ca="1">AC82/AC117</f>
-        <v>5.4344482496975171E-4</v>
+        <v>4.8715026287731166E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34558,7 +34587,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="158">
         <f ca="1">-AC63/AC153</f>
-        <v>1.0038939273865808E-3</v>
+        <v>8.999021945871507E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34595,7 +34624,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="158">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.5112093078038635E-3</v>
+        <v>1.354665603081727E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35098,7 +35127,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>2.1836929760959793E-2</v>
+        <v>1.9574877861937613E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -36973,15 +37002,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="240" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36989,7 +37018,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37005,7 +37034,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>1117647.96</v>
+        <v>1246802.1600000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37025,7 +37054,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>1093241.96</v>
+        <v>1222396.1600000001</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37045,7 +37074,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>22.079692098709529</v>
+        <v>24.63119764546072</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>248</v>
@@ -37065,7 +37094,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>12.304995236723752</v>
+        <v>13.726947293794449</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>249</v>
@@ -37085,7 +37114,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>10.931541042849767</v>
+        <v>12.19477820579008</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37105,7 +37134,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>12.110263863349358</v>
+        <v>13.5409548707269</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37114,18 +37143,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>18.453521259895684</v>
+        <v>20.633596543051503</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="240" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>251</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37176,14 +37205,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="240" t="s">
         <v>250</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>254</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37252,14 +37281,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="240" t="s">
         <v>255</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>261</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37335,14 +37364,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="240" t="s">
         <v>273</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>276</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37350,7 +37379,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>4.5290486639460246E-2</v>
+        <v>4.0598919077907275E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>275</v>
@@ -37366,7 +37395,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>2.233977146077375E-2</v>
+        <v>2.002563101109802E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>277</v>
@@ -37382,7 +37411,7 @@
       </c>
       <c r="C40" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>5.4344482496975171E-4</v>
+        <v>4.8715026287731166E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>278</v>
@@ -37398,7 +37427,7 @@
       </c>
       <c r="C41" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.0038939273865808E-3</v>
+        <v>8.999021945871507E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37407,18 +37436,18 @@
       </c>
       <c r="C42" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.5112093078038635E-3</v>
+        <v>1.354665603081727E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="240" t="s">
         <v>284</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>290</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37451,18 +37480,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>2.1836929760959793E-2</v>
+        <v>1.9574877861937613E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="240" t="s">
         <v>287</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>308</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37630,7 +37659,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC116</f>
-        <v>975.26</v>
+        <v>1087.96</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37659,7 +37688,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>1117647.96</v>
+        <v>1246802.1600000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37688,7 +37717,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>1093241.96</v>
+        <v>1222396.1600000001</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37717,7 +37746,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>22.079692098709529</v>
+        <v>24.63119764546072</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37746,7 +37775,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>12.304995236723752</v>
+        <v>13.726947293794449</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37775,7 +37804,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>10.931541042849767</v>
+        <v>12.19477820579008</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37804,7 +37833,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>12.110263863349358</v>
+        <v>13.5409548707269</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37833,7 +37862,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>18.453521259895684</v>
+        <v>20.633596543051503</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38606,7 +38635,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>4.5290486639460246E-2</v>
+        <v>4.0598919077907275E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38635,7 +38664,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>2.233977146077375E-2</v>
+        <v>2.002563101109802E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38664,7 +38693,7 @@
       </c>
       <c r="I53" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>5.4344482496975171E-4</v>
+        <v>4.8715026287731166E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38693,7 +38722,7 @@
       </c>
       <c r="I54" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.0038939273865808E-3</v>
+        <v>8.999021945871507E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38722,7 +38751,7 @@
       </c>
       <c r="I55" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.5112093078038635E-3</v>
+        <v>1.354665603081727E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38958,7 +38987,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>2.1836929760959793E-2</v>
+        <v>1.9574877861937613E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39564,14 +39593,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="244" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="245"/>
+      <c r="F3" s="246" t="s">
         <v>319</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="245"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39638,19 +39667,19 @@
       <c r="B7" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="247">
         <f>Statement!AA89</f>
         <v>0.73746856663872595</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.4571551446081066</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -39677,19 +39706,19 @@
       <c r="B9" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="247">
         <f>Statement!AA90</f>
         <v>4.8321048321048318E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.10478163300535129</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -39716,19 +39745,19 @@
       <c r="B11" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="247">
         <f>Statement!AA91</f>
         <v>0.97442973810194311</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.9931584948688705</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -39755,19 +39784,19 @@
       <c r="B13" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="247">
         <f>Statement!AA95</f>
         <v>7.2839506172839505E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.29798356982823004</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -39794,19 +39823,19 @@
       <c r="B15" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="247">
         <f>Statement!AA96</f>
         <v>1.0649519677719244</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>14.360995850622407</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -39833,19 +39862,19 @@
       <c r="B17" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="247">
         <f>Statement!AA98</f>
         <v>1.0488211824446863</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>13.983023872679045</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -39872,22 +39901,22 @@
       <c r="B19" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6269702276707531E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -39914,22 +39943,22 @@
       <c r="B21" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.0439105219552611</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>13.684523809523812</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39978,22 +40007,22 @@
       <c r="B25" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.66922421142369992</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>3.4304907368123319</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40021,22 +40050,22 @@
       <c r="B27" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.98979387632579552</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.613921113689095</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40064,22 +40093,22 @@
       <c r="B29" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.94736842105263153</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.4666666666666666</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="188" t="str">
@@ -40107,22 +40136,22 @@
       <c r="B32" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C32" s="244">
+      <c r="C32" s="247">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.77687443541102075</v>
       </c>
-      <c r="D32" s="245"/>
-      <c r="F32" s="244">
+      <c r="D32" s="248"/>
+      <c r="F32" s="247">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>3.066450088600118</v>
       </c>
-      <c r="G32" s="245"/>
+      <c r="G32" s="248"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="188" t="str">
@@ -40150,22 +40179,22 @@
       <c r="B34" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="244">
+      <c r="C34" s="247">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.0263759451380341</v>
       </c>
-      <c r="D34" s="245"/>
-      <c r="F34" s="244">
+      <c r="D34" s="248"/>
+      <c r="F34" s="247">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>6.5320261437908496</v>
       </c>
-      <c r="G34" s="245"/>
+      <c r="G34" s="248"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="188" t="str">
@@ -40193,22 +40222,22 @@
       <c r="B36" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="244">
+      <c r="C36" s="247">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.49409933860718452</v>
       </c>
-      <c r="D36" s="245"/>
-      <c r="F36" s="244">
+      <c r="D36" s="248"/>
+      <c r="F36" s="247">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.5394777265745008</v>
       </c>
-      <c r="G36" s="245"/>
+      <c r="G36" s="248"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="188" t="str">
@@ -40236,49 +40265,25 @@
       <c r="B38" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="244">
+      <c r="C38" s="247">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.71122599704579026</v>
       </c>
-      <c r="D38" s="245"/>
-      <c r="F38" s="244">
+      <c r="D38" s="248"/>
+      <c r="F38" s="247">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.1118012422360248</v>
       </c>
-      <c r="G38" s="245"/>
+      <c r="G38" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40287,6 +40292,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC0139E-74FC-5F4B-9791-BA49DFDE1B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7497E187-33D6-7647-BE24-3DD92919E1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2387,10 +2357,42 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2402,36 +2404,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2441,8 +2413,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15149,7 +15119,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15169,8 +15139,10 @@
     <v>1255</v>
     <v>154.65</v>
     <v>2.2311999999999999</v>
-    <v>1.3087</v>
-    <v>1.2110000000000001E-3</v>
+    <v>1.75</v>
+    <v>1.6200000000000001E-3</v>
+    <v>-0.44</v>
+    <v>-4.0649999999999996E-4</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15181,46 +15153,32 @@
     <v>1108.72</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.724240277341</v>
+    <v>46290.840277360934</v>
     <v>0</v>
     <v>1073</v>
-    <v>1221821054909</v>
+    <v>1222319456040</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>1095</v>
-    <v>24.491399999999999</v>
+    <v>24.5014</v>
     <v>1080.53</v>
-    <v>1081.8387</v>
+    <v>1082.28</v>
+    <v>1081.8399999999999</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>13678342</v>
+    <v>19500891</v>
     <v>24917533</v>
     <v>1984</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15239,7 +15197,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -15249,13 +15207,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15277,6 +15235,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15297,6 +15257,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15306,11 +15267,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15346,7 +15302,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15357,13 +15313,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15457,13 +15416,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15535,6 +15500,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15542,6 +15510,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16026,18 +15997,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="241" t="s">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="242"/>
-      <c r="E2" s="241" t="s">
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="242"/>
-      <c r="H2" s="241" t="s">
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="242"/>
+      <c r="I2" s="240"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -16052,7 +16023,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1239787.1502</v>
+        <v>1240292.8799999999</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16060,7 +16031,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>525.53755182109433</v>
+        <v>525.53677107452643</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16076,7 +16047,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>1215381.1502</v>
+        <v>1215886.8799999999</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16084,7 +16055,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>712.71223026739199</v>
+        <v>715.01621993125616</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16093,7 +16064,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16115,16 +16086,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>1081.8399999999999</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>24.492612633008829</v>
+        <v>24.502603577088522</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16132,7 +16103,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>979.65561350226164</v>
+        <v>981.95936167423486</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16141,14 +16112,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.3087</v>
+        <v>1.75</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>13.649713974123225</v>
+        <v>13.655281919489553</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -16156,23 +16127,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>611.10866959654049</v>
+        <v>612.26040886885789</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.44</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>2.0138940781869057E-2</v>
+        <v>2.013072912262465E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -16180,7 +16151,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.43512034687191309</v>
+        <v>-0.43428649806994685</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16189,30 +16160,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.2110000000000001E-3</v>
+        <v>1.6200000000000001E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.0828637392986589E-2</v>
+        <v>4.0811989503640463E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-4.0649999999999996E-4</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>9.0499405468027409E-4</v>
+        <v>9.0462504307853493E-4</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>367</v>
@@ -16235,7 +16206,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>4.8990667462718801E-4</v>
+        <v>4.8970691503123038E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16292,7 +16263,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>1.9685637164462363E-2</v>
+        <v>1.9677610339906171E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16305,10 +16276,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="243" t="s">
+      <c r="B17" s="241" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="243"/>
+      <c r="C17" s="241"/>
       <c r="E17" s="184" t="s">
         <v>296</v>
       </c>
@@ -16381,14 +16352,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="243" t="s">
+      <c r="B25" s="241" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="243"/>
-      <c r="E25" s="241" t="s">
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="242"/>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -16397,7 +16368,7 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
@@ -16437,15 +16408,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="238" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
+      <c r="C33" s="238"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="238"/>
+      <c r="F33" s="238"/>
+      <c r="G33" s="238"/>
+      <c r="H33" s="238"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16490,24 +16461,24 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="237"/>
-      <c r="C43" s="237"/>
-      <c r="D43" s="237"/>
-      <c r="E43" s="237"/>
-      <c r="F43" s="237"/>
-      <c r="G43" s="237"/>
-      <c r="H43" s="237"/>
+      <c r="B43" s="238"/>
+      <c r="C43" s="238"/>
+      <c r="D43" s="238"/>
+      <c r="E43" s="238"/>
+      <c r="F43" s="238"/>
+      <c r="G43" s="238"/>
+      <c r="H43" s="238"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="237" t="s">
+      <c r="B46" s="238" t="s">
         <v>338</v>
       </c>
-      <c r="C46" s="237"/>
-      <c r="D46" s="237"/>
-      <c r="E46" s="237"/>
-      <c r="F46" s="237"/>
-      <c r="G46" s="237"/>
-      <c r="H46" s="237"/>
+      <c r="C46" s="238"/>
+      <c r="D46" s="238"/>
+      <c r="E46" s="238"/>
+      <c r="F46" s="238"/>
+      <c r="G46" s="238"/>
+      <c r="H46" s="238"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="41" t="s">
@@ -16626,24 +16597,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="237"/>
-      <c r="C66" s="237"/>
-      <c r="D66" s="237"/>
-      <c r="E66" s="237"/>
-      <c r="F66" s="237"/>
-      <c r="G66" s="237"/>
-      <c r="H66" s="237"/>
+      <c r="B66" s="238"/>
+      <c r="C66" s="238"/>
+      <c r="D66" s="238"/>
+      <c r="E66" s="238"/>
+      <c r="F66" s="238"/>
+      <c r="G66" s="238"/>
+      <c r="H66" s="238"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="237" t="s">
+      <c r="B69" s="238" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="237"/>
-      <c r="D69" s="237"/>
-      <c r="E69" s="237"/>
-      <c r="F69" s="237"/>
-      <c r="G69" s="237"/>
-      <c r="H69" s="237"/>
+      <c r="C69" s="238"/>
+      <c r="D69" s="238"/>
+      <c r="E69" s="238"/>
+      <c r="F69" s="238"/>
+      <c r="G69" s="238"/>
+      <c r="H69" s="238"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -16658,28 +16629,28 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="237"/>
-      <c r="C76" s="237"/>
-      <c r="D76" s="237"/>
-      <c r="E76" s="237"/>
-      <c r="F76" s="237"/>
-      <c r="G76" s="237"/>
-      <c r="H76" s="237"/>
+      <c r="B76" s="238"/>
+      <c r="C76" s="238"/>
+      <c r="D76" s="238"/>
+      <c r="E76" s="238"/>
+      <c r="F76" s="238"/>
+      <c r="G76" s="238"/>
+      <c r="H76" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B76:H76"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16749,36 +16720,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="237" t="s">
+      <c r="S2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="237" t="s">
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="238" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -16789,32 +16760,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="247" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
+      <c r="D4" s="247"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="247"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="249" t="s">
+      <c r="S4" s="248" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
-      <c r="AC4" s="250"/>
+      <c r="T4" s="249"/>
+      <c r="U4" s="249"/>
+      <c r="V4" s="249"/>
+      <c r="W4" s="249"/>
+      <c r="X4" s="249"/>
+      <c r="Y4" s="249"/>
+      <c r="Z4" s="249"/>
+      <c r="AA4" s="249"/>
+      <c r="AB4" s="249"/>
+      <c r="AC4" s="249"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17407,33 +17378,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="236" t="s">
+      <c r="C12" s="247" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="236"/>
-      <c r="E12" s="236"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
+      <c r="D12" s="247"/>
+      <c r="E12" s="247"/>
+      <c r="F12" s="247"/>
+      <c r="G12" s="247"/>
+      <c r="H12" s="247"/>
+      <c r="I12" s="247"/>
+      <c r="J12" s="247"/>
+      <c r="K12" s="247"/>
+      <c r="L12" s="247"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="249" t="s">
+      <c r="S12" s="248" t="s">
         <v>122</v>
       </c>
-      <c r="T12" s="250"/>
-      <c r="U12" s="250"/>
-      <c r="V12" s="250"/>
-      <c r="W12" s="250"/>
-      <c r="X12" s="250"/>
-      <c r="Y12" s="250"/>
-      <c r="Z12" s="250"/>
-      <c r="AA12" s="250"/>
-      <c r="AB12" s="250"/>
-      <c r="AC12" s="250"/>
+      <c r="T12" s="249"/>
+      <c r="U12" s="249"/>
+      <c r="V12" s="249"/>
+      <c r="W12" s="249"/>
+      <c r="X12" s="249"/>
+      <c r="Y12" s="249"/>
+      <c r="Z12" s="249"/>
+      <c r="AA12" s="249"/>
+      <c r="AB12" s="249"/>
+      <c r="AC12" s="249"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -17978,35 +17949,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="P2" s="237" t="s">
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="P2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="237"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237" t="s">
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -18015,31 +17986,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="247" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
-      <c r="P4" s="250" t="s">
+      <c r="D4" s="247"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="247"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
+      <c r="P4" s="249" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="250"/>
-      <c r="R4" s="250"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
+      <c r="Q4" s="249"/>
+      <c r="R4" s="249"/>
+      <c r="S4" s="249"/>
+      <c r="T4" s="249"/>
+      <c r="U4" s="249"/>
+      <c r="V4" s="249"/>
+      <c r="W4" s="249"/>
+      <c r="X4" s="249"/>
+      <c r="Y4" s="249"/>
+      <c r="Z4" s="249"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -18234,32 +18205,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="236" t="s">
+      <c r="C9" s="247" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
+      <c r="D9" s="247"/>
+      <c r="E9" s="247"/>
+      <c r="F9" s="247"/>
+      <c r="G9" s="247"/>
+      <c r="H9" s="247"/>
+      <c r="I9" s="247"/>
+      <c r="J9" s="247"/>
+      <c r="K9" s="247"/>
+      <c r="L9" s="247"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="250" t="s">
+      <c r="P9" s="249" t="s">
         <v>126</v>
       </c>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
+      <c r="Q9" s="249"/>
+      <c r="R9" s="249"/>
+      <c r="S9" s="249"/>
+      <c r="T9" s="249"/>
+      <c r="U9" s="249"/>
+      <c r="V9" s="249"/>
+      <c r="W9" s="249"/>
+      <c r="X9" s="249"/>
+      <c r="Y9" s="249"/>
+      <c r="Z9" s="249"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -19197,31 +19168,31 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C22" s="236" t="s">
+      <c r="C22" s="247" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="236"/>
-      <c r="E22" s="236"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="236"/>
-      <c r="H22" s="236"/>
-      <c r="I22" s="236"/>
-      <c r="J22" s="236"/>
-      <c r="K22" s="236"/>
-      <c r="L22" s="236"/>
-      <c r="P22" s="250" t="s">
+      <c r="D22" s="247"/>
+      <c r="E22" s="247"/>
+      <c r="F22" s="247"/>
+      <c r="G22" s="247"/>
+      <c r="H22" s="247"/>
+      <c r="I22" s="247"/>
+      <c r="J22" s="247"/>
+      <c r="K22" s="247"/>
+      <c r="L22" s="247"/>
+      <c r="P22" s="249" t="s">
         <v>128</v>
       </c>
-      <c r="Q22" s="250"/>
-      <c r="R22" s="250"/>
-      <c r="S22" s="250"/>
-      <c r="T22" s="250"/>
-      <c r="U22" s="250"/>
-      <c r="V22" s="250"/>
-      <c r="W22" s="250"/>
-      <c r="X22" s="250"/>
-      <c r="Y22" s="250"/>
-      <c r="Z22" s="250"/>
+      <c r="Q22" s="249"/>
+      <c r="R22" s="249"/>
+      <c r="S22" s="249"/>
+      <c r="T22" s="249"/>
+      <c r="U22" s="249"/>
+      <c r="V22" s="249"/>
+      <c r="W22" s="249"/>
+      <c r="X22" s="249"/>
+      <c r="Y22" s="249"/>
+      <c r="Z22" s="249"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B23" s="16" t="s">
@@ -20036,60 +20007,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="250"/>
+      <c r="H3" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
+      <c r="P3" s="252"/>
+      <c r="Q3" s="252"/>
+      <c r="R3" s="252"/>
+      <c r="S3" s="252"/>
+      <c r="T3" s="252"/>
+      <c r="U3" s="252"/>
+      <c r="V3" s="252"/>
+      <c r="W3" s="252"/>
+      <c r="X3" s="252"/>
+      <c r="Y3" s="252"/>
+      <c r="Z3" s="252"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="247" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="247"/>
+      <c r="E5" s="247"/>
+      <c r="F5" s="247"/>
+      <c r="G5" s="247"/>
+      <c r="H5" s="247"/>
+      <c r="I5" s="247"/>
+      <c r="J5" s="247"/>
+      <c r="K5" s="247"/>
+      <c r="L5" s="247"/>
+      <c r="P5" s="252"/>
+      <c r="Q5" s="252"/>
+      <c r="R5" s="252"/>
+      <c r="S5" s="252"/>
+      <c r="T5" s="252"/>
+      <c r="U5" s="252"/>
+      <c r="V5" s="252"/>
+      <c r="W5" s="252"/>
+      <c r="X5" s="252"/>
+      <c r="Y5" s="252"/>
+      <c r="Z5" s="252"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20275,30 +20246,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="236" t="s">
+      <c r="C11" s="247" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
+      <c r="D11" s="247"/>
+      <c r="E11" s="247"/>
+      <c r="F11" s="247"/>
+      <c r="G11" s="247"/>
+      <c r="H11" s="247"/>
+      <c r="I11" s="247"/>
+      <c r="J11" s="247"/>
+      <c r="K11" s="247"/>
+      <c r="L11" s="247"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="240"/>
-      <c r="Q11" s="240"/>
-      <c r="R11" s="240"/>
-      <c r="S11" s="240"/>
-      <c r="T11" s="240"/>
-      <c r="U11" s="240"/>
-      <c r="V11" s="240"/>
-      <c r="W11" s="240"/>
-      <c r="X11" s="240"/>
-      <c r="Y11" s="240"/>
-      <c r="Z11" s="240"/>
+      <c r="P11" s="252"/>
+      <c r="Q11" s="252"/>
+      <c r="R11" s="252"/>
+      <c r="S11" s="252"/>
+      <c r="T11" s="252"/>
+      <c r="U11" s="252"/>
+      <c r="V11" s="252"/>
+      <c r="W11" s="252"/>
+      <c r="X11" s="252"/>
+      <c r="Y11" s="252"/>
+      <c r="Z11" s="252"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20540,18 +20511,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="236" t="s">
+      <c r="C18" s="247" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="236"/>
-      <c r="E18" s="236"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="236"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="236"/>
+      <c r="D18" s="247"/>
+      <c r="E18" s="247"/>
+      <c r="F18" s="247"/>
+      <c r="G18" s="247"/>
+      <c r="H18" s="247"/>
+      <c r="I18" s="247"/>
+      <c r="J18" s="247"/>
+      <c r="K18" s="247"/>
+      <c r="L18" s="247"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20764,23 +20735,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="240"/>
-      <c r="C25" s="240"/>
+      <c r="B25" s="252"/>
+      <c r="C25" s="252"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="236" t="s">
+      <c r="C26" s="247" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="236"/>
-      <c r="E26" s="236"/>
-      <c r="F26" s="236"/>
-      <c r="G26" s="236"/>
-      <c r="H26" s="236"/>
-      <c r="I26" s="236"/>
-      <c r="J26" s="236"/>
-      <c r="K26" s="236"/>
-      <c r="L26" s="236"/>
+      <c r="D26" s="247"/>
+      <c r="E26" s="247"/>
+      <c r="F26" s="247"/>
+      <c r="G26" s="247"/>
+      <c r="H26" s="247"/>
+      <c r="I26" s="247"/>
+      <c r="J26" s="247"/>
+      <c r="K26" s="247"/>
+      <c r="L26" s="247"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20972,18 +20943,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="236" t="s">
+      <c r="C33" s="247" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="236"/>
-      <c r="E33" s="236"/>
-      <c r="F33" s="236"/>
-      <c r="G33" s="236"/>
-      <c r="H33" s="236"/>
-      <c r="I33" s="236"/>
-      <c r="J33" s="236"/>
-      <c r="K33" s="236"/>
-      <c r="L33" s="236"/>
+      <c r="D33" s="247"/>
+      <c r="E33" s="247"/>
+      <c r="F33" s="247"/>
+      <c r="G33" s="247"/>
+      <c r="H33" s="247"/>
+      <c r="I33" s="247"/>
+      <c r="J33" s="247"/>
+      <c r="K33" s="247"/>
+      <c r="L33" s="247"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -21167,18 +21138,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="236" t="s">
+      <c r="C40" s="247" t="s">
         <v>150</v>
       </c>
-      <c r="D40" s="236"/>
-      <c r="E40" s="236"/>
-      <c r="F40" s="236"/>
-      <c r="G40" s="236"/>
-      <c r="H40" s="236"/>
-      <c r="I40" s="236"/>
-      <c r="J40" s="236"/>
-      <c r="K40" s="236"/>
-      <c r="L40" s="236"/>
+      <c r="D40" s="247"/>
+      <c r="E40" s="247"/>
+      <c r="F40" s="247"/>
+      <c r="G40" s="247"/>
+      <c r="H40" s="247"/>
+      <c r="I40" s="247"/>
+      <c r="J40" s="247"/>
+      <c r="K40" s="247"/>
+      <c r="L40" s="247"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21442,12 +21413,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21455,6 +21420,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21492,60 +21463,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240"/>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="247" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
-      <c r="AA4" s="240"/>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
+      <c r="D4" s="247"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="247"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
+      <c r="S4" s="252"/>
+      <c r="T4" s="252"/>
+      <c r="U4" s="252"/>
+      <c r="V4" s="252"/>
+      <c r="W4" s="252"/>
+      <c r="X4" s="252"/>
+      <c r="Y4" s="252"/>
+      <c r="Z4" s="252"/>
+      <c r="AA4" s="252"/>
+      <c r="AB4" s="252"/>
+      <c r="AC4" s="252"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21908,18 +21879,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="236" t="s">
+      <c r="C13" s="247" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="236"/>
-      <c r="E13" s="236"/>
-      <c r="F13" s="236"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="247"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="247"/>
+      <c r="H13" s="247"/>
+      <c r="I13" s="247"/>
+      <c r="J13" s="247"/>
+      <c r="K13" s="247"/>
+      <c r="L13" s="247"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -22012,18 +21983,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="236" t="s">
+      <c r="C18" s="247" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="236"/>
-      <c r="E18" s="236"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="236"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="236"/>
+      <c r="D18" s="247"/>
+      <c r="E18" s="247"/>
+      <c r="F18" s="247"/>
+      <c r="G18" s="247"/>
+      <c r="H18" s="247"/>
+      <c r="I18" s="247"/>
+      <c r="J18" s="247"/>
+      <c r="K18" s="247"/>
+      <c r="L18" s="247"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -22215,18 +22186,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="236" t="s">
+      <c r="C25" s="247" t="s">
         <v>262</v>
       </c>
-      <c r="D25" s="236"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="236"/>
-      <c r="G25" s="236"/>
-      <c r="H25" s="236"/>
-      <c r="I25" s="236"/>
-      <c r="J25" s="236"/>
-      <c r="K25" s="236"/>
-      <c r="L25" s="236"/>
+      <c r="D25" s="247"/>
+      <c r="E25" s="247"/>
+      <c r="F25" s="247"/>
+      <c r="G25" s="247"/>
+      <c r="H25" s="247"/>
+      <c r="I25" s="247"/>
+      <c r="J25" s="247"/>
+      <c r="K25" s="247"/>
+      <c r="L25" s="247"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -22364,18 +22335,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="236" t="s">
+      <c r="C31" s="247" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="236"/>
-      <c r="E31" s="236"/>
-      <c r="F31" s="236"/>
-      <c r="G31" s="236"/>
-      <c r="H31" s="236"/>
-      <c r="I31" s="236"/>
-      <c r="J31" s="236"/>
-      <c r="K31" s="236"/>
-      <c r="L31" s="236"/>
+      <c r="D31" s="247"/>
+      <c r="E31" s="247"/>
+      <c r="F31" s="247"/>
+      <c r="G31" s="247"/>
+      <c r="H31" s="247"/>
+      <c r="I31" s="247"/>
+      <c r="J31" s="247"/>
+      <c r="K31" s="247"/>
+      <c r="L31" s="247"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22514,16 +22485,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22586,10 +22557,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="238" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="238"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22606,7 +22577,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22615,7 +22586,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1239787.1502</v>
+        <v>1240292.8799999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22674,10 +22645,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="238" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="238"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22685,7 +22656,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.5941051489514781E-3</v>
+        <v>4.5922405035805037E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22694,7 +22665,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99540589485104847</v>
+        <v>0.99540775949641946</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22721,7 +22692,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15151068225528705</v>
+        <v>0.15151089059957293</v>
       </c>
     </row>
   </sheetData>
@@ -22766,60 +22737,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="250"/>
+      <c r="H3" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
+      <c r="P3" s="252"/>
+      <c r="Q3" s="252"/>
+      <c r="R3" s="252"/>
+      <c r="S3" s="252"/>
+      <c r="T3" s="252"/>
+      <c r="U3" s="252"/>
+      <c r="V3" s="252"/>
+      <c r="W3" s="252"/>
+      <c r="X3" s="252"/>
+      <c r="Y3" s="252"/>
+      <c r="Z3" s="252"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="247" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="247"/>
+      <c r="E5" s="247"/>
+      <c r="F5" s="247"/>
+      <c r="G5" s="247"/>
+      <c r="H5" s="247"/>
+      <c r="I5" s="247"/>
+      <c r="J5" s="247"/>
+      <c r="K5" s="247"/>
+      <c r="L5" s="247"/>
+      <c r="P5" s="252"/>
+      <c r="Q5" s="252"/>
+      <c r="R5" s="252"/>
+      <c r="S5" s="252"/>
+      <c r="T5" s="252"/>
+      <c r="U5" s="252"/>
+      <c r="V5" s="252"/>
+      <c r="W5" s="252"/>
+      <c r="X5" s="252"/>
+      <c r="Y5" s="252"/>
+      <c r="Z5" s="252"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22972,7 +22943,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>637146.24810424191</v>
+        <v>637145.31004371878</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23026,23 +22997,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37667.403088912579</v>
+        <v>37667.396273702871</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>53308.463983096772</v>
+        <v>53308.444692766207</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>66253.888634398812</v>
+        <v>66253.852672211899</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>61835.700526873872</v>
+        <v>61835.655774847692</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>44092.743842015494</v>
+        <v>44092.703953257231</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23061,14 +23032,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>314701.83431167656</v>
+        <v>314701.08628462133</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="238" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="237"/>
+      <c r="C13" s="238"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23084,14 +23055,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151068225528705</v>
+        <v>0.15151089059957293</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="238" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="237"/>
+      <c r="C18" s="238"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23099,7 +23070,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>263158.20007529756</v>
+        <v>263158.05336678587</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23108,7 +23079,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>314701.83431167656</v>
+        <v>314701.08628462133</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23117,7 +23088,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>577860.03438697406</v>
+        <v>577859.13965140725</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23144,7 +23115,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>602266.03438697406</v>
+        <v>602265.13965140725</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23157,12 +23128,12 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="236" t="s">
         <v>192</v>
       </c>
-      <c r="C26" s="255">
+      <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>525.53755182109433</v>
+        <v>525.53677107452643</v>
       </c>
     </row>
   </sheetData>
@@ -23205,37 +23176,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="247" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
+      <c r="D4" s="247"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="247"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23431,23 +23402,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>37667.403088912579</v>
+        <v>37667.396273702871</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>53308.463983096772</v>
+        <v>53308.444692766207</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>66253.888634398812</v>
+        <v>66253.852672211899</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>61835.700526873872</v>
+        <v>61835.655774847692</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>44092.743842015494</v>
+        <v>44092.703953257231</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -23455,18 +23426,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="236" t="s">
+      <c r="C11" s="247" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
+      <c r="D11" s="247"/>
+      <c r="E11" s="247"/>
+      <c r="F11" s="247"/>
+      <c r="G11" s="247"/>
+      <c r="H11" s="247"/>
+      <c r="I11" s="247"/>
+      <c r="J11" s="247"/>
+      <c r="K11" s="247"/>
+      <c r="L11" s="247"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23660,18 +23631,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="236" t="s">
+      <c r="C17" s="247" t="s">
         <v>196</v>
       </c>
-      <c r="D17" s="236"/>
-      <c r="E17" s="236"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="236"/>
-      <c r="J17" s="236"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="236"/>
+      <c r="D17" s="247"/>
+      <c r="E17" s="247"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="247"/>
+      <c r="H17" s="247"/>
+      <c r="I17" s="247"/>
+      <c r="J17" s="247"/>
+      <c r="K17" s="247"/>
+      <c r="L17" s="247"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23805,18 +23776,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="236" t="s">
+      <c r="C22" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="236"/>
-      <c r="E22" s="236"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="236"/>
-      <c r="H22" s="236"/>
-      <c r="I22" s="236"/>
-      <c r="J22" s="236"/>
-      <c r="K22" s="236"/>
-      <c r="L22" s="236"/>
+      <c r="D22" s="247"/>
+      <c r="E22" s="247"/>
+      <c r="F22" s="247"/>
+      <c r="G22" s="247"/>
+      <c r="H22" s="247"/>
+      <c r="I22" s="247"/>
+      <c r="J22" s="247"/>
+      <c r="K22" s="247"/>
+      <c r="L22" s="247"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23900,18 +23871,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="236" t="s">
+      <c r="C27" s="247" t="s">
         <v>200</v>
       </c>
-      <c r="D27" s="236"/>
-      <c r="E27" s="236"/>
-      <c r="F27" s="236"/>
-      <c r="G27" s="236"/>
-      <c r="H27" s="236"/>
-      <c r="I27" s="236"/>
-      <c r="J27" s="236"/>
-      <c r="K27" s="236"/>
-      <c r="L27" s="236"/>
+      <c r="D27" s="247"/>
+      <c r="E27" s="247"/>
+      <c r="F27" s="247"/>
+      <c r="G27" s="247"/>
+      <c r="H27" s="247"/>
+      <c r="I27" s="247"/>
+      <c r="J27" s="247"/>
+      <c r="K27" s="247"/>
+      <c r="L27" s="247"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -24181,10 +24152,10 @@
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="237" t="s">
+      <c r="B38" s="238" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="237"/>
+      <c r="C38" s="238"/>
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -24202,7 +24173,7 @@
       </c>
       <c r="C40" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151068225528705</v>
+        <v>0.15151089059957293</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -24227,8 +24198,8 @@
         <v>424</v>
       </c>
       <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5-G31+G32</f>
-        <v>573296.75965314917</v>
+        <f ca="1">C42/(1+C40)^5</f>
+        <v>575937.23862769082</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -24237,7 +24208,7 @@
       </c>
       <c r="C44" s="110">
         <f ca="1">SUM(H9:K9)+C43</f>
-        <v>792362.21588643128</v>
+        <v>795002.58804121951</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24264,7 +24235,7 @@
       </c>
       <c r="C47" s="110">
         <f ca="1">C44+C45-C46</f>
-        <v>816768.21588643128</v>
+        <v>819408.58804121951</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -24277,19 +24248,19 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="254" t="s">
+      <c r="B49" s="236" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="255">
+      <c r="C49" s="237">
         <f ca="1">C47/C48</f>
-        <v>712.71223026739199</v>
+        <v>715.01621993125616</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="237"/>
+      <c r="C51" s="238"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -24336,19 +24307,19 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="254" t="s">
+      <c r="B57" s="236" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="255">
+      <c r="C57" s="237">
         <f ca="1">C56/(1+C53)^5</f>
         <v>226.52928279541413</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="237" t="s">
+      <c r="B59" s="238" t="s">
         <v>322</v>
       </c>
-      <c r="C59" s="237"/>
+      <c r="C59" s="238"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -24365,7 +24336,7 @@
       </c>
       <c r="C61" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151068225528705</v>
+        <v>0.15151089059957293</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -24390,8 +24361,8 @@
         <v>424</v>
       </c>
       <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5-G31+G32</f>
-        <v>879213.87684030971</v>
+        <f ca="1">C63/(1+C61)^5</f>
+        <v>881854.07906514453</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -24400,7 +24371,7 @@
       </c>
       <c r="C65" s="110">
         <f ca="1">SUM(H9:K9)+C64</f>
-        <v>1098279.3330735918</v>
+        <v>1100919.4284786731</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24427,7 +24398,7 @@
       </c>
       <c r="C68" s="110">
         <f ca="1">C65+C66-C67</f>
-        <v>1122685.3330735918</v>
+        <v>1125325.4284786731</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -24440,12 +24411,12 @@
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="254" t="s">
+      <c r="B70" s="236" t="s">
         <v>209</v>
       </c>
-      <c r="C70" s="255">
+      <c r="C70" s="237">
         <f ca="1">C68/C69</f>
-        <v>979.65561350226164</v>
+        <v>981.95936167423486</v>
       </c>
     </row>
   </sheetData>
@@ -24497,10 +24468,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="238" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="238"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24509,7 +24480,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>525.53755182109433</v>
+        <v>525.53677107452643</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24518,7 +24489,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C49</f>
-        <v>712.71223026739199</v>
+        <v>715.01621993125616</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24536,16 +24507,16 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C70</f>
-        <v>979.65561350226164</v>
+        <v>981.95936167423486</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="254" t="s">
+      <c r="B9" s="236" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="237">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>611.10866959654049</v>
+        <v>612.26040886885789</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24554,7 +24525,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24563,7 +24534,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.43512034687191309</v>
+        <v>-0.43428649806994685</v>
       </c>
     </row>
   </sheetData>
@@ -24619,37 +24590,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="247" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
+      <c r="D4" s="247"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="247"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24762,18 +24733,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="236" t="s">
+      <c r="C9" s="247" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
+      <c r="D9" s="247"/>
+      <c r="E9" s="247"/>
+      <c r="F9" s="247"/>
+      <c r="G9" s="247"/>
+      <c r="H9" s="247"/>
+      <c r="I9" s="247"/>
+      <c r="J9" s="247"/>
+      <c r="K9" s="247"/>
+      <c r="L9" s="247"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24894,18 +24865,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="236" t="s">
+      <c r="C14" s="247" t="s">
         <v>360</v>
       </c>
-      <c r="D14" s="236"/>
-      <c r="E14" s="236"/>
-      <c r="F14" s="236"/>
-      <c r="G14" s="236"/>
-      <c r="H14" s="236"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="236"/>
-      <c r="K14" s="236"/>
-      <c r="L14" s="236"/>
+      <c r="D14" s="247"/>
+      <c r="E14" s="247"/>
+      <c r="F14" s="247"/>
+      <c r="G14" s="247"/>
+      <c r="H14" s="247"/>
+      <c r="I14" s="247"/>
+      <c r="J14" s="247"/>
+      <c r="K14" s="247"/>
+      <c r="L14" s="247"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24995,10 +24966,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="238" t="s">
         <v>362</v>
       </c>
-      <c r="C20" s="237"/>
+      <c r="C20" s="238"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -25045,10 +25016,10 @@
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="236" t="s">
         <v>209</v>
       </c>
-      <c r="C26" s="255">
+      <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
         <v>3.9582377237264805</v>
       </c>
@@ -25099,60 +25070,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="250"/>
+      <c r="H3" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
+      <c r="P3" s="252"/>
+      <c r="Q3" s="252"/>
+      <c r="R3" s="252"/>
+      <c r="S3" s="252"/>
+      <c r="T3" s="252"/>
+      <c r="U3" s="252"/>
+      <c r="V3" s="252"/>
+      <c r="W3" s="252"/>
+      <c r="X3" s="252"/>
+      <c r="Y3" s="252"/>
+      <c r="Z3" s="252"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="247" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="247"/>
+      <c r="E5" s="247"/>
+      <c r="F5" s="247"/>
+      <c r="G5" s="247"/>
+      <c r="H5" s="247"/>
+      <c r="I5" s="247"/>
+      <c r="J5" s="247"/>
+      <c r="K5" s="247"/>
+      <c r="L5" s="247"/>
+      <c r="P5" s="252"/>
+      <c r="Q5" s="252"/>
+      <c r="R5" s="252"/>
+      <c r="S5" s="252"/>
+      <c r="T5" s="252"/>
+      <c r="U5" s="252"/>
+      <c r="V5" s="252"/>
+      <c r="W5" s="252"/>
+      <c r="X5" s="252"/>
+      <c r="Y5" s="252"/>
+      <c r="Z5" s="252"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -25287,7 +25258,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1981042.3555820691</v>
+        <v>1981039.4389241843</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25341,23 +25312,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>2214.5401146490381</v>
+        <v>2214.5397139695633</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6211.8091308601506</v>
+        <v>6211.8068830397751</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>17424.192238826421</v>
+        <v>17424.182781086336</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48875.048923716509</v>
+        <v>48875.013551634518</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>137095.04432422257</v>
+        <v>137094.92030038996</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25376,15 +25347,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>978484.39821433683</v>
+        <v>978482.07241663511</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="253" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="254"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25392,7 +25363,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25401,7 +25372,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1075.9176554000103</v>
+        <v>1075.915443442653</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25411,20 +25382,20 @@
       <c r="C17" s="160">
         <v>2.23</v>
       </c>
-      <c r="E17" s="253" t="s">
+      <c r="E17" s="255" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="253"/>
-      <c r="G17" s="253"/>
-      <c r="H17" s="253"/>
-      <c r="I17" s="253"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="253" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="254"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25440,7 +25411,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151068225528705</v>
+        <v>0.15151089059957293</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25458,7 +25429,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1221395.8922999999</v>
+        <v>1221894.1199999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25485,15 +25456,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>1196989.8922999999</v>
+        <v>1197488.1199999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="253" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="254"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25501,7 +25472,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>211820.63473227469</v>
+        <v>211820.46323012013</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25510,7 +25481,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>978484.39821433683</v>
+        <v>978482.07241663511</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25519,7 +25490,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1190305.0329466115</v>
+        <v>1190302.5356467552</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25546,7 +25517,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1214711.0329466115</v>
+        <v>1214708.5356467552</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25564,21 +25535,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1075.9176554000103</v>
+        <v>1075.915443442653</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32185,7 +32156,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32256,7 +32227,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33562,7 +33533,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>24.492612633008829</v>
+        <v>24.502603577088522</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33599,7 +33570,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>13.649713974123225</v>
+        <v>13.655281919489553</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33660,7 +33631,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>12.1261654848894</v>
+        <v>12.131111949485723</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33721,7 +33692,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1239787.1502</v>
+        <v>1240292.8799999999</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -33782,7 +33753,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>1215381.1502</v>
+        <v>1215886.8799999999</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -33819,7 +33790,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>13.463246895008529</v>
+        <v>13.468849059529875</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33856,7 +33827,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>20.515185763718922</v>
+        <v>20.523722296305046</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -33991,7 +33962,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
-        <v>49.655044464915093</v>
+        <v>49.675299583466831</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34028,7 +33999,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="102"/>
-        <v>49.150165876790389</v>
+        <v>49.1706176532185</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34065,7 +34036,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
-        <v>2.0138940781869057E-2</v>
+        <v>2.013072912262465E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34102,7 +34073,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.0828637392986589E-2</v>
+        <v>4.0811989503640463E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34139,7 +34110,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>4.8990667462718801E-4</v>
+        <v>4.8970691503123038E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34176,7 +34147,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>9.0499405468027409E-4</v>
+        <v>9.0462504307853493E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34213,7 +34184,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.3623306224197708E-3</v>
+        <v>1.3617751316930887E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -34716,7 +34687,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>1.9685637164462363E-2</v>
+        <v>1.9677610339906171E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -36591,15 +36562,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="238" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="E4" s="237" t="s">
+      <c r="C4" s="238"/>
+      <c r="E4" s="238" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36607,7 +36578,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -36623,7 +36594,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1239787.1502</v>
+        <v>1240292.8799999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -36643,7 +36614,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1215381.1502</v>
+        <v>1215886.8799999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -36663,7 +36634,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>24.492612633008829</v>
+        <v>24.502603577088522</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -36683,7 +36654,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>13.649713974123225</v>
+        <v>13.655281919489553</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -36703,7 +36674,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>12.1261654848894</v>
+        <v>12.131111949485723</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36723,7 +36694,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>13.463246895008529</v>
+        <v>13.468849059529875</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36732,18 +36703,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>20.515185763718922</v>
+        <v>20.523722296305046</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="238" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="237"/>
-      <c r="E15" s="237" t="s">
+      <c r="C15" s="238"/>
+      <c r="E15" s="238" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="237"/>
+      <c r="F15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36794,14 +36765,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="238" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="237"/>
-      <c r="E21" s="237" t="s">
+      <c r="C21" s="238"/>
+      <c r="E21" s="238" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="237"/>
+      <c r="F21" s="238"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36870,14 +36841,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="237" t="s">
+      <c r="B29" s="238" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="237"/>
-      <c r="E29" s="237" t="s">
+      <c r="C29" s="238"/>
+      <c r="E29" s="238" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="237"/>
+      <c r="F29" s="238"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36953,14 +36924,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="238" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="237"/>
-      <c r="E37" s="237" t="s">
+      <c r="C37" s="238"/>
+      <c r="E37" s="238" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="237"/>
+      <c r="F37" s="238"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36968,7 +36939,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>4.0828637392986589E-2</v>
+        <v>4.0811989503640463E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -36984,7 +36955,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>2.0138940781869057E-2</v>
+        <v>2.013072912262465E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -37000,7 +36971,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.8990667462718801E-4</v>
+        <v>4.8970691503123038E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -37016,7 +36987,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>9.0499405468027409E-4</v>
+        <v>9.0462504307853493E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37025,18 +36996,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.3623306224197708E-3</v>
+        <v>1.3617751316930887E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="237" t="s">
+      <c r="B45" s="238" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="237"/>
-      <c r="E45" s="237" t="s">
+      <c r="C45" s="238"/>
+      <c r="E45" s="238" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="237"/>
+      <c r="F45" s="238"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37069,18 +37040,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>1.9685637164462363E-2</v>
+        <v>1.9677610339906171E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="238" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="237"/>
-      <c r="E51" s="237" t="s">
+      <c r="C51" s="238"/>
+      <c r="E51" s="238" t="s">
         <v>303</v>
       </c>
-      <c r="F51" s="237"/>
+      <c r="F51" s="238"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37248,7 +37219,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>1081.8387</v>
+        <v>1082.28</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37277,7 +37248,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1239787.1502</v>
+        <v>1240292.8799999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37306,7 +37277,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1215381.1502</v>
+        <v>1215886.8799999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37335,7 +37306,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>24.492612633008829</v>
+        <v>24.502603577088522</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37364,7 +37335,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>13.649713974123225</v>
+        <v>13.655281919489553</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37393,7 +37364,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>12.1261654848894</v>
+        <v>12.131111949485723</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37422,7 +37393,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>13.463246895008529</v>
+        <v>13.468849059529875</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37451,7 +37422,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>20.515185763718922</v>
+        <v>20.523722296305046</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38224,7 +38195,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>4.0828637392986589E-2</v>
+        <v>4.0811989503640463E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38253,7 +38224,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>2.0138940781869057E-2</v>
+        <v>2.013072912262465E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38282,7 +38253,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.8990667462718801E-4</v>
+        <v>4.8970691503123038E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38311,7 +38282,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>9.0499405468027409E-4</v>
+        <v>9.0462504307853493E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38340,7 +38311,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.3623306224197708E-3</v>
+        <v>1.3617751316930887E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38576,7 +38547,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>1.9685637164462363E-2</v>
+        <v>1.9677610339906171E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39182,14 +39153,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="242" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="243"/>
+      <c r="F3" s="244" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="243"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39256,19 +39227,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="245">
         <f>Statement!AA89</f>
         <v>0.73746856663872595</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="246"/>
+      <c r="F7" s="245">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.4571551446081066</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="246"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -39295,19 +39266,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="245">
         <f>Statement!AA90</f>
         <v>4.8321048321048318E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="246"/>
+      <c r="F9" s="245">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.10478163300535129</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="246"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -39334,19 +39305,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="245">
         <f>Statement!AA91</f>
         <v>0.97442973810194311</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="246"/>
+      <c r="F11" s="245">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.9931584948688705</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="246"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -39373,19 +39344,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="245">
         <f>Statement!AA95</f>
         <v>7.2839506172839505E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="246"/>
+      <c r="F13" s="245">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.29798356982823004</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="246"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -39412,19 +39383,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="245">
         <f>Statement!AA96</f>
         <v>1.0649519677719244</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="246"/>
+      <c r="F15" s="245">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>14.360995850622407</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="246"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -39451,19 +39422,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="245">
         <f>Statement!AA98</f>
         <v>1.0488211824446863</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="246"/>
+      <c r="F17" s="245">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>13.983023872679045</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="246"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -39490,22 +39461,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="245">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6269702276707531E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="246"/>
+      <c r="F19" s="245">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="246"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -39532,22 +39503,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="245">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.0439105219552611</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="246"/>
+      <c r="F21" s="245">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>13.684523809523812</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="246"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39596,22 +39567,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="245">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.66922421142369992</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="246"/>
+      <c r="F25" s="245">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>3.4304907368123319</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="246"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39639,22 +39610,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="245">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.98979387632579552</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="246"/>
+      <c r="F27" s="245">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.613921113689095</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="246"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39682,22 +39653,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="245">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.94736842105263153</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="246"/>
+      <c r="F29" s="245">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.4666666666666666</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="246"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -39725,22 +39696,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="244">
+      <c r="C32" s="245">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.77687443541102075</v>
       </c>
-      <c r="D32" s="245"/>
-      <c r="F32" s="244">
+      <c r="D32" s="246"/>
+      <c r="F32" s="245">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>3.066450088600118</v>
       </c>
-      <c r="G32" s="245"/>
+      <c r="G32" s="246"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -39768,22 +39739,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="244">
+      <c r="C34" s="245">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.0263759451380341</v>
       </c>
-      <c r="D34" s="245"/>
-      <c r="F34" s="244">
+      <c r="D34" s="246"/>
+      <c r="F34" s="245">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>6.5320261437908496</v>
       </c>
-      <c r="G34" s="245"/>
+      <c r="G34" s="246"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -39811,22 +39782,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="244">
+      <c r="C36" s="245">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.49409933860718452</v>
       </c>
-      <c r="D36" s="245"/>
-      <c r="F36" s="244">
+      <c r="D36" s="246"/>
+      <c r="F36" s="245">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.5394777265745008</v>
       </c>
-      <c r="G36" s="245"/>
+      <c r="G36" s="246"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -39854,49 +39825,25 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="244">
+      <c r="C38" s="245">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.71122599704579026</v>
       </c>
-      <c r="D38" s="245"/>
-      <c r="F38" s="244">
+      <c r="D38" s="246"/>
+      <c r="F38" s="245">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.1118012422360248</v>
       </c>
-      <c r="G38" s="245"/>
+      <c r="G38" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -39905,6 +39852,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7497E187-33D6-7647-BE24-3DD92919E1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0948D7-B5FC-CE4D-8387-6A4FE28503B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="432">
   <si>
     <t>Ticker</t>
   </si>
@@ -1433,6 +1433,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>EV/Sales price</t>
   </si>
 </sst>
 </file>
@@ -15138,11 +15153,11 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>154.65</v>
-    <v>2.2311999999999999</v>
+    <v>2.2349999999999999</v>
     <v>1.75</v>
     <v>1.6200000000000001E-3</v>
-    <v>-0.44</v>
-    <v>-4.0649999999999996E-4</v>
+    <v>2.95</v>
+    <v>2.7260000000000001E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15153,21 +15168,21 @@
     <v>1108.72</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.840277360934</v>
+    <v>46290.999997175779</v>
     <v>0</v>
     <v>1073</v>
     <v>1222319456040</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>1095</v>
-    <v>24.5014</v>
+    <v>1095.83</v>
+    <v>24.4618</v>
     <v>1080.53</v>
     <v>1082.28</v>
-    <v>1081.8399999999999</v>
+    <v>1085.23</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>19500891</v>
+    <v>20947931</v>
     <v>24917533</v>
     <v>1984</v>
   </rv>
@@ -15190,19 +15205,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15424,9 +15439,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16031,7 +16046,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>525.53677107452643</v>
+        <v>524.08227389549859</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16055,7 +16070,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>715.01621993125616</v>
+        <v>713.99375770269091</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16079,7 +16094,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>226.52928279541413</v>
+        <v>226.14525071246968</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -16088,7 +16103,7 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>1081.8399999999999</v>
+        <v>1085.23</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
@@ -16103,7 +16118,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>981.95936167423486</v>
+        <v>980.4862298516731</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16122,12 +16137,12 @@
         <v>13.655281919489553</v>
       </c>
       <c r="H7" s="184" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="212">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>612.26040886885789</v>
+        <f ca="1">'AVG target price'!C10</f>
+        <v>573.80147882378026</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16136,7 +16151,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.44</v>
+        <v>2.95</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
@@ -16146,12 +16161,12 @@
         <v>2.013072912262465E-2</v>
       </c>
       <c r="H8" s="184" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="213">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>-0.43428649806994685</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.46982159993367678</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16176,7 +16191,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.0649999999999996E-4</v>
+        <v>2.7260000000000001E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
@@ -16190,7 +16205,7 @@
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>3.9582377237264805</v>
+        <v>3.945594902585468</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16231,7 +16246,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2311999999999999</v>
+        <v>2.2349999999999999</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16373,7 +16388,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16388,7 +16403,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22604,7 +22619,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22613,7 +22628,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.2311999999999999</v>
+        <v>2.2349999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22683,7 +22698,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15202399999999999</v>
+        <v>0.15241499999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22692,7 +22707,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15151089059957293</v>
+        <v>0.15190009503353602</v>
       </c>
     </row>
   </sheetData>
@@ -22943,7 +22958,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>637145.31004371878</v>
+        <v>635397.74405590747</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22997,23 +23012,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37667.396273702871</v>
+        <v>37654.669199793614</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>53308.444692766207</v>
+        <v>53272.427024254313</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>66253.852672211899</v>
+        <v>66186.717731506869</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>61835.655774847692</v>
+        <v>61752.125903632463</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>44092.703953257231</v>
+        <v>44018.263977541508</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23032,7 +23047,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>314701.08628462133</v>
+        <v>313308.08204751258</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23055,7 +23070,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151089059957293</v>
+        <v>0.15190009503353602</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23070,7 +23085,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>263158.05336678587</v>
+        <v>262884.20383672876</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23079,7 +23094,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>314701.08628462133</v>
+        <v>313308.08204751258</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23088,7 +23103,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>577859.13965140725</v>
+        <v>576192.28588424134</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23115,7 +23130,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>602265.13965140725</v>
+        <v>600598.28588424134</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23133,7 +23148,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>525.53677107452643</v>
+        <v>524.08227389549859</v>
       </c>
     </row>
   </sheetData>
@@ -23154,7 +23169,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -23402,23 +23417,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>37667.396273702871</v>
+        <v>37654.669199793614</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>53308.444692766207</v>
+        <v>53272.427024254313</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>66253.852672211899</v>
+        <v>66186.717731506869</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>61835.655774847692</v>
+        <v>61752.125903632463</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>44092.703953257231</v>
+        <v>44018.263977541508</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24146,291 +24161,427 @@
       <c r="N35" s="91"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C36" s="151">
+        <f>C33/C6</f>
+        <v>3.300708175419599</v>
+      </c>
+      <c r="D36" s="151">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>1.9581838871187986</v>
+      </c>
+      <c r="E36" s="151">
+        <f t="shared" si="14"/>
+        <v>4.9751846846846854</v>
+      </c>
+      <c r="F36" s="151">
+        <f t="shared" si="14"/>
+        <v>4.4240476285293298</v>
+      </c>
+      <c r="G36" s="152">
+        <f t="shared" si="14"/>
+        <v>3.7426026004601636</v>
+      </c>
+      <c r="H36" s="141"/>
+      <c r="I36" s="141"/>
+      <c r="J36" s="141"/>
+      <c r="K36" s="141"/>
+      <c r="L36" s="141"/>
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="238" t="s">
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="238" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="238"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="238"/>
+      <c r="N39" s="91"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>97170.438463650018</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C40" s="139">
+      <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151089059957293</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+        <v>0.15190009503353602</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C42" s="105">
         <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>1166045.2615638003</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>1166045.2615638003</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5</f>
-        <v>575937.23862769082</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="24">
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>574964.90646809654</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="C44" s="110">
-        <f ca="1">SUM(H9:K9)+C43</f>
-        <v>795002.58804121951</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="110">
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>793830.84632728377</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C45" s="88">
+      <c r="C46" s="88">
         <f>Statement!AC107</f>
         <v>30128</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C46" s="88">
+      <c r="C47" s="88">
         <f>Statement!AC108</f>
         <v>5722</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C47" s="110">
-        <f ca="1">C44+C45-C46</f>
-        <v>819408.58804121951</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="110">
+        <f ca="1">C45+C46-C47</f>
+        <v>818236.84632728377</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C49" s="88">
         <f>Statement!AC78</f>
         <v>1146</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="236" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="236" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="237">
-        <f ca="1">C47/C48</f>
-        <v>715.01621993125616</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="C50" s="237">
+        <f ca="1">C48/C49</f>
+        <v>713.99375770269091</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="238"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="238"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>123190.42843500002</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C53" s="139">
+      <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15202399999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+        <v>0.15241499999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="C54" s="105">
+      <c r="C55" s="105">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>1072.02514716</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>459.65499507676691</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="236" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="236" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="237">
-        <f ca="1">C56/(1+C53)^5</f>
-        <v>226.52928279541413</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="238" t="s">
+      <c r="C58" s="237">
+        <f ca="1">C57/(1+C54)^5</f>
+        <v>226.14525071246968</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="238" t="s">
         <v>322</v>
       </c>
-      <c r="C59" s="238"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="238"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>89270.297292700649</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="139">
+      <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151089059957293</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+        <v>0.15190009503353602</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>347</v>
       </c>
-      <c r="C62" s="105">
+      <c r="C63" s="105">
         <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>1785405.9458540129</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>1785405.9458540129</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5</f>
-        <v>881854.07906514453</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="24">
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>880365.27955083014</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="C65" s="110">
-        <f ca="1">SUM(H9:K9)+C64</f>
-        <v>1100919.4284786731</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="110">
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>1099231.2194100174</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C66" s="88">
+      <c r="C67" s="88">
         <f>Statement!AC107</f>
         <v>30128</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C67" s="88">
+      <c r="C68" s="88">
         <f>Statement!AC108</f>
         <v>5722</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C68" s="110">
-        <f ca="1">C65+C66-C67</f>
-        <v>1125325.4284786731</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="110">
+        <f ca="1">C66+C67-C68</f>
+        <v>1123637.2194100174</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="88">
+      <c r="C70" s="88">
         <f>Statement!AC78</f>
         <v>1146</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="236" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="236" t="s">
         <v>209</v>
       </c>
-      <c r="C70" s="237">
-        <f ca="1">C68/C69</f>
-        <v>981.95936167423486</v>
+      <c r="C71" s="237">
+        <f ca="1">C69/C70</f>
+        <v>980.4862298516731</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="238" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="238"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>123190.42843500002</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" s="139">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.15190009503353602</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>430</v>
+      </c>
+      <c r="C76" s="105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>492761.71374000009</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C78" s="24">
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>242975.72486304055</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="C79" s="110">
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>461841.66472222784</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C80" s="88">
+        <f>Statement!AC107</f>
+        <v>30128</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C81" s="88">
+        <f>Statement!AC108</f>
+        <v>5722</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C82" s="110">
+        <f ca="1">C79+C80-C81</f>
+        <v>486247.66472222784</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" s="88">
+        <f>Statement!AC78</f>
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="236" t="s">
+        <v>209</v>
+      </c>
+      <c r="C84" s="237">
+        <f ca="1">C82/C83</f>
+        <v>424.29988195656881</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+  <mergeCells count="11">
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24441,7 +24592,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -24480,7 +24631,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>525.53677107452643</v>
+        <v>524.08227389549859</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24488,8 +24639,8 @@
         <v>216</v>
       </c>
       <c r="C6" s="137">
-        <f ca="1">Multiples!C49</f>
-        <v>715.01621993125616</v>
+        <f ca="1">Multiples!C50</f>
+        <v>713.99375770269091</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24497,8 +24648,8 @@
         <v>217</v>
       </c>
       <c r="C7" s="137">
-        <f ca="1">Multiples!C57</f>
-        <v>226.52928279541413</v>
+        <f ca="1">Multiples!C58</f>
+        <v>226.14525071246968</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24506,35 +24657,44 @@
         <v>323</v>
       </c>
       <c r="C8" s="137">
-        <f ca="1">Multiples!C70</f>
-        <v>981.95936167423486</v>
+        <f ca="1">Multiples!C71</f>
+        <v>980.4862298516731</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="236" t="s">
+      <c r="B9" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="137">
+        <f ca="1">Multiples!C84</f>
+        <v>424.29988195656881</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="236" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="237">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>612.26040886885789</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="237">
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>573.80147882378026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="137">
+      <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
         <v>1082.28</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="156">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>-0.43428649806994685</v>
+      <c r="C12" s="156">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>-0.46982159993367678</v>
       </c>
     </row>
   </sheetData>
@@ -25004,7 +25164,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15202399999999999</v>
+        <v>0.15241499999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25021,7 +25181,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>3.9582377237264805</v>
+        <v>3.945594902585468</v>
       </c>
     </row>
   </sheetData>
@@ -25258,7 +25418,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1981039.4389241843</v>
+        <v>1975605.8320382775</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25312,23 +25472,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>2214.5397139695633</v>
+        <v>2213.7914644646103</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6211.8068830397751</v>
+        <v>6207.6098969438071</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>17424.182781086336</v>
+        <v>17406.526879872123</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48875.013551634518</v>
+        <v>48808.991391176227</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>137094.92030038996</v>
+        <v>136863.46834523819</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25347,7 +25507,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>978482.07241663511</v>
+        <v>974150.8840851828</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25372,7 +25532,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1075.915443442653</v>
+        <v>1071.7956351309811</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25411,7 +25571,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15151089059957293</v>
+        <v>0.15190009503353602</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25472,7 +25632,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>211820.46323012013</v>
+        <v>211500.38797769495</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25481,7 +25641,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>978482.07241663511</v>
+        <v>974150.8840851828</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25490,7 +25650,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1190302.5356467552</v>
+        <v>1185651.2720628777</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25517,7 +25677,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1214708.5356467552</v>
+        <v>1210057.2720628777</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25535,12 +25695,11 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1075.915443442653</v>
+        <v>1071.7956351309811</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
@@ -25550,6 +25709,7 @@
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0948D7-B5FC-CE4D-8387-6A4FE28503B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88243BD-E59C-BE4E-A54A-681A0CFA14DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="433">
   <si>
     <t>Ticker</t>
   </si>
@@ -1448,6 +1448,9 @@
   </si>
   <si>
     <t>EV/Sales price</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2374,7 +2377,28 @@
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2386,6 +2410,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2395,38 +2425,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15152,12 +15155,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>154.65</v>
-    <v>2.2349999999999999</v>
-    <v>1.75</v>
-    <v>1.6200000000000001E-3</v>
-    <v>2.95</v>
-    <v>2.7260000000000001E-3</v>
+    <v>159.97059999999999</v>
+    <v>2.2313999999999998</v>
+    <v>11.1</v>
+    <v>1.0532E-2</v>
+    <v>5.6689999999999996</v>
+    <v>5.3229999999999996E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15165,25 +15168,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>1108.72</v>
+    <v>1082.6599000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.999997175779</v>
+    <v>46294.959048171091</v>
     <v>0</v>
-    <v>1073</v>
-    <v>1222319456040</v>
+    <v>1057.7</v>
+    <v>1202893896440</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>1095.83</v>
-    <v>24.4618</v>
-    <v>1080.53</v>
-    <v>1082.28</v>
-    <v>1085.23</v>
+    <v>1076.69</v>
+    <v>23.860800000000001</v>
+    <v>1053.98</v>
+    <v>1065.08</v>
+    <v>1070.749</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>20947931</v>
-    <v>24917533</v>
+    <v>19651134</v>
+    <v>24763109</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15205,19 +15208,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>52.74</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.56000000000000005</v>
+    <v>1.0802000000000001E-2</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.74</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>52.05</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
+    <v>52.09</v>
     <v>51.84</v>
+    <v>52.4</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15439,9 +15442,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16012,18 +16015,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="239" t="s">
+      <c r="B2" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="240"/>
-      <c r="E2" s="239" t="s">
+      <c r="C2" s="247"/>
+      <c r="E2" s="246" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="H2" s="239" t="s">
+      <c r="F2" s="247"/>
+      <c r="H2" s="246" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="240"/>
+      <c r="I2" s="247"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -16038,7 +16041,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1240292.8799999999</v>
+        <v>1220581.68</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16046,7 +16049,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>524.08227389549859</v>
+        <v>522.64069236593184</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16062,7 +16065,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>1215886.8799999999</v>
+        <v>1196175.68</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16070,7 +16073,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>713.99375770269091</v>
+        <v>712.97676003818322</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16079,7 +16082,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16094,7 +16097,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>226.14525071246968</v>
+        <v>225.75514545003378</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -16103,14 +16106,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>1085.23</v>
+        <v>1070.749</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>24.502603577088522</v>
+        <v>24.113199003848763</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16118,7 +16121,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>980.4862298516731</v>
+        <v>979.02101983341845</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16127,22 +16130,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.75</v>
+        <v>11.1</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>13.655281919489553</v>
-      </c>
-      <c r="H7" s="184" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="212">
-        <f ca="1">'AVG target price'!C10</f>
-        <v>573.80147882378026</v>
+        <v>13.438267053636705</v>
+      </c>
+      <c r="H7" s="185" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales price</v>
+      </c>
+      <c r="I7" s="211">
+        <f ca="1">'AVG target price'!C9</f>
+        <v>423.77011897027614</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16151,22 +16154,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>2.95</v>
+        <v>5.6689999999999996</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>2.013072912262465E-2</v>
+        <v>2.0455820703453455E-2</v>
       </c>
       <c r="H8" s="184" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="213">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>-0.46982159993367678</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="212">
+        <f ca="1">'AVG target price'!C10</f>
+        <v>572.83274733156873</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16175,14 +16178,22 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.6200000000000001E-3</v>
+        <v>1.0532E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.0811989503640463E-2</v>
+        <v>4.14710632065197E-2</v>
+      </c>
+      <c r="H9" s="184" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="213">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.46216927617496456</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16191,21 +16202,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.7260000000000001E-3</v>
+        <v>5.3229999999999996E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>9.0462504307853493E-4</v>
-      </c>
-      <c r="H10" s="184" t="s">
-        <v>367</v>
-      </c>
-      <c r="I10" s="212">
-        <f ca="1">DDM!C26</f>
-        <v>3.945594902585468</v>
+        <v>9.1923385250219393E-4</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16221,7 +16225,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>4.8970691503123038E-4</v>
+        <v>4.976152026138882E-4</v>
+      </c>
+      <c r="H11" s="184" t="s">
+        <v>367</v>
+      </c>
+      <c r="I11" s="212">
+        <f ca="1">DDM!C26</f>
+        <v>3.9328084160471621</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16230,7 +16241,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>154.65</v>
+        <v>159.97059999999999</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>102</v>
@@ -16246,7 +16257,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2349999999999999</v>
+        <v>2.2313999999999998</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16255,6 +16266,13 @@
         <f>Statement!AC125</f>
         <v>0.50106230888368219</v>
       </c>
+      <c r="H13" s="184" t="s">
+        <v>432</v>
+      </c>
+      <c r="I13" s="213">
+        <f>'Reverse DCF'!C17</f>
+        <v>2.2400000000000002</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="186" t="s">
@@ -16262,7 +16280,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>24917533</v>
+        <v>24763109</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16278,7 +16296,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>1.9677610339906171E-2</v>
+        <v>1.999538449569389E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16291,10 +16309,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="248" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="241"/>
+      <c r="C17" s="248"/>
       <c r="E17" s="184" t="s">
         <v>296</v>
       </c>
@@ -16317,7 +16335,6 @@
         <f>Statement!AC144</f>
         <v>22.941609834516981</v>
       </c>
-      <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="184" t="s">
@@ -16333,6 +16350,7 @@
         <f>Statement!AC146</f>
         <v>-0.24230570668361065</v>
       </c>
+      <c r="I19" s="50"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="184" t="s">
@@ -16356,7 +16374,6 @@
       <c r="C21" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="184" t="s">
@@ -16365,16 +16382,17 @@
       <c r="C22" s="69" t="s">
         <v>92</v>
       </c>
+      <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="241" t="s">
+      <c r="B25" s="248" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="241"/>
-      <c r="E25" s="239" t="s">
+      <c r="C25" s="248"/>
+      <c r="E25" s="246" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="240"/>
+      <c r="F25" s="247"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -16388,7 +16406,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16403,7 +16421,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2399999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16423,15 +16441,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="238" t="s">
+      <c r="B33" s="136" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="238"/>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
+      <c r="C33" s="136"/>
+      <c r="D33" s="136"/>
+      <c r="E33" s="136"/>
+      <c r="F33" s="136"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="136"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16476,24 +16494,24 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="238"/>
-      <c r="C43" s="238"/>
-      <c r="D43" s="238"/>
-      <c r="E43" s="238"/>
-      <c r="F43" s="238"/>
-      <c r="G43" s="238"/>
-      <c r="H43" s="238"/>
+      <c r="B43" s="136"/>
+      <c r="C43" s="136"/>
+      <c r="D43" s="136"/>
+      <c r="E43" s="136"/>
+      <c r="F43" s="136"/>
+      <c r="G43" s="136"/>
+      <c r="H43" s="136"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="238" t="s">
+      <c r="B46" s="136" t="s">
         <v>338</v>
       </c>
-      <c r="C46" s="238"/>
-      <c r="D46" s="238"/>
-      <c r="E46" s="238"/>
-      <c r="F46" s="238"/>
-      <c r="G46" s="238"/>
-      <c r="H46" s="238"/>
+      <c r="C46" s="136"/>
+      <c r="D46" s="136"/>
+      <c r="E46" s="136"/>
+      <c r="F46" s="136"/>
+      <c r="G46" s="136"/>
+      <c r="H46" s="136"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="41" t="s">
@@ -16612,24 +16630,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="238"/>
-      <c r="C66" s="238"/>
-      <c r="D66" s="238"/>
-      <c r="E66" s="238"/>
-      <c r="F66" s="238"/>
-      <c r="G66" s="238"/>
-      <c r="H66" s="238"/>
+      <c r="B66" s="136"/>
+      <c r="C66" s="136"/>
+      <c r="D66" s="136"/>
+      <c r="E66" s="136"/>
+      <c r="F66" s="136"/>
+      <c r="G66" s="136"/>
+      <c r="H66" s="136"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="238" t="s">
+      <c r="B69" s="136" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="238"/>
-      <c r="D69" s="238"/>
-      <c r="E69" s="238"/>
-      <c r="F69" s="238"/>
-      <c r="G69" s="238"/>
-      <c r="H69" s="238"/>
+      <c r="C69" s="136"/>
+      <c r="D69" s="136"/>
+      <c r="E69" s="136"/>
+      <c r="F69" s="136"/>
+      <c r="G69" s="136"/>
+      <c r="H69" s="136"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -16644,28 +16662,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="238"/>
-      <c r="C76" s="238"/>
-      <c r="D76" s="238"/>
-      <c r="E76" s="238"/>
-      <c r="F76" s="238"/>
-      <c r="G76" s="238"/>
-      <c r="H76" s="238"/>
+      <c r="B76" s="136"/>
+      <c r="C76" s="136"/>
+      <c r="D76" s="136"/>
+      <c r="E76" s="136"/>
+      <c r="F76" s="136"/>
+      <c r="G76" s="136"/>
+      <c r="H76" s="136"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16735,36 +16747,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251" t="s">
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="238" t="s">
+      <c r="S2" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238" t="s">
+      <c r="T2" s="241"/>
+      <c r="U2" s="241"/>
+      <c r="V2" s="241"/>
+      <c r="W2" s="241"/>
+      <c r="X2" s="241"/>
+      <c r="Y2" s="241"/>
+      <c r="Z2" s="241"/>
+      <c r="AA2" s="241" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="AB2" s="241"/>
+      <c r="AC2" s="241"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -16775,32 +16787,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="247" t="s">
+      <c r="C4" s="245" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
-      <c r="H4" s="247"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="247"/>
-      <c r="K4" s="247"/>
-      <c r="L4" s="247"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="248" t="s">
+      <c r="S4" s="254" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="249"/>
-      <c r="U4" s="249"/>
-      <c r="V4" s="249"/>
-      <c r="W4" s="249"/>
-      <c r="X4" s="249"/>
-      <c r="Y4" s="249"/>
-      <c r="Z4" s="249"/>
-      <c r="AA4" s="249"/>
-      <c r="AB4" s="249"/>
-      <c r="AC4" s="249"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
+      <c r="AA4" s="255"/>
+      <c r="AB4" s="255"/>
+      <c r="AC4" s="255"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17393,33 +17405,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="247" t="s">
+      <c r="C12" s="245" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="247"/>
-      <c r="E12" s="247"/>
-      <c r="F12" s="247"/>
-      <c r="G12" s="247"/>
-      <c r="H12" s="247"/>
-      <c r="I12" s="247"/>
-      <c r="J12" s="247"/>
-      <c r="K12" s="247"/>
-      <c r="L12" s="247"/>
+      <c r="D12" s="245"/>
+      <c r="E12" s="245"/>
+      <c r="F12" s="245"/>
+      <c r="G12" s="245"/>
+      <c r="H12" s="245"/>
+      <c r="I12" s="245"/>
+      <c r="J12" s="245"/>
+      <c r="K12" s="245"/>
+      <c r="L12" s="245"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="248" t="s">
+      <c r="S12" s="254" t="s">
         <v>122</v>
       </c>
-      <c r="T12" s="249"/>
-      <c r="U12" s="249"/>
-      <c r="V12" s="249"/>
-      <c r="W12" s="249"/>
-      <c r="X12" s="249"/>
-      <c r="Y12" s="249"/>
-      <c r="Z12" s="249"/>
-      <c r="AA12" s="249"/>
-      <c r="AB12" s="249"/>
-      <c r="AC12" s="249"/>
+      <c r="T12" s="255"/>
+      <c r="U12" s="255"/>
+      <c r="V12" s="255"/>
+      <c r="W12" s="255"/>
+      <c r="X12" s="255"/>
+      <c r="Y12" s="255"/>
+      <c r="Z12" s="255"/>
+      <c r="AA12" s="255"/>
+      <c r="AB12" s="255"/>
+      <c r="AC12" s="255"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -17964,35 +17976,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251" t="s">
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="P2" s="238" t="s">
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="P2" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238" t="s">
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="241"/>
+      <c r="U2" s="241"/>
+      <c r="V2" s="241"/>
+      <c r="W2" s="241"/>
+      <c r="X2" s="241" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
+      <c r="Y2" s="241"/>
+      <c r="Z2" s="241"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -18001,31 +18013,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="247" t="s">
+      <c r="C4" s="245" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
-      <c r="H4" s="247"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="247"/>
-      <c r="K4" s="247"/>
-      <c r="L4" s="247"/>
-      <c r="P4" s="249" t="s">
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="P4" s="255" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="249"/>
-      <c r="R4" s="249"/>
-      <c r="S4" s="249"/>
-      <c r="T4" s="249"/>
-      <c r="U4" s="249"/>
-      <c r="V4" s="249"/>
-      <c r="W4" s="249"/>
-      <c r="X4" s="249"/>
-      <c r="Y4" s="249"/>
-      <c r="Z4" s="249"/>
+      <c r="Q4" s="255"/>
+      <c r="R4" s="255"/>
+      <c r="S4" s="255"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -18220,32 +18232,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="247" t="s">
+      <c r="C9" s="245" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="E9" s="247"/>
-      <c r="F9" s="247"/>
-      <c r="G9" s="247"/>
-      <c r="H9" s="247"/>
-      <c r="I9" s="247"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="247"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="245"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="249" t="s">
+      <c r="P9" s="255" t="s">
         <v>126</v>
       </c>
-      <c r="Q9" s="249"/>
-      <c r="R9" s="249"/>
-      <c r="S9" s="249"/>
-      <c r="T9" s="249"/>
-      <c r="U9" s="249"/>
-      <c r="V9" s="249"/>
-      <c r="W9" s="249"/>
-      <c r="X9" s="249"/>
-      <c r="Y9" s="249"/>
-      <c r="Z9" s="249"/>
+      <c r="Q9" s="255"/>
+      <c r="R9" s="255"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="255"/>
+      <c r="U9" s="255"/>
+      <c r="V9" s="255"/>
+      <c r="W9" s="255"/>
+      <c r="X9" s="255"/>
+      <c r="Y9" s="255"/>
+      <c r="Z9" s="255"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -19183,31 +19195,31 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C22" s="247" t="s">
+      <c r="C22" s="245" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="247"/>
-      <c r="E22" s="247"/>
-      <c r="F22" s="247"/>
-      <c r="G22" s="247"/>
-      <c r="H22" s="247"/>
-      <c r="I22" s="247"/>
-      <c r="J22" s="247"/>
-      <c r="K22" s="247"/>
-      <c r="L22" s="247"/>
-      <c r="P22" s="249" t="s">
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
+      <c r="G22" s="245"/>
+      <c r="H22" s="245"/>
+      <c r="I22" s="245"/>
+      <c r="J22" s="245"/>
+      <c r="K22" s="245"/>
+      <c r="L22" s="245"/>
+      <c r="P22" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="Q22" s="249"/>
-      <c r="R22" s="249"/>
-      <c r="S22" s="249"/>
-      <c r="T22" s="249"/>
-      <c r="U22" s="249"/>
-      <c r="V22" s="249"/>
-      <c r="W22" s="249"/>
-      <c r="X22" s="249"/>
-      <c r="Y22" s="249"/>
-      <c r="Z22" s="249"/>
+      <c r="Q22" s="255"/>
+      <c r="R22" s="255"/>
+      <c r="S22" s="255"/>
+      <c r="T22" s="255"/>
+      <c r="U22" s="255"/>
+      <c r="V22" s="255"/>
+      <c r="W22" s="255"/>
+      <c r="X22" s="255"/>
+      <c r="Y22" s="255"/>
+      <c r="Z22" s="255"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B23" s="16" t="s">
@@ -20022,60 +20034,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="250"/>
-      <c r="H3" s="251" t="s">
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="252"/>
-      <c r="Q3" s="252"/>
-      <c r="R3" s="252"/>
-      <c r="S3" s="252"/>
-      <c r="T3" s="252"/>
-      <c r="U3" s="252"/>
-      <c r="V3" s="252"/>
-      <c r="W3" s="252"/>
-      <c r="X3" s="252"/>
-      <c r="Y3" s="252"/>
-      <c r="Z3" s="252"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="247" t="s">
+      <c r="C5" s="245" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="247"/>
-      <c r="E5" s="247"/>
-      <c r="F5" s="247"/>
-      <c r="G5" s="247"/>
-      <c r="H5" s="247"/>
-      <c r="I5" s="247"/>
-      <c r="J5" s="247"/>
-      <c r="K5" s="247"/>
-      <c r="L5" s="247"/>
-      <c r="P5" s="252"/>
-      <c r="Q5" s="252"/>
-      <c r="R5" s="252"/>
-      <c r="S5" s="252"/>
-      <c r="T5" s="252"/>
-      <c r="U5" s="252"/>
-      <c r="V5" s="252"/>
-      <c r="W5" s="252"/>
-      <c r="X5" s="252"/>
-      <c r="Y5" s="252"/>
-      <c r="Z5" s="252"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20261,30 +20273,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="247" t="s">
+      <c r="C11" s="245" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="E11" s="247"/>
-      <c r="F11" s="247"/>
-      <c r="G11" s="247"/>
-      <c r="H11" s="247"/>
-      <c r="I11" s="247"/>
-      <c r="J11" s="247"/>
-      <c r="K11" s="247"/>
-      <c r="L11" s="247"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="252"/>
-      <c r="Q11" s="252"/>
-      <c r="R11" s="252"/>
-      <c r="S11" s="252"/>
-      <c r="T11" s="252"/>
-      <c r="U11" s="252"/>
-      <c r="V11" s="252"/>
-      <c r="W11" s="252"/>
-      <c r="X11" s="252"/>
-      <c r="Y11" s="252"/>
-      <c r="Z11" s="252"/>
+      <c r="P11" s="244"/>
+      <c r="Q11" s="244"/>
+      <c r="R11" s="244"/>
+      <c r="S11" s="244"/>
+      <c r="T11" s="244"/>
+      <c r="U11" s="244"/>
+      <c r="V11" s="244"/>
+      <c r="W11" s="244"/>
+      <c r="X11" s="244"/>
+      <c r="Y11" s="244"/>
+      <c r="Z11" s="244"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20526,18 +20538,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="247" t="s">
+      <c r="C18" s="245" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="247"/>
-      <c r="E18" s="247"/>
-      <c r="F18" s="247"/>
-      <c r="G18" s="247"/>
-      <c r="H18" s="247"/>
-      <c r="I18" s="247"/>
-      <c r="J18" s="247"/>
-      <c r="K18" s="247"/>
-      <c r="L18" s="247"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20750,23 +20762,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="252"/>
-      <c r="C25" s="252"/>
+      <c r="B25" s="244"/>
+      <c r="C25" s="244"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="247" t="s">
+      <c r="C26" s="245" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="247"/>
-      <c r="E26" s="247"/>
-      <c r="F26" s="247"/>
-      <c r="G26" s="247"/>
-      <c r="H26" s="247"/>
-      <c r="I26" s="247"/>
-      <c r="J26" s="247"/>
-      <c r="K26" s="247"/>
-      <c r="L26" s="247"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20958,18 +20970,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="247" t="s">
+      <c r="C33" s="245" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="247"/>
-      <c r="E33" s="247"/>
-      <c r="F33" s="247"/>
-      <c r="G33" s="247"/>
-      <c r="H33" s="247"/>
-      <c r="I33" s="247"/>
-      <c r="J33" s="247"/>
-      <c r="K33" s="247"/>
-      <c r="L33" s="247"/>
+      <c r="D33" s="245"/>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
+      <c r="K33" s="245"/>
+      <c r="L33" s="245"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -21153,18 +21165,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="247" t="s">
+      <c r="C40" s="245" t="s">
         <v>150</v>
       </c>
-      <c r="D40" s="247"/>
-      <c r="E40" s="247"/>
-      <c r="F40" s="247"/>
-      <c r="G40" s="247"/>
-      <c r="H40" s="247"/>
-      <c r="I40" s="247"/>
-      <c r="J40" s="247"/>
-      <c r="K40" s="247"/>
-      <c r="L40" s="247"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21428,6 +21440,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21435,12 +21453,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21478,60 +21490,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251" t="s">
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252"/>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="S2" s="244"/>
+      <c r="T2" s="244"/>
+      <c r="U2" s="244"/>
+      <c r="V2" s="244"/>
+      <c r="W2" s="244"/>
+      <c r="X2" s="244"/>
+      <c r="Y2" s="244"/>
+      <c r="Z2" s="244"/>
+      <c r="AA2" s="244"/>
+      <c r="AB2" s="244"/>
+      <c r="AC2" s="244"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="247" t="s">
+      <c r="C4" s="245" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
-      <c r="H4" s="247"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="247"/>
-      <c r="K4" s="247"/>
-      <c r="L4" s="247"/>
-      <c r="S4" s="252"/>
-      <c r="T4" s="252"/>
-      <c r="U4" s="252"/>
-      <c r="V4" s="252"/>
-      <c r="W4" s="252"/>
-      <c r="X4" s="252"/>
-      <c r="Y4" s="252"/>
-      <c r="Z4" s="252"/>
-      <c r="AA4" s="252"/>
-      <c r="AB4" s="252"/>
-      <c r="AC4" s="252"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="S4" s="244"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
+      <c r="AA4" s="244"/>
+      <c r="AB4" s="244"/>
+      <c r="AC4" s="244"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21894,18 +21906,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="247" t="s">
+      <c r="C13" s="245" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="E13" s="247"/>
-      <c r="F13" s="247"/>
-      <c r="G13" s="247"/>
-      <c r="H13" s="247"/>
-      <c r="I13" s="247"/>
-      <c r="J13" s="247"/>
-      <c r="K13" s="247"/>
-      <c r="L13" s="247"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21998,18 +22010,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="247" t="s">
+      <c r="C18" s="245" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="247"/>
-      <c r="E18" s="247"/>
-      <c r="F18" s="247"/>
-      <c r="G18" s="247"/>
-      <c r="H18" s="247"/>
-      <c r="I18" s="247"/>
-      <c r="J18" s="247"/>
-      <c r="K18" s="247"/>
-      <c r="L18" s="247"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -22201,18 +22213,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="247" t="s">
+      <c r="C25" s="245" t="s">
         <v>262</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="E25" s="247"/>
-      <c r="F25" s="247"/>
-      <c r="G25" s="247"/>
-      <c r="H25" s="247"/>
-      <c r="I25" s="247"/>
-      <c r="J25" s="247"/>
-      <c r="K25" s="247"/>
-      <c r="L25" s="247"/>
+      <c r="D25" s="245"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
+      <c r="J25" s="245"/>
+      <c r="K25" s="245"/>
+      <c r="L25" s="245"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -22350,18 +22362,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="247" t="s">
+      <c r="C31" s="245" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="247"/>
-      <c r="E31" s="247"/>
-      <c r="F31" s="247"/>
-      <c r="G31" s="247"/>
-      <c r="H31" s="247"/>
-      <c r="I31" s="247"/>
-      <c r="J31" s="247"/>
-      <c r="K31" s="247"/>
-      <c r="L31" s="247"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22500,16 +22512,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22572,10 +22584,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="241" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="241"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22592,7 +22604,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22601,7 +22613,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1240292.8799999999</v>
+        <v>1220581.68</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22619,7 +22631,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2399999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22628,7 +22640,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.2349999999999999</v>
+        <v>2.2313999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22660,10 +22672,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="241" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="238"/>
+      <c r="C15" s="241"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22671,7 +22683,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.5922405035805037E-3</v>
+        <v>4.6660546594788008E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22680,7 +22692,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99540775949641946</v>
+        <v>0.99533394534052122</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22698,7 +22710,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15241499999999999</v>
+        <v>0.15281299999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22707,7 +22719,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15190009503353602</v>
+        <v>0.15228796153155144</v>
       </c>
     </row>
   </sheetData>
@@ -22752,60 +22764,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="250"/>
-      <c r="H3" s="251" t="s">
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="252"/>
-      <c r="Q3" s="252"/>
-      <c r="R3" s="252"/>
-      <c r="S3" s="252"/>
-      <c r="T3" s="252"/>
-      <c r="U3" s="252"/>
-      <c r="V3" s="252"/>
-      <c r="W3" s="252"/>
-      <c r="X3" s="252"/>
-      <c r="Y3" s="252"/>
-      <c r="Z3" s="252"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="247" t="s">
+      <c r="C5" s="245" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="247"/>
-      <c r="E5" s="247"/>
-      <c r="F5" s="247"/>
-      <c r="G5" s="247"/>
-      <c r="H5" s="247"/>
-      <c r="I5" s="247"/>
-      <c r="J5" s="247"/>
-      <c r="K5" s="247"/>
-      <c r="L5" s="247"/>
-      <c r="P5" s="252"/>
-      <c r="Q5" s="252"/>
-      <c r="R5" s="252"/>
-      <c r="S5" s="252"/>
-      <c r="T5" s="252"/>
-      <c r="U5" s="252"/>
-      <c r="V5" s="252"/>
-      <c r="W5" s="252"/>
-      <c r="X5" s="252"/>
-      <c r="Y5" s="252"/>
-      <c r="Z5" s="252"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22958,7 +22970,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>635397.74405590747</v>
+        <v>633665.69662771223</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23012,23 +23024,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37654.669199793614</v>
+        <v>37641.994429975624</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>53272.427024254313</v>
+        <v>53236.569473313211</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>66186.717731506869</v>
+        <v>66119.903781239293</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>61752.125903632463</v>
+        <v>61669.023446676387</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>44018.263977541508</v>
+        <v>43944.22987989465</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23047,14 +23059,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>313308.08204751258</v>
+        <v>311928.51244025875</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="241" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="238"/>
+      <c r="C13" s="241"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23070,14 +23082,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15190009503353602</v>
+        <v>0.15228796153155144</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="238" t="s">
+      <c r="B18" s="241" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="238"/>
+      <c r="C18" s="241"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23085,7 +23097,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>262884.20383672876</v>
+        <v>262611.72101109917</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23094,7 +23106,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>313308.08204751258</v>
+        <v>311928.51244025875</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23103,7 +23115,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>576192.28588424134</v>
+        <v>574540.23345135793</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23130,7 +23142,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>600598.28588424134</v>
+        <v>598946.23345135793</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23148,7 +23160,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>524.08227389549859</v>
+        <v>522.64069236593184</v>
       </c>
     </row>
   </sheetData>
@@ -23191,37 +23203,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251" t="s">
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="247" t="s">
+      <c r="C4" s="245" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
-      <c r="H4" s="247"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="247"/>
-      <c r="K4" s="247"/>
-      <c r="L4" s="247"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23417,23 +23429,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>37654.669199793614</v>
+        <v>37641.994429975624</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>53272.427024254313</v>
+        <v>53236.569473313211</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>66186.717731506869</v>
+        <v>66119.903781239293</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>61752.125903632463</v>
+        <v>61669.023446676387</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>44018.263977541508</v>
+        <v>43944.22987989465</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -23441,18 +23453,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="247" t="s">
+      <c r="C11" s="245" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="E11" s="247"/>
-      <c r="F11" s="247"/>
-      <c r="G11" s="247"/>
-      <c r="H11" s="247"/>
-      <c r="I11" s="247"/>
-      <c r="J11" s="247"/>
-      <c r="K11" s="247"/>
-      <c r="L11" s="247"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23646,18 +23658,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="247" t="s">
+      <c r="C17" s="245" t="s">
         <v>196</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="E17" s="247"/>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
-      <c r="J17" s="247"/>
-      <c r="K17" s="247"/>
-      <c r="L17" s="247"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
+      <c r="J17" s="245"/>
+      <c r="K17" s="245"/>
+      <c r="L17" s="245"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23791,18 +23803,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="247" t="s">
+      <c r="C22" s="245" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="247"/>
-      <c r="E22" s="247"/>
-      <c r="F22" s="247"/>
-      <c r="G22" s="247"/>
-      <c r="H22" s="247"/>
-      <c r="I22" s="247"/>
-      <c r="J22" s="247"/>
-      <c r="K22" s="247"/>
-      <c r="L22" s="247"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
+      <c r="G22" s="245"/>
+      <c r="H22" s="245"/>
+      <c r="I22" s="245"/>
+      <c r="J22" s="245"/>
+      <c r="K22" s="245"/>
+      <c r="L22" s="245"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23886,18 +23898,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="247" t="s">
+      <c r="C27" s="245" t="s">
         <v>200</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="E27" s="247"/>
-      <c r="F27" s="247"/>
-      <c r="G27" s="247"/>
-      <c r="H27" s="247"/>
-      <c r="I27" s="247"/>
-      <c r="J27" s="247"/>
-      <c r="K27" s="247"/>
-      <c r="L27" s="247"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -24198,10 +24210,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="238" t="s">
+      <c r="B39" s="241" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="238"/>
+      <c r="C39" s="241"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24219,7 +24231,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15190009503353602</v>
+        <v>0.15228796153155144</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24245,7 +24257,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>574964.90646809654</v>
+        <v>573997.87587255344</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24254,7 +24266,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>793830.84632728377</v>
+        <v>792665.36700375797</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24281,7 +24293,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>818236.84632728377</v>
+        <v>817071.36700375797</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24299,14 +24311,14 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>713.99375770269091</v>
+        <v>712.97676003818322</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="238" t="s">
+      <c r="B52" s="241" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="238"/>
+      <c r="C52" s="241"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -24323,7 +24335,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15241499999999999</v>
+        <v>0.15281299999999998</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24358,14 +24370,14 @@
       </c>
       <c r="C58" s="237">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>226.14525071246968</v>
+        <v>225.75514545003378</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="238" t="s">
+      <c r="B60" s="241" t="s">
         <v>322</v>
       </c>
-      <c r="C60" s="238"/>
+      <c r="C60" s="241"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -24382,7 +24394,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15190009503353602</v>
+        <v>0.15228796153155144</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24408,7 +24420,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>880365.27955083014</v>
+        <v>878884.59759789298</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24417,7 +24429,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1099231.2194100174</v>
+        <v>1097552.0887290975</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24444,7 +24456,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1123637.2194100174</v>
+        <v>1121958.0887290975</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24462,14 +24474,14 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>980.4862298516731</v>
+        <v>979.02101983341845</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="238" t="s">
+      <c r="B73" s="241" t="s">
         <v>428</v>
       </c>
-      <c r="C73" s="238"/>
+      <c r="C73" s="241"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -24486,7 +24498,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15190009503353602</v>
+        <v>0.15228796153155144</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24512,7 +24524,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>242975.72486304055</v>
+        <v>242567.06520873198</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24521,7 +24533,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>461841.66472222784</v>
+        <v>461234.55633993645</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24548,7 +24560,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>486247.66472222784</v>
+        <v>485640.55633993645</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24566,22 +24578,22 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>424.29988195656881</v>
+        <v>423.77011897027614</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24619,10 +24631,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="241" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="241"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24631,7 +24643,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>524.08227389549859</v>
+        <v>522.64069236593184</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24640,7 +24652,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>713.99375770269091</v>
+        <v>712.97676003818322</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24649,7 +24661,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>226.14525071246968</v>
+        <v>225.75514545003378</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24658,7 +24670,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>980.4862298516731</v>
+        <v>979.02101983341845</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24667,7 +24679,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>424.29988195656881</v>
+        <v>423.77011897027614</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24676,7 +24688,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>573.80147882378026</v>
+        <v>572.83274733156873</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24685,7 +24697,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24694,7 +24706,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.46982159993367678</v>
+        <v>-0.46216927617496456</v>
       </c>
     </row>
   </sheetData>
@@ -24750,37 +24762,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251" t="s">
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="247" t="s">
+      <c r="C4" s="245" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
-      <c r="H4" s="247"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="247"/>
-      <c r="K4" s="247"/>
-      <c r="L4" s="247"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24893,18 +24905,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="247" t="s">
+      <c r="C9" s="245" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="E9" s="247"/>
-      <c r="F9" s="247"/>
-      <c r="G9" s="247"/>
-      <c r="H9" s="247"/>
-      <c r="I9" s="247"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="247"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="245"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25025,18 +25037,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="247" t="s">
+      <c r="C14" s="245" t="s">
         <v>360</v>
       </c>
-      <c r="D14" s="247"/>
-      <c r="E14" s="247"/>
-      <c r="F14" s="247"/>
-      <c r="G14" s="247"/>
-      <c r="H14" s="247"/>
-      <c r="I14" s="247"/>
-      <c r="J14" s="247"/>
-      <c r="K14" s="247"/>
-      <c r="L14" s="247"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -25126,10 +25138,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="241" t="s">
         <v>362</v>
       </c>
-      <c r="C20" s="238"/>
+      <c r="C20" s="241"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -25164,7 +25176,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15241499999999999</v>
+        <v>0.15281299999999998</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25181,7 +25193,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>3.945594902585468</v>
+        <v>3.9328084160471621</v>
       </c>
     </row>
   </sheetData>
@@ -25230,60 +25242,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="250"/>
-      <c r="H3" s="251" t="s">
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="252"/>
-      <c r="Q3" s="252"/>
-      <c r="R3" s="252"/>
-      <c r="S3" s="252"/>
-      <c r="T3" s="252"/>
-      <c r="U3" s="252"/>
-      <c r="V3" s="252"/>
-      <c r="W3" s="252"/>
-      <c r="X3" s="252"/>
-      <c r="Y3" s="252"/>
-      <c r="Z3" s="252"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="247" t="s">
+      <c r="C5" s="245" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="247"/>
-      <c r="E5" s="247"/>
-      <c r="F5" s="247"/>
-      <c r="G5" s="247"/>
-      <c r="H5" s="247"/>
-      <c r="I5" s="247"/>
-      <c r="J5" s="247"/>
-      <c r="K5" s="247"/>
-      <c r="L5" s="247"/>
-      <c r="P5" s="252"/>
-      <c r="Q5" s="252"/>
-      <c r="R5" s="252"/>
-      <c r="S5" s="252"/>
-      <c r="T5" s="252"/>
-      <c r="U5" s="252"/>
-      <c r="V5" s="252"/>
-      <c r="W5" s="252"/>
-      <c r="X5" s="252"/>
-      <c r="Y5" s="252"/>
-      <c r="Z5" s="252"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -25370,23 +25382,23 @@
       </c>
       <c r="H7" s="130">
         <f>G7*(1+$C$17)</f>
-        <v>2550.0665983012154</v>
+        <v>2557.9615413300121</v>
       </c>
       <c r="I7" s="130">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>8236.7151125129258</v>
+        <v>8287.7953939092404</v>
       </c>
       <c r="J7" s="130">
         <f t="shared" si="0"/>
-        <v>26604.589813416751</v>
+        <v>26852.457076265942</v>
       </c>
       <c r="K7" s="130">
         <f t="shared" si="0"/>
-        <v>85932.825097336099</v>
+        <v>87001.960927101652</v>
       </c>
       <c r="L7" s="130">
         <f t="shared" si="0"/>
-        <v>277563.02506439562</v>
+        <v>281886.35340380936</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -25418,7 +25430,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1975605.8320382775</v>
+        <v>2000908.6775392161</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25472,23 +25484,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>2213.7914644646103</v>
+        <v>2219.8978265208325</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6207.6098969438071</v>
+        <v>6241.9023699316476</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>17406.526879872123</v>
+        <v>17550.963260692522</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>48808.991391176227</v>
+        <v>49349.748381526158</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>136863.46834523819</v>
+        <v>138761.48158627329</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25507,15 +25519,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>974150.8840851828</v>
+        <v>984968.05276853195</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="253" t="s">
+      <c r="B14" s="239" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="254"/>
+      <c r="C14" s="240"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25523,7 +25535,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25532,7 +25544,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1071.7956351309811</v>
+        <v>1083.7006609331056</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25540,22 +25552,22 @@
         <v>324</v>
       </c>
       <c r="C17" s="160">
-        <v>2.23</v>
-      </c>
-      <c r="E17" s="255" t="s">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E17" s="238" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
+      <c r="F17" s="238"/>
+      <c r="G17" s="238"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="238"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="253" t="s">
+      <c r="B19" s="239" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="254"/>
+      <c r="C19" s="240"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25571,7 +25583,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15190009503353602</v>
+        <v>0.15228796153155144</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25589,7 +25601,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1221894.1199999999</v>
+        <v>1202475.3199999998</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25616,15 +25628,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>1197488.1199999999</v>
+        <v>1178069.3199999998</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="253" t="s">
+      <c r="B28" s="239" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="254"/>
+      <c r="C28" s="240"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25632,7 +25644,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>211500.38797769495</v>
+        <v>214123.99342494446</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25641,7 +25653,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>974150.8840851828</v>
+        <v>984968.05276853195</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25650,7 +25662,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1185651.2720628777</v>
+        <v>1199092.0461934763</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25677,7 +25689,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1210057.2720628777</v>
+        <v>1223498.0461934763</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25695,21 +25707,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1071.7956351309811</v>
+        <v>1083.7006609331056</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32316,7 +32328,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32387,7 +32399,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33693,7 +33705,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>24.502603577088522</v>
+        <v>24.113199003848763</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33730,7 +33742,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>13.655281919489553</v>
+        <v>13.438267053636705</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33791,7 +33803,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>12.131111949485723</v>
+        <v>11.938319764902108</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33852,7 +33864,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1240292.8799999999</v>
+        <v>1220581.68</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -33913,7 +33925,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>1215886.8799999999</v>
+        <v>1196175.68</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -33950,7 +33962,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>13.468849059529875</v>
+        <v>13.250500476327623</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33987,7 +33999,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>20.523722296305046</v>
+        <v>20.191004506861567</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34122,7 +34134,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
-        <v>49.675299583466831</v>
+        <v>48.885841076578018</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34159,7 +34171,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="102"/>
-        <v>49.1706176532185</v>
+        <v>48.3734942574252</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34196,7 +34208,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
-        <v>2.013072912262465E-2</v>
+        <v>2.0455820703453455E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34233,7 +34245,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.0811989503640463E-2</v>
+        <v>4.14710632065197E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34270,7 +34282,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>4.8970691503123038E-4</v>
+        <v>4.976152026138882E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34307,7 +34319,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>9.0462504307853493E-4</v>
+        <v>9.1923385250219393E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34344,7 +34356,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.3617751316930887E-3</v>
+        <v>1.3837664678041047E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -34847,7 +34859,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>1.9677610339906171E-2</v>
+        <v>1.999538449569389E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -36722,15 +36734,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="241" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="241"/>
+      <c r="E4" s="241" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36738,7 +36750,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -36754,7 +36766,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1240292.8799999999</v>
+        <v>1220581.68</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -36774,7 +36786,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1215886.8799999999</v>
+        <v>1196175.68</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -36794,7 +36806,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>24.502603577088522</v>
+        <v>24.113199003848763</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -36814,7 +36826,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>13.655281919489553</v>
+        <v>13.438267053636705</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -36834,7 +36846,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>12.131111949485723</v>
+        <v>11.938319764902108</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36854,7 +36866,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>13.468849059529875</v>
+        <v>13.250500476327623</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36863,18 +36875,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>20.523722296305046</v>
+        <v>20.191004506861567</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="241" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="238"/>
-      <c r="E15" s="238" t="s">
+      <c r="C15" s="241"/>
+      <c r="E15" s="241" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="238"/>
+      <c r="F15" s="241"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36925,14 +36937,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="241" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="238"/>
-      <c r="E21" s="238" t="s">
+      <c r="C21" s="241"/>
+      <c r="E21" s="241" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="238"/>
+      <c r="F21" s="241"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37001,14 +37013,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="241" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="241"/>
+      <c r="E29" s="241" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="238"/>
+      <c r="F29" s="241"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37084,14 +37096,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="241" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="238"/>
-      <c r="E37" s="238" t="s">
+      <c r="C37" s="241"/>
+      <c r="E37" s="241" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="238"/>
+      <c r="F37" s="241"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37099,7 +37111,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>4.0811989503640463E-2</v>
+        <v>4.14710632065197E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -37115,7 +37127,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>2.013072912262465E-2</v>
+        <v>2.0455820703453455E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -37131,7 +37143,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.8970691503123038E-4</v>
+        <v>4.976152026138882E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -37147,7 +37159,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>9.0462504307853493E-4</v>
+        <v>9.1923385250219393E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37156,18 +37168,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.3617751316930887E-3</v>
+        <v>1.3837664678041047E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="238" t="s">
+      <c r="B45" s="241" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="238"/>
-      <c r="E45" s="238" t="s">
+      <c r="C45" s="241"/>
+      <c r="E45" s="241" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="238"/>
+      <c r="F45" s="241"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37200,18 +37212,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>1.9677610339906171E-2</v>
+        <v>1.999538449569389E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="B51" s="241" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="238"/>
-      <c r="E51" s="238" t="s">
+      <c r="C51" s="241"/>
+      <c r="E51" s="241" t="s">
         <v>303</v>
       </c>
-      <c r="F51" s="238"/>
+      <c r="F51" s="241"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37379,7 +37391,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>1082.28</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37408,7 +37420,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1240292.8799999999</v>
+        <v>1220581.68</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37437,7 +37449,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1215886.8799999999</v>
+        <v>1196175.68</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37466,7 +37478,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>24.502603577088522</v>
+        <v>24.113199003848763</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37495,7 +37507,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>13.655281919489553</v>
+        <v>13.438267053636705</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37524,7 +37536,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>12.131111949485723</v>
+        <v>11.938319764902108</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37553,7 +37565,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>13.468849059529875</v>
+        <v>13.250500476327623</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37582,7 +37594,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>20.523722296305046</v>
+        <v>20.191004506861567</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38355,7 +38367,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>4.0811989503640463E-2</v>
+        <v>4.14710632065197E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38384,7 +38396,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>2.013072912262465E-2</v>
+        <v>2.0455820703453455E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38413,7 +38425,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.8970691503123038E-4</v>
+        <v>4.976152026138882E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38442,7 +38454,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>9.0462504307853493E-4</v>
+        <v>9.1923385250219393E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38471,7 +38483,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.3617751316930887E-3</v>
+        <v>1.3837664678041047E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38707,7 +38719,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>1.9677610339906171E-2</v>
+        <v>1.999538449569389E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39313,14 +39325,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="251" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="F3" s="244" t="s">
+      <c r="D3" s="252"/>
+      <c r="F3" s="253" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="243"/>
+      <c r="G3" s="252"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39387,19 +39399,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="245">
+      <c r="C7" s="249">
         <f>Statement!AA89</f>
         <v>0.73746856663872595</v>
       </c>
-      <c r="D7" s="246"/>
-      <c r="F7" s="245">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.4571551446081066</v>
       </c>
-      <c r="G7" s="246"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -39426,19 +39438,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="245">
+      <c r="C9" s="249">
         <f>Statement!AA90</f>
         <v>4.8321048321048318E-2</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="F9" s="245">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.10478163300535129</v>
       </c>
-      <c r="G9" s="246"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -39465,19 +39477,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="245">
+      <c r="C11" s="249">
         <f>Statement!AA91</f>
         <v>0.97442973810194311</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="F11" s="245">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.9931584948688705</v>
       </c>
-      <c r="G11" s="246"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -39504,19 +39516,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="245">
+      <c r="C13" s="249">
         <f>Statement!AA95</f>
         <v>7.2839506172839505E-2</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="F13" s="245">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.29798356982823004</v>
       </c>
-      <c r="G13" s="246"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -39543,19 +39555,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="245">
+      <c r="C15" s="249">
         <f>Statement!AA96</f>
         <v>1.0649519677719244</v>
       </c>
-      <c r="D15" s="246"/>
-      <c r="F15" s="245">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>14.360995850622407</v>
       </c>
-      <c r="G15" s="246"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -39582,19 +39594,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="245">
+      <c r="C17" s="249">
         <f>Statement!AA98</f>
         <v>1.0488211824446863</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="F17" s="245">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>13.983023872679045</v>
       </c>
-      <c r="G17" s="246"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -39621,22 +39633,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="245">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6269702276707531E-3</v>
       </c>
-      <c r="D19" s="246"/>
-      <c r="F19" s="245">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G19" s="246"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -39663,22 +39675,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="245">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.0439105219552611</v>
       </c>
-      <c r="D21" s="246"/>
-      <c r="F21" s="245">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>13.684523809523812</v>
       </c>
-      <c r="G21" s="246"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39727,22 +39739,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="245">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.66922421142369992</v>
       </c>
-      <c r="D25" s="246"/>
-      <c r="F25" s="245">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>3.4304907368123319</v>
       </c>
-      <c r="G25" s="246"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39770,22 +39782,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="245">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.98979387632579552</v>
       </c>
-      <c r="D27" s="246"/>
-      <c r="F27" s="245">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.613921113689095</v>
       </c>
-      <c r="G27" s="246"/>
+      <c r="G27" s="250"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39813,22 +39825,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="245">
+      <c r="C29" s="249">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.94736842105263153</v>
       </c>
-      <c r="D29" s="246"/>
-      <c r="F29" s="245">
+      <c r="D29" s="250"/>
+      <c r="F29" s="249">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.4666666666666666</v>
       </c>
-      <c r="G29" s="246"/>
+      <c r="G29" s="250"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -39856,22 +39868,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="245">
+      <c r="C32" s="249">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.77687443541102075</v>
       </c>
-      <c r="D32" s="246"/>
-      <c r="F32" s="245">
+      <c r="D32" s="250"/>
+      <c r="F32" s="249">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>3.066450088600118</v>
       </c>
-      <c r="G32" s="246"/>
+      <c r="G32" s="250"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -39899,22 +39911,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="245">
+      <c r="C34" s="249">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.0263759451380341</v>
       </c>
-      <c r="D34" s="246"/>
-      <c r="F34" s="245">
+      <c r="D34" s="250"/>
+      <c r="F34" s="249">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>6.5320261437908496</v>
       </c>
-      <c r="G34" s="246"/>
+      <c r="G34" s="250"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -39942,22 +39954,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="245">
+      <c r="C36" s="249">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.49409933860718452</v>
       </c>
-      <c r="D36" s="246"/>
-      <c r="F36" s="245">
+      <c r="D36" s="250"/>
+      <c r="F36" s="249">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.5394777265745008</v>
       </c>
-      <c r="G36" s="246"/>
+      <c r="G36" s="250"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -39985,25 +39997,49 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="245">
+      <c r="C38" s="249">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.71122599704579026</v>
       </c>
-      <c r="D38" s="246"/>
-      <c r="F38" s="245">
+      <c r="D38" s="250"/>
+      <c r="F38" s="249">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.1118012422360248</v>
       </c>
-      <c r="G38" s="246"/>
+      <c r="G38" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40012,30 +40048,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4798302B-C7E7-B043-B3C2-6D5B4D25F976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D315567D-30FC-584D-82D0-0160322AD033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -15148,12 +15148,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>179.61</v>
-    <v>2.3340000000000001</v>
-    <v>-18.399999999999999</v>
-    <v>-1.7294E-2</v>
-    <v>0</v>
-    <v>0</v>
+    <v>186.25</v>
+    <v>2.3264999999999998</v>
+    <v>-6.84</v>
+    <v>-6.6030000000000004E-3</v>
+    <v>-0.55000000000000004</v>
+    <v>-5.3449999999999993E-4</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15161,25 +15161,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>1074.31</v>
+    <v>1054.17</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46301.860930092189</v>
+    <v>46304.999930890626</v>
     <v>0</v>
-    <v>1045.26</v>
-    <v>1180848145080</v>
+    <v>1017</v>
+    <v>1162145397000</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>1064.48</v>
-    <v>14.089</v>
-    <v>1063.96</v>
-    <v>1045.56</v>
-    <v>1045.56</v>
+    <v>1054.17</v>
+    <v>13.958</v>
+    <v>1035.8399999999999</v>
+    <v>1029</v>
+    <v>1028.45</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>20805581</v>
-    <v>25664506</v>
+    <v>19918874</v>
+    <v>26095676</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15201,19 +15201,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.49</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.34</v>
-    <v>6.4429999999999999E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>53.49</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.64</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.73</v>
-    <v>52.77</v>
-    <v>53.11</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15435,9 +15435,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1198211.76</v>
+        <v>1179234</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>916.06954752211414</v>
+        <v>922.22734663899018</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>1129937.76</v>
+        <v>1110960</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>1271.8262229408333</v>
+        <v>1276.424251985522</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>562.59146884506481</v>
+        <v>565.04494238496375</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -16099,14 +16099,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>1045.56</v>
+        <v>1028.45</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>14.089206306427704</v>
+        <v>13.866055787629698</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>1716.3715513868774</v>
+        <v>1722.9156209789164</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16123,14 +16123,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-18.399999999999999</v>
+        <v>-6.84</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>8.9728434994143615</v>
+        <v>8.8307279935129301</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>906.26445284980252</v>
+        <v>909.26219957987337</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16147,14 +16147,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>4.809667366309274E-2</v>
+        <v>4.8870707594930271E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>1074.6246487089384</v>
+        <v>1079.1748723136532</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16171,14 +16171,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.7294E-2</v>
+        <v>-6.6030000000000004E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>7.0976318910440345E-2</v>
+        <v>7.2118561710398446E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>2.7798164341537954E-2</v>
+        <v>4.8760808856805803E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16195,14 +16195,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-5.3449999999999993E-4</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>5.4247506300555753E-4</v>
+        <v>5.5120527393206099E-4</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16218,14 +16218,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>5.4038027468533614E-4</v>
+        <v>5.4907677356656954E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
       </c>
       <c r="I11" s="212">
         <f ca="1">DDM!C26</f>
-        <v>5.1154986733260488</v>
+        <v>5.156037991858887</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>179.61</v>
+        <v>186.25</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>102</v>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3340000000000001</v>
+        <v>2.3264999999999998</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="I13" s="213">
         <f>'Reverse DCF'!C17</f>
-        <v>0.31</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>25664506</v>
+        <v>26095676</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>5.6979911464063747E-2</v>
+        <v>5.7896905957596202E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>53.11</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.3109999999999997E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22657,7 +22657,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1198211.76</v>
+        <v>1179234</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.3109999999999997E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22693,7 +22693,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.3340000000000001</v>
+        <v>2.3264999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22736,7 +22736,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.3036727322054557E-3</v>
+        <v>4.3726301551907992E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22745,7 +22745,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99569632726779456</v>
+        <v>0.99562736984480915</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22763,7 +22763,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15814</v>
+        <v>0.15713249999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15765321157726025</v>
+        <v>0.15664231722802771</v>
       </c>
     </row>
   </sheetData>
@@ -23023,7 +23023,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1072725.0293382211</v>
+        <v>1080119.9729734343</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23077,23 +23077,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79445.199940780803</v>
+        <v>79514.634287508015</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>92574.526511526245</v>
+        <v>92736.415731196175</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>113137.08115438007</v>
+        <v>113433.98268067047</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>105023.29909439164</v>
+        <v>105390.93815840858</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>75425.384559414131</v>
+        <v>75755.566539202744</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23112,7 +23112,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>515936.21019985009</v>
+        <v>521767.00185129675</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23135,7 +23135,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15765321157726025</v>
+        <v>0.15664231722802771</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>465605.49126049288</v>
+        <v>466831.53739698598</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>515936.21019985009</v>
+        <v>521767.00185129675</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23168,7 +23168,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>981541.70146034297</v>
+        <v>988598.53924828279</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23195,7 +23195,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1049815.7014603429</v>
+        <v>1056872.5392482828</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>916.06954752211414</v>
+        <v>922.22734663899018</v>
       </c>
     </row>
   </sheetData>
@@ -23482,23 +23482,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>79445.199940780803</v>
+        <v>79514.634287508015</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>92574.526511526245</v>
+        <v>92736.415731196175</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>113137.08115438007</v>
+        <v>113433.98268067047</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>105023.29909439164</v>
+        <v>105390.93815840858</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>75425.384559414131</v>
+        <v>75755.566539202744</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24284,7 +24284,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15765321157726025</v>
+        <v>0.15664231722802771</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>999058.74478911608</v>
+        <v>1003432.2219176252</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1389238.8514901949</v>
+        <v>1394508.1927754083</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>1457512.8514901949</v>
+        <v>1462782.1927754083</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>1271.8262229408333</v>
+        <v>1276.424251985522</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15814</v>
+        <v>0.15713249999999998</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C58" s="237">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>562.59146884506481</v>
+        <v>565.04494238496375</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15765321157726025</v>
+        <v>0.15664231722802771</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1508507.6911882828</v>
+        <v>1515111.3307840549</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1898687.7978893616</v>
+        <v>1906187.3016418382</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1966961.7978893616</v>
+        <v>1974461.3016418382</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24527,7 +24527,7 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>1716.3715513868774</v>
+        <v>1722.9156209789164</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24551,7 +24551,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15765321157726025</v>
+        <v>0.15664231722802771</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>580124.9562647948</v>
+        <v>582664.50986075168</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>970305.06296587363</v>
+        <v>973740.48071853491</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24613,7 +24613,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>1038579.0629658736</v>
+        <v>1042014.4807185349</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>906.26445284980252</v>
+        <v>909.26219957987337</v>
       </c>
     </row>
   </sheetData>
@@ -24696,7 +24696,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>916.06954752211414</v>
+        <v>922.22734663899018</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>1271.8262229408333</v>
+        <v>1276.424251985522</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24714,7 +24714,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>562.59146884506481</v>
+        <v>565.04494238496375</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24723,7 +24723,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>1716.3715513868774</v>
+        <v>1722.9156209789164</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>906.26445284980252</v>
+        <v>909.26219957987337</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1074.6246487089384</v>
+        <v>1079.1748723136532</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>2.7798164341537954E-2</v>
+        <v>4.8760808856805803E-2</v>
       </c>
     </row>
   </sheetData>
@@ -25229,7 +25229,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15814</v>
+        <v>0.15713249999999998</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25246,7 +25246,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>5.1154986733260488</v>
+        <v>5.156037991858887</v>
       </c>
     </row>
   </sheetData>
@@ -25435,23 +25435,23 @@
       </c>
       <c r="H7" s="130">
         <f>G7*(1+$C$17)</f>
-        <v>75556.89644420144</v>
+        <v>74403.356040473169</v>
       </c>
       <c r="I7" s="130">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>98979.534341903884</v>
+        <v>95980.329292210386</v>
       </c>
       <c r="J7" s="130">
         <f t="shared" si="0"/>
-        <v>129663.18998789409</v>
+        <v>123814.6247869514</v>
       </c>
       <c r="K7" s="130">
         <f t="shared" si="0"/>
-        <v>169858.77888414127</v>
+        <v>159720.86597516731</v>
       </c>
       <c r="L7" s="130">
         <f t="shared" si="0"/>
-        <v>222515.00033822507</v>
+        <v>206039.91710796583</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -25483,7 +25483,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1522081.0163279853</v>
+        <v>1419101.3904632388</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25537,23 +25537,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>65267.297398378854</v>
+        <v>64327.022219614002</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>73856.452637820141</v>
+        <v>71743.751224815758</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>83575.937930257525</v>
+        <v>80015.60871628263</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>94574.504345276917</v>
+        <v>89241.188660102533</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>107020.47854513668</v>
+        <v>99530.452635891721</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25572,7 +25572,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>732057.78713474912</v>
+        <v>685516.69847070018</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25588,7 +25588,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1084.7001399394323</v>
+        <v>1026.2610468798996</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25605,7 +25605,7 @@
         <v>324</v>
       </c>
       <c r="C17" s="160">
-        <v>0.31</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E17" s="256" t="s">
         <v>225</v>
@@ -25636,7 +25636,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15765321157726025</v>
+        <v>0.15664231722802771</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25654,7 +25654,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1180437.24</v>
+        <v>1161741</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>1112163.24</v>
+        <v>1093467</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25697,7 +25697,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>424294.67085687013</v>
+        <v>404858.02345670667</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>732057.78713474912</v>
+        <v>685516.69847070018</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25715,7 +25715,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1156352.4579916191</v>
+        <v>1090374.7219274067</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1224626.4579916191</v>
+        <v>1158648.7219274067</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1084.7001399394323</v>
+        <v>1026.2610468798996</v>
       </c>
     </row>
   </sheetData>
@@ -30327,7 +30327,7 @@
         <v>9</v>
       </c>
       <c r="Q76" s="238">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T76" s="21">
         <v>11</v>
@@ -30393,7 +30393,7 @@
       </c>
       <c r="Q77" s="25">
         <f>Q76*Q85</f>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T77" s="25">
         <f t="shared" ref="T77:Y77" si="57">T76*T85</f>
@@ -30467,7 +30467,7 @@
       </c>
       <c r="Q78" s="25">
         <f>Q75+Q77</f>
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="T78" s="25">
         <f t="shared" ref="T78:Y78" si="60">T75+T77</f>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32739,7 +32739,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34108,7 +34108,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>14.089206306427704</v>
+        <v>13.866055787629698</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34149,7 +34149,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>8.9728434994143615</v>
+        <v>8.8307279935129301</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34214,7 +34214,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.5305268178467664</v>
+        <v>8.3954169015305897</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="Q153" s="145">
         <f>Statement!Q117*Statement!Q78</f>
-        <v>1090386.08</v>
+        <v>1098051.3599999999</v>
       </c>
       <c r="T153" s="145">
         <f>Statement!T117*Statement!T78</f>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1198211.76</v>
+        <v>1179234</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="Q154" s="145">
         <f t="shared" si="197"/>
-        <v>1022112.0800000001</v>
+        <v>1029777.3599999999</v>
       </c>
       <c r="T154" s="145">
         <f t="shared" ref="T154:Z154" si="198">T153+T108-T107+T48+T45</f>
@@ -34344,7 +34344,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>1129937.76</v>
+        <v>1110960</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34373,7 +34373,7 @@
       </c>
       <c r="Q155" s="183">
         <f t="shared" si="200"/>
-        <v>7.674205483977536</v>
+        <v>7.73175781601946</v>
       </c>
       <c r="T155" s="49"/>
       <c r="U155" s="49"/>
@@ -34385,7 +34385,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>8.4837805207676364</v>
+        <v>8.3412920082890345</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34414,7 +34414,7 @@
       </c>
       <c r="Q156" s="183">
         <f t="shared" si="201"/>
-        <v>10.289028387356554</v>
+        <v>10.366190457016307</v>
       </c>
       <c r="T156" s="49"/>
       <c r="U156" s="49"/>
@@ -34426,7 +34426,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>11.374448963156835</v>
+        <v>11.183410509361789</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="Q159" s="72">
         <f t="shared" ref="Q159" si="207">Q153/Q157</f>
-        <v>18.92045948290821</v>
+        <v>19.053467985424255</v>
       </c>
       <c r="T159" s="49"/>
       <c r="U159" s="49"/>
@@ -34573,7 +34573,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>20.791458615304528</v>
+        <v>20.462155127537741</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34602,7 +34602,7 @@
       </c>
       <c r="Q160" s="72">
         <f t="shared" ref="Q160" si="210">Q154/Q158</f>
-        <v>17.721305239010491</v>
+        <v>17.854205308660855</v>
       </c>
       <c r="T160" s="49"/>
       <c r="U160" s="49"/>
@@ -34614,7 +34614,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>19.590779071942656</v>
+        <v>19.261744043110316</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="Q161" s="74">
         <f t="shared" ref="Q161" si="212">Q157/Q153</f>
-        <v>5.2852839060454619E-2</v>
+        <v>5.2483883813959312E-2</v>
       </c>
       <c r="T161" s="49"/>
       <c r="U161" s="49"/>
@@ -34655,7 +34655,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>4.809667366309274E-2</v>
+        <v>4.8870707594930271E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34696,7 +34696,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.0976318910440345E-2</v>
+        <v>7.2118561710398446E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34737,7 +34737,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>5.4038027468533614E-4</v>
+        <v>5.4907677356656954E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="Q164" s="156">
         <f t="shared" si="216"/>
-        <v>5.9611912874016142E-4</v>
+        <v>5.9195773866169621E-4</v>
       </c>
       <c r="T164" s="49"/>
       <c r="U164" s="49"/>
@@ -34778,7 +34778,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>5.4247506300555753E-4</v>
+        <v>5.5120527393206099E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34807,7 +34807,7 @@
       </c>
       <c r="Q165" s="156">
         <f t="shared" si="217"/>
-        <v>1.1555540034040052E-3</v>
+        <v>1.147487308790365E-3</v>
       </c>
       <c r="T165" s="49"/>
       <c r="U165" s="49"/>
@@ -34819,7 +34819,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.0515670452107731E-3</v>
+        <v>1.0684902233144566E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35053,7 +35053,7 @@
       </c>
       <c r="Q171" s="156">
         <f t="shared" si="223"/>
-        <v>2.6362038664323375E-3</v>
+        <v>2.617801047120419E-3</v>
       </c>
       <c r="T171" s="49"/>
       <c r="U171" s="49"/>
@@ -35354,7 +35354,7 @@
       </c>
       <c r="Q176" s="156">
         <f t="shared" si="236"/>
-        <v>6.2614519070162744E-2</v>
+        <v>6.2177419460597919E-2</v>
       </c>
       <c r="T176" s="49"/>
       <c r="U176" s="49"/>
@@ -35366,7 +35366,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>5.6979911464063747E-2</v>
+        <v>5.7896905957596202E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37376,7 +37376,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37392,7 +37392,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1198211.76</v>
+        <v>1179234</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37412,7 +37412,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1129937.76</v>
+        <v>1110960</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37432,7 +37432,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>14.089206306427704</v>
+        <v>13.866055787629698</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37452,7 +37452,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>8.9728434994143615</v>
+        <v>8.8307279935129301</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37472,7 +37472,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>8.5305268178467664</v>
+        <v>8.3954169015305897</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37492,7 +37492,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>8.4837805207676364</v>
+        <v>8.3412920082890345</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37501,7 +37501,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>11.374448963156835</v>
+        <v>11.183410509361789</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.0976318910440345E-2</v>
+        <v>7.2118561710398446E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -37753,7 +37753,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>4.809667366309274E-2</v>
+        <v>4.8870707594930271E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -37769,7 +37769,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>5.4038027468533614E-4</v>
+        <v>5.4907677356656954E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.4247506300555753E-4</v>
+        <v>5.5120527393206099E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.0515670452107731E-3</v>
+        <v>1.0684902233144566E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -37838,7 +37838,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>5.6979911464063747E-2</v>
+        <v>5.7896905957596202E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38017,7 +38017,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>1045.56</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38042,11 +38042,11 @@
       </c>
       <c r="G7" s="173">
         <f>Statement!Q153</f>
-        <v>1090386.08</v>
+        <v>1098051.3599999999</v>
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1198211.76</v>
+        <v>1179234</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38071,11 +38071,11 @@
       </c>
       <c r="G8" s="173">
         <f>Statement!Q154</f>
-        <v>1022112.0800000001</v>
+        <v>1029777.3599999999</v>
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1129937.76</v>
+        <v>1110960</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38104,7 +38104,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>14.089206306427704</v>
+        <v>13.866055787629698</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>8.9728434994143615</v>
+        <v>8.8307279935129301</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38162,7 +38162,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>8.5305268178467664</v>
+        <v>8.3954169015305897</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38187,11 +38187,11 @@
       </c>
       <c r="G12" s="174">
         <f>Statement!Q155</f>
-        <v>7.674205483977536</v>
+        <v>7.73175781601946</v>
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>8.4837805207676364</v>
+        <v>8.3412920082890345</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38216,11 +38216,11 @@
       </c>
       <c r="G13" s="174">
         <f>Statement!Q156</f>
-        <v>10.289028387356554</v>
+        <v>10.366190457016307</v>
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>11.374448963156835</v>
+        <v>11.183410509361789</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38993,7 +38993,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.0976318910440345E-2</v>
+        <v>7.2118561710398446E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39018,11 +39018,11 @@
       </c>
       <c r="G52" s="175">
         <f>Statement!Q161</f>
-        <v>5.2852839060454619E-2</v>
+        <v>5.2483883813959312E-2</v>
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>4.809667366309274E-2</v>
+        <v>4.8870707594930271E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39051,7 +39051,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>5.4038027468533614E-4</v>
+        <v>5.4907677356656954E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39076,11 +39076,11 @@
       </c>
       <c r="G54" s="175">
         <f>Statement!Q164</f>
-        <v>5.9611912874016142E-4</v>
+        <v>5.9195773866169621E-4</v>
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.4247506300555753E-4</v>
+        <v>5.5120527393206099E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39105,11 +39105,11 @@
       </c>
       <c r="G55" s="175">
         <f>Statement!Q165</f>
-        <v>1.1555540034040052E-3</v>
+        <v>1.147487308790365E-3</v>
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.0515670452107731E-3</v>
+        <v>1.0684902233144566E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="G63" s="175">
         <f>Statement!Q171</f>
-        <v>2.6362038664323375E-3</v>
+        <v>2.617801047120419E-3</v>
       </c>
       <c r="I63" s="175">
         <f>Statement!AC171</f>
@@ -39341,11 +39341,11 @@
       </c>
       <c r="G68" s="196">
         <f>Statement!Q176</f>
-        <v>6.2614519070162744E-2</v>
+        <v>6.2177419460597919E-2</v>
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>5.6979911464063747E-2</v>
+        <v>5.7896905957596202E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D315567D-30FC-584D-82D0-0160322AD033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A5949C-B52F-7144-8809-17531A694A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="447">
   <si>
     <t>Ticker</t>
   </si>
@@ -1469,6 +1469,30 @@
   </si>
   <si>
     <t>Datacenter revenue increased because of higher pricing and higher bit shipments</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1509,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1657,6 +1681,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2080,11 +2112,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2402,6 +2435,14 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2414,6 +2455,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2421,12 +2468,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2447,17 +2488,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -15150,10 +15192,10 @@
     <v>1255</v>
     <v>186.25</v>
     <v>2.3264999999999998</v>
-    <v>-6.84</v>
-    <v>-6.6030000000000004E-3</v>
-    <v>-0.55000000000000004</v>
-    <v>-5.3449999999999993E-4</v>
+    <v>-39.96</v>
+    <v>-3.8834E-2</v>
+    <v>-1.57</v>
+    <v>-1.5870000000000001E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15161,25 +15203,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>1054.17</v>
+    <v>1002.67</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46304.999930890626</v>
+    <v>46307.86130399297</v>
     <v>0</v>
-    <v>1017</v>
-    <v>1162145397000</v>
+    <v>978.5</v>
+    <v>1117014852720</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>1054.17</v>
-    <v>13.958</v>
-    <v>1035.8399999999999</v>
+    <v>1002.4450000000001</v>
+    <v>13.327400000000001</v>
     <v>1029</v>
-    <v>1028.45</v>
+    <v>989.04</v>
+    <v>987.47</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>19918874</v>
-    <v>26095676</v>
+    <v>23549395</v>
+    <v>25925396</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15435,9 +15477,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -15991,7 +16033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I85"/>
+  <dimension ref="B1:K85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -16003,25 +16045,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="239" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="240"/>
-      <c r="E2" s="239" t="s">
+      <c r="C2" s="244"/>
+      <c r="E2" s="243" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="H2" s="239" t="s">
+      <c r="F2" s="244"/>
+      <c r="H2" s="243" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="240"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="244"/>
+      <c r="K2" s="136" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
         <v>11</v>
       </c>
@@ -16034,7 +16081,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1179234</v>
+        <v>1133439.8399999999</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16042,10 +16089,13 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>922.22734663899018</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+        <v>922.34828108400495</v>
+      </c>
+      <c r="K3" s="241" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="185" t="s">
         <v>0</v>
       </c>
@@ -16058,7 +16108,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>1110960</v>
+        <v>1065165.8399999999</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16066,16 +16116,19 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>1276.424251985522</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1276.514150508963</v>
+      </c>
+      <c r="K4" s="241" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="185" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16092,21 +16145,24 @@
         <f ca="1">'AVG target price'!C7</f>
         <v>565.04494238496375</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="241" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>1028.45</v>
+        <v>987.47</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>13.866055787629698</v>
+        <v>13.32758388357364</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16114,23 +16170,26 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>1722.9156209789164</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1723.0435731224111</v>
+      </c>
+      <c r="K6" s="242" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="185" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-6.84</v>
+        <v>-39.96</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>8.8307279935129301</v>
+        <v>8.4877970988377331</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -16138,23 +16197,23 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>909.26219957987337</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+        <v>909.3208055717879</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.55000000000000004</v>
+        <v>-1.57</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>4.8870707594930271E-2</v>
+        <v>5.0845221745514084E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -16162,23 +16221,23 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>1079.1748723136532</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1079.2543505344261</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="185" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.6030000000000004E-3</v>
+        <v>-3.8834E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>7.2118561710398446E-2</v>
+        <v>7.5032354606487106E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16186,26 +16245,26 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>4.8760808856805803E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>9.1214056594704065E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.3449999999999993E-4</v>
+        <v>-1.5870000000000001E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>5.5120527393206099E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>5.73475518559503E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="185" t="s">
         <v>7</v>
       </c>
@@ -16218,7 +16277,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>5.4907677356656954E-4</v>
+        <v>5.7126102078783477E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
@@ -16228,7 +16287,7 @@
         <v>5.156037991858887</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="185" t="s">
         <v>8</v>
       </c>
@@ -16244,7 +16303,7 @@
         <v>0.43376317079147264</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="185" t="s">
         <v>9</v>
       </c>
@@ -16267,13 +16326,13 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="186" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>26095676</v>
+        <v>25925396</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16283,16 +16342,16 @@
         <v>1.2071781950589597</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>5.7896905957596202E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>6.0236103929433085E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="186" t="s">
         <v>295</v>
       </c>
@@ -16300,12 +16359,16 @@
         <f>Statement!AC175</f>
         <v>60.472984942426926</v>
       </c>
+      <c r="H16" s="243" t="s">
+        <v>439</v>
+      </c>
+      <c r="I16" s="244"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="245" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="241"/>
+      <c r="C17" s="245"/>
       <c r="E17" s="184" t="s">
         <v>296</v>
       </c>
@@ -16313,6 +16376,13 @@
         <f>Statement!AC171</f>
         <v>2.617801047120419E-3</v>
       </c>
+      <c r="H17" s="185" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" s="239">
+        <f ca="1">DCF!C15</f>
+        <v>0.15662260254608118</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="184" t="s">
@@ -16328,6 +16398,13 @@
         <f>Statement!AC144</f>
         <v>-74.647977446327559</v>
       </c>
+      <c r="H18" s="186" t="s">
+        <v>440</v>
+      </c>
+      <c r="I18" s="240">
+        <f ca="1">Multiples!C54</f>
+        <v>0.15713249999999998</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="184" t="s">
@@ -16378,14 +16455,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="241" t="s">
+      <c r="B25" s="245" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="241"/>
-      <c r="E25" s="239" t="s">
+      <c r="C25" s="245"/>
+      <c r="E25" s="243" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="240"/>
+      <c r="F25" s="244"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -16724,13 +16801,14 @@
       <c r="H85" s="136"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16743,6 +16821,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{FFB0360C-24EF-5241-8066-E09C4813D663}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{AE5E1E03-D186-2C41-A6CC-06129118B7F8}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{21AA7E56-DA1B-FC46-AFAD-5FD96DEC8511}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{E7BF3B29-E6B2-DE41-8BB5-EB1F2EF0A763}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16752,18 +16836,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{7873638F-C7CC-CC44-83D9-20F3C6CE307B}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{E45A0110-B3F9-104A-B761-6A88FFB7BD32}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{6CB7E4FF-E3B0-8646-8263-E1791C14848A}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{0BC2D033-0850-7447-A695-2D6A3F1C3B97}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{FA605B8D-7A34-7A4D-B373-0B8C7BA56553}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16800,36 +16923,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -16840,32 +16963,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="249" t="s">
+      <c r="S4" s="253" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
-      <c r="AC4" s="250"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
+      <c r="AA4" s="254"/>
+      <c r="AB4" s="254"/>
+      <c r="AC4" s="254"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17458,33 +17581,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="248" t="s">
+      <c r="C12" s="252" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
+      <c r="D12" s="252"/>
+      <c r="E12" s="252"/>
+      <c r="F12" s="252"/>
+      <c r="G12" s="252"/>
+      <c r="H12" s="252"/>
+      <c r="I12" s="252"/>
+      <c r="J12" s="252"/>
+      <c r="K12" s="252"/>
+      <c r="L12" s="252"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="249" t="s">
+      <c r="S12" s="253" t="s">
         <v>122</v>
       </c>
-      <c r="T12" s="250"/>
-      <c r="U12" s="250"/>
-      <c r="V12" s="250"/>
-      <c r="W12" s="250"/>
-      <c r="X12" s="250"/>
-      <c r="Y12" s="250"/>
-      <c r="Z12" s="250"/>
-      <c r="AA12" s="250"/>
-      <c r="AB12" s="250"/>
-      <c r="AC12" s="250"/>
+      <c r="T12" s="254"/>
+      <c r="U12" s="254"/>
+      <c r="V12" s="254"/>
+      <c r="W12" s="254"/>
+      <c r="X12" s="254"/>
+      <c r="Y12" s="254"/>
+      <c r="Z12" s="254"/>
+      <c r="AA12" s="254"/>
+      <c r="AB12" s="254"/>
+      <c r="AC12" s="254"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -18029,35 +18152,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="P2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="246"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -18066,31 +18189,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="P4" s="250" t="s">
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
+      <c r="P4" s="254" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="250"/>
-      <c r="R4" s="250"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
+      <c r="Q4" s="254"/>
+      <c r="R4" s="254"/>
+      <c r="S4" s="254"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -18285,32 +18408,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="252" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="252"/>
+      <c r="E9" s="252"/>
+      <c r="F9" s="252"/>
+      <c r="G9" s="252"/>
+      <c r="H9" s="252"/>
+      <c r="I9" s="252"/>
+      <c r="J9" s="252"/>
+      <c r="K9" s="252"/>
+      <c r="L9" s="252"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="250" t="s">
+      <c r="P9" s="254" t="s">
         <v>126</v>
       </c>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
+      <c r="Q9" s="254"/>
+      <c r="R9" s="254"/>
+      <c r="S9" s="254"/>
+      <c r="T9" s="254"/>
+      <c r="U9" s="254"/>
+      <c r="V9" s="254"/>
+      <c r="W9" s="254"/>
+      <c r="X9" s="254"/>
+      <c r="Y9" s="254"/>
+      <c r="Z9" s="254"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -19248,31 +19371,31 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C22" s="248" t="s">
+      <c r="C22" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
-      <c r="K22" s="248"/>
-      <c r="L22" s="248"/>
-      <c r="P22" s="250" t="s">
+      <c r="D22" s="252"/>
+      <c r="E22" s="252"/>
+      <c r="F22" s="252"/>
+      <c r="G22" s="252"/>
+      <c r="H22" s="252"/>
+      <c r="I22" s="252"/>
+      <c r="J22" s="252"/>
+      <c r="K22" s="252"/>
+      <c r="L22" s="252"/>
+      <c r="P22" s="254" t="s">
         <v>128</v>
       </c>
-      <c r="Q22" s="250"/>
-      <c r="R22" s="250"/>
-      <c r="S22" s="250"/>
-      <c r="T22" s="250"/>
-      <c r="U22" s="250"/>
-      <c r="V22" s="250"/>
-      <c r="W22" s="250"/>
-      <c r="X22" s="250"/>
-      <c r="Y22" s="250"/>
-      <c r="Z22" s="250"/>
+      <c r="Q22" s="254"/>
+      <c r="R22" s="254"/>
+      <c r="S22" s="254"/>
+      <c r="T22" s="254"/>
+      <c r="U22" s="254"/>
+      <c r="V22" s="254"/>
+      <c r="W22" s="254"/>
+      <c r="X22" s="254"/>
+      <c r="Y22" s="254"/>
+      <c r="Z22" s="254"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B23" s="16" t="s">
@@ -20087,60 +20210,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="257"/>
+      <c r="Q3" s="257"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="257"/>
+      <c r="T3" s="257"/>
+      <c r="U3" s="257"/>
+      <c r="V3" s="257"/>
+      <c r="W3" s="257"/>
+      <c r="X3" s="257"/>
+      <c r="Y3" s="257"/>
+      <c r="Z3" s="257"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="252" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="252"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="252"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="252"/>
+      <c r="L5" s="252"/>
+      <c r="P5" s="257"/>
+      <c r="Q5" s="257"/>
+      <c r="R5" s="257"/>
+      <c r="S5" s="257"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="257"/>
+      <c r="V5" s="257"/>
+      <c r="W5" s="257"/>
+      <c r="X5" s="257"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20326,30 +20449,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="252" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="253"/>
-      <c r="Q11" s="253"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
-      <c r="T11" s="253"/>
-      <c r="U11" s="253"/>
-      <c r="V11" s="253"/>
-      <c r="W11" s="253"/>
-      <c r="X11" s="253"/>
-      <c r="Y11" s="253"/>
-      <c r="Z11" s="253"/>
+      <c r="P11" s="257"/>
+      <c r="Q11" s="257"/>
+      <c r="R11" s="257"/>
+      <c r="S11" s="257"/>
+      <c r="T11" s="257"/>
+      <c r="U11" s="257"/>
+      <c r="V11" s="257"/>
+      <c r="W11" s="257"/>
+      <c r="X11" s="257"/>
+      <c r="Y11" s="257"/>
+      <c r="Z11" s="257"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20591,18 +20714,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="252"/>
+      <c r="J18" s="252"/>
+      <c r="K18" s="252"/>
+      <c r="L18" s="252"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20815,23 +20938,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="253"/>
-      <c r="C25" s="253"/>
+      <c r="B25" s="257"/>
+      <c r="C25" s="257"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="248" t="s">
+      <c r="C26" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="248"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="248"/>
-      <c r="I26" s="248"/>
-      <c r="J26" s="248"/>
-      <c r="K26" s="248"/>
-      <c r="L26" s="248"/>
+      <c r="D26" s="252"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="252"/>
+      <c r="K26" s="252"/>
+      <c r="L26" s="252"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -21023,18 +21146,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="248" t="s">
+      <c r="C33" s="252" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="248"/>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
-      <c r="J33" s="248"/>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="252"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="252"/>
+      <c r="H33" s="252"/>
+      <c r="I33" s="252"/>
+      <c r="J33" s="252"/>
+      <c r="K33" s="252"/>
+      <c r="L33" s="252"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -21218,18 +21341,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="248" t="s">
+      <c r="C40" s="252" t="s">
         <v>150</v>
       </c>
-      <c r="D40" s="248"/>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
-      <c r="I40" s="248"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="248"/>
-      <c r="L40" s="248"/>
+      <c r="D40" s="252"/>
+      <c r="E40" s="252"/>
+      <c r="F40" s="252"/>
+      <c r="G40" s="252"/>
+      <c r="H40" s="252"/>
+      <c r="I40" s="252"/>
+      <c r="J40" s="252"/>
+      <c r="K40" s="252"/>
+      <c r="L40" s="252"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21493,6 +21616,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21500,12 +21629,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21543,60 +21666,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="253"/>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="253"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="S2" s="257"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="257"/>
+      <c r="V2" s="257"/>
+      <c r="W2" s="257"/>
+      <c r="X2" s="257"/>
+      <c r="Y2" s="257"/>
+      <c r="Z2" s="257"/>
+      <c r="AA2" s="257"/>
+      <c r="AB2" s="257"/>
+      <c r="AC2" s="257"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
+      <c r="S4" s="257"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
+      <c r="AA4" s="257"/>
+      <c r="AB4" s="257"/>
+      <c r="AC4" s="257"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21959,18 +22082,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="248" t="s">
+      <c r="C13" s="252" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="248"/>
-      <c r="K13" s="248"/>
-      <c r="L13" s="248"/>
+      <c r="D13" s="252"/>
+      <c r="E13" s="252"/>
+      <c r="F13" s="252"/>
+      <c r="G13" s="252"/>
+      <c r="H13" s="252"/>
+      <c r="I13" s="252"/>
+      <c r="J13" s="252"/>
+      <c r="K13" s="252"/>
+      <c r="L13" s="252"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -22063,18 +22186,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="252" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="252"/>
+      <c r="J18" s="252"/>
+      <c r="K18" s="252"/>
+      <c r="L18" s="252"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -22266,18 +22389,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="248" t="s">
+      <c r="C25" s="252" t="s">
         <v>262</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="248"/>
-      <c r="I25" s="248"/>
-      <c r="J25" s="248"/>
-      <c r="K25" s="248"/>
-      <c r="L25" s="248"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="252"/>
+      <c r="F25" s="252"/>
+      <c r="G25" s="252"/>
+      <c r="H25" s="252"/>
+      <c r="I25" s="252"/>
+      <c r="J25" s="252"/>
+      <c r="K25" s="252"/>
+      <c r="L25" s="252"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -22415,18 +22538,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="248" t="s">
+      <c r="C31" s="252" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
+      <c r="D31" s="252"/>
+      <c r="E31" s="252"/>
+      <c r="F31" s="252"/>
+      <c r="G31" s="252"/>
+      <c r="H31" s="252"/>
+      <c r="I31" s="252"/>
+      <c r="J31" s="252"/>
+      <c r="K31" s="252"/>
+      <c r="L31" s="252"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22565,16 +22688,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22588,18 +22711,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>164</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{FB08413C-2DC9-214F-A7A3-5EEBC25D4AEA}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{8781F548-F632-C24D-A095-8FAAFBFC1F9E}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{783E7A6F-FF22-AC4A-8256-5B348A6FE7F4}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{EDB7FD73-84D0-3E45-A3D1-4B7A600FF95D}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{6F3044C1-A65B-DE4E-A0D9-1565B33C281C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -22637,10 +22799,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="246" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="246"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22657,7 +22819,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22666,7 +22828,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1179234</v>
+        <v>1133439.8399999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22725,10 +22887,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="246" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="246"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22736,7 +22898,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.3726301551907992E-3</v>
+        <v>4.5484931550930606E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22745,7 +22907,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99562736984480915</v>
+        <v>0.99545150684490691</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22772,7 +22934,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15664231722802771</v>
+        <v>0.15662260254608118</v>
       </c>
     </row>
   </sheetData>
@@ -22817,60 +22979,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="257"/>
+      <c r="Q3" s="257"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="257"/>
+      <c r="T3" s="257"/>
+      <c r="U3" s="257"/>
+      <c r="V3" s="257"/>
+      <c r="W3" s="257"/>
+      <c r="X3" s="257"/>
+      <c r="Y3" s="257"/>
+      <c r="Z3" s="257"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="252" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="252"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="252"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="252"/>
+      <c r="L5" s="252"/>
+      <c r="P5" s="257"/>
+      <c r="Q5" s="257"/>
+      <c r="R5" s="257"/>
+      <c r="S5" s="257"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="257"/>
+      <c r="V5" s="257"/>
+      <c r="W5" s="257"/>
+      <c r="X5" s="257"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23023,7 +23185,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1080119.9729734343</v>
+        <v>1080265.2044818203</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23077,23 +23239,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79514.634287508015</v>
+        <v>79515.989617865242</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>92736.415731196175</v>
+        <v>92739.577150519064</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>113433.98268067047</v>
+        <v>113439.78324086327</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>105390.93815840858</v>
+        <v>105398.12391440151</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>75755.566539202744</v>
+        <v>75762.023043731693</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23112,14 +23274,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>521767.00185129675</v>
+        <v>521881.63315488893</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="246" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="246"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23135,14 +23297,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664231722802771</v>
+        <v>0.15662260254608118</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="246" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="246"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23150,7 +23312,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>466831.53739698598</v>
+        <v>466855.49696738075</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23159,7 +23321,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>521767.00185129675</v>
+        <v>521881.63315488893</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23168,7 +23330,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>988598.53924828279</v>
+        <v>988737.13012226974</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23195,7 +23357,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1056872.5392482828</v>
+        <v>1057011.1301222697</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23213,7 +23375,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>922.22734663899018</v>
+        <v>922.34828108400495</v>
       </c>
     </row>
   </sheetData>
@@ -23256,37 +23418,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23482,23 +23644,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>79514.634287508015</v>
+        <v>79515.989617865242</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>92736.415731196175</v>
+        <v>92739.577150519064</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>113433.98268067047</v>
+        <v>113439.78324086327</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>105390.93815840858</v>
+        <v>105398.12391440151</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>75755.566539202744</v>
+        <v>75762.023043731693</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -23506,18 +23668,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="252" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23711,18 +23873,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="248" t="s">
+      <c r="C17" s="252" t="s">
         <v>196</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
+      <c r="D17" s="252"/>
+      <c r="E17" s="252"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
+      <c r="J17" s="252"/>
+      <c r="K17" s="252"/>
+      <c r="L17" s="252"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -23856,18 +24018,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="248" t="s">
+      <c r="C22" s="252" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
-      <c r="K22" s="248"/>
-      <c r="L22" s="248"/>
+      <c r="D22" s="252"/>
+      <c r="E22" s="252"/>
+      <c r="F22" s="252"/>
+      <c r="G22" s="252"/>
+      <c r="H22" s="252"/>
+      <c r="I22" s="252"/>
+      <c r="J22" s="252"/>
+      <c r="K22" s="252"/>
+      <c r="L22" s="252"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -23951,18 +24113,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="248" t="s">
+      <c r="C27" s="252" t="s">
         <v>200</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
-      <c r="F27" s="248"/>
-      <c r="G27" s="248"/>
-      <c r="H27" s="248"/>
-      <c r="I27" s="248"/>
-      <c r="J27" s="248"/>
-      <c r="K27" s="248"/>
-      <c r="L27" s="248"/>
+      <c r="D27" s="252"/>
+      <c r="E27" s="252"/>
+      <c r="F27" s="252"/>
+      <c r="G27" s="252"/>
+      <c r="H27" s="252"/>
+      <c r="I27" s="252"/>
+      <c r="J27" s="252"/>
+      <c r="K27" s="252"/>
+      <c r="L27" s="252"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -24263,10 +24425,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="242" t="s">
+      <c r="B39" s="246" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="242"/>
+      <c r="C39" s="246"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24284,7 +24446,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664231722802771</v>
+        <v>0.15662260254608118</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24310,7 +24472,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1003432.2219176252</v>
+        <v>1003517.7425596225</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24319,7 +24481,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1394508.1927754083</v>
+        <v>1394611.2164832717</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24346,7 +24508,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>1462782.1927754083</v>
+        <v>1462885.2164832717</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24364,14 +24526,14 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>1276.424251985522</v>
+        <v>1276.514150508963</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="246" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="242"/>
+      <c r="C52" s="246"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -24427,10 +24589,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="242" t="s">
+      <c r="B60" s="246" t="s">
         <v>322</v>
       </c>
-      <c r="C60" s="242"/>
+      <c r="C60" s="246"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -24447,7 +24609,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664231722802771</v>
+        <v>0.15662260254608118</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24473,7 +24635,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1515111.3307840549</v>
+        <v>1515240.4608746341</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24482,7 +24644,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1906187.3016418382</v>
+        <v>1906333.934798283</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24509,7 +24671,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1974461.3016418382</v>
+        <v>1974607.934798283</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24527,14 +24689,14 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>1722.9156209789164</v>
+        <v>1723.0435731224111</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="242" t="s">
+      <c r="B73" s="246" t="s">
         <v>427</v>
       </c>
-      <c r="C73" s="242"/>
+      <c r="C73" s="246"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -24551,7 +24713,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664231722802771</v>
+        <v>0.15662260254608118</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24577,7 +24739,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>582664.50986075168</v>
+        <v>582714.16926161991</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24586,7 +24748,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>973740.48071853491</v>
+        <v>973807.64318526897</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24613,7 +24775,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>1042014.4807185349</v>
+        <v>1042081.643185269</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24631,22 +24793,22 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>909.26219957987337</v>
+        <v>909.3208055717879</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24684,10 +24846,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="246" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="246"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24696,7 +24858,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>922.22734663899018</v>
+        <v>922.34828108400495</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24705,7 +24867,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>1276.424251985522</v>
+        <v>1276.514150508963</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24723,7 +24885,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>1722.9156209789164</v>
+        <v>1723.0435731224111</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24732,7 +24894,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>909.26219957987337</v>
+        <v>909.3208055717879</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24741,7 +24903,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1079.1748723136532</v>
+        <v>1079.2543505344261</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24750,7 +24912,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24759,7 +24921,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>4.8760808856805803E-2</v>
+        <v>9.1214056594704065E-2</v>
       </c>
     </row>
   </sheetData>
@@ -24775,18 +24937,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="19.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{EBB45001-6307-E34A-9590-9E471CF7DF8E}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{7FEFED7B-6F49-6345-A225-CD95CFFF29F3}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{97C85210-ECF5-F54E-A672-0A0AF9713E1E}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{514F83DF-19BB-4C44-B9EA-53F46030EC1E}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{3A1BB07F-F506-1E46-9D87-5DA805869BDB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24815,37 +25016,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24958,18 +25159,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="252" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="252"/>
+      <c r="E9" s="252"/>
+      <c r="F9" s="252"/>
+      <c r="G9" s="252"/>
+      <c r="H9" s="252"/>
+      <c r="I9" s="252"/>
+      <c r="J9" s="252"/>
+      <c r="K9" s="252"/>
+      <c r="L9" s="252"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25090,18 +25291,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="248" t="s">
+      <c r="C14" s="252" t="s">
         <v>360</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="248"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="248"/>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="D14" s="252"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="252"/>
+      <c r="G14" s="252"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="252"/>
+      <c r="J14" s="252"/>
+      <c r="K14" s="252"/>
+      <c r="L14" s="252"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -25191,10 +25392,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="242" t="s">
+      <c r="B20" s="246" t="s">
         <v>362</v>
       </c>
-      <c r="C20" s="242"/>
+      <c r="C20" s="246"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -25295,60 +25496,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="256" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="257"/>
+      <c r="Q3" s="257"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="257"/>
+      <c r="T3" s="257"/>
+      <c r="U3" s="257"/>
+      <c r="V3" s="257"/>
+      <c r="W3" s="257"/>
+      <c r="X3" s="257"/>
+      <c r="Y3" s="257"/>
+      <c r="Z3" s="257"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="252" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="252"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="252"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="252"/>
+      <c r="L5" s="252"/>
+      <c r="P5" s="257"/>
+      <c r="Q5" s="257"/>
+      <c r="R5" s="257"/>
+      <c r="S5" s="257"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="257"/>
+      <c r="V5" s="257"/>
+      <c r="W5" s="257"/>
+      <c r="X5" s="257"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -25483,7 +25684,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1419101.3904632388</v>
+        <v>1419292.2009663745</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25537,23 +25738,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>64327.022219614002</v>
+        <v>64328.118676471102</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>71743.751224815758</v>
+        <v>71746.196996302941</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>80015.60871628263</v>
+        <v>80019.700394488362</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>89241.188660102533</v>
+        <v>89247.27329524704</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>99530.452635891721</v>
+        <v>99538.935429270074</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25572,15 +25773,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>685516.69847070018</v>
+        <v>685667.30529807927</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="259" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="255"/>
+      <c r="C14" s="260"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25588,7 +25789,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25597,7 +25798,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1026.2610468798996</v>
+        <v>1026.414109911301</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25607,20 +25808,20 @@
       <c r="C17" s="160">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E17" s="256" t="s">
+      <c r="E17" s="258" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="256"/>
-      <c r="G17" s="256"/>
-      <c r="H17" s="256"/>
-      <c r="I17" s="256"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="254" t="s">
+      <c r="B19" s="259" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="255"/>
+      <c r="C19" s="260"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25636,7 +25837,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664231722802771</v>
+        <v>0.15662260254608118</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25654,7 +25855,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1161741</v>
+        <v>1116626.1599999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25681,15 +25882,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>1093467</v>
+        <v>1048352.1599999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="259" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="255"/>
+      <c r="C28" s="260"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25697,7 +25898,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>404858.02345670667</v>
+        <v>404880.22479177953</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25706,7 +25907,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>685516.69847070018</v>
+        <v>685667.30529807927</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25715,7 +25916,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1090374.7219274067</v>
+        <v>1090547.5300898589</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25742,7 +25943,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1158648.7219274067</v>
+        <v>1158821.5300898589</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25760,21 +25961,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1026.2610468798996</v>
+        <v>1026.414109911301</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32665,7 +32866,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32739,7 +32940,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34108,7 +34309,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.866055787629698</v>
+        <v>13.32758388357364</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34149,7 +34350,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>8.8307279935129301</v>
+        <v>8.4877970988377331</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34214,7 +34415,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.3954169015305897</v>
+        <v>8.0693907991154656</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34279,7 +34480,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1179234</v>
+        <v>1133439.8399999999</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34344,7 +34545,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>1110960</v>
+        <v>1065165.8399999999</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34385,7 +34586,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>8.3412920082890345</v>
+        <v>7.997461032525452</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34426,7 +34627,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>11.183410509361789</v>
+        <v>10.722426414334606</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34573,7 +34774,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>20.462155127537741</v>
+        <v>19.667531494013531</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34614,7 +34815,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>19.261744043110316</v>
+        <v>18.467768212667057</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34655,7 +34856,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>4.8870707594930271E-2</v>
+        <v>5.0845221745514084E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34696,7 +34897,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.2118561710398446E-2</v>
+        <v>7.5032354606487106E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34737,7 +34938,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>5.4907677356656954E-4</v>
+        <v>5.7126102078783477E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34778,7 +34979,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>5.5120527393206099E-4</v>
+        <v>5.73475518559503E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34819,7 +35020,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.0684902233144566E-3</v>
+        <v>1.1116602359768828E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35366,7 +35567,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>5.7896905957596202E-2</v>
+        <v>6.0236103929433085E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37325,18 +37526,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="136" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>232</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{2D2E2E7A-1782-2E45-B2AF-6B92CD26F498}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{75461525-E62C-A846-8E25-6C7CD29F3D0E}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{16661906-4EE6-6C4F-BF37-F970A41507A5}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{83CB84D2-B751-C248-AB8A-2C5C6BF156DB}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{65D9E256-408A-9B48-8BD4-251AFFF46CCE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -37360,15 +37600,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="246" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="242"/>
-      <c r="E4" s="242" t="s">
+      <c r="C4" s="246"/>
+      <c r="E4" s="246" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -37376,7 +37616,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37392,7 +37632,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1179234</v>
+        <v>1133439.8399999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37412,7 +37652,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1110960</v>
+        <v>1065165.8399999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37432,7 +37672,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>13.866055787629698</v>
+        <v>13.32758388357364</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37452,7 +37692,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>8.8307279935129301</v>
+        <v>8.4877970988377331</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37472,7 +37712,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>8.3954169015305897</v>
+        <v>8.0693907991154656</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37492,7 +37732,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>8.3412920082890345</v>
+        <v>7.997461032525452</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37501,18 +37741,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>11.183410509361789</v>
+        <v>10.722426414334606</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="246" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="242"/>
-      <c r="E15" s="242" t="s">
+      <c r="C15" s="246"/>
+      <c r="E15" s="246" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="242"/>
+      <c r="F15" s="246"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37563,14 +37803,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="242" t="s">
+      <c r="B21" s="246" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="242"/>
-      <c r="E21" s="242" t="s">
+      <c r="C21" s="246"/>
+      <c r="E21" s="246" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="242"/>
+      <c r="F21" s="246"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37639,14 +37879,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="242" t="s">
+      <c r="B29" s="246" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="242"/>
-      <c r="E29" s="242" t="s">
+      <c r="C29" s="246"/>
+      <c r="E29" s="246" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="242"/>
+      <c r="F29" s="246"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37722,14 +37962,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="246" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="242"/>
-      <c r="E37" s="242" t="s">
+      <c r="C37" s="246"/>
+      <c r="E37" s="246" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="242"/>
+      <c r="F37" s="246"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37737,7 +37977,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.2118561710398446E-2</v>
+        <v>7.5032354606487106E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -37753,7 +37993,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>4.8870707594930271E-2</v>
+        <v>5.0845221745514084E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -37769,7 +38009,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>5.4907677356656954E-4</v>
+        <v>5.7126102078783477E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -37785,7 +38025,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.5120527393206099E-4</v>
+        <v>5.73475518559503E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37794,18 +38034,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.0684902233144566E-3</v>
+        <v>1.1116602359768828E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="242" t="s">
+      <c r="B45" s="246" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="242"/>
-      <c r="E45" s="242" t="s">
+      <c r="C45" s="246"/>
+      <c r="E45" s="246" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="242"/>
+      <c r="F45" s="246"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37838,18 +38078,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>5.7896905957596202E-2</v>
+        <v>6.0236103929433085E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="246" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="242"/>
-      <c r="E51" s="242" t="s">
+      <c r="C51" s="246"/>
+      <c r="E51" s="246" t="s">
         <v>303</v>
       </c>
-      <c r="F51" s="242"/>
+      <c r="F51" s="246"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -38017,7 +38257,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>1029</v>
+        <v>989.04</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38046,7 +38286,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1179234</v>
+        <v>1133439.8399999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38075,7 +38315,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1110960</v>
+        <v>1065165.8399999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38104,7 +38344,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>13.866055787629698</v>
+        <v>13.32758388357364</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38133,7 +38373,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>8.8307279935129301</v>
+        <v>8.4877970988377331</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38162,7 +38402,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>8.3954169015305897</v>
+        <v>8.0693907991154656</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38191,7 +38431,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>8.3412920082890345</v>
+        <v>7.997461032525452</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38220,7 +38460,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>11.183410509361789</v>
+        <v>10.722426414334606</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38993,7 +39233,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.2118561710398446E-2</v>
+        <v>7.5032354606487106E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39022,7 +39262,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>4.8870707594930271E-2</v>
+        <v>5.0845221745514084E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39051,7 +39291,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>5.4907677356656954E-4</v>
+        <v>5.7126102078783477E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39080,7 +39320,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.5120527393206099E-4</v>
+        <v>5.73475518559503E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39109,7 +39349,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.0684902233144566E-3</v>
+        <v>1.1116602359768828E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39345,7 +39585,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>5.7896905957596202E-2</v>
+        <v>6.0236103929433085E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39951,14 +40191,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="249" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="250"/>
+      <c r="F3" s="251" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="250"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40025,19 +40265,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="247">
         <f>Statement!AA89</f>
         <v>0.30810980316480124</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.7926646045072911</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -40064,19 +40304,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="247">
         <f>Statement!AA90</f>
         <v>0.1221875</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14710110206037375</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -40103,19 +40343,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="247">
         <f>Statement!AA91</f>
         <v>0.3420527156549521</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3088642659279781</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -40142,19 +40382,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="247">
         <f>Statement!AA95</f>
         <v>0.89643268124280784</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3542857142857143</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -40181,19 +40421,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="247">
         <f>Statement!AA96</f>
         <v>0.3131340416591632</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>10.973453749315818</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -40220,19 +40460,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="247">
         <f>Statement!AA98</f>
         <v>0.33487943915306445</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>10.777881911902531</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -40259,22 +40499,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.7467248908296944E-3</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.4146772767462422E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -40301,22 +40541,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.33238751520064835</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>10.614840989399292</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40365,22 +40605,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.26950331971399388</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.79326359455316076</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40408,22 +40648,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.41828422005430954</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.2519961673586713</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40451,22 +40691,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.92432432432432432</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.55458515283842791</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -40494,22 +40734,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="246">
+      <c r="C32" s="247">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.18258406565473165</v>
       </c>
-      <c r="D32" s="247"/>
-      <c r="F32" s="246">
+      <c r="D32" s="248"/>
+      <c r="F32" s="247">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>2.5841954655513977</v>
       </c>
-      <c r="G32" s="247"/>
+      <c r="G32" s="248"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -40537,22 +40777,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="246">
+      <c r="C34" s="247">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.56213120444290177</v>
       </c>
-      <c r="D34" s="247"/>
-      <c r="F34" s="246">
+      <c r="D34" s="248"/>
+      <c r="F34" s="247">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>10.415345592897907</v>
       </c>
-      <c r="G34" s="247"/>
+      <c r="G34" s="248"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -40580,22 +40820,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="246">
+      <c r="C36" s="247">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.13826924746115787</v>
       </c>
-      <c r="D36" s="247"/>
-      <c r="F36" s="246">
+      <c r="D36" s="248"/>
+      <c r="F36" s="247">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.4877659574468085</v>
       </c>
-      <c r="G36" s="247"/>
+      <c r="G36" s="248"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -40623,25 +40863,49 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="246">
+      <c r="C38" s="247">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.47259387138541215</v>
       </c>
-      <c r="D38" s="247"/>
-      <c r="F38" s="246">
+      <c r="D38" s="248"/>
+      <c r="F38" s="247">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.7587168758716878</v>
       </c>
-      <c r="G38" s="247"/>
+      <c r="G38" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40650,30 +40914,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A5949C-B52F-7144-8809-17531A694A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029379A9-4E5D-FD49-9D3C-929F0065A458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2455,12 +2455,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2468,6 +2462,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2488,14 +2488,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15190,38 +15190,38 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>186.25</v>
-    <v>2.3264999999999998</v>
-    <v>-39.96</v>
-    <v>-3.8834E-2</v>
-    <v>-1.57</v>
-    <v>-1.5870000000000001E-3</v>
+    <v>187.42349999999999</v>
+    <v>2.3397000000000001</v>
+    <v>17.11</v>
+    <v>1.8716999999999998E-2</v>
+    <v>-3.2399</v>
+    <v>-3.4789999999999999E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
-    <v>53000</v>
+    <v>61000</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>1002.67</v>
+    <v>931.65</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46307.86130399297</v>
+    <v>46310.904098147657</v>
     <v>0</v>
-    <v>978.5</v>
-    <v>1117014852720</v>
+    <v>858</v>
+    <v>1053626354520</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>1002.4450000000001</v>
-    <v>13.327400000000001</v>
-    <v>1029</v>
-    <v>989.04</v>
-    <v>987.47</v>
-    <v>1129393000</v>
+    <v>871.57500000000005</v>
+    <v>12.3132</v>
+    <v>914.13</v>
+    <v>931.24</v>
+    <v>928.00009999999997</v>
+    <v>1131423000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>23549395</v>
-    <v>25925396</v>
+    <v>38837183</v>
+    <v>25740926</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15245,17 +15245,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1133439.8399999999</v>
+        <v>1067201.04</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>922.34828108400495</v>
+        <v>922.21183448633883</v>
       </c>
       <c r="K3" s="241" t="s">
         <v>442</v>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>1065165.8399999999</v>
+        <v>998927.04</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>1276.514150508963</v>
+        <v>1276.4127196632564</v>
       </c>
       <c r="K4" s="241" t="s">
         <v>443</v>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16143,7 +16143,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>565.04494238496375</v>
+        <v>564.91311584143534</v>
       </c>
       <c r="K5" s="241" t="s">
         <v>444</v>
@@ -16155,14 +16155,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>987.47</v>
+        <v>928.00009999999997</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>13.32758388357364</v>
+        <v>12.548713111440506</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>1723.0435731224111</v>
+        <v>1722.8992070944962</v>
       </c>
       <c r="K6" s="242" t="s">
         <v>445</v>
@@ -16182,14 +16182,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-39.96</v>
+        <v>17.11</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>8.4877970988377331</v>
+        <v>7.9917659248580959</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>909.3208055717879</v>
+        <v>909.2546814995485</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16206,14 +16206,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.57</v>
+        <v>-3.2399</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>5.0845221745514084E-2</v>
+        <v>5.400107181304846E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>1079.2543505344261</v>
+        <v>1079.1383117170151</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16230,14 +16230,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.8834E-2</v>
+        <v>1.8716999999999998E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>7.5032354606487106E-2</v>
+        <v>7.9689446329625019E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>9.1214056594704065E-2</v>
+        <v>0.15881868446052047</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16254,14 +16254,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.5870000000000001E-3</v>
+        <v>-3.4789999999999999E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>5.73475518559503E-4</v>
+        <v>6.090698712212649E-4</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16277,14 +16277,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>5.7126102078783477E-4</v>
+        <v>6.0671792448777984E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
       </c>
       <c r="I11" s="212">
         <f ca="1">DDM!C26</f>
-        <v>5.156037991858887</v>
+        <v>5.1538488754702723</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>186.25</v>
+        <v>187.42349999999999</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>102</v>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3264999999999998</v>
+        <v>2.3397000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="I13" s="213">
         <f>'Reverse DCF'!C17</f>
-        <v>0.28999999999999998</v>
+        <v>0.28399999999999997</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>25925396</v>
+        <v>25740926</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>6.0236103929433085E-2</v>
+        <v>6.3974825211939451E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="I17" s="239">
         <f ca="1">DCF!C15</f>
-        <v>0.15662260254608118</v>
+        <v>0.15664484639602208</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="I18" s="240">
         <f ca="1">Multiples!C54</f>
-        <v>0.15713249999999998</v>
+        <v>0.15718650000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21616,12 +21616,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21629,6 +21623,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22688,16 +22688,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22819,7 +22819,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1133439.8399999999</v>
+        <v>1067201.04</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22855,7 +22855,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.3264999999999998</v>
+        <v>2.3397000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.5484931550930606E-3</v>
+        <v>4.8294446062237409E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99545150684490691</v>
+        <v>0.9951705553937763</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15713249999999998</v>
+        <v>0.15718650000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22934,7 +22934,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15662260254608118</v>
+        <v>0.15664484639602208</v>
       </c>
     </row>
   </sheetData>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1080265.2044818203</v>
+        <v>1080101.3442596889</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23239,23 +23239,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79515.989617865242</v>
+        <v>79514.46041748322</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>92739.577150519064</v>
+        <v>92736.010168989465</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>113439.78324086327</v>
+        <v>113433.2385638259</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>105398.12391440151</v>
+        <v>105390.01635249994</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>75762.023043731693</v>
+        <v>75754.738291374699</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23274,7 +23274,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>521881.63315488893</v>
+        <v>521752.29852717102</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15662260254608118</v>
+        <v>0.15664484639602208</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>466855.49696738075</v>
+        <v>466828.46379417327</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>521881.63315488893</v>
+        <v>521752.29852717102</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23330,7 +23330,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>988737.13012226974</v>
+        <v>988580.76232134434</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23357,7 +23357,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1057011.1301222697</v>
+        <v>1056854.7623213443</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>922.34828108400495</v>
+        <v>922.21183448633883</v>
       </c>
     </row>
   </sheetData>
@@ -23644,23 +23644,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>79515.989617865242</v>
+        <v>79514.46041748322</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>92739.577150519064</v>
+        <v>92736.010168989465</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>113439.78324086327</v>
+        <v>113433.2385638259</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>105398.12391440151</v>
+        <v>105390.01635249994</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>75762.023043731693</v>
+        <v>75754.738291374699</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24446,7 +24446,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15662260254608118</v>
+        <v>0.15664484639602208</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24472,7 +24472,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1003517.7425596225</v>
+        <v>1003421.2512312934</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24481,7 +24481,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1394611.2164832717</v>
+        <v>1394494.976734092</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>1462885.2164832717</v>
+        <v>1462768.976734092</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>1276.514150508963</v>
+        <v>1276.4127196632564</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15713249999999998</v>
+        <v>0.15718650000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="C58" s="237">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>565.04494238496375</v>
+        <v>564.91311584143534</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24609,7 +24609,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15662260254608118</v>
+        <v>0.15664484639602208</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24635,7 +24635,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1515240.4608746341</v>
+        <v>1515094.7658274942</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1906333.934798283</v>
+        <v>1906168.4913302928</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24671,7 +24671,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1974607.934798283</v>
+        <v>1974442.4913302928</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24689,7 +24689,7 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>1723.0435731224111</v>
+        <v>1722.8992070944962</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15662260254608118</v>
+        <v>0.15664484639602208</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>582714.16926161991</v>
+        <v>582658.13949568395</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24748,7 +24748,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>973807.64318526897</v>
+        <v>973731.86499848252</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>1042081.643185269</v>
+        <v>1042005.8649984825</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24793,22 +24793,22 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>909.3208055717879</v>
+        <v>909.2546814995485</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24858,7 +24858,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>922.34828108400495</v>
+        <v>922.21183448633883</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>1276.514150508963</v>
+        <v>1276.4127196632564</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>565.04494238496375</v>
+        <v>564.91311584143534</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>1723.0435731224111</v>
+        <v>1722.8992070944962</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>909.3208055717879</v>
+        <v>909.2546814995485</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1079.2543505344261</v>
+        <v>1079.1383117170151</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24912,7 +24912,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24921,7 +24921,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>9.1214056594704065E-2</v>
+        <v>0.15881868446052047</v>
       </c>
     </row>
   </sheetData>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15713249999999998</v>
+        <v>0.15718650000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25447,7 +25447,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>5.156037991858887</v>
+        <v>5.1538488754702723</v>
       </c>
     </row>
   </sheetData>
@@ -25636,23 +25636,23 @@
       </c>
       <c r="H7" s="130">
         <f>G7*(1+$C$17)</f>
-        <v>74403.356040473169</v>
+        <v>74057.293919354692</v>
       </c>
       <c r="I7" s="130">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>95980.329292210386</v>
+        <v>95089.565392451434</v>
       </c>
       <c r="J7" s="130">
         <f t="shared" si="0"/>
-        <v>123814.6247869514</v>
+        <v>122095.00196390765</v>
       </c>
       <c r="K7" s="130">
         <f t="shared" si="0"/>
-        <v>159720.86597516731</v>
+        <v>156769.98252165742</v>
       </c>
       <c r="L7" s="130">
         <f t="shared" si="0"/>
-        <v>206039.91710796583</v>
+        <v>201292.65755780812</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -25684,7 +25684,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1419292.2009663745</v>
+        <v>1386380.6954684849</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25738,23 +25738,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>64328.118676471102</v>
+        <v>64027.686761505967</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>71746.196996302941</v>
+        <v>71077.608704120197</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>80019.700394488362</v>
+        <v>78903.779202801816</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>89247.27329524704</v>
+        <v>87591.668965695004</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>99538.935429270074</v>
+        <v>97236.159658160701</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25773,15 +25773,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>685667.30529807927</v>
+        <v>669703.18881527602</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="259" t="s">
+      <c r="B14" s="258" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="260"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25789,7 +25789,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1026.414109911301</v>
+        <v>1006.9212507595746</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25806,22 +25806,22 @@
         <v>324</v>
       </c>
       <c r="C17" s="160">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="E17" s="258" t="s">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="E17" s="260" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="258"/>
-      <c r="G17" s="258"/>
-      <c r="H17" s="258"/>
-      <c r="I17" s="258"/>
+      <c r="F17" s="260"/>
+      <c r="G17" s="260"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="260"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="259" t="s">
+      <c r="B19" s="258" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="260"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25837,7 +25837,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15662260254608118</v>
+        <v>0.15664484639602208</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1116626.1599999999</v>
+        <v>1051369.96</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25882,15 +25882,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>1048352.1599999999</v>
+        <v>983095.96</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="259" t="s">
+      <c r="B28" s="258" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="260"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25898,7 +25898,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>404880.22479177953</v>
+        <v>398836.90329228371</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>685667.30529807927</v>
+        <v>669703.18881527602</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1090547.5300898589</v>
+        <v>1068540.0921075598</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25943,7 +25943,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1158821.5300898589</v>
+        <v>1136814.0921075598</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25961,21 +25961,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1026.414109911301</v>
+        <v>1006.9212507595746</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34309,7 +34309,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.32758388357364</v>
+        <v>12.548713111440506</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34350,7 +34350,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>8.4877970988377331</v>
+        <v>7.9917659248580959</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.0693907991154656</v>
+        <v>7.5978115018283248</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1133439.8399999999</v>
+        <v>1067201.04</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34545,7 +34545,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>1065165.8399999999</v>
+        <v>998927.04</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34586,7 +34586,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>7.997461032525452</v>
+        <v>7.5001279394540052</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34627,7 +34627,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>10.722426414334606</v>
+        <v>10.055637608214214</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34774,7 +34774,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>19.667531494013531</v>
+        <v>18.518150963040085</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34815,7 +34815,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>18.467768212667057</v>
+        <v>17.319324694158045</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34856,7 +34856,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>5.0845221745514084E-2</v>
+        <v>5.400107181304846E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34897,7 +34897,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.5032354606487106E-2</v>
+        <v>7.9689446329625019E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34938,7 +34938,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>5.7126102078783477E-4</v>
+        <v>6.0671792448777984E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34979,7 +34979,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>5.73475518559503E-4</v>
+        <v>6.090698712212649E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -35020,7 +35020,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.1116602359768828E-3</v>
+        <v>1.1806585195981443E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35567,7 +35567,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>6.0236103929433085E-2</v>
+        <v>6.3974825211939451E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37616,7 +37616,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37632,7 +37632,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1133439.8399999999</v>
+        <v>1067201.04</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37652,7 +37652,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1065165.8399999999</v>
+        <v>998927.04</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37672,7 +37672,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>13.32758388357364</v>
+        <v>12.548713111440506</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37692,7 +37692,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>8.4877970988377331</v>
+        <v>7.9917659248580959</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37712,7 +37712,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>8.0693907991154656</v>
+        <v>7.5978115018283248</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.997461032525452</v>
+        <v>7.5001279394540052</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37741,7 +37741,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>10.722426414334606</v>
+        <v>10.055637608214214</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37977,7 +37977,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.5032354606487106E-2</v>
+        <v>7.9689446329625019E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -37993,7 +37993,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>5.0845221745514084E-2</v>
+        <v>5.400107181304846E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -38009,7 +38009,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>5.7126102078783477E-4</v>
+        <v>6.0671792448777984E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -38025,7 +38025,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.73475518559503E-4</v>
+        <v>6.090698712212649E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.1116602359768828E-3</v>
+        <v>1.1806585195981443E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38078,7 +38078,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>6.0236103929433085E-2</v>
+        <v>6.3974825211939451E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38257,7 +38257,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>989.04</v>
+        <v>931.24</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38286,7 +38286,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1133439.8399999999</v>
+        <v>1067201.04</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38315,7 +38315,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>1065165.8399999999</v>
+        <v>998927.04</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38344,7 +38344,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>13.32758388357364</v>
+        <v>12.548713111440506</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>8.4877970988377331</v>
+        <v>7.9917659248580959</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38402,7 +38402,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>8.0693907991154656</v>
+        <v>7.5978115018283248</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38431,7 +38431,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.997461032525452</v>
+        <v>7.5001279394540052</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38460,7 +38460,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>10.722426414334606</v>
+        <v>10.055637608214214</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39233,7 +39233,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.5032354606487106E-2</v>
+        <v>7.9689446329625019E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39262,7 +39262,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>5.0845221745514084E-2</v>
+        <v>5.400107181304846E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39291,7 +39291,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>5.7126102078783477E-4</v>
+        <v>6.0671792448777984E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39320,7 +39320,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.73475518559503E-4</v>
+        <v>6.090698712212649E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.1116602359768828E-3</v>
+        <v>1.1806585195981443E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39585,7 +39585,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>6.0236103929433085E-2</v>
+        <v>6.3974825211939451E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40191,14 +40191,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="247" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="248"/>
+      <c r="F3" s="249" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="248"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40265,19 +40265,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="250">
         <f>Statement!AA89</f>
         <v>0.30810980316480124</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.7926646045072911</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -40304,19 +40304,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="250">
         <f>Statement!AA90</f>
         <v>0.1221875</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14710110206037375</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -40343,19 +40343,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="250">
         <f>Statement!AA91</f>
         <v>0.3420527156549521</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3088642659279781</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -40382,19 +40382,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="250">
         <f>Statement!AA95</f>
         <v>0.89643268124280784</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3542857142857143</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -40421,19 +40421,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="250">
         <f>Statement!AA96</f>
         <v>0.3131340416591632</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>10.973453749315818</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -40460,19 +40460,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="250">
         <f>Statement!AA98</f>
         <v>0.33487943915306445</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>10.777881911902531</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -40499,22 +40499,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.7467248908296944E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.4146772767462422E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -40541,22 +40541,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.33238751520064835</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>10.614840989399292</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40605,22 +40605,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.26950331971399388</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.79326359455316076</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40648,22 +40648,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.41828422005430954</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.2519961673586713</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="251"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40691,22 +40691,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="250">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.92432432432432432</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="251"/>
+      <c r="F29" s="250">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.55458515283842791</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="251"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -40734,22 +40734,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="247">
+      <c r="C32" s="250">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.18258406565473165</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="F32" s="247">
+      <c r="D32" s="251"/>
+      <c r="F32" s="250">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>2.5841954655513977</v>
       </c>
-      <c r="G32" s="248"/>
+      <c r="G32" s="251"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -40777,22 +40777,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="247">
+      <c r="C34" s="250">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.56213120444290177</v>
       </c>
-      <c r="D34" s="248"/>
-      <c r="F34" s="247">
+      <c r="D34" s="251"/>
+      <c r="F34" s="250">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>10.415345592897907</v>
       </c>
-      <c r="G34" s="248"/>
+      <c r="G34" s="251"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -40820,22 +40820,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="247">
+      <c r="C36" s="250">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.13826924746115787</v>
       </c>
-      <c r="D36" s="248"/>
-      <c r="F36" s="247">
+      <c r="D36" s="251"/>
+      <c r="F36" s="250">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.4877659574468085</v>
       </c>
-      <c r="G36" s="248"/>
+      <c r="G36" s="251"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -40863,49 +40863,25 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="247">
+      <c r="C38" s="250">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.47259387138541215</v>
       </c>
-      <c r="D38" s="248"/>
-      <c r="F38" s="247">
+      <c r="D38" s="251"/>
+      <c r="F38" s="250">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.7587168758716878</v>
       </c>
-      <c r="G38" s="248"/>
+      <c r="G38" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40914,6 +40890,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029379A9-4E5D-FD49-9D3C-929F0065A458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2024085D-4C6B-8444-A549-084DF7E60DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,19 +161,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="448">
   <si>
     <t>Ticker</t>
   </si>
@@ -1493,6 +1523,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2117,7 +2150,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2455,6 +2488,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2462,12 +2501,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2488,15 +2521,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -15172,7 +15208,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15190,12 +15226,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>187.42349999999999</v>
-    <v>2.3397000000000001</v>
-    <v>17.11</v>
-    <v>1.8716999999999998E-2</v>
-    <v>-3.2399</v>
-    <v>-3.4789999999999999E-3</v>
+    <v>192.4</v>
+    <v>2.3460000000000001</v>
+    <v>5.18</v>
+    <v>5.7239999999999999E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>61000</v>
@@ -15203,35 +15237,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>931.65</v>
+    <v>918.89</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46310.904098147657</v>
+    <v>46315.718867510936</v>
     <v>0</v>
-    <v>858</v>
-    <v>1053626354520</v>
+    <v>881.52</v>
+    <v>1029685443840</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>871.57500000000005</v>
-    <v>12.3132</v>
-    <v>914.13</v>
-    <v>931.24</v>
-    <v>928.00009999999997</v>
+    <v>885</v>
+    <v>12.258699999999999</v>
+    <v>904.9</v>
+    <v>910.08</v>
     <v>1131423000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>38837183</v>
-    <v>25740926</v>
+    <v>12708528</v>
+    <v>26550431</v>
     <v>1984</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15245,28 +15293,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>51.77</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15288,8 +15336,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15310,7 +15356,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15320,6 +15365,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15355,7 +15405,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15366,16 +15416,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15469,19 +15516,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15553,9 +15594,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15563,9 +15601,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16043,7 +16078,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -16081,7 +16116,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1067201.04</v>
+        <v>1042951.6800000001</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16089,7 +16124,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>922.21183448633883</v>
+        <v>923.85708759013744</v>
       </c>
       <c r="K3" s="241" t="s">
         <v>442</v>
@@ -16108,7 +16143,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>998927.04</v>
+        <v>974677.68</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16116,7 +16151,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>1276.4127196632564</v>
+        <v>1277.6344465261868</v>
       </c>
       <c r="K4" s="241" t="s">
         <v>443</v>
@@ -16128,7 +16163,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16143,7 +16178,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>564.91311584143534</v>
+        <v>565.53962081310044</v>
       </c>
       <c r="K5" s="241" t="s">
         <v>444</v>
@@ -16153,16 +16188,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>928.00009999999997</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>12.548713111440506</v>
+        <v>12.263576337420831</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16170,7 +16205,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>1722.8992070944962</v>
+        <v>1724.6381029326601</v>
       </c>
       <c r="K6" s="242" t="s">
         <v>445</v>
@@ -16182,14 +16217,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>17.11</v>
+        <v>5.18</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>7.9917659248580959</v>
+        <v>7.8101738895395991</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -16197,23 +16232,23 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>909.2546814995485</v>
+        <v>910.05112618330634</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-3.2399</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>5.400107181304846E-2</v>
+        <v>5.5256634708139116E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -16221,7 +16256,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>1079.1383117170151</v>
+        <v>1080.3440768090782</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16230,14 +16265,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.8716999999999998E-2</v>
+        <v>5.7239999999999999E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>7.9689446329625019E-2</v>
+        <v>8.1542281997187063E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16245,23 +16280,23 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.15881868446052047</v>
+        <v>0.18708693390589631</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.4789999999999999E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>6.090698712212649E-4</v>
+        <v>6.2323117404633737E-4</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16277,14 +16312,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>6.0671792448777984E-4</v>
+        <v>6.2082454289732775E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
       </c>
       <c r="I11" s="212">
         <f ca="1">DDM!C26</f>
-        <v>5.1538488754702723</v>
+        <v>5.1642637674308656</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -16293,7 +16328,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>187.42349999999999</v>
+        <v>192.4</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>102</v>
@@ -16309,7 +16344,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3397000000000001</v>
+        <v>2.3460000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16318,10 +16353,10 @@
         <f>Statement!AC125</f>
         <v>0.61403546806573295</v>
       </c>
-      <c r="H13" s="184" t="s">
+      <c r="H13" s="263" t="s">
         <v>431</v>
       </c>
-      <c r="I13" s="213">
+      <c r="I13" s="261">
         <f>'Reverse DCF'!C17</f>
         <v>0.28399999999999997</v>
       </c>
@@ -16332,7 +16367,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>25740926</v>
+        <v>26550431</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16341,6 +16376,13 @@
         <f>Statement!AC140</f>
         <v>1.2071781950589597</v>
       </c>
+      <c r="H14" s="186" t="s">
+        <v>447</v>
+      </c>
+      <c r="I14" s="262">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>1008.957186410955</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="185" t="s">
@@ -16348,7 +16390,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>6.3974825211939451E-2</v>
+        <v>6.5462284887445599E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16381,7 +16423,7 @@
       </c>
       <c r="I17" s="239">
         <f ca="1">DCF!C15</f>
-        <v>0.15664484639602208</v>
+        <v>0.15637708220925278</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16403,7 +16445,7 @@
       </c>
       <c r="I18" s="240">
         <f ca="1">Multiples!C54</f>
-        <v>0.15718650000000001</v>
+        <v>0.15693000000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16471,12 +16513,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16491,7 +16533,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21616,6 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21623,12 +21671,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22688,16 +22730,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22819,7 +22861,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22828,7 +22870,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1067201.04</v>
+        <v>1042951.6800000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22846,7 +22888,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22855,7 +22897,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.3397000000000001</v>
+        <v>2.3460000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22898,7 +22940,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.8294446062237409E-3</v>
+        <v>4.941177754667004E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22907,7 +22949,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9951705553937763</v>
+        <v>0.99505882224533304</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22925,7 +22967,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15718650000000001</v>
+        <v>0.15693000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22934,7 +22976,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15664484639602208</v>
+        <v>0.15637708220925278</v>
       </c>
     </row>
   </sheetData>
@@ -23185,7 +23227,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1080101.3442596889</v>
+        <v>1082077.148488801</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23239,23 +23281,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79514.46041748322</v>
+        <v>79532.872339647423</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>92736.010168989465</v>
+        <v>92778.962001288761</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>113433.2385638259</v>
+        <v>113512.0547034003</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>105390.01635249994</v>
+        <v>105487.66434484777</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>75754.738291374699</v>
+        <v>75842.485628582188</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23274,7 +23316,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>521752.29852717102</v>
+        <v>523312.18336053105</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23297,7 +23339,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664484639602208</v>
+        <v>0.15637708220925278</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23312,7 +23354,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>466828.46379417327</v>
+        <v>467154.03901776648</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23321,7 +23363,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>521752.29852717102</v>
+        <v>523312.18336053105</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23330,7 +23372,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>988580.76232134434</v>
+        <v>990466.22237829748</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23357,7 +23399,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1056854.7623213443</v>
+        <v>1058740.2223782975</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23375,7 +23417,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>922.21183448633883</v>
+        <v>923.85708759013744</v>
       </c>
     </row>
   </sheetData>
@@ -23644,23 +23686,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>79514.46041748322</v>
+        <v>79532.872339647423</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>92736.010168989465</v>
+        <v>92778.962001288761</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>113433.2385638259</v>
+        <v>113512.0547034003</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>105390.01635249994</v>
+        <v>105487.66434484777</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>75754.738291374699</v>
+        <v>75842.485628582188</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24446,7 +24488,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664484639602208</v>
+        <v>0.15637708220925278</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24472,7 +24514,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1003421.2512312934</v>
+        <v>1004583.5223298258</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24481,7 +24523,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1394494.976734092</v>
+        <v>1395895.0757190101</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24508,7 +24550,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>1462768.976734092</v>
+        <v>1464169.0757190101</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24526,7 +24568,7 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>1276.4127196632564</v>
+        <v>1277.6344465261868</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24550,7 +24592,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15718650000000001</v>
+        <v>0.15693000000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24585,7 +24627,7 @@
       </c>
       <c r="C58" s="237">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>564.91311584143534</v>
+        <v>565.53962081310044</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24609,7 +24651,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664484639602208</v>
+        <v>0.15637708220925278</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24635,7 +24677,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1515094.7658274942</v>
+        <v>1516849.712571644</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24644,7 +24686,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1906168.4913302928</v>
+        <v>1908161.2659608284</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24671,7 +24713,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1974442.4913302928</v>
+        <v>1976435.2659608284</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24689,7 +24731,7 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>1722.8992070944962</v>
+        <v>1724.6381029326601</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24713,7 +24755,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664484639602208</v>
+        <v>0.15637708220925278</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24739,7 +24781,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>582658.13949568395</v>
+        <v>583333.03721688478</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24748,7 +24790,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>973731.86499848252</v>
+        <v>974644.59060606908</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24775,7 +24817,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>1042005.8649984825</v>
+        <v>1042918.5906060691</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24793,22 +24835,22 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>909.2546814995485</v>
+        <v>910.05112618330634</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24858,7 +24900,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>922.21183448633883</v>
+        <v>923.85708759013744</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24867,7 +24909,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>1276.4127196632564</v>
+        <v>1277.6344465261868</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24876,7 +24918,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>564.91311584143534</v>
+        <v>565.53962081310044</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24885,7 +24927,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>1722.8992070944962</v>
+        <v>1724.6381029326601</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24894,7 +24936,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>909.2546814995485</v>
+        <v>910.05112618330634</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24903,7 +24945,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1079.1383117170151</v>
+        <v>1080.3440768090782</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24912,7 +24954,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24921,7 +24963,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.15881868446052047</v>
+        <v>0.18708693390589631</v>
       </c>
     </row>
   </sheetData>
@@ -25430,7 +25472,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15718650000000001</v>
+        <v>0.15693000000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25447,7 +25489,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>5.1538488754702723</v>
+        <v>5.1642637674308656</v>
       </c>
     </row>
   </sheetData>
@@ -25684,7 +25726,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1386380.6954684849</v>
+        <v>1388916.7693802745</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25738,23 +25780,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>64027.686761505967</v>
+        <v>64042.512653284859</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>71077.608704120197</v>
+        <v>71110.529179388992</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>78903.779202801816</v>
+        <v>78958.60344438508</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>87591.668965695004</v>
+        <v>87672.826089651484</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>97236.159658160701</v>
+        <v>97348.789102638068</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25773,15 +25815,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>669703.18881527602</v>
+        <v>671705.40298861975</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="259" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="260"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25789,7 +25831,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25798,7 +25840,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1006.9212507595746</v>
+        <v>1008.957186410955</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25808,20 +25850,20 @@
       <c r="C17" s="160">
         <v>0.28399999999999997</v>
       </c>
-      <c r="E17" s="260" t="s">
+      <c r="E17" s="258" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="259" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="260"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25837,7 +25879,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15664484639602208</v>
+        <v>0.15637708220925278</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25855,7 +25897,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1051369.96</v>
+        <v>1027480.3200000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25882,15 +25924,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>983095.96</v>
+        <v>959206.32000000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="259" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="260"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25898,7 +25940,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>398836.90329228371</v>
+        <v>399133.26046934852</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25907,7 +25949,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>669703.18881527602</v>
+        <v>671705.40298861975</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25916,7 +25958,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1068540.0921075598</v>
+        <v>1070838.6634579683</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25943,7 +25985,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1136814.0921075598</v>
+        <v>1139112.6634579683</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25961,21 +26003,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1006.9212507595746</v>
+        <v>1008.957186410955</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32866,7 +32908,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32940,7 +32982,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34309,7 +34351,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>12.548713111440506</v>
+        <v>12.263576337420831</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34350,7 +34392,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.9917659248580959</v>
+        <v>7.8101738895395991</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34415,7 +34457,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.5978115018283248</v>
+        <v>7.4251710532020985</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34480,7 +34522,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1067201.04</v>
+        <v>1042951.6800000001</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34545,7 +34587,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>998927.04</v>
+        <v>974677.68</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34586,7 +34628,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>7.5001279394540052</v>
+        <v>7.3180592846202366</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34627,7 +34669,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>10.055637608214214</v>
+        <v>9.8115329172538761</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34774,7 +34816,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>18.518150963040085</v>
+        <v>18.097374284226966</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34815,7 +34857,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>17.319324694158045</v>
+        <v>16.898891046205609</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34856,7 +34898,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>5.400107181304846E-2</v>
+        <v>5.5256634708139116E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34897,7 +34939,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.9689446329625019E-2</v>
+        <v>8.1542281997187063E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34938,7 +34980,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>6.0671792448777984E-4</v>
+        <v>6.2082454289732775E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34979,7 +35021,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>6.090698712212649E-4</v>
+        <v>6.2323117404633737E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -35020,7 +35062,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.1806585195981443E-3</v>
+        <v>1.2081096604590539E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35567,7 +35609,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>6.3974825211939451E-2</v>
+        <v>6.5462284887445599E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37616,7 +37658,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37632,7 +37674,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1067201.04</v>
+        <v>1042951.6800000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37652,7 +37694,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>998927.04</v>
+        <v>974677.68</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37672,7 +37714,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.548713111440506</v>
+        <v>12.263576337420831</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37692,7 +37734,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.9917659248580959</v>
+        <v>7.8101738895395991</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37712,7 +37754,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.5978115018283248</v>
+        <v>7.4251710532020985</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37732,7 +37774,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.5001279394540052</v>
+        <v>7.3180592846202366</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37741,7 +37783,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>10.055637608214214</v>
+        <v>9.8115329172538761</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37977,7 +38019,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.9689446329625019E-2</v>
+        <v>8.1542281997187063E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -37993,7 +38035,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>5.400107181304846E-2</v>
+        <v>5.5256634708139116E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -38009,7 +38051,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.0671792448777984E-4</v>
+        <v>6.2082454289732775E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -38025,7 +38067,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.090698712212649E-4</v>
+        <v>6.2323117404633737E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38034,7 +38076,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.1806585195981443E-3</v>
+        <v>1.2081096604590539E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38078,7 +38120,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>6.3974825211939451E-2</v>
+        <v>6.5462284887445599E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38257,7 +38299,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>931.24</v>
+        <v>910.08</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38286,7 +38328,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1067201.04</v>
+        <v>1042951.6800000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38315,7 +38357,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>998927.04</v>
+        <v>974677.68</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38344,7 +38386,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.548713111440506</v>
+        <v>12.263576337420831</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38373,7 +38415,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.9917659248580959</v>
+        <v>7.8101738895395991</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38402,7 +38444,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.5978115018283248</v>
+        <v>7.4251710532020985</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38431,7 +38473,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.5001279394540052</v>
+        <v>7.3180592846202366</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38460,7 +38502,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>10.055637608214214</v>
+        <v>9.8115329172538761</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39233,7 +39275,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.9689446329625019E-2</v>
+        <v>8.1542281997187063E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39262,7 +39304,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>5.400107181304846E-2</v>
+        <v>5.5256634708139116E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39291,7 +39333,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.0671792448777984E-4</v>
+        <v>6.2082454289732775E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39320,7 +39362,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.090698712212649E-4</v>
+        <v>6.2323117404633737E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39349,7 +39391,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.1806585195981443E-3</v>
+        <v>1.2081096604590539E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39585,7 +39627,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>6.3974825211939451E-2</v>
+        <v>6.5462284887445599E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40191,14 +40233,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="249" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="F3" s="249" t="s">
+      <c r="D3" s="250"/>
+      <c r="F3" s="251" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="248"/>
+      <c r="G3" s="250"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40265,19 +40307,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="247">
         <f>Statement!AA89</f>
         <v>0.30810980316480124</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.7926646045072911</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -40304,19 +40346,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="247">
         <f>Statement!AA90</f>
         <v>0.1221875</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14710110206037375</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -40343,19 +40385,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="247">
         <f>Statement!AA91</f>
         <v>0.3420527156549521</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3088642659279781</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -40382,19 +40424,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="247">
         <f>Statement!AA95</f>
         <v>0.89643268124280784</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3542857142857143</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -40421,19 +40463,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="247">
         <f>Statement!AA96</f>
         <v>0.3131340416591632</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>10.973453749315818</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -40460,19 +40502,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="247">
         <f>Statement!AA98</f>
         <v>0.33487943915306445</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>10.777881911902531</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -40499,22 +40541,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.7467248908296944E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.4146772767462422E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -40541,22 +40583,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.33238751520064835</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>10.614840989399292</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40605,22 +40647,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.26950331971399388</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.79326359455316076</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40648,22 +40690,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.41828422005430954</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.2519961673586713</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40691,22 +40733,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="250">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.92432432432432432</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="F29" s="250">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.55458515283842791</v>
       </c>
-      <c r="G29" s="251"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -40734,22 +40776,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="250">
+      <c r="C32" s="247">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.18258406565473165</v>
       </c>
-      <c r="D32" s="251"/>
-      <c r="F32" s="250">
+      <c r="D32" s="248"/>
+      <c r="F32" s="247">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>2.5841954655513977</v>
       </c>
-      <c r="G32" s="251"/>
+      <c r="G32" s="248"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -40777,22 +40819,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="250">
+      <c r="C34" s="247">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.56213120444290177</v>
       </c>
-      <c r="D34" s="251"/>
-      <c r="F34" s="250">
+      <c r="D34" s="248"/>
+      <c r="F34" s="247">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>10.415345592897907</v>
       </c>
-      <c r="G34" s="251"/>
+      <c r="G34" s="248"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -40820,22 +40862,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="250">
+      <c r="C36" s="247">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.13826924746115787</v>
       </c>
-      <c r="D36" s="251"/>
-      <c r="F36" s="250">
+      <c r="D36" s="248"/>
+      <c r="F36" s="247">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.4877659574468085</v>
       </c>
-      <c r="G36" s="251"/>
+      <c r="G36" s="248"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -40863,25 +40905,49 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="250">
+      <c r="C38" s="247">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.47259387138541215</v>
       </c>
-      <c r="D38" s="251"/>
-      <c r="F38" s="250">
+      <c r="D38" s="248"/>
+      <c r="F38" s="247">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.7587168758716878</v>
       </c>
-      <c r="G38" s="251"/>
+      <c r="G38" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40890,30 +40956,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2024085D-4C6B-8444-A549-084DF7E60DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D11A53-1D0A-8745-9820-12DECA141707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2476,6 +2446,9 @@
     <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2530,9 +2503,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -15208,7 +15178,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15226,10 +15196,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1255</v>
-    <v>192.4</v>
-    <v>2.3460000000000001</v>
-    <v>5.18</v>
-    <v>5.7239999999999999E-3</v>
+    <v>192.59</v>
+    <v>2.3546999999999998</v>
+    <v>21.06</v>
+    <v>2.4589E-2</v>
+    <v>-2.96</v>
+    <v>-3.3729999999999997E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>61000</v>
@@ -15237,49 +15209,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>918.89</v>
+    <v>891.89</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46315.718867510936</v>
+    <v>46318.955657615625</v>
     <v>0</v>
-    <v>881.52</v>
-    <v>1029685443840</v>
+    <v>858.34</v>
+    <v>992880253650</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>885</v>
-    <v>12.258699999999999</v>
-    <v>904.9</v>
-    <v>910.08</v>
+    <v>862.29</v>
+    <v>11.820499999999999</v>
+    <v>856.49</v>
+    <v>877.55</v>
+    <v>874.59</v>
     <v>1131423000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>12708528</v>
-    <v>26550431</v>
+    <v>21198510</v>
+    <v>26981467</v>
     <v>1984</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15293,28 +15251,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>6</v>
-    <v>50.9</v>
+    <v>3</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15336,6 +15294,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15356,6 +15316,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15365,11 +15326,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15405,7 +15361,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15416,13 +15372,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15516,13 +15475,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15594,6 +15559,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15601,6 +15569,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16087,18 +16058,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="E2" s="243" t="s">
+      <c r="C2" s="247"/>
+      <c r="E2" s="246" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="247"/>
+      <c r="H2" s="246" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="244"/>
+      <c r="I2" s="247"/>
       <c r="K2" s="136" t="s">
         <v>441</v>
       </c>
@@ -16116,7 +16087,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1042951.6800000001</v>
+        <v>1005672.2999999999</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16124,7 +16095,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>923.85708759013744</v>
+        <v>932.88157967910399</v>
       </c>
       <c r="K3" s="241" t="s">
         <v>442</v>
@@ -16143,7 +16114,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>974677.68</v>
+        <v>937398.29999999993</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16151,7 +16122,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>1277.6344465261868</v>
+        <v>1284.2853119480187</v>
       </c>
       <c r="K4" s="241" t="s">
         <v>443</v>
@@ -16163,7 +16134,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16178,7 +16149,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>565.53962081310044</v>
+        <v>569.06866811448378</v>
       </c>
       <c r="K5" s="241" t="s">
         <v>444</v>
@@ -16188,16 +16159,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>874.59</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>12.263576337420831</v>
+        <v>11.825225710820643</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16205,7 +16176,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>1724.6381029326601</v>
+        <v>1734.1050296500732</v>
       </c>
       <c r="K6" s="242" t="s">
         <v>445</v>
@@ -16217,14 +16188,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.18</v>
+        <v>21.06</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>7.8101738895395991</v>
+        <v>7.5310061717271823</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -16232,23 +16203,23 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>910.05112618330634</v>
+        <v>914.38626745728595</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-2.96</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>5.5256634708139116E-2</v>
+        <v>5.730494913701014E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -16256,7 +16227,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>1080.3440768090782</v>
+        <v>1086.9453713697931</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16265,14 +16236,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>5.7239999999999999E-3</v>
+        <v>2.4589E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>8.1542281997187063E-2</v>
+        <v>8.4564982052304727E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16280,23 +16251,23 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.18708693390589631</v>
+        <v>0.2386136076232615</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-3.3729999999999997E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>6.2323117404633737E-4</v>
+        <v>6.4633380078182531E-4</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16312,14 +16283,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>6.2082454289732775E-4</v>
+        <v>6.4383795795111402E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
       </c>
       <c r="I11" s="212">
         <f ca="1">DDM!C26</f>
-        <v>5.1642637674308656</v>
+        <v>5.2234613499719087</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -16328,7 +16299,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>192.4</v>
+        <v>192.59</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>102</v>
@@ -16344,7 +16315,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3460000000000001</v>
+        <v>2.3546999999999998</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16353,12 +16324,12 @@
         <f>Statement!AC125</f>
         <v>0.61403546806573295</v>
       </c>
-      <c r="H13" s="263" t="s">
+      <c r="H13" s="245" t="s">
         <v>431</v>
       </c>
-      <c r="I13" s="261">
+      <c r="I13" s="243">
         <f>'Reverse DCF'!C17</f>
-        <v>0.28399999999999997</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -16367,7 +16338,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>26550431</v>
+        <v>26981467</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16379,9 +16350,9 @@
       <c r="H14" s="186" t="s">
         <v>447</v>
       </c>
-      <c r="I14" s="262">
+      <c r="I14" s="244">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>1008.957186410955</v>
+        <v>886.16737391155391</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16390,7 +16361,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>6.5462284887445599E-2</v>
+        <v>6.7888913714735905E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16401,16 +16372,16 @@
         <f>Statement!AC175</f>
         <v>60.472984942426926</v>
       </c>
-      <c r="H16" s="243" t="s">
+      <c r="H16" s="246" t="s">
         <v>439</v>
       </c>
-      <c r="I16" s="244"/>
+      <c r="I16" s="247"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="245" t="s">
+      <c r="B17" s="248" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="245"/>
+      <c r="C17" s="248"/>
       <c r="E17" s="184" t="s">
         <v>296</v>
       </c>
@@ -16423,7 +16394,7 @@
       </c>
       <c r="I17" s="239">
         <f ca="1">DCF!C15</f>
-        <v>0.15637708220925278</v>
+        <v>0.15492556106466895</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16445,7 +16416,7 @@
       </c>
       <c r="I18" s="240">
         <f ca="1">Multiples!C54</f>
-        <v>0.15693000000000001</v>
+        <v>0.1554915</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16497,14 +16468,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="248" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="E25" s="243" t="s">
+      <c r="C25" s="248"/>
+      <c r="E25" s="246" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="244"/>
+      <c r="F25" s="247"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -16513,12 +16484,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16533,7 +16504,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16965,36 +16936,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="246" t="s">
+      <c r="S2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -17005,32 +16976,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="253" t="s">
+      <c r="S4" s="256" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
-      <c r="AA4" s="254"/>
-      <c r="AB4" s="254"/>
-      <c r="AC4" s="254"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
+      <c r="AA4" s="257"/>
+      <c r="AB4" s="257"/>
+      <c r="AC4" s="257"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17623,33 +17594,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="252" t="s">
+      <c r="C12" s="255" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="252"/>
-      <c r="E12" s="252"/>
-      <c r="F12" s="252"/>
-      <c r="G12" s="252"/>
-      <c r="H12" s="252"/>
-      <c r="I12" s="252"/>
-      <c r="J12" s="252"/>
-      <c r="K12" s="252"/>
-      <c r="L12" s="252"/>
+      <c r="D12" s="255"/>
+      <c r="E12" s="255"/>
+      <c r="F12" s="255"/>
+      <c r="G12" s="255"/>
+      <c r="H12" s="255"/>
+      <c r="I12" s="255"/>
+      <c r="J12" s="255"/>
+      <c r="K12" s="255"/>
+      <c r="L12" s="255"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="253" t="s">
+      <c r="S12" s="256" t="s">
         <v>122</v>
       </c>
-      <c r="T12" s="254"/>
-      <c r="U12" s="254"/>
-      <c r="V12" s="254"/>
-      <c r="W12" s="254"/>
-      <c r="X12" s="254"/>
-      <c r="Y12" s="254"/>
-      <c r="Z12" s="254"/>
-      <c r="AA12" s="254"/>
-      <c r="AB12" s="254"/>
-      <c r="AC12" s="254"/>
+      <c r="T12" s="257"/>
+      <c r="U12" s="257"/>
+      <c r="V12" s="257"/>
+      <c r="W12" s="257"/>
+      <c r="X12" s="257"/>
+      <c r="Y12" s="257"/>
+      <c r="Z12" s="257"/>
+      <c r="AA12" s="257"/>
+      <c r="AB12" s="257"/>
+      <c r="AC12" s="257"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -18194,35 +18165,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="P2" s="246" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="246"/>
-      <c r="R2" s="246"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -18231,31 +18202,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="P4" s="254" t="s">
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="P4" s="257" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="254"/>
-      <c r="R4" s="254"/>
-      <c r="S4" s="254"/>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
+      <c r="Q4" s="257"/>
+      <c r="R4" s="257"/>
+      <c r="S4" s="257"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -18450,32 +18421,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="252" t="s">
+      <c r="C9" s="255" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="254" t="s">
+      <c r="P9" s="257" t="s">
         <v>126</v>
       </c>
-      <c r="Q9" s="254"/>
-      <c r="R9" s="254"/>
-      <c r="S9" s="254"/>
-      <c r="T9" s="254"/>
-      <c r="U9" s="254"/>
-      <c r="V9" s="254"/>
-      <c r="W9" s="254"/>
-      <c r="X9" s="254"/>
-      <c r="Y9" s="254"/>
-      <c r="Z9" s="254"/>
+      <c r="Q9" s="257"/>
+      <c r="R9" s="257"/>
+      <c r="S9" s="257"/>
+      <c r="T9" s="257"/>
+      <c r="U9" s="257"/>
+      <c r="V9" s="257"/>
+      <c r="W9" s="257"/>
+      <c r="X9" s="257"/>
+      <c r="Y9" s="257"/>
+      <c r="Z9" s="257"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -19413,31 +19384,31 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C22" s="252" t="s">
+      <c r="C22" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="252"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="252"/>
-      <c r="G22" s="252"/>
-      <c r="H22" s="252"/>
-      <c r="I22" s="252"/>
-      <c r="J22" s="252"/>
-      <c r="K22" s="252"/>
-      <c r="L22" s="252"/>
-      <c r="P22" s="254" t="s">
+      <c r="D22" s="255"/>
+      <c r="E22" s="255"/>
+      <c r="F22" s="255"/>
+      <c r="G22" s="255"/>
+      <c r="H22" s="255"/>
+      <c r="I22" s="255"/>
+      <c r="J22" s="255"/>
+      <c r="K22" s="255"/>
+      <c r="L22" s="255"/>
+      <c r="P22" s="257" t="s">
         <v>128</v>
       </c>
-      <c r="Q22" s="254"/>
-      <c r="R22" s="254"/>
-      <c r="S22" s="254"/>
-      <c r="T22" s="254"/>
-      <c r="U22" s="254"/>
-      <c r="V22" s="254"/>
-      <c r="W22" s="254"/>
-      <c r="X22" s="254"/>
-      <c r="Y22" s="254"/>
-      <c r="Z22" s="254"/>
+      <c r="Q22" s="257"/>
+      <c r="R22" s="257"/>
+      <c r="S22" s="257"/>
+      <c r="T22" s="257"/>
+      <c r="U22" s="257"/>
+      <c r="V22" s="257"/>
+      <c r="W22" s="257"/>
+      <c r="X22" s="257"/>
+      <c r="Y22" s="257"/>
+      <c r="Z22" s="257"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B23" s="16" t="s">
@@ -20252,60 +20223,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="255" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20491,30 +20462,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="252" t="s">
+      <c r="C11" s="255" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="257"/>
-      <c r="Q11" s="257"/>
-      <c r="R11" s="257"/>
-      <c r="S11" s="257"/>
-      <c r="T11" s="257"/>
-      <c r="U11" s="257"/>
-      <c r="V11" s="257"/>
-      <c r="W11" s="257"/>
-      <c r="X11" s="257"/>
-      <c r="Y11" s="257"/>
-      <c r="Z11" s="257"/>
+      <c r="P11" s="260"/>
+      <c r="Q11" s="260"/>
+      <c r="R11" s="260"/>
+      <c r="S11" s="260"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="260"/>
+      <c r="W11" s="260"/>
+      <c r="X11" s="260"/>
+      <c r="Y11" s="260"/>
+      <c r="Z11" s="260"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20756,18 +20727,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="252"/>
-      <c r="I18" s="252"/>
-      <c r="J18" s="252"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="252"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20980,23 +20951,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="257"/>
-      <c r="C25" s="257"/>
+      <c r="B25" s="260"/>
+      <c r="C25" s="260"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="252" t="s">
+      <c r="C26" s="255" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="252"/>
-      <c r="E26" s="252"/>
-      <c r="F26" s="252"/>
-      <c r="G26" s="252"/>
-      <c r="H26" s="252"/>
-      <c r="I26" s="252"/>
-      <c r="J26" s="252"/>
-      <c r="K26" s="252"/>
-      <c r="L26" s="252"/>
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="255"/>
+      <c r="H26" s="255"/>
+      <c r="I26" s="255"/>
+      <c r="J26" s="255"/>
+      <c r="K26" s="255"/>
+      <c r="L26" s="255"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -21188,18 +21159,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="252" t="s">
+      <c r="C33" s="255" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
-      <c r="I33" s="252"/>
-      <c r="J33" s="252"/>
-      <c r="K33" s="252"/>
-      <c r="L33" s="252"/>
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="255"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="255"/>
+      <c r="J33" s="255"/>
+      <c r="K33" s="255"/>
+      <c r="L33" s="255"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -21383,18 +21354,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="252" t="s">
+      <c r="C40" s="255" t="s">
         <v>150</v>
       </c>
-      <c r="D40" s="252"/>
-      <c r="E40" s="252"/>
-      <c r="F40" s="252"/>
-      <c r="G40" s="252"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="252"/>
-      <c r="J40" s="252"/>
-      <c r="K40" s="252"/>
-      <c r="L40" s="252"/>
+      <c r="D40" s="255"/>
+      <c r="E40" s="255"/>
+      <c r="F40" s="255"/>
+      <c r="G40" s="255"/>
+      <c r="H40" s="255"/>
+      <c r="I40" s="255"/>
+      <c r="J40" s="255"/>
+      <c r="K40" s="255"/>
+      <c r="L40" s="255"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21708,60 +21679,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="S2" s="257"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="257"/>
-      <c r="V2" s="257"/>
-      <c r="W2" s="257"/>
-      <c r="X2" s="257"/>
-      <c r="Y2" s="257"/>
-      <c r="Z2" s="257"/>
-      <c r="AA2" s="257"/>
-      <c r="AB2" s="257"/>
-      <c r="AC2" s="257"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
+      <c r="AA2" s="260"/>
+      <c r="AB2" s="260"/>
+      <c r="AC2" s="260"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="S4" s="257"/>
-      <c r="T4" s="257"/>
-      <c r="U4" s="257"/>
-      <c r="V4" s="257"/>
-      <c r="W4" s="257"/>
-      <c r="X4" s="257"/>
-      <c r="Y4" s="257"/>
-      <c r="Z4" s="257"/>
-      <c r="AA4" s="257"/>
-      <c r="AB4" s="257"/>
-      <c r="AC4" s="257"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -22124,18 +22095,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="252" t="s">
+      <c r="C13" s="255" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="252"/>
-      <c r="G13" s="252"/>
-      <c r="H13" s="252"/>
-      <c r="I13" s="252"/>
-      <c r="J13" s="252"/>
-      <c r="K13" s="252"/>
-      <c r="L13" s="252"/>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="255"/>
+      <c r="G13" s="255"/>
+      <c r="H13" s="255"/>
+      <c r="I13" s="255"/>
+      <c r="J13" s="255"/>
+      <c r="K13" s="255"/>
+      <c r="L13" s="255"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -22228,18 +22199,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="255" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="252"/>
-      <c r="I18" s="252"/>
-      <c r="J18" s="252"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="252"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -22431,18 +22402,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="252" t="s">
+      <c r="C25" s="255" t="s">
         <v>262</v>
       </c>
-      <c r="D25" s="252"/>
-      <c r="E25" s="252"/>
-      <c r="F25" s="252"/>
-      <c r="G25" s="252"/>
-      <c r="H25" s="252"/>
-      <c r="I25" s="252"/>
-      <c r="J25" s="252"/>
-      <c r="K25" s="252"/>
-      <c r="L25" s="252"/>
+      <c r="D25" s="255"/>
+      <c r="E25" s="255"/>
+      <c r="F25" s="255"/>
+      <c r="G25" s="255"/>
+      <c r="H25" s="255"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="255"/>
+      <c r="K25" s="255"/>
+      <c r="L25" s="255"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -22580,18 +22551,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="252" t="s">
+      <c r="C31" s="255" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="252"/>
-      <c r="E31" s="252"/>
-      <c r="F31" s="252"/>
-      <c r="G31" s="252"/>
-      <c r="H31" s="252"/>
-      <c r="I31" s="252"/>
-      <c r="J31" s="252"/>
-      <c r="K31" s="252"/>
-      <c r="L31" s="252"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="255"/>
+      <c r="G31" s="255"/>
+      <c r="H31" s="255"/>
+      <c r="I31" s="255"/>
+      <c r="J31" s="255"/>
+      <c r="K31" s="255"/>
+      <c r="L31" s="255"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22841,10 +22812,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="249" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22861,7 +22832,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22870,7 +22841,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1042951.6800000001</v>
+        <v>1005672.2999999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22888,7 +22859,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22897,7 +22868,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.3460000000000001</v>
+        <v>2.3546999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22929,10 +22900,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="249" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="246"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22940,7 +22911,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.941177754667004E-3</v>
+        <v>5.1234044018145901E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22949,7 +22920,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99505882224533304</v>
+        <v>0.99487659559818542</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22967,7 +22938,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15693000000000001</v>
+        <v>0.1554915</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22976,7 +22947,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15637708220925278</v>
+        <v>0.15492556106466895</v>
       </c>
     </row>
   </sheetData>
@@ -23021,60 +22992,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="255" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23227,7 +23198,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1082077.148488801</v>
+        <v>1092914.8354334913</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23281,23 +23252,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79532.872339647423</v>
+        <v>79632.829990410697</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>92778.962001288761</v>
+        <v>93012.319470038216</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>113512.0547034003</v>
+        <v>113940.5818351358</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>105487.66434484777</v>
+        <v>106018.97642859606</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>75842.485628582188</v>
+        <v>76320.282812740144</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23316,14 +23287,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>523312.18336053105</v>
+        <v>531883.29977533233</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="246" t="s">
+      <c r="B13" s="249" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="246"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23339,14 +23310,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15637708220925278</v>
+        <v>0.15492556106466895</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="246" t="s">
+      <c r="B18" s="249" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="246"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23354,7 +23325,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>467154.03901776648</v>
+        <v>468924.9905369209</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23363,7 +23334,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>523312.18336053105</v>
+        <v>531883.29977533233</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23372,7 +23343,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>990466.22237829748</v>
+        <v>1000808.2903122532</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23399,7 +23370,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1058740.2223782975</v>
+        <v>1069082.2903122532</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23417,7 +23388,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>923.85708759013744</v>
+        <v>932.88157967910399</v>
       </c>
     </row>
   </sheetData>
@@ -23460,37 +23431,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23686,23 +23657,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>79532.872339647423</v>
+        <v>79632.829990410697</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>92778.962001288761</v>
+        <v>93012.319470038216</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>113512.0547034003</v>
+        <v>113940.5818351358</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>105487.66434484777</v>
+        <v>106018.97642859606</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>75842.485628582188</v>
+        <v>76320.282812740144</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -23710,18 +23681,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="252" t="s">
+      <c r="C11" s="255" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23915,18 +23886,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="252" t="s">
+      <c r="C17" s="255" t="s">
         <v>196</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
-      <c r="J17" s="252"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="252"/>
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="255"/>
+      <c r="K17" s="255"/>
+      <c r="L17" s="255"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -24060,18 +24031,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="252" t="s">
+      <c r="C22" s="255" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="252"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="252"/>
-      <c r="G22" s="252"/>
-      <c r="H22" s="252"/>
-      <c r="I22" s="252"/>
-      <c r="J22" s="252"/>
-      <c r="K22" s="252"/>
-      <c r="L22" s="252"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="255"/>
+      <c r="F22" s="255"/>
+      <c r="G22" s="255"/>
+      <c r="H22" s="255"/>
+      <c r="I22" s="255"/>
+      <c r="J22" s="255"/>
+      <c r="K22" s="255"/>
+      <c r="L22" s="255"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -24155,18 +24126,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="252" t="s">
+      <c r="C27" s="255" t="s">
         <v>200</v>
       </c>
-      <c r="D27" s="252"/>
-      <c r="E27" s="252"/>
-      <c r="F27" s="252"/>
-      <c r="G27" s="252"/>
-      <c r="H27" s="252"/>
-      <c r="I27" s="252"/>
-      <c r="J27" s="252"/>
-      <c r="K27" s="252"/>
-      <c r="L27" s="252"/>
+      <c r="D27" s="255"/>
+      <c r="E27" s="255"/>
+      <c r="F27" s="255"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="255"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="255"/>
+      <c r="K27" s="255"/>
+      <c r="L27" s="255"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -24467,10 +24438,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="246" t="s">
+      <c r="B39" s="249" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="246"/>
+      <c r="C39" s="249"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24488,7 +24459,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15637708220925278</v>
+        <v>0.15492556106466895</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24514,7 +24485,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1004583.5223298258</v>
+        <v>1010912.2597682489</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24523,7 +24494,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1395895.0757190101</v>
+        <v>1403516.9674924295</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24550,7 +24521,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>1464169.0757190101</v>
+        <v>1471790.9674924295</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24568,14 +24539,14 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>1277.6344465261868</v>
+        <v>1284.2853119480187</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="246" t="s">
+      <c r="B52" s="249" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="246"/>
+      <c r="C52" s="249"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -24592,7 +24563,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15693000000000001</v>
+        <v>0.1554915</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24627,14 +24598,14 @@
       </c>
       <c r="C58" s="237">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>565.53962081310044</v>
+        <v>569.06866811448378</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="246" t="s">
+      <c r="B60" s="249" t="s">
         <v>322</v>
       </c>
-      <c r="C60" s="246"/>
+      <c r="C60" s="249"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -24651,7 +24622,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15637708220925278</v>
+        <v>0.15492556106466895</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24677,7 +24648,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1516849.712571644</v>
+        <v>1526405.6562548031</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24686,7 +24657,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1908161.2659608284</v>
+        <v>1919010.3639789838</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24713,7 +24684,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1976435.2659608284</v>
+        <v>1987284.3639789838</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24731,14 +24702,14 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>1724.6381029326601</v>
+        <v>1734.1050296500732</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="246" t="s">
+      <c r="B73" s="249" t="s">
         <v>427</v>
       </c>
-      <c r="C73" s="246"/>
+      <c r="C73" s="249"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -24755,7 +24726,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15637708220925278</v>
+        <v>0.15492556106466895</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24781,7 +24752,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>583333.03721688478</v>
+        <v>587007.95478186896</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24790,7 +24761,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>974644.59060606908</v>
+        <v>979612.66250604973</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24817,7 +24788,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>1042918.5906060691</v>
+        <v>1047886.6625060497</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24835,7 +24806,7 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>910.05112618330634</v>
+        <v>914.38626745728595</v>
       </c>
     </row>
   </sheetData>
@@ -24888,10 +24859,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="249" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24900,7 +24871,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>923.85708759013744</v>
+        <v>932.88157967910399</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24909,7 +24880,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>1277.6344465261868</v>
+        <v>1284.2853119480187</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24918,7 +24889,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>565.53962081310044</v>
+        <v>569.06866811448378</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24927,7 +24898,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>1724.6381029326601</v>
+        <v>1734.1050296500732</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24936,7 +24907,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>910.05112618330634</v>
+        <v>914.38626745728595</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24945,7 +24916,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1080.3440768090782</v>
+        <v>1086.9453713697931</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24954,7 +24925,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24963,7 +24934,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.18708693390589631</v>
+        <v>0.2386136076232615</v>
       </c>
     </row>
   </sheetData>
@@ -25058,37 +25029,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -25201,18 +25172,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="252" t="s">
+      <c r="C9" s="255" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25333,18 +25304,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="252" t="s">
+      <c r="C14" s="255" t="s">
         <v>360</v>
       </c>
-      <c r="D14" s="252"/>
-      <c r="E14" s="252"/>
-      <c r="F14" s="252"/>
-      <c r="G14" s="252"/>
-      <c r="H14" s="252"/>
-      <c r="I14" s="252"/>
-      <c r="J14" s="252"/>
-      <c r="K14" s="252"/>
-      <c r="L14" s="252"/>
+      <c r="D14" s="255"/>
+      <c r="E14" s="255"/>
+      <c r="F14" s="255"/>
+      <c r="G14" s="255"/>
+      <c r="H14" s="255"/>
+      <c r="I14" s="255"/>
+      <c r="J14" s="255"/>
+      <c r="K14" s="255"/>
+      <c r="L14" s="255"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -25434,10 +25405,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="246" t="s">
+      <c r="B20" s="249" t="s">
         <v>362</v>
       </c>
-      <c r="C20" s="246"/>
+      <c r="C20" s="249"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -25472,7 +25443,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15693000000000001</v>
+        <v>0.1554915</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25489,7 +25460,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>5.1642637674308656</v>
+        <v>5.2234613499719087</v>
       </c>
     </row>
   </sheetData>
@@ -25538,60 +25509,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="255" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -25678,23 +25649,23 @@
       </c>
       <c r="H7" s="130">
         <f>G7*(1+$C$17)</f>
-        <v>74057.293919354692</v>
+        <v>71519.505031152512</v>
       </c>
       <c r="I7" s="130">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>95089.565392451434</v>
+        <v>88684.186238629118</v>
       </c>
       <c r="J7" s="130">
         <f t="shared" si="0"/>
-        <v>122095.00196390765</v>
+        <v>109968.39093590011</v>
       </c>
       <c r="K7" s="130">
         <f t="shared" si="0"/>
-        <v>156769.98252165742</v>
+        <v>136360.80476051613</v>
       </c>
       <c r="L7" s="130">
         <f t="shared" si="0"/>
-        <v>201292.65755780812</v>
+        <v>169087.39790303999</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -25726,7 +25697,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1388916.7693802745</v>
+        <v>1178386.1358029549</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25780,23 +25751,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>64042.512653284859</v>
+        <v>61925.640441468975</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>71110.529179388992</v>
+        <v>66487.22371044819</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>78958.60344438508</v>
+        <v>71384.823559498123</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>87672.826089651484</v>
+        <v>76643.191732788429</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>97348.789102638068</v>
+        <v>82288.903244159927</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25815,15 +25786,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>671705.40298861975</v>
+        <v>573479.18245778081</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="259" t="s">
+      <c r="B14" s="262" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="260"/>
+      <c r="C14" s="263"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25831,7 +25802,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25840,7 +25811,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>1008.957186410955</v>
+        <v>886.16737391155391</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25848,22 +25819,22 @@
         <v>324</v>
       </c>
       <c r="C17" s="160">
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="E17" s="258" t="s">
+        <v>0.24</v>
+      </c>
+      <c r="E17" s="261" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="258"/>
-      <c r="G17" s="258"/>
-      <c r="H17" s="258"/>
-      <c r="I17" s="258"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="259" t="s">
+      <c r="B19" s="262" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="260"/>
+      <c r="C19" s="263"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25879,7 +25850,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15637708220925278</v>
+        <v>0.15492556106466895</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25897,7 +25868,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1027480.3200000001</v>
+        <v>990753.95</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25924,15 +25895,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>959206.32000000007</v>
+        <v>922479.95</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="259" t="s">
+      <c r="B28" s="262" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="260"/>
+      <c r="C28" s="263"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25940,7 +25911,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>399133.26046934852</v>
+        <v>358729.78268836363</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25949,7 +25920,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>671705.40298861975</v>
+        <v>573479.18245778081</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25958,7 +25929,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>1070838.6634579683</v>
+        <v>932208.96514614439</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25985,7 +25956,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1139112.6634579683</v>
+        <v>1000482.9651461444</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26003,7 +25974,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>1008.957186410955</v>
+        <v>886.16737391155391</v>
       </c>
     </row>
   </sheetData>
@@ -32908,7 +32879,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32982,7 +32953,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34351,7 +34322,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>12.263576337420831</v>
+        <v>11.825225710820643</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34392,7 +34363,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.8101738895395991</v>
+        <v>7.5310061717271823</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34457,7 +34428,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.4251710532020985</v>
+        <v>7.1597649192790751</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34522,7 +34493,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1042951.6800000001</v>
+        <v>1005672.2999999999</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34587,7 +34558,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>974677.68</v>
+        <v>937398.29999999993</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34628,7 +34599,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>7.3180592846202366</v>
+        <v>7.038158843139021</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34669,7 +34640,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>9.8115329172538761</v>
+        <v>9.4362623313871552</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34816,7 +34787,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>18.097374284226966</v>
+        <v>17.450499739718897</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34857,7 +34828,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>16.898891046205609</v>
+        <v>16.252543854906328</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34898,7 +34869,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>5.5256634708139116E-2</v>
+        <v>5.730494913701014E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34939,7 +34910,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>8.1542281997187063E-2</v>
+        <v>8.4564982052304727E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34980,7 +34951,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>6.2082454289732775E-4</v>
+        <v>6.4383795795111402E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35021,7 +34992,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>6.2323117404633737E-4</v>
+        <v>6.4633380078182531E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -35062,7 +35033,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.2081096604590539E-3</v>
+        <v>1.2528932138232305E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35609,7 +35580,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>6.5462284887445599E-2</v>
+        <v>6.7888913714735905E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37642,15 +37613,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="249" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="246"/>
-      <c r="E4" s="246" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -37658,7 +37629,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37674,7 +37645,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1042951.6800000001</v>
+        <v>1005672.2999999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37694,7 +37665,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>974677.68</v>
+        <v>937398.29999999993</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37714,7 +37685,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.263576337420831</v>
+        <v>11.825225710820643</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37734,7 +37705,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.8101738895395991</v>
+        <v>7.5310061717271823</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37754,7 +37725,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.4251710532020985</v>
+        <v>7.1597649192790751</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37774,7 +37745,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.3180592846202366</v>
+        <v>7.038158843139021</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37783,18 +37754,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>9.8115329172538761</v>
+        <v>9.4362623313871552</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="249" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="246"/>
-      <c r="E15" s="246" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="246"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37845,14 +37816,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="246" t="s">
+      <c r="B21" s="249" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="246"/>
-      <c r="E21" s="246" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="246"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37921,14 +37892,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="246" t="s">
+      <c r="B29" s="249" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="246"/>
-      <c r="E29" s="246" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="246"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -38004,14 +37975,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="246" t="s">
+      <c r="B37" s="249" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="246"/>
-      <c r="E37" s="246" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="246"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -38019,7 +37990,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.1542281997187063E-2</v>
+        <v>8.4564982052304727E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -38035,7 +38006,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>5.5256634708139116E-2</v>
+        <v>5.730494913701014E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -38051,7 +38022,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.2082454289732775E-4</v>
+        <v>6.4383795795111402E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -38067,7 +38038,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.2323117404633737E-4</v>
+        <v>6.4633380078182531E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38076,18 +38047,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.2081096604590539E-3</v>
+        <v>1.2528932138232305E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="246" t="s">
+      <c r="B45" s="249" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="246"/>
-      <c r="E45" s="246" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="246"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -38120,18 +38091,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>6.5462284887445599E-2</v>
+        <v>6.7888913714735905E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="246" t="s">
+      <c r="B51" s="249" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="246"/>
-      <c r="E51" s="246" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>303</v>
       </c>
-      <c r="F51" s="246"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -38299,7 +38270,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>910.08</v>
+        <v>877.55</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38328,7 +38299,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1042951.6800000001</v>
+        <v>1005672.2999999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38357,7 +38328,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>974677.68</v>
+        <v>937398.29999999993</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38386,7 +38357,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.263576337420831</v>
+        <v>11.825225710820643</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38415,7 +38386,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.8101738895395991</v>
+        <v>7.5310061717271823</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38444,7 +38415,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.4251710532020985</v>
+        <v>7.1597649192790751</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38473,7 +38444,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.3180592846202366</v>
+        <v>7.038158843139021</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38502,7 +38473,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>9.8115329172538761</v>
+        <v>9.4362623313871552</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39275,7 +39246,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.1542281997187063E-2</v>
+        <v>8.4564982052304727E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39304,7 +39275,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>5.5256634708139116E-2</v>
+        <v>5.730494913701014E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39333,7 +39304,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.2082454289732775E-4</v>
+        <v>6.4383795795111402E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39362,7 +39333,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.2323117404633737E-4</v>
+        <v>6.4633380078182531E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39391,7 +39362,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.2081096604590539E-3</v>
+        <v>1.2528932138232305E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39627,7 +39598,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>6.5462284887445599E-2</v>
+        <v>6.7888913714735905E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40233,14 +40204,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="253"/>
+      <c r="F3" s="254" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="253"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40307,19 +40278,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="250">
         <f>Statement!AA89</f>
         <v>0.30810980316480124</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.7926646045072911</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -40346,19 +40317,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="250">
         <f>Statement!AA90</f>
         <v>0.1221875</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14710110206037375</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -40385,19 +40356,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="250">
         <f>Statement!AA91</f>
         <v>0.3420527156549521</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3088642659279781</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -40424,19 +40395,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="250">
         <f>Statement!AA95</f>
         <v>0.89643268124280784</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3542857142857143</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -40463,19 +40434,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="250">
         <f>Statement!AA96</f>
         <v>0.3131340416591632</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>10.973453749315818</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -40502,19 +40473,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="250">
         <f>Statement!AA98</f>
         <v>0.33487943915306445</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>10.777881911902531</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -40541,22 +40512,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.7467248908296944E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.4146772767462422E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -40583,22 +40554,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.33238751520064835</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>10.614840989399292</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40647,22 +40618,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.26950331971399388</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.79326359455316076</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40690,22 +40661,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.41828422005430954</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.2519961673586713</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="251"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40733,22 +40704,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="250">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.92432432432432432</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="251"/>
+      <c r="F29" s="250">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.55458515283842791</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="251"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -40776,22 +40747,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="247">
+      <c r="C32" s="250">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.18258406565473165</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="F32" s="247">
+      <c r="D32" s="251"/>
+      <c r="F32" s="250">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>2.5841954655513977</v>
       </c>
-      <c r="G32" s="248"/>
+      <c r="G32" s="251"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -40819,22 +40790,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="247">
+      <c r="C34" s="250">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.56213120444290177</v>
       </c>
-      <c r="D34" s="248"/>
-      <c r="F34" s="247">
+      <c r="D34" s="251"/>
+      <c r="F34" s="250">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>10.415345592897907</v>
       </c>
-      <c r="G34" s="248"/>
+      <c r="G34" s="251"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -40862,22 +40833,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="247">
+      <c r="C36" s="250">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.13826924746115787</v>
       </c>
-      <c r="D36" s="248"/>
-      <c r="F36" s="247">
+      <c r="D36" s="251"/>
+      <c r="F36" s="250">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.4877659574468085</v>
       </c>
-      <c r="G36" s="248"/>
+      <c r="G36" s="251"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -40905,22 +40876,22 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="247">
+      <c r="C38" s="250">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.47259387138541215</v>
       </c>
-      <c r="D38" s="248"/>
-      <c r="F38" s="247">
+      <c r="D38" s="251"/>
+      <c r="F38" s="250">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.7587168758716878</v>
       </c>
-      <c r="G38" s="248"/>
+      <c r="G38" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="32">

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D11A53-1D0A-8745-9820-12DECA141707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5827A8-2161-CA4E-AE3C-436ED3EACB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2461,12 +2461,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2474,6 +2468,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2494,14 +2494,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15197,11 +15197,11 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>192.59</v>
-    <v>2.3546999999999998</v>
-    <v>21.06</v>
-    <v>2.4589E-2</v>
-    <v>-2.96</v>
-    <v>-3.3729999999999997E-3</v>
+    <v>2.3616000000000001</v>
+    <v>26.15</v>
+    <v>2.9799000000000003E-2</v>
+    <v>1.05</v>
+    <v>1.1620000000000001E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>61000</v>
@@ -15209,25 +15209,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>891.89</v>
+    <v>915.75</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46318.955657615625</v>
+    <v>46321.854071435155</v>
     <v>0</v>
-    <v>858.34</v>
-    <v>992880253650</v>
+    <v>882.77</v>
+    <v>1022466965100</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>862.29</v>
-    <v>11.820499999999999</v>
-    <v>856.49</v>
+    <v>889.875</v>
+    <v>12.172700000000001</v>
     <v>877.55</v>
-    <v>874.59</v>
+    <v>903.7</v>
+    <v>904.75</v>
     <v>1131423000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>21198510</v>
-    <v>26981467</v>
+    <v>22585355</v>
+    <v>26399323</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15251,17 +15251,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1005672.2999999999</v>
+        <v>1035640.2000000001</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16095,7 +16095,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>932.88157967910399</v>
+        <v>928.67183632982017</v>
       </c>
       <c r="K3" s="241" t="s">
         <v>442</v>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>937398.29999999993</v>
+        <v>967366.20000000007</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16122,7 +16122,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>1284.2853119480187</v>
+        <v>1281.1934048502171</v>
       </c>
       <c r="K4" s="241" t="s">
         <v>443</v>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>569.06866811448378</v>
+        <v>567.44500341495586</v>
       </c>
       <c r="K5" s="241" t="s">
         <v>444</v>
@@ -16161,14 +16161,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>874.59</v>
+        <v>904.75</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>11.825225710820643</v>
+        <v>12.177604096482954</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>1734.1050296500732</v>
+        <v>1729.7038260158818</v>
       </c>
       <c r="K6" s="242" t="s">
         <v>445</v>
@@ -16188,14 +16188,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>21.06</v>
+        <v>26.15</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>7.5310061717271823</v>
+        <v>7.7554216596089747</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>914.38626745728595</v>
+        <v>912.37103067584906</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16212,14 +16212,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-2.96</v>
+        <v>1.05</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>5.730494913701014E-2</v>
+        <v>5.5646739089502316E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>1086.9453713697931</v>
+        <v>1083.8770202573448</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.4589E-2</v>
+        <v>2.9799000000000003E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>8.4564982052304727E-2</v>
+        <v>8.2117959499834026E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.2386136076232615</v>
+        <v>0.19937702805947194</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16260,14 +16260,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.3729999999999997E-3</v>
+        <v>1.1620000000000001E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>6.4633380078182531E-4</v>
+        <v>6.2763110199855123E-4</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16283,14 +16283,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>6.4383795795111402E-4</v>
+        <v>6.2520748035852609E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
       </c>
       <c r="I11" s="212">
         <f ca="1">DDM!C26</f>
-        <v>5.2234613499719087</v>
+        <v>5.1961126260384285</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3546999999999998</v>
+        <v>2.3616000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>26981467</v>
+        <v>26399323</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="I14" s="244">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>886.16737391155391</v>
+        <v>881.76467397672604</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>6.7888913714735905E-2</v>
+        <v>6.5924439781306285E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="I17" s="239">
         <f ca="1">DCF!C15</f>
-        <v>0.15492556106466895</v>
+        <v>0.15559906934883602</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16416,7 +16416,7 @@
       </c>
       <c r="I18" s="240">
         <f ca="1">Multiples!C54</f>
-        <v>0.1554915</v>
+        <v>0.15615200000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21629,12 +21629,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21642,6 +21636,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22701,16 +22701,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22832,7 +22832,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1005672.2999999999</v>
+        <v>1035640.2000000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22868,7 +22868,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.3546999999999998</v>
+        <v>2.3616000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22911,7 +22911,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.1234044018145901E-3</v>
+        <v>4.9758882234301593E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99487659559818542</v>
+        <v>0.9950241117765698</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1554915</v>
+        <v>0.15615200000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15492556106466895</v>
+        <v>0.15559906934883602</v>
       </c>
     </row>
   </sheetData>
@@ -23198,7 +23198,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1092914.8354334913</v>
+        <v>1087859.2591935773</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23252,23 +23252,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79632.829990410697</v>
+        <v>79586.418244232642</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93012.319470038216</v>
+        <v>92903.931856989439</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>113940.5818351358</v>
+        <v>113741.47677146767</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>106018.97642859606</v>
+        <v>105772.03175456983</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>76320.282812740144</v>
+        <v>76098.136299347054</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23287,7 +23287,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>531883.29977533233</v>
+        <v>527881.9295073672</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23310,7 +23310,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15492556106466895</v>
+        <v>0.15559906934883602</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23325,7 +23325,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>468924.9905369209</v>
+        <v>468101.99492660665</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23334,7 +23334,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>531883.29977533233</v>
+        <v>527881.9295073672</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23343,7 +23343,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1000808.2903122532</v>
+        <v>995983.92443397385</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1069082.2903122532</v>
+        <v>1064257.9244339739</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>932.88157967910399</v>
+        <v>928.67183632982017</v>
       </c>
     </row>
   </sheetData>
@@ -23657,23 +23657,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>79632.829990410697</v>
+        <v>79586.418244232642</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>93012.319470038216</v>
+        <v>92903.931856989439</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>113940.5818351358</v>
+        <v>113741.47677146767</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>106018.97642859606</v>
+        <v>105772.03175456983</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>76320.282812740144</v>
+        <v>76098.136299347054</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15492556106466895</v>
+        <v>0.15559906934883602</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24485,7 +24485,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1010912.2597682489</v>
+        <v>1007969.7833310892</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1403516.9674924295</v>
+        <v>1399973.6419583489</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>1471790.9674924295</v>
+        <v>1468247.6419583489</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24539,7 +24539,7 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>1284.2853119480187</v>
+        <v>1281.1934048502171</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1554915</v>
+        <v>0.15615200000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24598,7 +24598,7 @@
       </c>
       <c r="C58" s="237">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>569.06866811448378</v>
+        <v>567.44500341495586</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24622,7 +24622,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15492556106466895</v>
+        <v>0.15559906934883602</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1526405.6562548031</v>
+        <v>1521962.725986941</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1919010.3639789838</v>
+        <v>1913966.5846142005</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1987284.3639789838</v>
+        <v>1982240.5846142005</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24702,7 +24702,7 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>1734.1050296500732</v>
+        <v>1729.7038260158818</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15492556106466895</v>
+        <v>0.15559906934883602</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>587007.95478186896</v>
+        <v>585299.34252726345</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>979612.66250604973</v>
+        <v>977303.20115452306</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24788,7 +24788,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>1047886.6625060497</v>
+        <v>1045577.2011545231</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24806,22 +24806,22 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>914.38626745728595</v>
+        <v>912.37103067584906</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24871,7 +24871,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>932.88157967910399</v>
+        <v>928.67183632982017</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>1284.2853119480187</v>
+        <v>1281.1934048502171</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24889,7 +24889,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>569.06866811448378</v>
+        <v>567.44500341495586</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24898,7 +24898,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>1734.1050296500732</v>
+        <v>1729.7038260158818</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>914.38626745728595</v>
+        <v>912.37103067584906</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1086.9453713697931</v>
+        <v>1083.8770202573448</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24925,7 +24925,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.2386136076232615</v>
+        <v>0.19937702805947194</v>
       </c>
     </row>
   </sheetData>
@@ -25443,7 +25443,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1554915</v>
+        <v>0.15615200000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>5.2234613499719087</v>
+        <v>5.1961126260384285</v>
       </c>
     </row>
   </sheetData>
@@ -25697,7 +25697,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1178386.1358029549</v>
+        <v>1172935.1887058313</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25751,23 +25751,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>61925.640441468975</v>
+        <v>61889.548830679443</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>66487.22371044819</v>
+        <v>66409.745893345302</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>71384.823559498123</v>
+        <v>71260.082403969209</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>76643.191732788429</v>
+        <v>76464.670597833596</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>82288.903244159927</v>
+        <v>82049.383783894242</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25786,15 +25786,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>573479.18245778081</v>
+        <v>569164.88541000197</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="262" t="s">
+      <c r="B14" s="261" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="263"/>
+      <c r="C14" s="262"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>886.16737391155391</v>
+        <v>881.76467397672604</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25821,20 +25821,20 @@
       <c r="C17" s="160">
         <v>0.24</v>
       </c>
-      <c r="E17" s="261" t="s">
+      <c r="E17" s="263" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="261"/>
-      <c r="G17" s="261"/>
-      <c r="H17" s="261"/>
-      <c r="I17" s="261"/>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="263"/>
+      <c r="I17" s="263"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="262" t="s">
+      <c r="B19" s="261" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="263"/>
+      <c r="C19" s="262"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15492556106466895</v>
+        <v>0.15559906934883602</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>990753.95</v>
+        <v>1020277.3</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25895,15 +25895,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>922479.95</v>
+        <v>952003.3</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="262" t="s">
+      <c r="B28" s="261" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="263"/>
+      <c r="C28" s="262"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>358729.78268836363</v>
+        <v>358073.43150972179</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>573479.18245778081</v>
+        <v>569164.88541000197</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>932208.96514614439</v>
+        <v>927238.31691972376</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25956,7 +25956,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>1000482.9651461444</v>
+        <v>995512.31691972376</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25974,21 +25974,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>886.16737391155391</v>
+        <v>881.76467397672604</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32953,7 +32953,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34322,7 +34322,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>11.825225710820643</v>
+        <v>12.177604096482954</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34363,7 +34363,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.5310061717271823</v>
+        <v>7.7554216596089747</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34428,7 +34428,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.1597649192790751</v>
+        <v>7.3731178366503345</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34493,7 +34493,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1005672.2999999999</v>
+        <v>1035640.2000000001</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34558,7 +34558,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>937398.29999999993</v>
+        <v>967366.20000000007</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34599,7 +34599,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>7.038158843139021</v>
+        <v>7.2631633480493747</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34640,7 +34640,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>9.4362623313871552</v>
+        <v>9.7379323535333207</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34787,7 +34787,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>17.450499739718897</v>
+        <v>17.97050494534097</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34828,7 +34828,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>16.252543854906328</v>
+        <v>16.772125135339042</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34869,7 +34869,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>5.730494913701014E-2</v>
+        <v>5.5646739089502316E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34910,7 +34910,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>8.4564982052304727E-2</v>
+        <v>8.2117959499834026E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34951,7 +34951,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>6.4383795795111402E-4</v>
+        <v>6.2520748035852609E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34992,7 +34992,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>6.4633380078182531E-4</v>
+        <v>6.2763110199855123E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -35033,7 +35033,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.2528932138232305E-3</v>
+        <v>1.2166387515664223E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35580,7 +35580,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>6.7888913714735905E-2</v>
+        <v>6.5924439781306285E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37629,7 +37629,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1005672.2999999999</v>
+        <v>1035640.2000000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37665,7 +37665,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>937398.29999999993</v>
+        <v>967366.20000000007</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37685,7 +37685,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>11.825225710820643</v>
+        <v>12.177604096482954</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37705,7 +37705,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.5310061717271823</v>
+        <v>7.7554216596089747</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37725,7 +37725,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.1597649192790751</v>
+        <v>7.3731178366503345</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.038158843139021</v>
+        <v>7.2631633480493747</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37754,7 +37754,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>9.4362623313871552</v>
+        <v>9.7379323535333207</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37990,7 +37990,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.4564982052304727E-2</v>
+        <v>8.2117959499834026E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -38006,7 +38006,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>5.730494913701014E-2</v>
+        <v>5.5646739089502316E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -38022,7 +38022,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.4383795795111402E-4</v>
+        <v>6.2520748035852609E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -38038,7 +38038,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.4633380078182531E-4</v>
+        <v>6.2763110199855123E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38047,7 +38047,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.2528932138232305E-3</v>
+        <v>1.2166387515664223E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38091,7 +38091,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>6.7888913714735905E-2</v>
+        <v>6.5924439781306285E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38270,7 +38270,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>877.55</v>
+        <v>903.7</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38299,7 +38299,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1005672.2999999999</v>
+        <v>1035640.2000000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38328,7 +38328,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>937398.29999999993</v>
+        <v>967366.20000000007</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38357,7 +38357,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>11.825225710820643</v>
+        <v>12.177604096482954</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38386,7 +38386,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.5310061717271823</v>
+        <v>7.7554216596089747</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.1597649192790751</v>
+        <v>7.3731178366503345</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38444,7 +38444,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.038158843139021</v>
+        <v>7.2631633480493747</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38473,7 +38473,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>9.4362623313871552</v>
+        <v>9.7379323535333207</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39246,7 +39246,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.4564982052304727E-2</v>
+        <v>8.2117959499834026E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39275,7 +39275,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>5.730494913701014E-2</v>
+        <v>5.5646739089502316E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39304,7 +39304,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.4383795795111402E-4</v>
+        <v>6.2520748035852609E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.4633380078182531E-4</v>
+        <v>6.2763110199855123E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39362,7 +39362,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.2528932138232305E-3</v>
+        <v>1.2166387515664223E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39598,7 +39598,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>6.7888913714735905E-2</v>
+        <v>6.5924439781306285E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40204,14 +40204,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="250" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="F3" s="254" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="253"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40278,19 +40278,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="253">
         <f>Statement!AA89</f>
         <v>0.30810980316480124</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.7926646045072911</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -40317,19 +40317,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="253">
         <f>Statement!AA90</f>
         <v>0.1221875</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14710110206037375</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -40356,19 +40356,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="253">
         <f>Statement!AA91</f>
         <v>0.3420527156549521</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3088642659279781</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -40395,19 +40395,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="253">
         <f>Statement!AA95</f>
         <v>0.89643268124280784</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3542857142857143</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -40434,19 +40434,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="253">
         <f>Statement!AA96</f>
         <v>0.3131340416591632</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>10.973453749315818</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -40473,19 +40473,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="253">
         <f>Statement!AA98</f>
         <v>0.33487943915306445</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>10.777881911902531</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -40512,22 +40512,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.7467248908296944E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.4146772767462422E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -40554,22 +40554,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.33238751520064835</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>10.614840989399292</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40618,22 +40618,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.26950331971399388</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.79326359455316076</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40661,22 +40661,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.41828422005430954</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.2519961673586713</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="254"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40704,22 +40704,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="250">
+      <c r="C29" s="253">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.92432432432432432</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="F29" s="250">
+      <c r="D29" s="254"/>
+      <c r="F29" s="253">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.55458515283842791</v>
       </c>
-      <c r="G29" s="251"/>
+      <c r="G29" s="254"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -40747,22 +40747,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="250">
+      <c r="C32" s="253">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.18258406565473165</v>
       </c>
-      <c r="D32" s="251"/>
-      <c r="F32" s="250">
+      <c r="D32" s="254"/>
+      <c r="F32" s="253">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>2.5841954655513977</v>
       </c>
-      <c r="G32" s="251"/>
+      <c r="G32" s="254"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -40790,22 +40790,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="250">
+      <c r="C34" s="253">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.56213120444290177</v>
       </c>
-      <c r="D34" s="251"/>
-      <c r="F34" s="250">
+      <c r="D34" s="254"/>
+      <c r="F34" s="253">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>10.415345592897907</v>
       </c>
-      <c r="G34" s="251"/>
+      <c r="G34" s="254"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -40833,22 +40833,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="250">
+      <c r="C36" s="253">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.13826924746115787</v>
       </c>
-      <c r="D36" s="251"/>
-      <c r="F36" s="250">
+      <c r="D36" s="254"/>
+      <c r="F36" s="253">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.4877659574468085</v>
       </c>
-      <c r="G36" s="251"/>
+      <c r="G36" s="254"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -40876,49 +40876,25 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="250">
+      <c r="C38" s="253">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.47259387138541215</v>
       </c>
-      <c r="D38" s="251"/>
-      <c r="F38" s="250">
+      <c r="D38" s="254"/>
+      <c r="F38" s="253">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.7587168758716878</v>
       </c>
-      <c r="G38" s="251"/>
+      <c r="G38" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40927,6 +40903,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5827A8-2161-CA4E-AE3C-436ED3EACB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5142677-9606-DC4D-BC4B-B0238FB773BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="452">
   <si>
     <t>Ticker</t>
   </si>
@@ -1496,6 +1496,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2461,6 +2473,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2468,12 +2486,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2494,14 +2506,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15197,11 +15209,11 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>192.59</v>
-    <v>2.3616000000000001</v>
-    <v>26.15</v>
-    <v>2.9799000000000003E-2</v>
-    <v>1.05</v>
-    <v>1.1620000000000001E-3</v>
+    <v>2.3490000000000002</v>
+    <v>25.06</v>
+    <v>2.7730000000000001E-2</v>
+    <v>-2.86</v>
+    <v>-3.0790000000000001E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>61000</v>
@@ -15209,25 +15221,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>915.75</v>
+    <v>935.87</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46321.854071435155</v>
+    <v>46322.899580474215</v>
     <v>0</v>
-    <v>882.77</v>
-    <v>1022466965100</v>
+    <v>910.67139999999995</v>
+    <v>1050820425480</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>889.875</v>
-    <v>12.172700000000001</v>
-    <v>877.55</v>
+    <v>920.99</v>
+    <v>12.510300000000001</v>
     <v>903.7</v>
-    <v>904.75</v>
+    <v>928.76</v>
+    <v>925.9</v>
     <v>1131423000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>22585355</v>
-    <v>26399323</v>
+    <v>22821262</v>
+    <v>26186304</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15251,17 +15263,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -16087,7 +16099,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1035640.2000000001</v>
+        <v>1064358.96</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -16095,7 +16107,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>928.67183632982017</v>
+        <v>932.22773953420062</v>
       </c>
       <c r="K3" s="241" t="s">
         <v>442</v>
@@ -16114,7 +16126,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>967366.20000000007</v>
+        <v>996084.96</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -16122,7 +16134,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>1281.1934048502171</v>
+        <v>1283.8062972527916</v>
       </c>
       <c r="K4" s="241" t="s">
         <v>443</v>
@@ -16134,7 +16146,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16149,7 +16161,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>567.44500341495586</v>
+        <v>568.88771236267064</v>
       </c>
       <c r="K5" s="241" t="s">
         <v>444</v>
@@ -16161,14 +16173,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>904.75</v>
+        <v>925.9</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>12.177604096482954</v>
+        <v>12.515294434712301</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -16176,7 +16188,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>1729.7038260158818</v>
+        <v>1733.4231554762671</v>
       </c>
       <c r="K6" s="242" t="s">
         <v>445</v>
@@ -16188,14 +16200,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>26.15</v>
+        <v>25.06</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>7.7554216596089747</v>
+        <v>7.9704829263897654</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -16203,7 +16215,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>912.37103067584906</v>
+        <v>914.07406965411394</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16212,14 +16224,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>1.05</v>
+        <v>-2.86</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>5.5646739089502316E-2</v>
+        <v>5.4145266931374357E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
@@ -16227,7 +16239,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C10</f>
-        <v>1083.8770202573448</v>
+        <v>1086.4837948560089</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16236,14 +16248,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.9799000000000003E-2</v>
+        <v>2.7730000000000001E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>8.2117959499834026E-2</v>
+        <v>7.9902235238382371E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16251,7 +16263,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.19937702805947194</v>
+        <v>0.16982190754986101</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16260,14 +16272,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.1620000000000001E-3</v>
+        <v>-3.0790000000000001E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>6.2763110199855123E-4</v>
+        <v>6.1069622601758343E-4</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16283,14 +16295,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>6.2520748035852609E-4</v>
+        <v>6.0833799905250015E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
       </c>
       <c r="I11" s="212">
         <f ca="1">DDM!C26</f>
-        <v>5.1961126260384285</v>
+        <v>5.2204037749372816</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -16315,7 +16327,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3616000000000001</v>
+        <v>2.3490000000000002</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16338,7 +16350,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>26399323</v>
+        <v>26186304</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16352,7 +16364,7 @@
       </c>
       <c r="I14" s="244">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>881.76467397672604</v>
+        <v>885.48347224369797</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16361,7 +16373,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>6.5924439781306285E-2</v>
+        <v>6.4145652515576135E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16394,7 +16406,7 @@
       </c>
       <c r="I17" s="239">
         <f ca="1">DCF!C15</f>
-        <v>0.15559906934883602</v>
+        <v>0.15502975881510556</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16416,7 +16428,7 @@
       </c>
       <c r="I18" s="240">
         <f ca="1">Multiples!C54</f>
-        <v>0.15615200000000001</v>
+        <v>0.15556500000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16489,7 +16501,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16504,7 +16516,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21629,6 +21641,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21636,12 +21654,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22701,16 +22713,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22832,7 +22844,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22841,7 +22853,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1035640.2000000001</v>
+        <v>1064358.96</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22859,7 +22871,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22868,7 +22880,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.3616000000000001</v>
+        <v>2.3490000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22911,7 +22923,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.9758882234301593E-3</v>
+        <v>4.8422778748311093E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22920,7 +22932,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9950241117765698</v>
+        <v>0.99515772212516884</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22938,7 +22950,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15615200000000001</v>
+        <v>0.15556500000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22947,7 +22959,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15559906934883602</v>
+        <v>0.15502975881510556</v>
       </c>
     </row>
   </sheetData>
@@ -23198,7 +23210,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1087859.2591935773</v>
+        <v>1092129.6223282544</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23252,23 +23264,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79586.418244232642</v>
+        <v>79625.64613936047</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>92903.931856989439</v>
+        <v>92995.538539115572</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>113741.47677146767</v>
+        <v>113909.748132658</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>105772.03175456983</v>
+        <v>105980.72479395052</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>76098.136299347054</v>
+        <v>76285.863928535866</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23287,7 +23299,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>527881.9295073672</v>
+        <v>531261.46797257336</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23310,7 +23322,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15559906934883602</v>
+        <v>0.15502975881510556</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23325,7 +23337,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>468101.99492660665</v>
+        <v>468797.52153362043</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23334,7 +23346,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>527881.9295073672</v>
+        <v>531261.46797257336</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23343,7 +23355,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>995983.92443397385</v>
+        <v>1000058.9895061938</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23370,7 +23382,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1064257.9244339739</v>
+        <v>1068332.9895061939</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23388,7 +23400,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C24/C25</f>
-        <v>928.67183632982017</v>
+        <v>932.22773953420062</v>
       </c>
     </row>
   </sheetData>
@@ -23657,23 +23669,23 @@
       <c r="G9" s="142"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>79586.418244232642</v>
+        <v>79625.64613936047</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>92903.931856989439</v>
+        <v>92995.538539115572</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>113741.47677146767</v>
+        <v>113909.748132658</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>105772.03175456983</v>
+        <v>105980.72479395052</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>76098.136299347054</v>
+        <v>76285.863928535866</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24459,7 +24471,7 @@
       </c>
       <c r="C41" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15559906934883602</v>
+        <v>0.15502975881510556</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24485,7 +24497,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>1007969.7833310892</v>
+        <v>1010456.3590466147</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24494,7 +24506,7 @@
       </c>
       <c r="C45" s="110">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1399973.6419583489</v>
+        <v>1402968.0166516993</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24521,7 +24533,7 @@
       </c>
       <c r="C48" s="110">
         <f ca="1">C45+C46-C47</f>
-        <v>1468247.6419583489</v>
+        <v>1471242.0166516993</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24539,7 +24551,7 @@
       </c>
       <c r="C50" s="237">
         <f ca="1">C48/C49</f>
-        <v>1281.1934048502171</v>
+        <v>1283.8062972527916</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24563,7 +24575,7 @@
       </c>
       <c r="C54" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15615200000000001</v>
+        <v>0.15556500000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24598,7 +24610,7 @@
       </c>
       <c r="C58" s="237">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>567.44500341495586</v>
+        <v>568.88771236267064</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24622,7 +24634,7 @@
       </c>
       <c r="C62" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15559906934883602</v>
+        <v>0.15502975881510556</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24648,7 +24660,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1521962.725986941</v>
+        <v>1525717.2785707174</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24657,7 +24669,7 @@
       </c>
       <c r="C66" s="110">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1913966.5846142005</v>
+        <v>1918228.936175802</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24684,7 +24696,7 @@
       </c>
       <c r="C69" s="110">
         <f ca="1">C66+C67-C68</f>
-        <v>1982240.5846142005</v>
+        <v>1986502.936175802</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24702,7 +24714,7 @@
       </c>
       <c r="C71" s="237">
         <f ca="1">C69/C70</f>
-        <v>1729.7038260158818</v>
+        <v>1733.4231554762671</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24726,7 +24738,7 @@
       </c>
       <c r="C75" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15559906934883602</v>
+        <v>0.15502975881510556</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24752,7 +24764,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>585299.34252726345</v>
+        <v>586743.22621853009</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24761,7 +24773,7 @@
       </c>
       <c r="C79" s="110">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>977303.20115452306</v>
+        <v>979254.88382361457</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24788,7 +24800,7 @@
       </c>
       <c r="C82" s="110">
         <f ca="1">C79+C80-C81</f>
-        <v>1045577.2011545231</v>
+        <v>1047528.8838236146</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24806,22 +24818,22 @@
       </c>
       <c r="C84" s="237">
         <f ca="1">C82/C83</f>
-        <v>912.37103067584906</v>
+        <v>914.07406965411394</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24871,7 +24883,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>928.67183632982017</v>
+        <v>932.22773953420062</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24880,7 +24892,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C50</f>
-        <v>1281.1934048502171</v>
+        <v>1283.8062972527916</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24889,7 +24901,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C58</f>
-        <v>567.44500341495586</v>
+        <v>568.88771236267064</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24898,7 +24910,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C71</f>
-        <v>1729.7038260158818</v>
+        <v>1733.4231554762671</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24907,7 +24919,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Multiples!C84</f>
-        <v>912.37103067584906</v>
+        <v>914.07406965411394</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24916,7 +24928,7 @@
       </c>
       <c r="C10" s="237">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1083.8770202573448</v>
+        <v>1086.4837948560089</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24925,7 +24937,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24934,7 +24946,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.19937702805947194</v>
+        <v>0.16982190754986101</v>
       </c>
     </row>
   </sheetData>
@@ -25443,7 +25455,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15615200000000001</v>
+        <v>0.15556500000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25460,7 +25472,7 @@
       </c>
       <c r="C26" s="237">
         <f ca="1">C23/(C24-C25)</f>
-        <v>5.1961126260384285</v>
+        <v>5.2204037749372816</v>
       </c>
     </row>
   </sheetData>
@@ -25697,7 +25709,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1172935.1887058313</v>
+        <v>1177539.5151817836</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25751,23 +25763,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>61889.548830679443</v>
+        <v>61920.053994557893</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>66409.745893345302</v>
+        <v>66475.228336989268</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>71260.082403969209</v>
+        <v>71365.505961012896</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>76464.670597833596</v>
+        <v>76615.538877922358</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>82049.383783894242</v>
+        <v>82251.792634402271</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25786,15 +25798,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>569164.88541000197</v>
+        <v>572808.72035825031</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="261" t="s">
+      <c r="B14" s="262" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="262"/>
+      <c r="C14" s="263"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25802,7 +25814,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25811,7 +25823,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>881.76467397672604</v>
+        <v>885.48347224369797</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25821,20 +25833,20 @@
       <c r="C17" s="160">
         <v>0.24</v>
       </c>
-      <c r="E17" s="263" t="s">
+      <c r="E17" s="261" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="263"/>
-      <c r="G17" s="263"/>
-      <c r="H17" s="263"/>
-      <c r="I17" s="263"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="261" t="s">
+      <c r="B19" s="262" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="262"/>
+      <c r="C19" s="263"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25850,7 +25862,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15559906934883602</v>
+        <v>0.15502975881510556</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25868,7 +25880,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1020277.3</v>
+        <v>1048570.04</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25895,15 +25907,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>952003.3</v>
+        <v>980296.04</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="261" t="s">
+      <c r="B28" s="262" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="262"/>
+      <c r="C28" s="263"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -25911,7 +25923,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>358073.43150972179</v>
+        <v>358628.11980488471</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25920,7 +25932,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>569164.88541000197</v>
+        <v>572808.72035825031</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25929,7 +25941,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>927238.31691972376</v>
+        <v>931436.84016313497</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25956,7 +25968,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>995512.31691972376</v>
+        <v>999710.84016313497</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25974,21 +25986,21 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>881.76467397672604</v>
+        <v>885.48347224369797</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32879,7 +32891,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32953,7 +32965,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34322,7 +34334,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>12.177604096482954</v>
+        <v>12.515294434712301</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34363,7 +34375,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.7554216596089747</v>
+        <v>7.9704829263897654</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34428,7 +34440,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.3731178366503345</v>
+        <v>7.5775776496263854</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34493,7 +34505,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1035640.2000000001</v>
+        <v>1064358.96</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34558,7 +34570,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>967366.20000000007</v>
+        <v>996084.96</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34599,7 +34611,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>7.2631633480493747</v>
+        <v>7.4787890800973056</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34640,7 +34652,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>9.7379323535333207</v>
+        <v>10.027027984699012</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34787,7 +34799,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>17.97050494534097</v>
+        <v>18.468834981780322</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34828,7 +34840,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>16.772125135339042</v>
+        <v>17.270048916893295</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34869,7 +34881,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>5.5646739089502316E-2</v>
+        <v>5.4145266931374357E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34910,7 +34922,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>8.2117959499834026E-2</v>
+        <v>7.9902235238382371E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34951,7 +34963,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>6.2520748035852609E-4</v>
+        <v>6.0833799905250015E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34992,7 +35004,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>6.2763110199855123E-4</v>
+        <v>6.1069622601758343E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -35033,7 +35045,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.2166387515664223E-3</v>
+        <v>1.1838111458187001E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35580,7 +35592,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>6.5924439781306285E-2</v>
+        <v>6.4145652515576135E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37596,7 +37608,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -37629,7 +37641,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37645,7 +37657,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1035640.2000000001</v>
+        <v>1064358.96</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37665,7 +37677,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>967366.20000000007</v>
+        <v>996084.96</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37685,7 +37697,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.177604096482954</v>
+        <v>12.515294434712301</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37705,7 +37717,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.7554216596089747</v>
+        <v>7.9704829263897654</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37725,7 +37737,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.3731178366503345</v>
+        <v>7.5775776496263854</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37745,7 +37757,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.2631633480493747</v>
+        <v>7.4787890800973056</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37754,7 +37766,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>9.7379323535333207</v>
+        <v>10.027027984699012</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37990,7 +38002,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.2117959499834026E-2</v>
+        <v>7.9902235238382371E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -38006,7 +38018,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>5.5646739089502316E-2</v>
+        <v>5.4145266931374357E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -38022,7 +38034,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.2520748035852609E-4</v>
+        <v>6.0833799905250015E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -38038,7 +38050,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.2763110199855123E-4</v>
+        <v>6.1069622601758343E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38047,7 +38059,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.2166387515664223E-3</v>
+        <v>1.1838111458187001E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38091,7 +38103,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>6.5924439781306285E-2</v>
+        <v>6.4145652515576135E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38145,8 +38157,51 @@
         <v>3.2318215300431441</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="249" t="s">
+        <v>448</v>
+      </c>
+      <c r="C57" s="249"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C58" s="174">
+        <f ca="1">Statement!AC159</f>
+        <v>18.468834981780322</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" s="174">
+        <f ca="1">Statement!AC160</f>
+        <v>17.270048916893295</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="C60" s="175">
+        <f>Statement!AC166</f>
+        <v>0.43304967554444329</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="C61" s="175">
+        <f>Statement!AC167</f>
+        <v>0.43269663933687719</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -38171,7 +38226,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I99"/>
+  <dimension ref="B1:I108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -38270,7 +38325,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>903.7</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38299,7 +38354,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1035640.2000000001</v>
+        <v>1064358.96</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38328,7 +38383,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>967366.20000000007</v>
+        <v>996084.96</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38357,7 +38412,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.177604096482954</v>
+        <v>12.515294434712301</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38386,7 +38441,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.7554216596089747</v>
+        <v>7.9704829263897654</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38415,7 +38470,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.3731178366503345</v>
+        <v>7.5775776496263854</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38444,7 +38499,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.2631633480493747</v>
+        <v>7.4787890800973056</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38473,7 +38528,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>9.7379323535333207</v>
+        <v>10.027027984699012</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39246,7 +39301,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.2117959499834026E-2</v>
+        <v>7.9902235238382371E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39275,7 +39330,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>5.5646739089502316E-2</v>
+        <v>5.4145266931374357E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39304,7 +39359,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.2520748035852609E-4</v>
+        <v>6.0833799905250015E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39333,7 +39388,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.2763110199855123E-4</v>
+        <v>6.1069622601758343E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39362,7 +39417,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.2166387515664223E-3</v>
+        <v>1.1838111458187001E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39598,7 +39653,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>6.5924439781306285E-2</v>
+        <v>6.4145652515576135E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39935,251 +39990,415 @@
       </c>
       <c r="I85" s="197"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C88" s="174">
+        <f>Statement!M159</f>
+        <v>24.180411538461538</v>
+      </c>
+      <c r="D88" s="174">
+        <f>Statement!N159</f>
+        <v>-11.137020706092658</v>
+      </c>
+      <c r="E88" s="174">
+        <f>Statement!O159</f>
+        <v>-150.60328651685393</v>
+      </c>
+      <c r="F88" s="174">
+        <f>Statement!P159</f>
+        <v>198.25</v>
+      </c>
+      <c r="G88" s="174">
+        <f>Statement!Q159</f>
+        <v>19.053467985424255</v>
+      </c>
+      <c r="I88" s="174">
+        <f ca="1">Statement!AC159</f>
+        <v>18.468834981780322</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C89" s="174">
+        <f>Statement!M160</f>
+        <v>22.563526344447098</v>
+      </c>
+      <c r="D89" s="174">
+        <f>Statement!N160</f>
+        <v>-9.0750052588524017</v>
+      </c>
+      <c r="E89" s="174">
+        <f>Statement!O160</f>
+        <v>-168.8298535317509</v>
+      </c>
+      <c r="F89" s="174">
+        <f>Statement!P160</f>
+        <v>178.11781476710598</v>
+      </c>
+      <c r="G89" s="174">
+        <f>Statement!Q160</f>
+        <v>17.854205308660855</v>
+      </c>
+      <c r="I89" s="174">
+        <f ca="1">Statement!AC160</f>
+        <v>17.270048916893295</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="C90" s="175">
+        <f>Statement!M166</f>
+        <v>8.4720911117094358E-2</v>
+      </c>
+      <c r="D90" s="175">
+        <f>Statement!N166</f>
+        <v>-0.55064350064350065</v>
+      </c>
+      <c r="E90" s="175">
+        <f>Statement!O166</f>
+        <v>-2.6294349860811573E-2</v>
+      </c>
+      <c r="F90" s="175">
+        <f>Statement!P166</f>
+        <v>2.1121897984901099E-2</v>
+      </c>
+      <c r="G90" s="175">
+        <f>Statement!Q166</f>
+        <v>0.43304967554444329</v>
+      </c>
+      <c r="I90" s="175">
+        <f>Statement!AC166</f>
+        <v>0.43304967554444329</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="C91" s="175">
+        <f>Statement!M167</f>
+        <v>8.453085376162299E-2</v>
+      </c>
+      <c r="D91" s="175">
+        <f>Statement!N167</f>
+        <v>-0.43198198198198196</v>
+      </c>
+      <c r="E91" s="175">
+        <f>Statement!O167</f>
+        <v>-2.8354107761538769E-2</v>
+      </c>
+      <c r="F91" s="175">
+        <f>Statement!P167</f>
+        <v>1.86205789501846E-2</v>
+      </c>
+      <c r="G91" s="175">
+        <f>Statement!Q167</f>
+        <v>0.43269663933687719</v>
+      </c>
+      <c r="I91" s="175">
+        <f>Statement!AC167</f>
+        <v>0.43269663933687719</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="C94" s="175">
+        <f>Statement!M214</f>
+        <v>-1</v>
+      </c>
+      <c r="D94" s="175">
+        <f>Statement!N214</f>
+        <v>9.3275488069414311E-2</v>
+      </c>
+      <c r="E94" s="175">
+        <f>Statement!O214</f>
+        <v>1.7857142857142856E-2</v>
+      </c>
+      <c r="F94" s="175">
+        <f>Statement!P214</f>
+        <v>1.7543859649122806E-2</v>
+      </c>
+      <c r="G94" s="175">
+        <f>Statement!Q214</f>
+        <v>0.16858237547892721</v>
+      </c>
+      <c r="I94" s="197"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
         <f>Statement!B203</f>
         <v>DRAM</v>
       </c>
-      <c r="C89" s="175">
+      <c r="C98" s="175">
         <f>Statement!M203</f>
         <v>0.11712161285493287</v>
       </c>
-      <c r="D89" s="175">
+      <c r="D98" s="175">
         <f>Statement!N203</f>
         <v>-0.5096042169212901</v>
       </c>
-      <c r="E89" s="175">
+      <c r="E98" s="175">
         <f>Statement!O203</f>
         <v>0.60347968664601936</v>
       </c>
-      <c r="F89" s="175">
+      <c r="F98" s="175">
         <f>Statement!P203</f>
         <v>0.62347327160143162</v>
       </c>
-      <c r="G89" s="175">
+      <c r="G98" s="175">
         <f>Statement!Q203</f>
         <v>2.5229547204143046</v>
       </c>
-      <c r="I89" s="197"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
+      <c r="I98" s="197"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
         <f>Statement!B204</f>
         <v>NAND</v>
       </c>
-      <c r="C90" s="175">
+      <c r="C99" s="175">
         <f>Statement!M204</f>
         <v>0.11474240045668617</v>
       </c>
-      <c r="D90" s="175">
+      <c r="D99" s="175">
         <f>Statement!N204</f>
         <v>-0.46152861349379082</v>
       </c>
-      <c r="E90" s="175">
+      <c r="E99" s="175">
         <f>Statement!O204</f>
         <v>0.71825962910128383</v>
       </c>
-      <c r="F90" s="175">
+      <c r="F99" s="175">
         <f>Statement!P204</f>
         <v>0.17656012176560121</v>
       </c>
-      <c r="G90" s="175">
+      <c r="G99" s="175">
         <f>Statement!Q204</f>
         <v>2.738092437963072</v>
       </c>
-      <c r="I90" s="197"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="str">
+      <c r="I99" s="197"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="str">
         <f>Statement!B205</f>
         <v>Other</v>
       </c>
-      <c r="C91" s="175">
+      <c r="C100" s="175">
         <f>Statement!M205</f>
         <v>-0.14871016691957512</v>
       </c>
-      <c r="D91" s="175">
+      <c r="D100" s="175">
         <f>Statement!N205</f>
         <v>-0.36541889483065954</v>
       </c>
-      <c r="E91" s="175">
+      <c r="E100" s="175">
         <f>Statement!O205</f>
         <v>-0.21067415730337077</v>
       </c>
-      <c r="F91" s="175">
+      <c r="F100" s="175">
         <f>Statement!P205</f>
         <v>5.6939501779359428E-2</v>
       </c>
-      <c r="G91" s="175">
+      <c r="G100" s="175">
         <f>Statement!Q205</f>
         <v>1.4377104377104377</v>
       </c>
-      <c r="I91" s="197"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B92" s="20"/>
-      <c r="C92" s="175"/>
-      <c r="D92" s="175"/>
-      <c r="E92" s="175"/>
-      <c r="F92" s="175"/>
-      <c r="G92" s="175"/>
-      <c r="I92" s="197"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="str">
+      <c r="I100" s="197"/>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B101" s="20"/>
+      <c r="C101" s="175"/>
+      <c r="D101" s="175"/>
+      <c r="E101" s="175"/>
+      <c r="F101" s="175"/>
+      <c r="G101" s="175"/>
+      <c r="I101" s="197"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B102" s="20" t="str">
         <f>Statement!B207</f>
         <v>Cloud Memory</v>
       </c>
-      <c r="C93" s="175">
+      <c r="C102" s="175">
         <f>Statement!M207</f>
         <v>0</v>
       </c>
-      <c r="D93" s="175">
+      <c r="D102" s="175">
         <f>Statement!N207</f>
         <v>1</v>
       </c>
-      <c r="E93" s="175">
+      <c r="E102" s="175">
         <f>Statement!O207</f>
         <v>1.0256410256410255</v>
       </c>
-      <c r="F93" s="175">
+      <c r="F102" s="175">
         <f>Statement!P207</f>
         <v>2.5664556962025316</v>
       </c>
-      <c r="G93" s="175">
+      <c r="G102" s="175">
         <f>Statement!Q207</f>
         <v>2.1858178053830226</v>
       </c>
-      <c r="I93" s="197"/>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B94" s="20" t="str">
+      <c r="I102" s="197"/>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B103" s="20" t="str">
         <f>Statement!B208</f>
         <v>Core Data Center</v>
       </c>
-      <c r="C94" s="175">
+      <c r="C103" s="175">
         <f>Statement!M208</f>
         <v>0</v>
       </c>
-      <c r="D94" s="175">
+      <c r="D103" s="175">
         <f>Statement!N208</f>
         <v>1</v>
       </c>
-      <c r="E94" s="175">
+      <c r="E103" s="175">
         <f>Statement!O208</f>
         <v>1.3465160075329567</v>
       </c>
-      <c r="F94" s="175">
+      <c r="F103" s="175">
         <f>Statement!P208</f>
         <v>0.4504414125200642</v>
       </c>
-      <c r="G94" s="175">
+      <c r="G103" s="175">
         <f>Statement!Q208</f>
         <v>4.2001659980633557</v>
       </c>
-      <c r="I94" s="197"/>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B95" s="20" t="str">
+      <c r="I103" s="197"/>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B104" s="20" t="str">
         <f>Statement!B209</f>
         <v>Mobile and Client</v>
       </c>
-      <c r="C95" s="175">
+      <c r="C104" s="175">
         <f>Statement!M209</f>
         <v>0</v>
       </c>
-      <c r="D95" s="175">
+      <c r="D104" s="175">
         <f>Statement!N209</f>
         <v>1</v>
       </c>
-      <c r="E95" s="175">
+      <c r="E104" s="175">
         <f>Statement!O209</f>
         <v>0.57790100081146878</v>
       </c>
-      <c r="F95" s="175">
+      <c r="F104" s="175">
         <f>Statement!P209</f>
         <v>1.6456672666495243E-2</v>
       </c>
-      <c r="G95" s="175">
+      <c r="G104" s="175">
         <f>Statement!Q209</f>
         <v>2.0863479214098994</v>
       </c>
-      <c r="I95" s="197"/>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B96" s="20" t="str">
+      <c r="I104" s="197"/>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B105" s="20" t="str">
         <f>Statement!B210</f>
         <v>Automotive and Embedded</v>
       </c>
-      <c r="C96" s="175">
+      <c r="C105" s="175">
         <f>Statement!M210</f>
         <v>0</v>
       </c>
-      <c r="D96" s="175">
+      <c r="D105" s="175">
         <f>Statement!N210</f>
         <v>1</v>
       </c>
-      <c r="E96" s="175">
+      <c r="E105" s="175">
         <f>Statement!O210</f>
         <v>0.11886929209954095</v>
       </c>
-      <c r="F96" s="175">
+      <c r="F105" s="175">
         <f>Statement!P210</f>
         <v>2.6344202116173613E-2</v>
       </c>
-      <c r="G96" s="175">
+      <c r="G105" s="175">
         <f>Statement!Q210</f>
         <v>2.3423101199242584</v>
       </c>
-      <c r="I96" s="197"/>
-    </row>
-    <row r="98" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
-      <c r="I98" s="14"/>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B99" s="20" t="s">
+      <c r="I105" s="197"/>
+    </row>
+    <row r="107" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+      <c r="I107" s="14"/>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B108" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="C99" s="175">
+      <c r="C108" s="175">
         <f>Statement!M214</f>
         <v>-1</v>
       </c>
-      <c r="D99" s="175">
+      <c r="D108" s="175">
         <f>Statement!N214</f>
         <v>9.3275488069414311E-2</v>
       </c>
-      <c r="E99" s="175">
+      <c r="E108" s="175">
         <f>Statement!O214</f>
         <v>1.7857142857142856E-2</v>
       </c>
-      <c r="F99" s="175">
+      <c r="F108" s="175">
         <f>Statement!P214</f>
         <v>1.7543859649122806E-2</v>
       </c>
-      <c r="G99" s="175">
+      <c r="G108" s="175">
         <f>Statement!Q214</f>
         <v>0.16858237547892721</v>
       </c>
-      <c r="I99" s="197"/>
+      <c r="I108" s="197"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40204,14 +40423,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="250" t="s">
+      <c r="C3" s="252" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="F3" s="252" t="s">
+      <c r="D3" s="253"/>
+      <c r="F3" s="254" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="251"/>
+      <c r="G3" s="253"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40278,19 +40497,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="253">
+      <c r="C7" s="250">
         <f>Statement!AA89</f>
         <v>0.30810980316480124</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="F7" s="253">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.7926646045072911</v>
       </c>
-      <c r="G7" s="254"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -40317,19 +40536,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="250">
         <f>Statement!AA90</f>
         <v>0.1221875</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="F9" s="253">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14710110206037375</v>
       </c>
-      <c r="G9" s="254"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -40356,19 +40575,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="253">
+      <c r="C11" s="250">
         <f>Statement!AA91</f>
         <v>0.3420527156549521</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="F11" s="253">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3088642659279781</v>
       </c>
-      <c r="G11" s="254"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -40395,19 +40614,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="253">
+      <c r="C13" s="250">
         <f>Statement!AA95</f>
         <v>0.89643268124280784</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="F13" s="253">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3542857142857143</v>
       </c>
-      <c r="G13" s="254"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -40434,19 +40653,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="253">
+      <c r="C15" s="250">
         <f>Statement!AA96</f>
         <v>0.3131340416591632</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="F15" s="253">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>10.973453749315818</v>
       </c>
-      <c r="G15" s="254"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -40473,19 +40692,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="250">
         <f>Statement!AA98</f>
         <v>0.33487943915306445</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="F17" s="253">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>10.777881911902531</v>
       </c>
-      <c r="G17" s="254"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -40512,22 +40731,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.7467248908296944E-3</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="F19" s="253">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.4146772767462422E-2</v>
       </c>
-      <c r="G19" s="254"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -40554,22 +40773,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="253">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.33238751520064835</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="F21" s="253">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>10.614840989399292</v>
       </c>
-      <c r="G21" s="254"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40618,22 +40837,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.26950331971399388</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="F25" s="253">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.79326359455316076</v>
       </c>
-      <c r="G25" s="254"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40661,22 +40880,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="253">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.41828422005430954</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="F27" s="253">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.2519961673586713</v>
       </c>
-      <c r="G27" s="254"/>
+      <c r="G27" s="251"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40704,22 +40923,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="253">
+      <c r="C29" s="250">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.92432432432432432</v>
       </c>
-      <c r="D29" s="254"/>
-      <c r="F29" s="253">
+      <c r="D29" s="251"/>
+      <c r="F29" s="250">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.55458515283842791</v>
       </c>
-      <c r="G29" s="254"/>
+      <c r="G29" s="251"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -40747,22 +40966,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="253">
+      <c r="C32" s="250">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.18258406565473165</v>
       </c>
-      <c r="D32" s="254"/>
-      <c r="F32" s="253">
+      <c r="D32" s="251"/>
+      <c r="F32" s="250">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>2.5841954655513977</v>
       </c>
-      <c r="G32" s="254"/>
+      <c r="G32" s="251"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -40790,22 +41009,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="253">
+      <c r="C34" s="250">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.56213120444290177</v>
       </c>
-      <c r="D34" s="254"/>
-      <c r="F34" s="253">
+      <c r="D34" s="251"/>
+      <c r="F34" s="250">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>10.415345592897907</v>
       </c>
-      <c r="G34" s="254"/>
+      <c r="G34" s="251"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -40833,22 +41052,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="253">
+      <c r="C36" s="250">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.13826924746115787</v>
       </c>
-      <c r="D36" s="254"/>
-      <c r="F36" s="253">
+      <c r="D36" s="251"/>
+      <c r="F36" s="250">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.4877659574468085</v>
       </c>
-      <c r="G36" s="254"/>
+      <c r="G36" s="251"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -40876,25 +41095,49 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="253">
+      <c r="C38" s="250">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.47259387138541215</v>
       </c>
-      <c r="D38" s="254"/>
-      <c r="F38" s="253">
+      <c r="D38" s="251"/>
+      <c r="F38" s="250">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.7587168758716878</v>
       </c>
-      <c r="G38" s="254"/>
+      <c r="G38" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40903,30 +41146,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5142677-9606-DC4D-BC4B-B0238FB773BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E18530B-5EFE-2E47-B4DC-AA618225C999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2473,12 +2473,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2486,6 +2480,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2506,14 +2506,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15209,11 +15209,11 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>192.59</v>
-    <v>2.3490000000000002</v>
-    <v>25.06</v>
-    <v>2.7730000000000001E-2</v>
-    <v>-2.86</v>
-    <v>-3.0790000000000001E-3</v>
+    <v>2.3683999999999998</v>
+    <v>-49.53</v>
+    <v>-5.3015E-2</v>
+    <v>4.4109999999999996</v>
+    <v>4.986E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>61000</v>
@@ -15221,25 +15221,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>935.87</v>
+    <v>906.54</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46322.899580474215</v>
+    <v>46325.999979895314</v>
     <v>0</v>
-    <v>910.67139999999995</v>
-    <v>1050820425480</v>
+    <v>861.58500000000004</v>
+    <v>1001015185020</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>920.99</v>
-    <v>12.510300000000001</v>
-    <v>903.7</v>
-    <v>928.76</v>
-    <v>925.9</v>
+    <v>883.995</v>
+    <v>12.5845</v>
+    <v>934.27</v>
+    <v>884.74</v>
+    <v>889.15099999999995</v>
     <v>1131423000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>22821262</v>
-    <v>26186304</v>
+    <v>30872693</v>
+    <v>26324868</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15262,18 +15262,18 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
-    <v>39.47</v>
-    <v>-0.02</v>
-    <v>-4.0099999999999999E-4</v>
+    <v>39.56</v>
+    <v>-0.6</v>
+    <v>-1.2025999999999998E-2</v>
     <v>US</v>
-    <v>50.03</v>
+    <v>49.58</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.61</v>
+    <v>49.08</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.03</v>
-    <v>49.88</v>
-    <v>49.86</v>
+    <v>49.21</v>
+    <v>49.89</v>
+    <v>49.29</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15495,9 +15495,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16099,15 +16099,15 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>1064358.96</v>
+        <v>1014796.78</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
       <c r="I3" s="211">
-        <f ca="1">'AVG target price'!C5</f>
-        <v>932.22773953420062</v>
+        <f>'AVG target price'!C5</f>
+        <v>1076.9938669933274</v>
       </c>
       <c r="K3" s="241" t="s">
         <v>442</v>
@@ -16126,15 +16126,15 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>996084.96</v>
+        <v>946522.78</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
       <c r="I4" s="211">
-        <f ca="1">'AVG target price'!C6</f>
-        <v>1283.8062972527916</v>
+        <f>'AVG target price'!C6</f>
+        <v>1379.3722084401454</v>
       </c>
       <c r="K4" s="241" t="s">
         <v>443</v>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>243</v>
@@ -16160,8 +16160,8 @@
         <v>PS price</v>
       </c>
       <c r="I5" s="211">
-        <f ca="1">'AVG target price'!C7</f>
-        <v>568.88771236267064</v>
+        <f>'AVG target price'!C7</f>
+        <v>622.32771512965348</v>
       </c>
       <c r="K5" s="241" t="s">
         <v>444</v>
@@ -16173,22 +16173,22 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>925.9</v>
+        <v>889.15099999999995</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>12.515294434712301</v>
+        <v>11.922112922786685</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
       <c r="I6" s="211">
-        <f ca="1">'AVG target price'!C8</f>
-        <v>1733.4231554762671</v>
+        <f>'AVG target price'!C8</f>
+        <v>1869.6591739854991</v>
       </c>
       <c r="K6" s="242" t="s">
         <v>445</v>
@@ -16200,22 +16200,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>25.06</v>
+        <v>-49.53</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>7.9704829263897654</v>
+        <v>7.5927097035768991</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
         <v>EV/Sales price</v>
       </c>
       <c r="I7" s="211">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>914.07406965411394</v>
+        <f>'AVG target price'!C9</f>
+        <v>976.19584034324487</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16224,22 +16224,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-2.86</v>
+        <v>4.4109999999999996</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>5.4145266931374357E-2</v>
+        <v>5.6789695371323508E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I8" s="212">
-        <f ca="1">'AVG target price'!C10</f>
-        <v>1086.4837948560089</v>
+        <f>'AVG target price'!C10</f>
+        <v>1184.9097609783739</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16248,14 +16248,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.7730000000000001E-2</v>
+        <v>-5.3015E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>7.9902235238382371E-2</v>
+        <v>8.3877749395302584E-2</v>
       </c>
       <c r="H9" s="184" t="str">
         <f>'AVG target price'!B12</f>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="I9" s="213">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.16982190754986101</v>
+        <v>0.33927454503964316</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16272,14 +16272,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.0790000000000001E-3</v>
+        <v>4.986E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>293</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>6.1069622601758343E-4</v>
+        <v>6.4052233196877108E-4</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16295,14 +16295,14 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>6.0833799905250015E-4</v>
+        <v>6.3860569206772614E-4</v>
       </c>
       <c r="H11" s="184" t="s">
         <v>367</v>
       </c>
       <c r="I11" s="212">
-        <f ca="1">DDM!C26</f>
-        <v>5.2204037749372816</v>
+        <f>DDM!C26</f>
+        <v>6.2428571428571411</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -16327,7 +16327,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3490000000000002</v>
+        <v>2.3683999999999998</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>104</v>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="I13" s="243">
         <f>'Reverse DCF'!C17</f>
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>26186304</v>
+        <v>26324868</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>105</v>
@@ -16363,8 +16363,8 @@
         <v>447</v>
       </c>
       <c r="I14" s="244">
-        <f ca="1">'Reverse DCF'!C16</f>
-        <v>885.48347224369797</v>
+        <f>'Reverse DCF'!C16</f>
+        <v>906.99840550744705</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>6.4145652515576135E-2</v>
+        <v>6.7278494912055203E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="F16" s="191">
         <f>Statement!AC175</f>
-        <v>60.472984942426926</v>
+        <v>60.366047745358088</v>
       </c>
       <c r="H16" s="246" t="s">
         <v>439</v>
@@ -16399,14 +16399,14 @@
       </c>
       <c r="F17" s="194">
         <f>Statement!AC171</f>
-        <v>2.617801047120419E-3</v>
+        <v>2.6155187445510027E-3</v>
       </c>
       <c r="H17" s="185" t="s">
         <v>165</v>
       </c>
       <c r="I17" s="239">
-        <f ca="1">DCF!C15</f>
-        <v>0.15502975881510556</v>
+        <f>DCF!C15</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16427,8 +16427,8 @@
         <v>440</v>
       </c>
       <c r="I18" s="240">
-        <f ca="1">Multiples!C54</f>
-        <v>0.15556500000000001</v>
+        <f>Multiples!C54</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.86</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.9860000000000002E-2</v>
+        <v>4.929E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16524,7 +16524,7 @@
         <v>345</v>
       </c>
       <c r="C28" s="221">
-        <v>0</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -16532,7 +16532,7 @@
         <v>357</v>
       </c>
       <c r="C29" s="221">
-        <v>0</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -21641,12 +21641,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21654,6 +21648,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22713,16 +22713,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22835,7 +22835,7 @@
       </c>
       <c r="C5" s="140">
         <f>Statement!AC78</f>
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22844,7 +22844,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22853,7 +22853,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>1064358.96</v>
+        <v>1014796.78</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22871,7 +22871,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.9860000000000002E-2</v>
+        <v>4.929E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.3490000000000002</v>
+        <v>2.3683999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.8422778748311093E-3</v>
+        <v>5.077571547826361E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99515772212516884</v>
+        <v>0.9949224284521736</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15556500000000001</v>
+        <v>0.15586800000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15502975881510556</v>
+        <v>0.15530521212478202</v>
       </c>
     </row>
   </sheetData>
@@ -23209,8 +23209,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="130">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1092129.6223282544</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>1267130.3657687923</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23263,24 +23263,24 @@
       <c r="F10" s="141"/>
       <c r="G10" s="142"/>
       <c r="H10" s="130">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>79625.64613936047</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>81030.828947878821</v>
       </c>
       <c r="I10" s="130">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>92995.538539115572</v>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
+        <v>96306.752439639677</v>
       </c>
       <c r="J10" s="130">
-        <f t="shared" ca="1" si="0"/>
-        <v>113909.748132658</v>
+        <f t="shared" si="0"/>
+        <v>120047.41929883401</v>
       </c>
       <c r="K10" s="130">
-        <f t="shared" ca="1" si="0"/>
-        <v>105980.72479395052</v>
+        <f t="shared" si="0"/>
+        <v>113662.220006845</v>
       </c>
       <c r="L10" s="130">
-        <f t="shared" ca="1" si="0"/>
-        <v>76285.863928535866</v>
+        <f t="shared" si="0"/>
+        <v>83258.892593408484</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23298,8 +23298,8 @@
       <c r="J11" s="141"/>
       <c r="K11" s="141"/>
       <c r="L11" s="130">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>531261.46797257336</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>672731.85215474048</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23321,8 +23321,8 @@
         <v>165</v>
       </c>
       <c r="C15" s="139">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15502975881510556</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23336,8 +23336,8 @@
         <v>187</v>
       </c>
       <c r="C19" s="64">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>468797.52153362043</v>
+        <f>SUM(H10:L10)</f>
+        <v>494306.11328660598</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23345,8 +23345,8 @@
         <v>183</v>
       </c>
       <c r="C20" s="64">
-        <f ca="1">L11</f>
-        <v>531261.46797257336</v>
+        <f>L11</f>
+        <v>672731.85215474048</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23354,8 +23354,8 @@
         <v>188</v>
       </c>
       <c r="C21" s="94">
-        <f ca="1">C19+C20</f>
-        <v>1000058.9895061938</v>
+        <f>C19+C20</f>
+        <v>1167037.9654413464</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23381,8 +23381,8 @@
         <v>191</v>
       </c>
       <c r="C24" s="94">
-        <f ca="1">C21+C22-C23</f>
-        <v>1068332.9895061939</v>
+        <f>C21+C22-C23</f>
+        <v>1235311.9654413464</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23391,7 +23391,7 @@
       </c>
       <c r="C25" s="88">
         <f>Statement!AC78</f>
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
@@ -23399,8 +23399,8 @@
         <v>192</v>
       </c>
       <c r="C26" s="237">
-        <f ca="1">C24/C25</f>
-        <v>932.22773953420062</v>
+        <f>C24/C25</f>
+        <v>1076.9938669933274</v>
       </c>
     </row>
   </sheetData>
@@ -23668,24 +23668,24 @@
       <c r="F9" s="141"/>
       <c r="G9" s="142"/>
       <c r="H9" s="92">
-        <f ca="1">DCF!H10</f>
-        <v>79625.64613936047</v>
+        <f>DCF!H10</f>
+        <v>81030.828947878821</v>
       </c>
       <c r="I9" s="92">
-        <f ca="1">DCF!I10</f>
-        <v>92995.538539115572</v>
+        <f>DCF!I10</f>
+        <v>96306.752439639677</v>
       </c>
       <c r="J9" s="92">
-        <f ca="1">DCF!J10</f>
-        <v>113909.748132658</v>
+        <f>DCF!J10</f>
+        <v>120047.41929883401</v>
       </c>
       <c r="K9" s="92">
-        <f ca="1">DCF!K10</f>
-        <v>105980.72479395052</v>
+        <f>DCF!K10</f>
+        <v>113662.220006845</v>
       </c>
       <c r="L9" s="92">
-        <f ca="1">DCF!L10</f>
-        <v>76285.863928535866</v>
+        <f>DCF!L10</f>
+        <v>83258.892593408484</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24470,8 +24470,8 @@
         <v>165</v>
       </c>
       <c r="C41" s="139">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15502975881510556</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24496,8 +24496,8 @@
         <v>423</v>
       </c>
       <c r="C44" s="24">
-        <f ca="1">C43/(1+C41)^5</f>
-        <v>1010456.3590466147</v>
+        <f>C43/(1+C41)^5</f>
+        <v>1102818.7023876491</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24505,8 +24505,8 @@
         <v>424</v>
       </c>
       <c r="C45" s="110">
-        <f ca="1">SUM(H9:K9)+C44</f>
-        <v>1402968.0166516993</v>
+        <f>SUM(H9:K9)+C44</f>
+        <v>1513865.9230808467</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24532,8 +24532,8 @@
         <v>191</v>
       </c>
       <c r="C48" s="110">
-        <f ca="1">C45+C46-C47</f>
-        <v>1471242.0166516993</v>
+        <f>C45+C46-C47</f>
+        <v>1582139.9230808467</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C49" s="88">
         <f>Statement!AC78</f>
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
@@ -24550,8 +24550,8 @@
         <v>209</v>
       </c>
       <c r="C50" s="237">
-        <f ca="1">C48/C49</f>
-        <v>1283.8062972527916</v>
+        <f>C48/C49</f>
+        <v>1379.3722084401454</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24574,8 +24574,8 @@
         <v>346</v>
       </c>
       <c r="C54" s="139">
-        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15556500000000001</v>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -24609,8 +24609,8 @@
         <v>209</v>
       </c>
       <c r="C58" s="237">
-        <f ca="1">C57/(1+C54)^5</f>
-        <v>568.88771236267064</v>
+        <f>C57/(1+C54)^5</f>
+        <v>622.32771512965348</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24633,8 +24633,8 @@
         <v>165</v>
       </c>
       <c r="C62" s="139">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15502975881510556</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24659,8 +24659,8 @@
         <v>423</v>
       </c>
       <c r="C65" s="24">
-        <f ca="1">C64/(1+C62)^5</f>
-        <v>1525717.2785707174</v>
+        <f>C64/(1+C62)^5</f>
+        <v>1665177.8518681696</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24668,8 +24668,8 @@
         <v>424</v>
       </c>
       <c r="C66" s="110">
-        <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1918228.936175802</v>
+        <f>SUM(H9:K9)+C65</f>
+        <v>2076225.0725613672</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -24695,8 +24695,8 @@
         <v>191</v>
       </c>
       <c r="C69" s="110">
-        <f ca="1">C66+C67-C68</f>
-        <v>1986502.936175802</v>
+        <f>C66+C67-C68</f>
+        <v>2144499.0725613674</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="C70" s="88">
         <f>Statement!AC78</f>
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.2">
@@ -24713,8 +24713,8 @@
         <v>209</v>
       </c>
       <c r="C71" s="237">
-        <f ca="1">C69/C70</f>
-        <v>1733.4231554762671</v>
+        <f>C69/C70</f>
+        <v>1869.6591739854991</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -24737,8 +24737,8 @@
         <v>165</v>
       </c>
       <c r="C75" s="139">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15502975881510556</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -24763,8 +24763,8 @@
         <v>423</v>
       </c>
       <c r="C78" s="24">
-        <f ca="1">C77/(1+C75)^5</f>
-        <v>586743.22621853009</v>
+        <f>C77/(1+C75)^5</f>
+        <v>640375.40818050446</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -24772,8 +24772,8 @@
         <v>424</v>
       </c>
       <c r="C79" s="110">
-        <f ca="1">SUM(H9:K9)+C78</f>
-        <v>979254.88382361457</v>
+        <f>SUM(H9:K9)+C78</f>
+        <v>1051422.6288737019</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -24799,8 +24799,8 @@
         <v>191</v>
       </c>
       <c r="C82" s="110">
-        <f ca="1">C79+C80-C81</f>
-        <v>1047528.8838236146</v>
+        <f>C79+C80-C81</f>
+        <v>1119696.6288737019</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -24809,7 +24809,7 @@
       </c>
       <c r="C83" s="88">
         <f>Statement!AC78</f>
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.2">
@@ -24817,23 +24817,23 @@
         <v>209</v>
       </c>
       <c r="C84" s="237">
-        <f ca="1">C82/C83</f>
-        <v>914.07406965411394</v>
+        <f>C82/C83</f>
+        <v>976.19584034324487</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -24882,8 +24882,8 @@
         <v>215</v>
       </c>
       <c r="C5" s="137">
-        <f ca="1">DCF!C26</f>
-        <v>932.22773953420062</v>
+        <f>DCF!C26</f>
+        <v>1076.9938669933274</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24891,8 +24891,8 @@
         <v>216</v>
       </c>
       <c r="C6" s="137">
-        <f ca="1">Multiples!C50</f>
-        <v>1283.8062972527916</v>
+        <f>Multiples!C50</f>
+        <v>1379.3722084401454</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24900,8 +24900,8 @@
         <v>217</v>
       </c>
       <c r="C7" s="137">
-        <f ca="1">Multiples!C58</f>
-        <v>568.88771236267064</v>
+        <f>Multiples!C58</f>
+        <v>622.32771512965348</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24909,8 +24909,8 @@
         <v>323</v>
       </c>
       <c r="C8" s="137">
-        <f ca="1">Multiples!C71</f>
-        <v>1733.4231554762671</v>
+        <f>Multiples!C71</f>
+        <v>1869.6591739854991</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24918,8 +24918,8 @@
         <v>430</v>
       </c>
       <c r="C9" s="137">
-        <f ca="1">Multiples!C84</f>
-        <v>914.07406965411394</v>
+        <f>Multiples!C84</f>
+        <v>976.19584034324487</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24927,8 +24927,8 @@
         <v>218</v>
       </c>
       <c r="C10" s="237">
-        <f ca="1">AVERAGE(C5:C9)</f>
-        <v>1086.4837948560089</v>
+        <f>AVERAGE(C5:C9)</f>
+        <v>1184.9097609783739</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="C11" s="137">
         <f ca="1">Overview!C5</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="C12" s="156">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.16982190754986101</v>
+        <v>0.33927454503964316</v>
       </c>
     </row>
   </sheetData>
@@ -25454,8 +25454,8 @@
         <v>346</v>
       </c>
       <c r="C24" s="139">
-        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15556500000000001</v>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -25471,8 +25471,8 @@
         <v>209</v>
       </c>
       <c r="C26" s="237">
-        <f ca="1">C23/(C24-C25)</f>
-        <v>5.2204037749372816</v>
+        <f>C23/(C24-C25)</f>
+        <v>6.2428571428571411</v>
       </c>
     </row>
   </sheetData>
@@ -25661,23 +25661,23 @@
       </c>
       <c r="H7" s="130">
         <f>G7*(1+$C$17)</f>
-        <v>71519.505031152512</v>
+        <v>69212.424223695969</v>
       </c>
       <c r="I7" s="130">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>88684.186238629118</v>
+        <v>83054.909068435154</v>
       </c>
       <c r="J7" s="130">
         <f t="shared" si="0"/>
-        <v>109968.39093590011</v>
+        <v>99665.890882122185</v>
       </c>
       <c r="K7" s="130">
         <f t="shared" si="0"/>
-        <v>136360.80476051613</v>
+        <v>119599.06905854662</v>
       </c>
       <c r="L7" s="130">
         <f t="shared" si="0"/>
-        <v>169087.39790303999</v>
+        <v>143518.88287025594</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -25708,8 +25708,8 @@
       <c r="J8" s="141"/>
       <c r="K8" s="141"/>
       <c r="L8" s="130">
-        <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1177539.5151817836</v>
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>1159632.5735916679</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25762,24 +25762,24 @@
       <c r="F10" s="141"/>
       <c r="G10" s="142"/>
       <c r="H10" s="130">
-        <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>61920.053994557893</v>
+        <f>H7/(1+$C$21)^H9</f>
+        <v>60980.109448190284</v>
       </c>
       <c r="I10" s="130">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>66475.228336989268</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>64472.362412183553</v>
       </c>
       <c r="J10" s="130">
-        <f t="shared" ca="1" si="1"/>
-        <v>71365.505961012896</v>
+        <f t="shared" si="1"/>
+        <v>68164.612241956187</v>
       </c>
       <c r="K10" s="130">
-        <f t="shared" ca="1" si="1"/>
-        <v>76615.538877922358</v>
+        <f t="shared" si="1"/>
+        <v>72068.312502508736</v>
       </c>
       <c r="L10" s="130">
-        <f t="shared" ca="1" si="1"/>
-        <v>82251.792634402271</v>
+        <f t="shared" si="1"/>
+        <v>76195.572689877081</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25797,16 +25797,16 @@
       <c r="J11" s="141"/>
       <c r="K11" s="141"/>
       <c r="L11" s="130">
-        <f ca="1">L8/(1+C21)^L9</f>
-        <v>572808.72035825031</v>
+        <f>L8/(1+C21)^L9</f>
+        <v>615660.22733420669</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="262" t="s">
+      <c r="B14" s="261" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="263"/>
+      <c r="C14" s="262"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -25814,7 +25814,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25822,8 +25822,8 @@
         <v>224</v>
       </c>
       <c r="C16" s="158">
-        <f ca="1">C36</f>
-        <v>885.48347224369797</v>
+        <f>C36</f>
+        <v>906.99840550744705</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25831,22 +25831,22 @@
         <v>324</v>
       </c>
       <c r="C17" s="160">
-        <v>0.24</v>
-      </c>
-      <c r="E17" s="261" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="263" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="261"/>
-      <c r="G17" s="261"/>
-      <c r="H17" s="261"/>
-      <c r="I17" s="261"/>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="263"/>
+      <c r="I17" s="263"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="262" t="s">
+      <c r="B19" s="261" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="263"/>
+      <c r="C19" s="262"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -25861,8 +25861,8 @@
         <v>165</v>
       </c>
       <c r="C21" s="222">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.15502975881510556</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="C22" s="223">
         <f>Statement!AC75</f>
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>1048570.04</v>
+        <v>1000640.9400000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25907,23 +25907,23 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>980296.04</v>
+        <v>932366.94000000006</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="262" t="s">
+      <c r="B28" s="261" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="263"/>
+      <c r="C28" s="262"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
         <v>187</v>
       </c>
       <c r="C29" s="163">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>358628.11980488471</v>
+        <f>SUM(H10:L10)</f>
+        <v>341880.96929471585</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25931,8 +25931,8 @@
         <v>183</v>
       </c>
       <c r="C30" s="163">
-        <f ca="1">L11</f>
-        <v>572808.72035825031</v>
+        <f>L11</f>
+        <v>615660.22733420669</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25940,8 +25940,8 @@
         <v>188</v>
       </c>
       <c r="C31" s="166">
-        <f ca="1">C29+C30</f>
-        <v>931436.84016313497</v>
+        <f>C29+C30</f>
+        <v>957541.1966289226</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25967,8 +25967,8 @@
         <v>191</v>
       </c>
       <c r="C34" s="166">
-        <f ca="1">C31+C32-C33</f>
-        <v>999710.84016313497</v>
+        <f>C31+C32-C33</f>
+        <v>1025815.1966289226</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="C35" s="163">
         <f>C22</f>
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25985,22 +25985,22 @@
         <v>192</v>
       </c>
       <c r="C36" s="169">
-        <f ca="1">C34/C35</f>
-        <v>885.48347224369797</v>
+        <f>C34/C35</f>
+        <v>906.99840550744705</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30418,8 +30418,8 @@
       <c r="P74" s="21">
         <v>1122</v>
       </c>
-      <c r="Q74" s="238">
-        <v>1129</v>
+      <c r="Q74" s="21">
+        <v>1131</v>
       </c>
       <c r="T74" s="21">
         <v>1114</v>
@@ -30442,12 +30442,12 @@
       <c r="Z74" s="21">
         <v>1129</v>
       </c>
-      <c r="AA74" s="238">
-        <v>1129</v>
+      <c r="AA74" s="21">
+        <v>1131</v>
       </c>
       <c r="AC74" s="24">
         <f>AA74</f>
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.2">
@@ -30485,7 +30485,7 @@
       </c>
       <c r="Q75" s="25">
         <f t="shared" ref="Q75" si="49">Q74*Q85</f>
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="T75" s="25">
         <f t="shared" ref="T75" si="50">T74*T85</f>
@@ -30517,11 +30517,11 @@
       </c>
       <c r="AA75" s="25">
         <f t="shared" ref="AA75" si="55">AA74*AA85</f>
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="AC75" s="24">
         <f>AA75</f>
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
@@ -30552,8 +30552,8 @@
       <c r="P76" s="21">
         <v>9</v>
       </c>
-      <c r="Q76" s="238">
-        <v>17</v>
+      <c r="Q76" s="21">
+        <v>16</v>
       </c>
       <c r="T76" s="21">
         <v>11</v>
@@ -30576,12 +30576,12 @@
       <c r="Z76" s="21">
         <v>17</v>
       </c>
-      <c r="AA76" s="238">
-        <v>17</v>
+      <c r="AA76" s="21">
+        <v>16</v>
       </c>
       <c r="AC76" s="21">
         <f>AA76</f>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="Q77" s="25">
         <f>Q76*Q85</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T77" s="25">
         <f t="shared" ref="T77:Y77" si="57">T76*T85</f>
@@ -30651,11 +30651,11 @@
       </c>
       <c r="AA77" s="25">
         <f t="shared" si="58"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC77" s="24">
         <f>AA77</f>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
@@ -30693,7 +30693,7 @@
       </c>
       <c r="Q78" s="25">
         <f>Q75+Q77</f>
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="T78" s="25">
         <f t="shared" ref="T78:Y78" si="60">T75+T77</f>
@@ -30725,11 +30725,11 @@
       </c>
       <c r="AA78" s="25">
         <f t="shared" si="61"/>
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="AC78" s="24">
         <f>AA78</f>
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
@@ -31089,8 +31089,8 @@
       <c r="P84" s="21">
         <v>60000</v>
       </c>
-      <c r="Q84" s="238">
-        <v>60000</v>
+      <c r="Q84" s="21">
+        <v>61000</v>
       </c>
       <c r="T84" s="68"/>
       <c r="U84" s="68"/>
@@ -31102,7 +31102,7 @@
       <c r="AA84" s="68"/>
       <c r="AC84" s="21">
         <f>Q84</f>
-        <v>60000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="85" spans="1:31" x14ac:dyDescent="0.2">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32965,7 +32965,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -34334,7 +34334,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>12.515294434712301</v>
+        <v>11.922112922786685</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -34375,7 +34375,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.9704829263897654</v>
+        <v>7.5927097035768991</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="Q152" s="72">
         <f>Q117/(Statement!Q49/Statement!Q75)</f>
-        <v>7.8174467039558309</v>
+        <v>7.8312951480726705</v>
       </c>
       <c r="T152" s="72">
         <f>T117/(Statement!T49/Statement!T75)</f>
@@ -34436,11 +34436,11 @@
       </c>
       <c r="AA152" s="72">
         <f>AA117/(Statement!AA49/Statement!AA75)</f>
-        <v>7.8174467039558309</v>
+        <v>7.8312951480726705</v>
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.5775776496263854</v>
+        <v>7.2312140658197119</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34469,7 +34469,7 @@
       </c>
       <c r="Q153" s="145">
         <f>Statement!Q117*Statement!Q78</f>
-        <v>1098051.3599999999</v>
+        <v>1099009.52</v>
       </c>
       <c r="T153" s="145">
         <f>Statement!T117*Statement!T78</f>
@@ -34501,11 +34501,11 @@
       </c>
       <c r="AA153" s="145">
         <f>Statement!AA117*Statement!AA78</f>
-        <v>1098051.3599999999</v>
+        <v>1099009.52</v>
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>1064358.96</v>
+        <v>1014796.78</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="Q154" s="145">
         <f t="shared" si="197"/>
-        <v>1029777.3599999999</v>
+        <v>1030735.52</v>
       </c>
       <c r="T154" s="145">
         <f t="shared" ref="T154:Z154" si="198">T153+T108-T107+T48+T45</f>
@@ -34566,11 +34566,11 @@
       </c>
       <c r="AA154" s="145">
         <f t="shared" ref="AA154" si="199">AA153+AA108-AA107+AA48+AA45</f>
-        <v>1029777.3599999999</v>
+        <v>1030735.52</v>
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>996084.96</v>
+        <v>946522.78</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="Q155" s="183">
         <f t="shared" si="200"/>
-        <v>7.73175781601946</v>
+        <v>7.738951857524702</v>
       </c>
       <c r="T155" s="49"/>
       <c r="U155" s="49"/>
@@ -34611,7 +34611,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>7.4787890800973056</v>
+        <v>7.1066671171577021</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="Q156" s="183">
         <f t="shared" si="201"/>
-        <v>10.366190457016307</v>
+        <v>10.375835715723777</v>
       </c>
       <c r="T156" s="49"/>
       <c r="U156" s="49"/>
@@ -34652,7 +34652,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>10.027027984699012</v>
+        <v>9.5281133480974436</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34787,7 +34787,7 @@
       </c>
       <c r="Q159" s="72">
         <f t="shared" ref="Q159" si="207">Q153/Q157</f>
-        <v>19.053467985424255</v>
+        <v>19.070094048238765</v>
       </c>
       <c r="T159" s="49"/>
       <c r="U159" s="49"/>
@@ -34799,7 +34799,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="208">AC153/AC157</f>
-        <v>18.468834981780322</v>
+        <v>17.608828387992364</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34828,7 +34828,7 @@
       </c>
       <c r="Q160" s="72">
         <f t="shared" ref="Q160" si="210">Q154/Q158</f>
-        <v>17.854205308660855</v>
+        <v>17.870817817367154</v>
       </c>
       <c r="T160" s="49"/>
       <c r="U160" s="49"/>
@@ -34840,7 +34840,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="208"/>
-        <v>17.270048916893295</v>
+        <v>16.410743428506169</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34869,7 +34869,7 @@
       </c>
       <c r="Q161" s="74">
         <f t="shared" ref="Q161" si="212">Q157/Q153</f>
-        <v>5.2483883813959312E-2</v>
+        <v>5.2438126286658553E-2</v>
       </c>
       <c r="T161" s="49"/>
       <c r="U161" s="49"/>
@@ -34881,7 +34881,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="213">AC157/AC153</f>
-        <v>5.4145266931374357E-2</v>
+        <v>5.6789695371323508E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34922,7 +34922,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.9902235238382371E-2</v>
+        <v>8.3877749395302584E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34963,7 +34963,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="156">
         <f ca="1">AC82/AC117</f>
-        <v>6.0833799905250015E-4</v>
+        <v>6.3860569206772614E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34992,7 +34992,7 @@
       </c>
       <c r="Q164" s="156">
         <f t="shared" si="216"/>
-        <v>5.9195773866169621E-4</v>
+        <v>5.914416464745455E-4</v>
       </c>
       <c r="T164" s="49"/>
       <c r="U164" s="49"/>
@@ -35004,7 +35004,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>6.1069622601758343E-4</v>
+        <v>6.4052233196877108E-4</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -35033,7 +35033,7 @@
       </c>
       <c r="Q165" s="156">
         <f t="shared" si="217"/>
-        <v>1.147487308790365E-3</v>
+        <v>1.1464868839352728E-3</v>
       </c>
       <c r="T165" s="49"/>
       <c r="U165" s="49"/>
@@ -35045,7 +35045,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.1838111458187001E-3</v>
+        <v>1.2416279050471563E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35279,7 +35279,7 @@
       </c>
       <c r="Q171" s="156">
         <f t="shared" si="223"/>
-        <v>2.617801047120419E-3</v>
+        <v>2.6155187445510027E-3</v>
       </c>
       <c r="T171" s="49"/>
       <c r="U171" s="49"/>
@@ -35291,7 +35291,7 @@
       <c r="AA171" s="49"/>
       <c r="AC171" s="156">
         <f>AC80/AC78</f>
-        <v>2.617801047120419E-3</v>
+        <v>2.6155187445510027E-3</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
@@ -35320,7 +35320,7 @@
       </c>
       <c r="Q172" s="72">
         <f t="shared" si="224"/>
-        <v>65.060230292294065</v>
+        <v>64.94518125552608</v>
       </c>
       <c r="T172" s="72">
         <f t="shared" ref="T172:Z172" si="225">T107/T75</f>
@@ -35352,11 +35352,11 @@
       </c>
       <c r="AA172" s="72">
         <f t="shared" ref="AA172" si="226">AA107/AA75</f>
-        <v>65.060230292294065</v>
+        <v>64.94518125552608</v>
       </c>
       <c r="AC172" s="72">
         <f>AC107/AC75</f>
-        <v>65.060230292294065</v>
+        <v>64.94518125552608</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="Q175" s="72">
         <f t="shared" si="233"/>
-        <v>60.472984942426926</v>
+        <v>60.366047745358088</v>
       </c>
       <c r="T175" s="72">
         <f t="shared" ref="T175:Z175" si="234">(T107-T108)/T75</f>
@@ -35547,11 +35547,11 @@
       </c>
       <c r="AA175" s="72">
         <f t="shared" ref="AA175" si="235">(AA107-AA108)/AA75</f>
-        <v>60.472984942426926</v>
+        <v>60.366047745358088</v>
       </c>
       <c r="AC175" s="72">
         <f>(AC107-AC108)/AC75</f>
-        <v>60.472984942426926</v>
+        <v>60.366047745358088</v>
       </c>
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="Q176" s="156">
         <f t="shared" si="236"/>
-        <v>6.2177419460597919E-2</v>
+        <v>6.2123210725235571E-2</v>
       </c>
       <c r="T176" s="49"/>
       <c r="U176" s="49"/>
@@ -35592,7 +35592,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>6.4145652515576135E-2</v>
+        <v>6.7278494912055203E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1064358.96</v>
+        <v>1014796.78</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37677,7 +37677,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>996084.96</v>
+        <v>946522.78</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.515294434712301</v>
+        <v>11.922112922786685</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -37717,7 +37717,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.9704829263897654</v>
+        <v>7.5927097035768991</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -37737,7 +37737,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.5775776496263854</v>
+        <v>7.2312140658197119</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.4787890800973056</v>
+        <v>7.1066671171577021</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>10.027027984699012</v>
+        <v>9.5281133480974436</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -38002,7 +38002,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.9902235238382371E-2</v>
+        <v>8.3877749395302584E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -38018,7 +38018,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>5.4145266931374357E-2</v>
+        <v>5.6789695371323508E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -38034,7 +38034,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.0833799905250015E-4</v>
+        <v>6.3860569206772614E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>273</v>
@@ -38050,7 +38050,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.1069622601758343E-4</v>
+        <v>6.4052233196877108E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38059,7 +38059,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.1838111458187001E-3</v>
+        <v>1.2416279050471563E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38078,14 +38078,14 @@
       </c>
       <c r="C46" s="175">
         <f>Statement!AC171</f>
-        <v>2.617801047120419E-3</v>
+        <v>2.6155187445510027E-3</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>278</v>
       </c>
       <c r="F46" s="174">
         <f>Statement!AC172</f>
-        <v>65.060230292294065</v>
+        <v>64.94518125552608</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
@@ -38094,7 +38094,7 @@
       </c>
       <c r="F47" s="174">
         <f>Statement!AC175</f>
-        <v>60.472984942426926</v>
+        <v>60.366047745358088</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>6.4145652515576135E-2</v>
+        <v>6.7278494912055203E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38169,7 +38169,7 @@
       </c>
       <c r="C58" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>18.468834981780322</v>
+        <v>17.608828387992364</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.2">
@@ -38178,7 +38178,7 @@
       </c>
       <c r="C59" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>17.270048916893295</v>
+        <v>16.410743428506169</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
@@ -38325,7 +38325,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>928.76</v>
+        <v>884.74</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38350,11 +38350,11 @@
       </c>
       <c r="G7" s="173">
         <f>Statement!Q153</f>
-        <v>1098051.3599999999</v>
+        <v>1099009.52</v>
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>1064358.96</v>
+        <v>1014796.78</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38379,11 +38379,11 @@
       </c>
       <c r="G8" s="173">
         <f>Statement!Q154</f>
-        <v>1029777.3599999999</v>
+        <v>1030735.52</v>
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>996084.96</v>
+        <v>946522.78</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38412,7 +38412,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>12.515294434712301</v>
+        <v>11.922112922786685</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38441,7 +38441,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>7.9704829263897654</v>
+        <v>7.5927097035768991</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38466,11 +38466,11 @@
       </c>
       <c r="G11" s="174">
         <f>Statement!Q152</f>
-        <v>7.8174467039558309</v>
+        <v>7.8312951480726705</v>
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>7.5775776496263854</v>
+        <v>7.2312140658197119</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38495,11 +38495,11 @@
       </c>
       <c r="G12" s="174">
         <f>Statement!Q155</f>
-        <v>7.73175781601946</v>
+        <v>7.738951857524702</v>
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.4787890800973056</v>
+        <v>7.1066671171577021</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38524,11 +38524,11 @@
       </c>
       <c r="G13" s="174">
         <f>Statement!Q156</f>
-        <v>10.366190457016307</v>
+        <v>10.375835715723777</v>
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>10.027027984699012</v>
+        <v>9.5281133480974436</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39301,7 +39301,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>7.9902235238382371E-2</v>
+        <v>8.3877749395302584E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39326,11 +39326,11 @@
       </c>
       <c r="G52" s="175">
         <f>Statement!Q161</f>
-        <v>5.2483883813959312E-2</v>
+        <v>5.2438126286658553E-2</v>
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>5.4145266931374357E-2</v>
+        <v>5.6789695371323508E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39359,7 +39359,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>6.0833799905250015E-4</v>
+        <v>6.3860569206772614E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -39384,11 +39384,11 @@
       </c>
       <c r="G54" s="175">
         <f>Statement!Q164</f>
-        <v>5.9195773866169621E-4</v>
+        <v>5.914416464745455E-4</v>
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>6.1069622601758343E-4</v>
+        <v>6.4052233196877108E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39413,11 +39413,11 @@
       </c>
       <c r="G55" s="175">
         <f>Statement!Q165</f>
-        <v>1.147487308790365E-3</v>
+        <v>1.1464868839352728E-3</v>
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>1.1838111458187001E-3</v>
+        <v>1.2416279050471563E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39551,11 +39551,11 @@
       </c>
       <c r="G63" s="175">
         <f>Statement!Q171</f>
-        <v>2.617801047120419E-3</v>
+        <v>2.6155187445510027E-3</v>
       </c>
       <c r="I63" s="175">
         <f>Statement!AC171</f>
-        <v>2.617801047120419E-3</v>
+        <v>2.6155187445510027E-3</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39591,11 +39591,11 @@
       </c>
       <c r="G66" s="174">
         <f>Statement!Q172</f>
-        <v>65.060230292294065</v>
+        <v>64.94518125552608</v>
       </c>
       <c r="I66" s="174">
         <f>Statement!AC172</f>
-        <v>65.060230292294065</v>
+        <v>64.94518125552608</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
@@ -39620,11 +39620,11 @@
       </c>
       <c r="G67" s="174">
         <f>Statement!Q175</f>
-        <v>60.472984942426926</v>
+        <v>60.366047745358088</v>
       </c>
       <c r="I67" s="174">
         <f>Statement!AC175</f>
-        <v>60.472984942426926</v>
+        <v>60.366047745358088</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
@@ -39649,11 +39649,11 @@
       </c>
       <c r="G68" s="196">
         <f>Statement!Q176</f>
-        <v>6.2177419460597919E-2</v>
+        <v>6.2123210725235571E-2</v>
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>6.4145652515576135E-2</v>
+        <v>6.7278494912055203E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40023,11 +40023,11 @@
       </c>
       <c r="G88" s="174">
         <f>Statement!Q159</f>
-        <v>19.053467985424255</v>
+        <v>19.070094048238765</v>
       </c>
       <c r="I88" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>18.468834981780322</v>
+        <v>17.608828387992364</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
@@ -40052,11 +40052,11 @@
       </c>
       <c r="G89" s="174">
         <f>Statement!Q160</f>
-        <v>17.854205308660855</v>
+        <v>17.870817817367154</v>
       </c>
       <c r="I89" s="174">
         <f ca="1">Statement!AC160</f>
-        <v>17.270048916893295</v>
+        <v>16.410743428506169</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
@@ -40423,14 +40423,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="250" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="F3" s="254" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="253"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40497,19 +40497,19 @@
       <c r="B7" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="253">
         <f>Statement!AA89</f>
         <v>0.30810980316480124</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.7926646045072911</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -40536,19 +40536,19 @@
       <c r="B9" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="253">
         <f>Statement!AA90</f>
         <v>0.1221875</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.14710110206037375</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -40575,19 +40575,19 @@
       <c r="B11" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="253">
         <f>Statement!AA91</f>
         <v>0.3420527156549521</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.3088642659279781</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -40614,19 +40614,19 @@
       <c r="B13" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="253">
         <f>Statement!AA95</f>
         <v>0.89643268124280784</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3542857142857143</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -40653,19 +40653,19 @@
       <c r="B15" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="253">
         <f>Statement!AA96</f>
         <v>0.3131340416591632</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>10.973453749315818</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -40692,19 +40692,19 @@
       <c r="B17" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="253">
         <f>Statement!AA98</f>
         <v>0.33487943915306445</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>10.777881911902531</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -40731,22 +40731,22 @@
       <c r="B19" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.7467248908296944E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.4146772767462422E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -40773,22 +40773,22 @@
       <c r="B21" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.33238751520064835</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>10.614840989399292</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40837,22 +40837,22 @@
       <c r="B25" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.26950331971399388</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.79326359455316076</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40880,22 +40880,22 @@
       <c r="B27" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.41828422005430954</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.2519961673586713</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="254"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -40923,22 +40923,22 @@
       <c r="B29" s="206" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="250">
+      <c r="C29" s="253">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.92432432432432432</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="F29" s="250">
+      <c r="D29" s="254"/>
+      <c r="F29" s="253">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.55458515283842791</v>
       </c>
-      <c r="G29" s="251"/>
+      <c r="G29" s="254"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="str">
@@ -40966,22 +40966,22 @@
       <c r="B32" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="250">
+      <c r="C32" s="253">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.18258406565473165</v>
       </c>
-      <c r="D32" s="251"/>
-      <c r="F32" s="250">
+      <c r="D32" s="254"/>
+      <c r="F32" s="253">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>2.5841954655513977</v>
       </c>
-      <c r="G32" s="251"/>
+      <c r="G32" s="254"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="184" t="str">
@@ -41009,22 +41009,22 @@
       <c r="B34" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="250">
+      <c r="C34" s="253">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.56213120444290177</v>
       </c>
-      <c r="D34" s="251"/>
-      <c r="F34" s="250">
+      <c r="D34" s="254"/>
+      <c r="F34" s="253">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>10.415345592897907</v>
       </c>
-      <c r="G34" s="251"/>
+      <c r="G34" s="254"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="184" t="str">
@@ -41052,22 +41052,22 @@
       <c r="B36" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="250">
+      <c r="C36" s="253">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.13826924746115787</v>
       </c>
-      <c r="D36" s="251"/>
-      <c r="F36" s="250">
+      <c r="D36" s="254"/>
+      <c r="F36" s="253">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.4877659574468085</v>
       </c>
-      <c r="G36" s="251"/>
+      <c r="G36" s="254"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="184" t="str">
@@ -41095,49 +41095,25 @@
       <c r="B38" s="233" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="250">
+      <c r="C38" s="253">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.47259387138541215</v>
       </c>
-      <c r="D38" s="251"/>
-      <c r="F38" s="250">
+      <c r="D38" s="254"/>
+      <c r="F38" s="253">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.7587168758716878</v>
       </c>
-      <c r="G38" s="251"/>
+      <c r="G38" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -41146,6 +41122,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
